--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1695,13 +1695,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.38873709491</v>
+        <v>46118.55540376157</v>
       </c>
       <c r="C4" s="5">
-        <v>46134.683067569444</v>
+        <v>46134.84973423611</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.683078692135</v>
+        <v>46134.84974535879</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46118.38890262731</v>
+        <v>46118.55556929398</v>
       </c>
       <c r="C5" s="9">
-        <v>46134.68074246528</v>
+        <v>46134.847409131944</v>
       </c>
       <c r="D5" s="9">
-        <v>46134.680787986115</v>
+        <v>46134.84745465278</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1811,13 +1811,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.388906099535</v>
+        <v>46118.5555727662</v>
       </c>
       <c r="C6" s="5">
-        <v>46134.68150766204</v>
+        <v>46134.848174328705</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.681521516206</v>
+        <v>46134.84818818287</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1874,13 +1874,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="9">
-        <v>46118.38890895833</v>
+        <v>46118.555575624996</v>
       </c>
       <c r="C7" s="9">
-        <v>46134.68180517361</v>
+        <v>46134.848471840276</v>
       </c>
       <c r="D7" s="9">
-        <v>46134.68181967593</v>
+        <v>46134.84848634259</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>40</v>
@@ -1937,13 +1937,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.38891162037</v>
+        <v>46118.555578287036</v>
       </c>
       <c r="C8" s="5">
-        <v>46134.68256634259</v>
+        <v>46134.849233009256</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.68311010417</v>
+        <v>46134.84977677083</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -2000,13 +2000,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="9">
-        <v>46118.38891502315</v>
+        <v>46118.55558168981</v>
       </c>
       <c r="C9" s="9">
-        <v>46134.683053368055</v>
+        <v>46134.84972003472</v>
       </c>
       <c r="D9" s="9">
-        <v>46134.683068425926</v>
+        <v>46134.84973509259</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>47</v>
@@ -2063,11 +2063,11 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.38874427084</v>
+        <v>46118.5554109375</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.68487490741</v>
+        <v>46134.85154157407</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2110,13 +2110,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="9">
-        <v>46118.38891834491</v>
+        <v>46118.55558501158</v>
       </c>
       <c r="C11" s="9">
-        <v>46134.68486908565</v>
+        <v>46134.851535752314</v>
       </c>
       <c r="D11" s="9">
-        <v>46171.74395131944</v>
+        <v>46171.91061798611</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>52</v>
@@ -2175,13 +2175,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.38892319445</v>
+        <v>46118.55558986111</v>
       </c>
       <c r="C12" s="5">
-        <v>46134.6842277199</v>
+        <v>46134.850894386575</v>
       </c>
       <c r="D12" s="5">
-        <v>46134.684243125</v>
+        <v>46134.85090979167</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2240,13 +2240,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46118.388928368055</v>
+        <v>46118.55559503472</v>
       </c>
       <c r="C13" s="9">
-        <v>46134.683779224535</v>
+        <v>46134.85044589121</v>
       </c>
       <c r="D13" s="9">
-        <v>46134.683796840276</v>
+        <v>46134.85046350694</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2305,11 +2305,11 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.38893346065</v>
+        <v>46118.555600127314</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46134.68259444444</v>
+        <v>46134.849261111114</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2368,11 +2368,11 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46118.388750972226</v>
+        <v>46118.55541763889</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46181.50501469907</v>
+        <v>46181.67168136574</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2415,13 +2415,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.38893851852</v>
+        <v>46118.55560518519</v>
       </c>
       <c r="C16" s="5">
-        <v>46134.685348425926</v>
+        <v>46134.85201509259</v>
       </c>
       <c r="D16" s="5">
-        <v>46134.6853625463</v>
+        <v>46134.85202921296</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2480,11 +2480,11 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46118.38894379629</v>
+        <v>46118.555610462965</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46169.688238159724</v>
+        <v>46169.85490482639</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2543,13 +2543,13 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.388948912034</v>
+        <v>46118.555615578705</v>
       </c>
       <c r="C18" s="5">
-        <v>46134.68573056713</v>
+        <v>46134.8523972338</v>
       </c>
       <c r="D18" s="5">
-        <v>46134.68574652778</v>
+        <v>46134.85241319444</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2608,13 +2608,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46118.388954560185</v>
+        <v>46118.55562122686</v>
       </c>
       <c r="C19" s="9">
-        <v>46181.5050077662</v>
+        <v>46181.67167443287</v>
       </c>
       <c r="D19" s="9">
-        <v>46181.50502488426</v>
+        <v>46181.671691550924</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2673,11 +2673,11 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.388759016205</v>
+        <v>46118.55542568287</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46182.51235268518</v>
+        <v>46182.679019351854</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -2720,13 +2720,13 @@
         <v>90</v>
       </c>
       <c r="B21" s="9">
-        <v>46118.388960254626</v>
+        <v>46118.5556269213</v>
       </c>
       <c r="C21" s="9">
-        <v>46182.51205171296</v>
+        <v>46182.678718379626</v>
       </c>
       <c r="D21" s="9">
-        <v>46182.51206596065</v>
+        <v>46182.67873262732</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -2785,13 +2785,13 @@
         <v>95</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.38896474537</v>
+        <v>46118.55563141203</v>
       </c>
       <c r="C22" s="5">
-        <v>46155.73059027777</v>
+        <v>46155.897256944445</v>
       </c>
       <c r="D22" s="5">
-        <v>46169.68891788194</v>
+        <v>46169.85558454861</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2846,13 +2846,13 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46118.38896940972</v>
+        <v>46118.55563607639</v>
       </c>
       <c r="C23" s="9">
-        <v>46182.512035775464</v>
+        <v>46182.67870244213</v>
       </c>
       <c r="D23" s="9">
-        <v>46182.51203774306</v>
+        <v>46182.67870440972</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -2907,11 +2907,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.38897395833</v>
+        <v>46118.555640624996</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.688194560185</v>
+        <v>46169.85486122685</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -2970,11 +2970,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46118.38897876158</v>
+        <v>46118.55564542824</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.688784513884</v>
+        <v>46169.855451180556</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3029,11 +3029,11 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.388983240744</v>
+        <v>46118.55564990741</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.68883799769</v>
+        <v>46169.85550466435</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3088,13 +3088,13 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46118.38898793982</v>
+        <v>46118.555654606476</v>
       </c>
       <c r="C27" s="9">
-        <v>46182.51234460648</v>
+        <v>46182.67901127315</v>
       </c>
       <c r="D27" s="9">
-        <v>46182.51235559028</v>
+        <v>46182.67902225694</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3153,13 +3153,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.38899260417</v>
+        <v>46118.55565927083</v>
       </c>
       <c r="C28" s="5">
-        <v>46134.72622774306</v>
+        <v>46134.89289440972</v>
       </c>
       <c r="D28" s="5">
-        <v>46169.68873444444</v>
+        <v>46169.85540111111</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3214,13 +3214,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46118.3889971412</v>
+        <v>46118.55566380787</v>
       </c>
       <c r="C29" s="9">
-        <v>46182.51233065972</v>
+        <v>46182.67899732639</v>
       </c>
       <c r="D29" s="9">
-        <v>46182.51233219907</v>
+        <v>46182.67899886574</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3275,13 +3275,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.38900215278</v>
+        <v>46118.55566881945</v>
       </c>
       <c r="C30" s="5">
-        <v>46134.72626876157</v>
+        <v>46134.892935428245</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.68868207176</v>
+        <v>46169.85534873843</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3336,13 +3336,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46118.389006736106</v>
+        <v>46118.55567340278</v>
       </c>
       <c r="C31" s="9">
-        <v>46181.50514034722</v>
+        <v>46181.67180701389</v>
       </c>
       <c r="D31" s="9">
-        <v>46181.50515181713</v>
+        <v>46181.671818483796</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3401,13 +3401,13 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.38901627315</v>
+        <v>46118.55568293981</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.50506538195</v>
+        <v>46181.671732048606</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.50506667824</v>
+        <v>46181.671733344905</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3462,13 +3462,13 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46118.38902135417</v>
+        <v>46118.55568802083</v>
       </c>
       <c r="C33" s="9">
-        <v>46181.505125208336</v>
+        <v>46181.671791875</v>
       </c>
       <c r="D33" s="9">
-        <v>46181.50512674768</v>
+        <v>46181.67179341435</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3523,11 +3523,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.38876453704</v>
+        <v>46118.5554312037</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46135.33895278935</v>
+        <v>46135.50561945602</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3570,13 +3570,13 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46118.389070578705</v>
+        <v>46118.55573724537</v>
       </c>
       <c r="C35" s="9">
-        <v>46134.68942313657</v>
+        <v>46134.856089803245</v>
       </c>
       <c r="D35" s="9">
-        <v>46134.6894368287</v>
+        <v>46134.856103495375</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -3635,13 +3635,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.422677361115</v>
+        <v>46118.58934402778</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.68922825232</v>
+        <v>46134.85589491898</v>
       </c>
       <c r="D36" s="5">
-        <v>46134.68922973379</v>
+        <v>46134.85589640046</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3690,13 +3690,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="9">
-        <v>46118.42269068287</v>
+        <v>46118.58935734954</v>
       </c>
       <c r="C37" s="9">
-        <v>46134.68923696759</v>
+        <v>46134.85590363426</v>
       </c>
       <c r="D37" s="9">
-        <v>46134.68923822917</v>
+        <v>46134.855904895834</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3745,13 +3745,13 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.42269825231</v>
+        <v>46118.58936491898</v>
       </c>
       <c r="C38" s="5">
-        <v>46134.689397372684</v>
+        <v>46134.856064039355</v>
       </c>
       <c r="D38" s="5">
-        <v>46134.68939890046</v>
+        <v>46134.85606556713</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3800,13 +3800,13 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46118.4227059838</v>
+        <v>46118.58937265046</v>
       </c>
       <c r="C39" s="9">
-        <v>46134.68940369213</v>
+        <v>46134.8560703588</v>
       </c>
       <c r="D39" s="9">
-        <v>46134.68940524306</v>
+        <v>46134.85607190972</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>143</v>
@@ -3855,13 +3855,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.42271239583</v>
+        <v>46118.5893790625</v>
       </c>
       <c r="C40" s="5">
-        <v>46134.68941011574</v>
+        <v>46134.85607678241</v>
       </c>
       <c r="D40" s="5">
-        <v>46134.68941144676</v>
+        <v>46134.85607811343</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>143</v>
@@ -3910,13 +3910,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="9">
-        <v>46118.38907722222</v>
+        <v>46118.55574388889</v>
       </c>
       <c r="C41" s="9">
-        <v>46135.33864765047</v>
+        <v>46135.505314317124</v>
       </c>
       <c r="D41" s="9">
-        <v>46135.35593564815</v>
+        <v>46135.52260231481</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>151</v>
@@ -3975,13 +3975,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.42281954861</v>
+        <v>46118.58948621528</v>
       </c>
       <c r="C42" s="5">
-        <v>46135.33860112268</v>
+        <v>46135.505267789355</v>
       </c>
       <c r="D42" s="5">
-        <v>46135.33860295139</v>
+        <v>46135.50526961806</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>143</v>
@@ -4030,13 +4030,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="9">
-        <v>46118.42295252315</v>
+        <v>46118.589619189814</v>
       </c>
       <c r="C43" s="9">
-        <v>46135.33861204861</v>
+        <v>46135.50527871528</v>
       </c>
       <c r="D43" s="9">
-        <v>46135.338613541666</v>
+        <v>46135.50528020834</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>143</v>
@@ -4085,13 +4085,13 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.4229690625</v>
+        <v>46118.589635729164</v>
       </c>
       <c r="C44" s="5">
-        <v>46135.33861910879</v>
+        <v>46135.50528577546</v>
       </c>
       <c r="D44" s="5">
-        <v>46135.33862041667</v>
+        <v>46135.50528708333</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4140,13 +4140,13 @@
         <v>159</v>
       </c>
       <c r="B45" s="9">
-        <v>46118.42298265046</v>
+        <v>46118.58964931713</v>
       </c>
       <c r="C45" s="9">
-        <v>46135.338626550925</v>
+        <v>46135.50529321759</v>
       </c>
       <c r="D45" s="9">
-        <v>46135.338628495374</v>
+        <v>46135.50529516204</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>158</v>
@@ -4195,13 +4195,13 @@
         <v>160</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.42299203704</v>
+        <v>46118.5896587037</v>
       </c>
       <c r="C46" s="5">
-        <v>46135.338634189815</v>
+        <v>46135.50530085649</v>
       </c>
       <c r="D46" s="5">
-        <v>46135.33863545139</v>
+        <v>46135.50530211805</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>143</v>
@@ -4250,13 +4250,13 @@
         <v>161</v>
       </c>
       <c r="B47" s="9">
-        <v>46118.38908443287</v>
+        <v>46118.55575109954</v>
       </c>
       <c r="C47" s="9">
-        <v>46135.33892616898</v>
+        <v>46135.505592835645</v>
       </c>
       <c r="D47" s="9">
-        <v>46135.338938298606</v>
+        <v>46135.50560496528</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>84</v>
@@ -4315,13 +4315,13 @@
         <v>163</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.423060127316</v>
+        <v>46118.58972679398</v>
       </c>
       <c r="C48" s="5">
-        <v>46135.3388865625</v>
+        <v>46135.505553229166</v>
       </c>
       <c r="D48" s="5">
-        <v>46135.33888840278</v>
+        <v>46135.505555069445</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>143</v>
@@ -4368,13 +4368,13 @@
         <v>165</v>
       </c>
       <c r="B49" s="9">
-        <v>46118.4230809375</v>
+        <v>46118.58974760417</v>
       </c>
       <c r="C49" s="9">
-        <v>46135.338892581014</v>
+        <v>46135.505559247686</v>
       </c>
       <c r="D49" s="9">
-        <v>46135.338893900465</v>
+        <v>46135.50556056713</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>143</v>
@@ -4421,13 +4421,13 @@
         <v>166</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.42308603009</v>
+        <v>46118.58975269676</v>
       </c>
       <c r="C50" s="5">
-        <v>46135.33889986111</v>
+        <v>46135.505566527776</v>
       </c>
       <c r="D50" s="5">
-        <v>46135.33890128472</v>
+        <v>46135.50556795139</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>143</v>
@@ -4474,13 +4474,13 @@
         <v>167</v>
       </c>
       <c r="B51" s="9">
-        <v>46118.423097245366</v>
+        <v>46118.58976391204</v>
       </c>
       <c r="C51" s="9">
-        <v>46135.3389065625</v>
+        <v>46135.505573229166</v>
       </c>
       <c r="D51" s="9">
-        <v>46135.33890837963</v>
+        <v>46135.50557504629</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>143</v>
@@ -4527,13 +4527,13 @@
         <v>168</v>
       </c>
       <c r="B52" s="5">
-        <v>46118.42309224537</v>
+        <v>46118.589758912036</v>
       </c>
       <c r="C52" s="5">
-        <v>46135.338914340275</v>
+        <v>46135.505581006946</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.33891574074</v>
+        <v>46135.50558240741</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>143</v>
@@ -4580,11 +4580,11 @@
         <v>169</v>
       </c>
       <c r="B53" s="9">
-        <v>46118.38909226852</v>
+        <v>46118.55575893518</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46182.03955732639</v>
+        <v>46182.20622399305</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>170</v>
@@ -4643,11 +4643,11 @@
         <v>173</v>
       </c>
       <c r="B54" s="5">
-        <v>46118.423202465274</v>
+        <v>46118.589869131945</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.0019809375</v>
+        <v>46181.168647604165</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>143</v>
@@ -4696,11 +4696,11 @@
         <v>175</v>
       </c>
       <c r="B55" s="9">
-        <v>46118.42321666666</v>
+        <v>46118.589883333334</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46181.0019824537</v>
+        <v>46181.16864912037</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>143</v>
@@ -4749,11 +4749,11 @@
         <v>176</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.423223645834</v>
+        <v>46118.589890312505</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46181.00198376157</v>
+        <v>46181.16865042824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>143</v>
@@ -4802,11 +4802,11 @@
         <v>177</v>
       </c>
       <c r="B57" s="9">
-        <v>46118.42325384259</v>
+        <v>46118.58992050926</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46181.0019865162</v>
+        <v>46181.168653182875</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>143</v>
@@ -4855,11 +4855,11 @@
         <v>178</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.42323288195</v>
+        <v>46118.589899548606</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46181.00198501158</v>
+        <v>46181.168651678236</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>143</v>
@@ -4908,13 +4908,13 @@
         <v>179</v>
       </c>
       <c r="B59" s="9">
-        <v>46118.38909813657</v>
+        <v>46118.55576480324</v>
       </c>
       <c r="C59" s="9">
-        <v>46181.505299675926</v>
+        <v>46181.67196634259</v>
       </c>
       <c r="D59" s="9">
-        <v>46181.50538365741</v>
+        <v>46181.67205032408</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>180</v>
@@ -4957,13 +4957,13 @@
         <v>182</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.3891028588</v>
+        <v>46118.55576952547</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.50523445602</v>
+        <v>46181.67190112268</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.50524850695</v>
+        <v>46181.67191517361</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>183</v>
@@ -5022,13 +5022,13 @@
         <v>187</v>
       </c>
       <c r="B61" s="9">
-        <v>46118.38910940972</v>
+        <v>46118.55577607639</v>
       </c>
       <c r="C61" s="9">
-        <v>46181.50528408565</v>
+        <v>46181.671950752316</v>
       </c>
       <c r="D61" s="9">
-        <v>46181.5053002662</v>
+        <v>46181.671966932874</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>188</v>
@@ -5087,11 +5087,11 @@
         <v>191</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.38911456018</v>
+        <v>46118.55578122685</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46181.505558206016</v>
+        <v>46181.67222487269</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>192</v>
@@ -5134,13 +5134,13 @@
         <v>194</v>
       </c>
       <c r="B63" s="9">
-        <v>46118.38911793982</v>
+        <v>46118.55578460648</v>
       </c>
       <c r="C63" s="9">
-        <v>46181.50554564815</v>
+        <v>46181.672212314814</v>
       </c>
       <c r="D63" s="9">
-        <v>46181.50556121528</v>
+        <v>46181.67222788194</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>195</v>
@@ -5199,11 +5199,11 @@
         <v>199</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.38912344907</v>
+        <v>46118.555790115744</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46181.5060237963</v>
+        <v>46181.67269046296</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>200</v>
@@ -5262,13 +5262,13 @@
         <v>201</v>
       </c>
       <c r="B65" s="9">
-        <v>46118.423391226854</v>
+        <v>46118.59005789352</v>
       </c>
       <c r="C65" s="9">
-        <v>46181.50567078704</v>
+        <v>46181.6723374537</v>
       </c>
       <c r="D65" s="9">
-        <v>46181.50567189815</v>
+        <v>46181.672338564815</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>143</v>
@@ -5317,13 +5317,13 @@
         <v>204</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.4234009375</v>
+        <v>46118.590067604164</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.50568425926</v>
+        <v>46181.672350925925</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.50568577547</v>
+        <v>46181.672352442125</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>143</v>
@@ -5372,13 +5372,13 @@
         <v>206</v>
       </c>
       <c r="B67" s="9">
-        <v>46118.423409317125</v>
+        <v>46118.5900759838</v>
       </c>
       <c r="C67" s="9">
-        <v>46181.505698368055</v>
+        <v>46181.67236503473</v>
       </c>
       <c r="D67" s="9">
-        <v>46181.5056996412</v>
+        <v>46181.672366307874</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>143</v>
@@ -5427,11 +5427,11 @@
         <v>207</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.423431296294</v>
+        <v>46118.590097962966</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46181.505556689815</v>
+        <v>46181.67222335648</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>143</v>
@@ -5480,11 +5480,11 @@
         <v>208</v>
       </c>
       <c r="B69" s="9">
-        <v>46118.423435868055</v>
+        <v>46118.59010253473</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46181.50555787037</v>
+        <v>46181.67222453703</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>143</v>
@@ -5533,11 +5533,11 @@
         <v>209</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.389130173615</v>
+        <v>46118.55579684028</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46181.50606773148</v>
+        <v>46181.67273439815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>210</v>
@@ -5596,13 +5596,13 @@
         <v>211</v>
       </c>
       <c r="B71" s="9">
-        <v>46118.42348722222</v>
+        <v>46118.59015388889</v>
       </c>
       <c r="C71" s="9">
-        <v>46181.50577675926</v>
+        <v>46181.67244342592</v>
       </c>
       <c r="D71" s="9">
-        <v>46181.505778067134</v>
+        <v>46181.67244473379</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>143</v>
@@ -5651,13 +5651,13 @@
         <v>214</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.42349569444</v>
+        <v>46118.59016236111</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.505789930554</v>
+        <v>46181.672456597225</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.50579141204</v>
+        <v>46181.672458078705</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>143</v>
@@ -5706,13 +5706,13 @@
         <v>215</v>
       </c>
       <c r="B73" s="9">
-        <v>46118.4235046875</v>
+        <v>46118.59017135417</v>
       </c>
       <c r="C73" s="9">
-        <v>46181.505796990736</v>
+        <v>46181.67246365741</v>
       </c>
       <c r="D73" s="9">
-        <v>46181.50579833333</v>
+        <v>46181.672464999996</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>143</v>
@@ -5761,11 +5761,11 @@
         <v>216</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.42352575231</v>
+        <v>46118.59019241898</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46167.00138289352</v>
+        <v>46167.16804956019</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>143</v>
@@ -5814,11 +5814,11 @@
         <v>217</v>
       </c>
       <c r="B75" s="9">
-        <v>46118.42353082176</v>
+        <v>46118.590197488425</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46167.00138434028</v>
+        <v>46167.16805100694</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>143</v>
@@ -5867,11 +5867,11 @@
         <v>218</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.38913660879</v>
+        <v>46118.55580327546</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.4187156713</v>
+        <v>46118.58538233796</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>180</v>
@@ -5914,11 +5914,11 @@
         <v>220</v>
       </c>
       <c r="B77" s="9">
-        <v>46118.38914018519</v>
+        <v>46118.55580685185</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46182.512058935186</v>
+        <v>46182.67872560185</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>221</v>
@@ -5975,11 +5975,11 @@
         <v>223</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.38914653935</v>
+        <v>46118.55581320602</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46130.026750868055</v>
+        <v>46130.19341753473</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>224</v>
@@ -6036,11 +6036,11 @@
         <v>225</v>
       </c>
       <c r="B79" s="9">
-        <v>46118.38915269676</v>
+        <v>46118.55581936342</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.512348703705</v>
+        <v>46182.67901537037</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>226</v>
@@ -6097,11 +6097,11 @@
         <v>227</v>
       </c>
       <c r="B80" s="5">
-        <v>46118.38915849537</v>
+        <v>46118.55582516204</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46118.4716127662</v>
+        <v>46118.63827943287</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>228</v>
@@ -6144,11 +6144,11 @@
         <v>230</v>
       </c>
       <c r="B81" s="9">
-        <v>46118.38916210648</v>
+        <v>46118.55582877315</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46175.01907461806</v>
+        <v>46175.185741284724</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>231</v>
@@ -6207,11 +6207,11 @@
         <v>232</v>
       </c>
       <c r="B82" s="5">
-        <v>46118.423583958334</v>
+        <v>46118.590250625</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46181.505782673616</v>
+        <v>46181.67244934027</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>143</v>
@@ -6260,11 +6260,11 @@
         <v>234</v>
       </c>
       <c r="B83" s="9">
-        <v>46118.423592974534</v>
+        <v>46118.590259641205</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46181.505797233796</v>
+        <v>46181.67246390047</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>143</v>
@@ -6313,11 +6313,11 @@
         <v>235</v>
       </c>
       <c r="B84" s="5">
-        <v>46118.42360094907</v>
+        <v>46118.59026761574</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46181.505803148146</v>
+        <v>46181.67246981482</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>143</v>
@@ -6366,11 +6366,11 @@
         <v>236</v>
       </c>
       <c r="B85" s="9">
-        <v>46118.42360896991</v>
+        <v>46118.590275636576</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46174.00253297454</v>
+        <v>46174.169199641205</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>143</v>
@@ -6419,11 +6419,11 @@
         <v>237</v>
       </c>
       <c r="B86" s="5">
-        <v>46118.42361763889</v>
+        <v>46118.59028430555</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46174.002534363426</v>
+        <v>46174.16920103009</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>143</v>
@@ -6472,11 +6472,11 @@
         <v>238</v>
       </c>
       <c r="B87" s="9">
-        <v>46118.38916792824</v>
+        <v>46118.55583459491</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46176.01475672454</v>
+        <v>46176.1814233912</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>239</v>
@@ -6535,11 +6535,11 @@
         <v>240</v>
       </c>
       <c r="B88" s="5">
-        <v>46118.42366811342</v>
+        <v>46118.59033478009</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46175.00144059028</v>
+        <v>46175.16810725695</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>143</v>
@@ -6586,11 +6586,11 @@
         <v>243</v>
       </c>
       <c r="B89" s="9">
-        <v>46118.423677812505</v>
+        <v>46118.59034447916</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46175.001442175926</v>
+        <v>46175.1681088426</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>143</v>
@@ -6637,11 +6637,11 @@
         <v>244</v>
       </c>
       <c r="B90" s="5">
-        <v>46118.42368547454</v>
+        <v>46118.590352141204</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46175.00144356482</v>
+        <v>46175.16811023148</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>143</v>
@@ -6688,11 +6688,11 @@
         <v>245</v>
       </c>
       <c r="B91" s="9">
-        <v>46118.42369300926</v>
+        <v>46118.59035967593</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46175.00144482639</v>
+        <v>46175.168111493054</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>143</v>
@@ -6739,11 +6739,11 @@
         <v>246</v>
       </c>
       <c r="B92" s="5">
-        <v>46118.42370167824</v>
+        <v>46118.59036834491</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46175.00144622685</v>
+        <v>46175.168112893516</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>143</v>
@@ -6790,11 +6790,11 @@
         <v>247</v>
       </c>
       <c r="B93" s="9">
-        <v>46118.38917577546</v>
+        <v>46118.55584244213</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46177.02791280093</v>
+        <v>46177.19457946759</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>248</v>
@@ -6851,11 +6851,11 @@
         <v>249</v>
       </c>
       <c r="B94" s="5">
-        <v>46118.4237540162</v>
+        <v>46118.59042068287</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46176.00152414352</v>
+        <v>46176.16819081019</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>143</v>
@@ -6902,11 +6902,11 @@
         <v>252</v>
       </c>
       <c r="B95" s="9">
-        <v>46118.423761365746</v>
+        <v>46118.5904280324</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46176.00152575232</v>
+        <v>46176.168192418976</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>143</v>
@@ -6953,11 +6953,11 @@
         <v>253</v>
       </c>
       <c r="B96" s="5">
-        <v>46118.423777986114</v>
+        <v>46118.59044465278</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46176.00152827546</v>
+        <v>46176.16819494213</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>143</v>
@@ -7004,11 +7004,11 @@
         <v>254</v>
       </c>
       <c r="B97" s="9">
-        <v>46118.423772442125</v>
+        <v>46118.5904391088</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46176.00152693287</v>
+        <v>46176.16819359954</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>143</v>
@@ -7055,11 +7055,11 @@
         <v>255</v>
       </c>
       <c r="B98" s="5">
-        <v>46118.4237856713</v>
+        <v>46118.59045233796</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46176.001529733796</v>
+        <v>46176.16819640047</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>143</v>
@@ -7106,11 +7106,11 @@
         <v>256</v>
       </c>
       <c r="B99" s="9">
-        <v>46118.38918320602</v>
+        <v>46118.55584987269</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46178.011843472224</v>
+        <v>46178.17851013889</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>257</v>
@@ -7167,11 +7167,11 @@
         <v>258</v>
       </c>
       <c r="B100" s="5">
-        <v>46118.42387261574</v>
+        <v>46118.590539282406</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46177.001502071755</v>
+        <v>46177.168168738426</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>143</v>
@@ -7218,11 +7218,11 @@
         <v>261</v>
       </c>
       <c r="B101" s="9">
-        <v>46118.42388</v>
+        <v>46118.590546666666</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46177.00150387731</v>
+        <v>46177.168170543984</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>143</v>
@@ -7269,11 +7269,11 @@
         <v>263</v>
       </c>
       <c r="B102" s="5">
-        <v>46118.42388736111</v>
+        <v>46118.590554027774</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46177.00150515046</v>
+        <v>46177.16817181713</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>143</v>
@@ -7320,11 +7320,11 @@
         <v>265</v>
       </c>
       <c r="B103" s="9">
-        <v>46118.42389449074</v>
+        <v>46118.59056115741</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46177.00150623843</v>
+        <v>46177.16817290509</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>143</v>
@@ -7371,11 +7371,11 @@
         <v>266</v>
       </c>
       <c r="B104" s="5">
-        <v>46118.42390262731</v>
+        <v>46118.590569293985</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46177.00150747685</v>
+        <v>46177.16817414352</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>143</v>
@@ -7422,11 +7422,11 @@
         <v>267</v>
       </c>
       <c r="B105" s="9">
-        <v>46118.38919078704</v>
+        <v>46118.5558574537</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46179.03771721065</v>
+        <v>46179.20438387731</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>268</v>
@@ -7485,11 +7485,11 @@
         <v>269</v>
       </c>
       <c r="B106" s="5">
-        <v>46118.42395989584</v>
+        <v>46118.5906265625</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46178.00245627315</v>
+        <v>46178.16912293981</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>143</v>
@@ -7536,11 +7536,11 @@
         <v>271</v>
       </c>
       <c r="B107" s="9">
-        <v>46118.42396721065</v>
+        <v>46118.59063387732</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46178.0024582176</v>
+        <v>46178.169124884254</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>143</v>
@@ -7587,11 +7587,11 @@
         <v>272</v>
       </c>
       <c r="B108" s="5">
-        <v>46118.42398881944</v>
+        <v>46118.590655486114</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46178.002473113425</v>
+        <v>46178.16913978009</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>143</v>
@@ -7638,11 +7638,11 @@
         <v>273</v>
       </c>
       <c r="B109" s="9">
-        <v>46118.4239949537</v>
+        <v>46118.59066162037</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46178.0024746875</v>
+        <v>46178.16914135417</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>143</v>
@@ -7689,11 +7689,11 @@
         <v>274</v>
       </c>
       <c r="B110" s="5">
-        <v>46118.424000439816</v>
+        <v>46118.59066710648</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46178.0024759838</v>
+        <v>46178.16914265046</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>143</v>
@@ -7740,11 +7740,11 @@
         <v>275</v>
       </c>
       <c r="B111" s="9">
-        <v>46118.38924604167</v>
+        <v>46118.55591270833</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46183.0281077199</v>
+        <v>46183.194774386575</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>276</v>
@@ -7801,11 +7801,11 @@
         <v>278</v>
       </c>
       <c r="B112" s="5">
-        <v>46118.424038576384</v>
+        <v>46118.590705243056</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.00144414352</v>
+        <v>46182.168110810184</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>143</v>
@@ -7854,11 +7854,11 @@
         <v>280</v>
       </c>
       <c r="B113" s="9">
-        <v>46118.42404608797</v>
+        <v>46118.59071275463</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46182.00144552083</v>
+        <v>46182.1681121875</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>143</v>
@@ -7907,11 +7907,11 @@
         <v>281</v>
       </c>
       <c r="B114" s="5">
-        <v>46118.42405342593</v>
+        <v>46118.590720092594</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.00144664352</v>
+        <v>46182.16811331018</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>143</v>
@@ -7960,11 +7960,11 @@
         <v>282</v>
       </c>
       <c r="B115" s="9">
-        <v>46118.42406116898</v>
+        <v>46118.590727835646</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46182.00144784722</v>
+        <v>46182.16811451389</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>143</v>
@@ -8013,11 +8013,11 @@
         <v>283</v>
       </c>
       <c r="B116" s="5">
-        <v>46118.42406868056</v>
+        <v>46118.59073534722</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46182.00144903935</v>
+        <v>46182.16811570602</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>143</v>
@@ -8066,11 +8066,11 @@
         <v>284</v>
       </c>
       <c r="B117" s="9">
-        <v>46118.38925288194</v>
+        <v>46118.55591954861</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46118.47284023148</v>
+        <v>46118.63950689815</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>285</v>
@@ -8113,11 +8113,11 @@
         <v>287</v>
       </c>
       <c r="B118" s="5">
-        <v>46118.38925648148</v>
+        <v>46118.555923148146</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46184.01397060185</v>
+        <v>46184.18063726852</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>288</v>
@@ -8174,11 +8174,11 @@
         <v>291</v>
       </c>
       <c r="B119" s="9">
-        <v>46118.42412635416</v>
+        <v>46118.590793020834</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46183.0015775</v>
+        <v>46183.16824416666</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>143</v>
@@ -8225,11 +8225,11 @@
         <v>292</v>
       </c>
       <c r="B120" s="5">
-        <v>46118.424133831024</v>
+        <v>46118.59080049768</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46183.00157905092</v>
+        <v>46183.16824571759</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>143</v>
@@ -8276,11 +8276,11 @@
         <v>293</v>
       </c>
       <c r="B121" s="9">
-        <v>46118.424140138886</v>
+        <v>46118.59080680556</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46183.001580208336</v>
+        <v>46183.168246875</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>143</v>
@@ -8327,11 +8327,11 @@
         <v>294</v>
       </c>
       <c r="B122" s="5">
-        <v>46118.42414888889</v>
+        <v>46118.59081555555</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46183.00158148148</v>
+        <v>46183.16824814815</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>143</v>
@@ -8378,11 +8378,11 @@
         <v>295</v>
       </c>
       <c r="B123" s="9">
-        <v>46118.42415611111</v>
+        <v>46118.590822777776</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46183.0015827662</v>
+        <v>46183.16824943287</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>143</v>
@@ -8429,11 +8429,11 @@
         <v>296</v>
       </c>
       <c r="B124" s="5">
-        <v>46118.38926131945</v>
+        <v>46118.55592798611</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46185.00765436343</v>
+        <v>46185.17432103009</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>297</v>
@@ -8490,11 +8490,11 @@
         <v>299</v>
       </c>
       <c r="B125" s="9">
-        <v>46118.424208530094</v>
+        <v>46118.59087519676</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46184.0013658449</v>
+        <v>46184.168032511574</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>143</v>
@@ -8541,11 +8541,11 @@
         <v>301</v>
       </c>
       <c r="B126" s="5">
-        <v>46118.42421657407</v>
+        <v>46118.590883240744</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46184.00136753472</v>
+        <v>46184.168034201386</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>143</v>
@@ -8592,11 +8592,11 @@
         <v>302</v>
       </c>
       <c r="B127" s="9">
-        <v>46118.42422490741</v>
+        <v>46118.59089157407</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46184.00136875</v>
+        <v>46184.16803541667</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>143</v>
@@ -8643,11 +8643,11 @@
         <v>303</v>
       </c>
       <c r="B128" s="5">
-        <v>46118.42423116898</v>
+        <v>46118.590897835646</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46184.001370196755</v>
+        <v>46184.168036863426</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>158</v>
@@ -8694,11 +8694,11 @@
         <v>304</v>
       </c>
       <c r="B129" s="9">
-        <v>46118.424238287036</v>
+        <v>46118.5909049537</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46184.001371446764</v>
+        <v>46184.16803811342</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>158</v>
@@ -8745,11 +8745,11 @@
         <v>305</v>
       </c>
       <c r="B130" s="5">
-        <v>46118.389265844904</v>
+        <v>46118.555932511576</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46185.00193493055</v>
+        <v>46185.16860159722</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>306</v>
@@ -8806,11 +8806,11 @@
         <v>308</v>
       </c>
       <c r="B131" s="9">
-        <v>46118.42428747685</v>
+        <v>46118.59095414352</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46185.00192829861</v>
+        <v>46185.168594965275</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>143</v>
@@ -8857,11 +8857,11 @@
         <v>310</v>
       </c>
       <c r="B132" s="5">
-        <v>46118.42430009259</v>
+        <v>46118.590966759264</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46185.00193006944</v>
+        <v>46185.16859673611</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>143</v>
@@ -8908,11 +8908,11 @@
         <v>311</v>
       </c>
       <c r="B133" s="9">
-        <v>46118.42430712963</v>
+        <v>46118.590973796294</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46185.00193128472</v>
+        <v>46185.168597951386</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>143</v>
@@ -8959,11 +8959,11 @@
         <v>312</v>
       </c>
       <c r="B134" s="5">
-        <v>46118.42431328703</v>
+        <v>46118.590979953704</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46185.00193237269</v>
+        <v>46185.16859903935</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>143</v>
@@ -9010,11 +9010,11 @@
         <v>313</v>
       </c>
       <c r="B135" s="9">
-        <v>46118.42431822917</v>
+        <v>46118.59098489583</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46185.00193356481</v>
+        <v>46185.16860023148</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>143</v>
@@ -9061,11 +9061,11 @@
         <v>314</v>
       </c>
       <c r="B136" s="5">
-        <v>46118.38927048611</v>
+        <v>46118.55593715278</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46181.0320891088</v>
+        <v>46181.19875577546</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>315</v>
@@ -9122,11 +9122,11 @@
         <v>317</v>
       </c>
       <c r="B137" s="9">
-        <v>46118.42436438658</v>
+        <v>46118.59103105324</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46118.48074289352</v>
+        <v>46118.64740956019</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>143</v>
@@ -9173,11 +9173,11 @@
         <v>318</v>
       </c>
       <c r="B138" s="5">
-        <v>46118.42437237268</v>
+        <v>46118.591039039355</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46118.48073887732</v>
+        <v>46118.64740554398</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>143</v>
@@ -9224,11 +9224,11 @@
         <v>319</v>
       </c>
       <c r="B139" s="9">
-        <v>46118.42437974537</v>
+        <v>46118.59104641204</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46118.480735439814</v>
+        <v>46118.64740210648</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>143</v>
@@ -9275,11 +9275,11 @@
         <v>320</v>
       </c>
       <c r="B140" s="5">
-        <v>46118.42438591435</v>
+        <v>46118.59105258102</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46118.48073234953</v>
+        <v>46118.647399016205</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>143</v>
@@ -9326,11 +9326,11 @@
         <v>321</v>
       </c>
       <c r="B141" s="9">
-        <v>46118.42439163194</v>
+        <v>46118.59105829861</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46118.480727476854</v>
+        <v>46118.64739414352</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>143</v>
@@ -9377,11 +9377,11 @@
         <v>322</v>
       </c>
       <c r="B142" s="5">
-        <v>46118.389275925925</v>
+        <v>46118.55594259259</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46118.48091908565</v>
+        <v>46118.64758575232</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>323</v>
@@ -9424,11 +9424,11 @@
         <v>325</v>
       </c>
       <c r="B143" s="9">
-        <v>46118.38927884259</v>
+        <v>46118.55594550926</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46118.48101511574</v>
+        <v>46118.64768178241</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>326</v>
@@ -9487,11 +9487,11 @@
         <v>329</v>
       </c>
       <c r="B144" s="5">
-        <v>46118.389283530094</v>
+        <v>46118.55595019676</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46118.48101552083</v>
+        <v>46118.6476821875</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>330</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -999,34 +999,34 @@
     <t>PACKING LIST</t>
   </si>
   <si>
+    <t>1213955238648475</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT 4280 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1213955238648476</t>
+  </si>
+  <si>
+    <t>1213955238648477</t>
+  </si>
+  <si>
+    <t>1213955238648478</t>
+  </si>
+  <si>
+    <t>1213955238648479</t>
+  </si>
+  <si>
+    <t>1213962358641005</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Logistica:,Gestion,Costos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213955238648475</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT 4280 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1213955238648476</t>
-  </si>
-  <si>
-    <t>1213955238648477</t>
-  </si>
-  <si>
-    <t>1213955238648478</t>
-  </si>
-  <si>
-    <t>1213955238648479</t>
-  </si>
-  <si>
-    <t>1213962358641005</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Logistica:,Gestion,Costos</t>
   </si>
   <si>
     <t>1213955238648480</t>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46185.16860159722</v>
+        <v>46186.16794060185</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>306</v>
@@ -8791,8 +8791,8 @@
       <c r="R130" s="5">
         <v>46185</v>
       </c>
-      <c r="S130" s="11" t="s">
-        <v>307</v>
+      <c r="S130" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
@@ -8803,7 +8803,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B131" s="9">
         <v>46118.59095414352</v>
@@ -8844,7 +8844,7 @@
         <v>143</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -8854,7 +8854,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B132" s="5">
         <v>46118.590966759264</v>
@@ -8895,7 +8895,7 @@
         <v>143</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -8905,7 +8905,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B133" s="9">
         <v>46118.590973796294</v>
@@ -8946,7 +8946,7 @@
         <v>143</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B134" s="5">
         <v>46118.590979953704</v>
@@ -8997,7 +8997,7 @@
         <v>158</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9007,7 +9007,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B135" s="9">
         <v>46118.59098489583</v>
@@ -9048,7 +9048,7 @@
         <v>158</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9058,7 +9058,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B136" s="5">
         <v>46118.55593715278</v>
@@ -9068,7 +9068,7 @@
         <v>46181.19875577546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9099,7 +9099,7 @@
         <v>141</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q136" s="5">
         <v>46188</v>
@@ -9108,7 +9108,7 @@
         <v>46188</v>
       </c>
       <c r="S136" s="11" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
@@ -9154,13 +9154,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>143</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9205,13 +9205,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9256,13 +9256,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>143</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9307,13 +9307,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9358,13 +9358,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O141" s="10" t="s">
         <v>143</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9461,7 +9461,7 @@
         <v>323</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>323</v>
@@ -9524,7 +9524,7 @@
         <v>323</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>323</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="330">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -1024,9 +1024,6 @@
   </si>
   <si>
     <t>Logistica:,Gestion,Costos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213955238648480</t>
@@ -9065,7 +9062,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46188.16859015047</v>
+        <v>46189.2078791088</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>314</v>
@@ -9107,8 +9104,8 @@
       <c r="R136" s="5">
         <v>46188</v>
       </c>
-      <c r="S136" s="11" t="s">
-        <v>316</v>
+      <c r="S136" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
@@ -9119,7 +9116,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B137" s="9">
         <v>46118.59103105324</v>
@@ -9170,7 +9167,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B138" s="5">
         <v>46118.591039039355</v>
@@ -9221,7 +9218,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B139" s="9">
         <v>46118.59104641204</v>
@@ -9272,7 +9269,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B140" s="5">
         <v>46118.59105258102</v>
@@ -9323,7 +9320,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B141" s="9">
         <v>46118.59105829861</v>
@@ -9374,7 +9371,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B142" s="5">
         <v>46118.55594259259</v>
@@ -9384,7 +9381,7 @@
         <v>46118.64758575232</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>25</v>
@@ -9408,7 +9405,7 @@
         <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>26</v>
@@ -9421,7 +9418,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B143" s="9">
         <v>46118.55594550926</v>
@@ -9431,16 +9428,16 @@
         <v>46118.64768178241</v>
       </c>
       <c r="E143" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="F143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G143" s="10" t="s">
+      <c r="H143" s="10" t="s">
         <v>327</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>328</v>
       </c>
       <c r="I143" s="9">
         <v>46189</v>
@@ -9458,13 +9455,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O143" s="10" t="s">
         <v>314</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q143" s="9">
         <v>46197</v>
@@ -9484,7 +9481,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B144" s="5">
         <v>46118.55595019676</v>
@@ -9494,16 +9491,16 @@
         <v>46118.6476821875</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>327</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>328</v>
       </c>
       <c r="I144" s="5">
         <v>46189</v>
@@ -9521,13 +9518,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>314</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q144" s="5">
         <v>46197</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="331">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -1060,6 +1060,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213964514232197</t>
@@ -9425,7 +9428,7 @@
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46118.64768178241</v>
+        <v>46190.178547442134</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>325</v>
@@ -9469,8 +9472,8 @@
       <c r="R143" s="9">
         <v>46189</v>
       </c>
-      <c r="S143" s="7" t="s">
-        <v>33</v>
+      <c r="S143" s="11" t="s">
+        <v>328</v>
       </c>
       <c r="T143" s="10">
         <v>0</v>
@@ -9481,17 +9484,17 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B144" s="5">
         <v>46118.55595019676</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46118.6476821875</v>
+        <v>46190.178546655094</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9532,8 +9535,8 @@
       <c r="R144" s="5">
         <v>46189</v>
       </c>
-      <c r="S144" s="7" t="s">
-        <v>33</v>
+      <c r="S144" s="11" t="s">
+        <v>328</v>
       </c>
       <c r="T144" s="6">
         <v>0</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="329">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -198,7 +198,7 @@
 ·         Se requiere duplicado de placas.</t>
   </si>
   <si>
-    <t>Ingenieria Basica Motor,Ingenieria basica Rodete,Ingenieria Detalle,Analisis de costeo</t>
+    <t>Ingenieria Basica Motor,Ingenieria basica Rodete,Ingenieria Detalle</t>
   </si>
   <si>
     <t>1213963044037391</t>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213955244874822</t>
@@ -261,15 +264,6 @@
   </si>
   <si>
     <t>OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1213962358561318</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213963037596629</t>
@@ -1592,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U144"/>
+  <dimension ref="A1:U143"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -1943,7 +1937,7 @@
         <v>46134.849233009256</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.84977677083</v>
+        <v>46191.71012979167</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -2067,7 +2061,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.85154157407</v>
+        <v>46191.71013903935</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2103,11 +2097,13 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="11" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="9">
         <v>46118.55558501158</v>
@@ -2119,7 +2115,7 @@
         <v>46171.91061798611</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
@@ -2140,7 +2136,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2152,7 +2148,7 @@
         <v>43</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q11" s="9">
         <v>46104</v>
@@ -2172,7 +2168,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="5">
         <v>46118.55558986111</v>
@@ -2184,7 +2180,7 @@
         <v>46134.85090979167</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2205,7 +2201,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2217,7 +2213,7 @@
         <v>43</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="5">
         <v>46104</v>
@@ -2237,7 +2233,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="9">
         <v>46118.55559503472</v>
@@ -2249,7 +2245,7 @@
         <v>46134.85046350694</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2270,7 +2266,7 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
@@ -2282,7 +2278,7 @@
         <v>43</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="9">
         <v>46105</v>
@@ -2302,33 +2298,27 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.555600127314</v>
+        <v>46118.55541763889</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46134.849261111114</v>
+        <v>46181.67168136574</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="5">
-        <v>46101</v>
-      </c>
-      <c r="J14" s="5">
-        <v>46108</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
         <v>26</v>
       </c>
@@ -2336,104 +2326,110 @@
         <v>26</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>46108</v>
-      </c>
-      <c r="R14" s="5">
-        <v>46101</v>
-      </c>
-      <c r="S14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>65</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46118.55541763889</v>
-      </c>
-      <c r="C15" s="10"/>
+        <v>46118.55560518519</v>
+      </c>
+      <c r="C15" s="9">
+        <v>46134.85201509259</v>
+      </c>
       <c r="D15" s="9">
-        <v>46181.67168136574</v>
+        <v>46134.85202921296</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="9">
+        <v>46105</v>
+      </c>
+      <c r="J15" s="9">
+        <v>46106</v>
+      </c>
       <c r="K15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>46106</v>
+      </c>
+      <c r="R15" s="9">
+        <v>46105</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="10">
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.55560518519</v>
-      </c>
-      <c r="C16" s="5">
-        <v>46134.85201509259</v>
-      </c>
+        <v>46118.555610462965</v>
+      </c>
+      <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46134.85202921296</v>
+        <v>46169.85490482639</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="I16" s="5">
         <v>46105</v>
@@ -2445,19 +2441,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="5">
         <v>46106</v>
@@ -2477,26 +2473,28 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B17" s="9">
-        <v>46118.555610462965</v>
-      </c>
-      <c r="C17" s="10"/>
+        <v>46118.555615578705</v>
+      </c>
+      <c r="C17" s="9">
+        <v>46134.8523972338</v>
+      </c>
       <c r="D17" s="9">
-        <v>46169.85490482639</v>
+        <v>46134.85241319444</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="I17" s="9">
         <v>46105</v>
@@ -2508,19 +2506,19 @@
         <v>26</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="9">
         <v>46106</v>
@@ -2540,61 +2538,61 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.555615578705</v>
+        <v>46118.55562122686</v>
       </c>
       <c r="C18" s="5">
-        <v>46134.8523972338</v>
+        <v>46181.67167443287</v>
       </c>
       <c r="D18" s="5">
-        <v>46134.85241319444</v>
+        <v>46181.671691550924</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="I18" s="5">
-        <v>46105</v>
+        <v>46135</v>
       </c>
       <c r="J18" s="5">
-        <v>46106</v>
+        <v>46135</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="5">
-        <v>46106</v>
+        <v>46121</v>
       </c>
       <c r="R18" s="5">
-        <v>46105</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>33</v>
+        <v>46121</v>
+      </c>
+      <c r="S18" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2605,35 +2603,27 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46118.55562122686</v>
-      </c>
-      <c r="C19" s="9">
-        <v>46181.67167443287</v>
-      </c>
+        <v>46118.55542568287</v>
+      </c>
+      <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46181.671691550924</v>
+        <v>46182.679019351854</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I19" s="9">
-        <v>46135</v>
-      </c>
-      <c r="J19" s="9">
-        <v>46135</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
       <c r="K19" s="10" t="s">
         <v>26</v>
       </c>
@@ -2641,56 +2631,54 @@
         <v>26</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>46121</v>
-      </c>
-      <c r="R19" s="9">
-        <v>46121</v>
-      </c>
-      <c r="S19" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T19" s="10">
-        <v>1</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.55542568287</v>
-      </c>
-      <c r="C20" s="6"/>
+        <v>46118.5556269213</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46182.678718379626</v>
+      </c>
       <c r="D20" s="5">
-        <v>46182.679019351854</v>
+        <v>46182.67873262732</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="5">
+        <v>46107</v>
+      </c>
+      <c r="J20" s="5">
+        <v>46112</v>
+      </c>
       <c r="K20" s="6" t="s">
         <v>26</v>
       </c>
@@ -2698,53 +2686,63 @@
         <v>26</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>46048</v>
+      </c>
+      <c r="R20" s="5">
+        <v>46043</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T20" s="6">
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46118.55563141203</v>
+      </c>
+      <c r="C21" s="9">
+        <v>46155.897256944445</v>
+      </c>
+      <c r="D21" s="9">
+        <v>46169.85558454861</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="9">
-        <v>46118.5556269213</v>
-      </c>
-      <c r="C21" s="9">
-        <v>46182.678718379626</v>
-      </c>
-      <c r="D21" s="9">
-        <v>46182.67873262732</v>
-      </c>
-      <c r="E21" s="10" t="s">
+      <c r="H21" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="I21" s="9">
         <v>46107</v>
       </c>
       <c r="J21" s="9">
-        <v>46112</v>
+        <v>46108</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>26</v>
@@ -2756,60 +2754,56 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>46048</v>
-      </c>
-      <c r="R21" s="9">
-        <v>46043</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
       <c r="S21" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>1</v>
-      </c>
-      <c r="U21" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U21" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.55563141203</v>
+        <v>46118.55563607639</v>
       </c>
       <c r="C22" s="5">
-        <v>46155.897256944445</v>
+        <v>46182.67870244213</v>
       </c>
       <c r="D22" s="5">
-        <v>46169.85558454861</v>
+        <v>46182.67870440972</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I22" s="5">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="J22" s="5">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>26</v>
@@ -2821,13 +2815,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2838,39 +2832,37 @@
         <v>0</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B23" s="9">
-        <v>46118.55563607639</v>
-      </c>
-      <c r="C23" s="9">
-        <v>46182.67870244213</v>
-      </c>
+        <v>46118.555640624996</v>
+      </c>
+      <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46182.67870440972</v>
+        <v>46169.85486122685</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I23" s="9">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="J23" s="9">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="K23" s="10" t="s">
         <v>26</v>
@@ -2882,54 +2874,58 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="7" t="s">
-        <v>33</v>
+        <v>86</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>46128</v>
+      </c>
+      <c r="R23" s="9">
+        <v>46107</v>
+      </c>
+      <c r="S23" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.555640624996</v>
+        <v>46118.55564542824</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.85486122685</v>
+        <v>46169.855451180556</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I24" s="5">
         <v>46107</v>
       </c>
       <c r="J24" s="5">
-        <v>46128</v>
+        <v>46108</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
@@ -2941,58 +2937,54 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>46128</v>
-      </c>
-      <c r="R24" s="5">
-        <v>46107</v>
-      </c>
-      <c r="S24" s="12" t="s">
-        <v>86</v>
+        <v>105</v>
+      </c>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46118.55564542824</v>
+        <v>46118.55564990741</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.855451180556</v>
+        <v>46169.85550466435</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I25" s="9">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="J25" s="9">
-        <v>46108</v>
+        <v>46128</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>26</v>
@@ -3004,13 +2996,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3021,37 +3013,39 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.55564990741</v>
-      </c>
-      <c r="C26" s="6"/>
+        <v>46118.555654606476</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46182.67901127315</v>
+      </c>
       <c r="D26" s="5">
-        <v>46169.85550466435</v>
+        <v>46182.67902225694</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I26" s="5">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="J26" s="5">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>26</v>
@@ -3063,56 +3057,60 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="7" t="s">
-        <v>33</v>
+        <v>86</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>46142</v>
+      </c>
+      <c r="R26" s="5">
+        <v>46107</v>
+      </c>
+      <c r="S26" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46118.555654606476</v>
+        <v>46118.55565927083</v>
       </c>
       <c r="C27" s="9">
-        <v>46182.67901127315</v>
+        <v>46134.89289440972</v>
       </c>
       <c r="D27" s="9">
-        <v>46182.67902225694</v>
+        <v>46169.85540111111</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I27" s="9">
         <v>46107</v>
       </c>
       <c r="J27" s="9">
-        <v>46142</v>
+        <v>46115</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>26</v>
@@ -3124,60 +3122,56 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>46142</v>
-      </c>
-      <c r="R27" s="9">
-        <v>46107</v>
-      </c>
-      <c r="S27" s="12" t="s">
-        <v>86</v>
+        <v>114</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T27" s="10">
-        <v>1</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U27" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.55565927083</v>
+        <v>46118.55566380787</v>
       </c>
       <c r="C28" s="5">
-        <v>46134.89289440972</v>
+        <v>46182.67899732639</v>
       </c>
       <c r="D28" s="5">
-        <v>46169.85540111111</v>
+        <v>46182.67899886574</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I28" s="5">
-        <v>46107</v>
+        <v>46118</v>
       </c>
       <c r="J28" s="5">
-        <v>46115</v>
+        <v>46142</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
@@ -3189,13 +3183,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3206,39 +3200,39 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46118.55566380787</v>
+        <v>46118.55566881945</v>
       </c>
       <c r="C29" s="9">
-        <v>46182.67899732639</v>
+        <v>46134.892935428245</v>
       </c>
       <c r="D29" s="9">
-        <v>46182.67899886574</v>
+        <v>46169.85534873843</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I29" s="9">
         <v>46118</v>
       </c>
       <c r="J29" s="9">
-        <v>46142</v>
+        <v>46126</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>26</v>
@@ -3250,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3267,39 +3261,39 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.55566881945</v>
+        <v>46118.55567340278</v>
       </c>
       <c r="C30" s="5">
-        <v>46134.892935428245</v>
+        <v>46181.67180701389</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.85534873843</v>
+        <v>46181.671818483796</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="I30" s="5">
-        <v>46118</v>
+        <v>46136</v>
       </c>
       <c r="J30" s="5">
-        <v>46126</v>
+        <v>46150</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -3311,56 +3305,60 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="7" t="s">
-        <v>33</v>
+        <v>86</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>46150</v>
+      </c>
+      <c r="R30" s="5">
+        <v>46136</v>
+      </c>
+      <c r="S30" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T30" s="6">
-        <v>0</v>
-      </c>
-      <c r="U30" s="12" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U30" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46118.55568293981</v>
+      </c>
+      <c r="C31" s="9">
+        <v>46181.671732048606</v>
+      </c>
+      <c r="D31" s="9">
+        <v>46181.671733344905</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="9">
-        <v>46118.55567340278</v>
-      </c>
-      <c r="C31" s="9">
-        <v>46181.67180701389</v>
-      </c>
-      <c r="D31" s="9">
-        <v>46181.671818483796</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="I31" s="9">
         <v>46136</v>
       </c>
       <c r="J31" s="9">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>26</v>
@@ -3372,60 +3370,56 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q31" s="9">
-        <v>46150</v>
-      </c>
-      <c r="R31" s="9">
-        <v>46136</v>
-      </c>
-      <c r="S31" s="12" t="s">
-        <v>86</v>
+        <v>128</v>
+      </c>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T31" s="10">
-        <v>1</v>
-      </c>
-      <c r="U31" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U31" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.55568293981</v>
+        <v>46118.55568802083</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.671732048606</v>
+        <v>46181.671791875</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.671733344905</v>
+        <v>46181.67179341435</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I32" s="5">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="J32" s="5">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3437,13 +3431,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3454,40 +3448,32 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B33" s="9">
-        <v>46118.55568802083</v>
-      </c>
-      <c r="C33" s="9">
-        <v>46181.671791875</v>
-      </c>
+        <v>46118.5554312037</v>
+      </c>
+      <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46181.67179341435</v>
+        <v>46135.50561945602</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="I33" s="9">
-        <v>46142</v>
-      </c>
-      <c r="J33" s="9">
-        <v>46150</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
       <c r="K33" s="10" t="s">
         <v>26</v>
       </c>
@@ -3495,52 +3481,54 @@
         <v>26</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
-      <c r="S33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="12" t="s">
-        <v>98</v>
-      </c>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.5554312037</v>
-      </c>
-      <c r="C34" s="6"/>
+        <v>46118.55573724537</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46134.856089803245</v>
+      </c>
       <c r="D34" s="5">
-        <v>46135.50561945602</v>
+        <v>46134.856103495375</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
+        <v>137</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="I34" s="5">
+        <v>46106</v>
+      </c>
+      <c r="J34" s="5">
+        <v>46112</v>
+      </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
       </c>
@@ -3548,47 +3536,57 @@
         <v>26</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
+        <v>133</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>46112</v>
+      </c>
+      <c r="R34" s="5">
+        <v>46106</v>
+      </c>
+      <c r="S34" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T34" s="6">
+        <v>1</v>
+      </c>
+      <c r="U34" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46118.58934402778</v>
+      </c>
+      <c r="C35" s="9">
+        <v>46134.85589491898</v>
+      </c>
+      <c r="D35" s="9">
+        <v>46134.85589640046</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="9">
-        <v>46118.55573724537</v>
-      </c>
-      <c r="C35" s="9">
-        <v>46134.856089803245</v>
-      </c>
-      <c r="D35" s="9">
-        <v>46134.856103495375</v>
-      </c>
-      <c r="E35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="I35" s="9">
         <v>46106</v>
@@ -3606,54 +3604,44 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q35" s="9">
-        <v>46112</v>
-      </c>
-      <c r="R35" s="9">
-        <v>46106</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T35" s="10">
-        <v>1</v>
-      </c>
-      <c r="U35" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.58934402778</v>
+        <v>46118.58935734954</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.85589491898</v>
+        <v>46134.85590363426</v>
       </c>
       <c r="D36" s="5">
-        <v>46134.85589640046</v>
+        <v>46134.855904895834</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46106</v>
@@ -3671,13 +3659,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3687,28 +3675,28 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46118.58935734954</v>
+        <v>46118.58936491898</v>
       </c>
       <c r="C37" s="9">
-        <v>46134.85590363426</v>
+        <v>46134.856064039355</v>
       </c>
       <c r="D37" s="9">
-        <v>46134.855904895834</v>
+        <v>46134.85606556713</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46106</v>
@@ -3726,13 +3714,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3745,25 +3733,25 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.58936491898</v>
+        <v>46118.58937265046</v>
       </c>
       <c r="C38" s="5">
-        <v>46134.856064039355</v>
+        <v>46134.8560703588</v>
       </c>
       <c r="D38" s="5">
-        <v>46134.85606556713</v>
+        <v>46134.85607190972</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I38" s="5">
         <v>46106</v>
@@ -3781,13 +3769,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3797,28 +3785,28 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46118.58937265046</v>
+        <v>46118.5893790625</v>
       </c>
       <c r="C39" s="9">
-        <v>46134.8560703588</v>
+        <v>46134.85607678241</v>
       </c>
       <c r="D39" s="9">
-        <v>46134.85607190972</v>
+        <v>46134.85607811343</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I39" s="9">
         <v>46106</v>
@@ -3836,13 +3824,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3852,34 +3840,34 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" s="5">
+        <v>46118.55574388889</v>
+      </c>
+      <c r="C40" s="5">
+        <v>46135.505314317124</v>
+      </c>
+      <c r="D40" s="5">
+        <v>46135.52260231481</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B40" s="5">
-        <v>46118.5893790625</v>
-      </c>
-      <c r="C40" s="5">
-        <v>46134.85607678241</v>
-      </c>
-      <c r="D40" s="5">
-        <v>46134.85607811343</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>143</v>
-      </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I40" s="5">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="J40" s="5">
-        <v>46112</v>
+        <v>46133</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -3891,44 +3879,54 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
+        <v>133</v>
+      </c>
+      <c r="Q40" s="5">
+        <v>46133</v>
+      </c>
+      <c r="R40" s="5">
+        <v>46127</v>
+      </c>
+      <c r="S40" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T40" s="6">
+        <v>1</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="9">
-        <v>46118.55574388889</v>
+        <v>46118.58948621528</v>
       </c>
       <c r="C41" s="9">
-        <v>46135.505314317124</v>
+        <v>46135.505267789355</v>
       </c>
       <c r="D41" s="9">
-        <v>46135.52260231481</v>
+        <v>46135.50526961806</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I41" s="9">
         <v>46127</v>
@@ -3946,54 +3944,44 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>152</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q41" s="9">
-        <v>46133</v>
-      </c>
-      <c r="R41" s="9">
-        <v>46127</v>
-      </c>
-      <c r="S41" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T41" s="10">
-        <v>1</v>
-      </c>
-      <c r="U41" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.58948621528</v>
+        <v>46118.589619189814</v>
       </c>
       <c r="C42" s="5">
-        <v>46135.505267789355</v>
+        <v>46135.50527871528</v>
       </c>
       <c r="D42" s="5">
-        <v>46135.50526961806</v>
+        <v>46135.50528020834</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46127</v>
@@ -4011,13 +3999,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4027,28 +4015,28 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46118.589635729164</v>
+      </c>
+      <c r="C43" s="9">
+        <v>46135.50528577546</v>
+      </c>
+      <c r="D43" s="9">
+        <v>46135.50528708333</v>
+      </c>
+      <c r="E43" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="9">
-        <v>46118.589619189814</v>
-      </c>
-      <c r="C43" s="9">
-        <v>46135.50527871528</v>
-      </c>
-      <c r="D43" s="9">
-        <v>46135.50528020834</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>143</v>
-      </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I43" s="9">
         <v>46127</v>
@@ -4066,13 +4054,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4085,25 +4073,25 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.589635729164</v>
+        <v>46118.58964931713</v>
       </c>
       <c r="C44" s="5">
-        <v>46135.50528577546</v>
+        <v>46135.50529321759</v>
       </c>
       <c r="D44" s="5">
-        <v>46135.50528708333</v>
+        <v>46135.50529516204</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I44" s="5">
         <v>46127</v>
@@ -4121,13 +4109,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4137,28 +4125,28 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="9">
-        <v>46118.58964931713</v>
+        <v>46118.5896587037</v>
       </c>
       <c r="C45" s="9">
-        <v>46135.50529321759</v>
+        <v>46135.50530085649</v>
       </c>
       <c r="D45" s="9">
-        <v>46135.50529516204</v>
+        <v>46135.50530211805</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I45" s="9">
         <v>46127</v>
@@ -4176,13 +4164,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4192,87 +4180,95 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46118.55575109954</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46135.505592835645</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46135.50560496528</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="I46" s="5">
+        <v>46134</v>
+      </c>
+      <c r="J46" s="5">
+        <v>46134</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="P46" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B46" s="5">
-        <v>46118.5896587037</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46135.50530085649</v>
-      </c>
-      <c r="D46" s="5">
-        <v>46135.50530211805</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="I46" s="5">
-        <v>46127</v>
-      </c>
-      <c r="J46" s="5">
-        <v>46133</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="Q46" s="5">
+        <v>46134</v>
+      </c>
+      <c r="R46" s="5">
+        <v>46134</v>
+      </c>
+      <c r="S46" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>161</v>
       </c>
       <c r="B47" s="9">
-        <v>46118.55575109954</v>
+        <v>46118.58972679398</v>
       </c>
       <c r="C47" s="9">
-        <v>46135.505592835645</v>
+        <v>46135.505553229166</v>
       </c>
       <c r="D47" s="9">
-        <v>46135.50560496528</v>
+        <v>46135.505555069445</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I47" s="9">
-        <v>46134</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="I47" s="10"/>
       <c r="J47" s="9">
         <v>46134</v>
       </c>
@@ -4286,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>141</v>
@@ -4294,46 +4290,36 @@
       <c r="P47" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="Q47" s="9">
-        <v>46134</v>
-      </c>
-      <c r="R47" s="9">
-        <v>46134</v>
-      </c>
-      <c r="S47" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T47" s="10">
-        <v>1</v>
-      </c>
-      <c r="U47" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.58972679398</v>
+        <v>46118.58974760417</v>
       </c>
       <c r="C48" s="5">
-        <v>46135.505553229166</v>
+        <v>46135.505559247686</v>
       </c>
       <c r="D48" s="5">
-        <v>46135.505555069445</v>
+        <v>46135.50556056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4349,13 +4335,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4365,28 +4351,28 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B49" s="9">
-        <v>46118.58974760417</v>
+        <v>46118.58975269676</v>
       </c>
       <c r="C49" s="9">
-        <v>46135.505559247686</v>
+        <v>46135.505566527776</v>
       </c>
       <c r="D49" s="9">
-        <v>46135.50556056713</v>
+        <v>46135.50556795139</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4402,13 +4388,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4418,28 +4404,28 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.58975269676</v>
+        <v>46118.58976391204</v>
       </c>
       <c r="C50" s="5">
-        <v>46135.505566527776</v>
+        <v>46135.505573229166</v>
       </c>
       <c r="D50" s="5">
-        <v>46135.50556795139</v>
+        <v>46135.50557504629</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4455,13 +4441,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4471,28 +4457,28 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B51" s="9">
-        <v>46118.58976391204</v>
+        <v>46118.589758912036</v>
       </c>
       <c r="C51" s="9">
-        <v>46135.505573229166</v>
+        <v>46135.505581006946</v>
       </c>
       <c r="D51" s="9">
-        <v>46135.50557504629</v>
+        <v>46135.50558240741</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4508,13 +4494,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4524,79 +4510,89 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" s="5">
+        <v>46118.55575893518</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="5">
+        <v>46182.20622399305</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B52" s="5">
-        <v>46118.589758912036</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46135.505581006946</v>
-      </c>
-      <c r="D52" s="5">
-        <v>46135.50558240741</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>143</v>
-      </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="I52" s="5">
+        <v>46181</v>
+      </c>
+      <c r="J52" s="5">
+        <v>46181</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O52" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="H52" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="I52" s="6"/>
-      <c r="J52" s="5">
-        <v>46134</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" s="6" t="s">
+      <c r="P52" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q52" s="5">
+        <v>46181</v>
+      </c>
+      <c r="R52" s="5">
+        <v>46181</v>
+      </c>
+      <c r="S52" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="O52" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
+      <c r="T52" s="6">
+        <v>0</v>
+      </c>
+      <c r="U52" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B53" s="9">
-        <v>46118.55575893518</v>
+        <v>46118.589869131945</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46182.20622399305</v>
+        <v>46181.168647604165</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="I53" s="9">
         <v>46181</v>
@@ -4614,52 +4610,42 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>141</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q53" s="9">
-        <v>46181</v>
-      </c>
-      <c r="R53" s="9">
-        <v>46181</v>
-      </c>
-      <c r="S53" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T53" s="10">
-        <v>0</v>
-      </c>
-      <c r="U53" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>173</v>
       </c>
       <c r="B54" s="5">
-        <v>46118.589869131945</v>
+        <v>46118.589883333334</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.168647604165</v>
+        <v>46181.16864912037</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I54" s="5">
         <v>46181</v>
@@ -4677,13 +4663,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4693,26 +4679,26 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B55" s="9">
-        <v>46118.589883333334</v>
+        <v>46118.589890312505</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46181.16864912037</v>
+        <v>46181.16865042824</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I55" s="9">
         <v>46181</v>
@@ -4730,13 +4716,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4746,26 +4732,26 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.589890312505</v>
+        <v>46118.58992050926</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46181.16865042824</v>
+        <v>46181.168653182875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I56" s="5">
         <v>46181</v>
@@ -4783,13 +4769,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4799,26 +4785,26 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B57" s="9">
-        <v>46118.58992050926</v>
+        <v>46118.589899548606</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46181.168653182875</v>
+        <v>46181.168651678236</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I57" s="9">
         <v>46181</v>
@@ -4836,13 +4822,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4852,33 +4838,29 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B58" s="5">
+        <v>46118.55576480324</v>
+      </c>
+      <c r="C58" s="5">
+        <v>46181.67196634259</v>
+      </c>
+      <c r="D58" s="5">
+        <v>46181.67205032408</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B58" s="5">
-        <v>46118.589899548606</v>
-      </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="5">
-        <v>46181.168651678236</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>143</v>
-      </c>
       <c r="F58" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="I58" s="5">
-        <v>46181</v>
-      </c>
-      <c r="J58" s="5">
-        <v>46181</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
       <c r="K58" s="6" t="s">
         <v>26</v>
       </c>
@@ -4886,16 +4868,16 @@
         <v>26</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4905,29 +4887,35 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B59" s="9">
-        <v>46118.55576480324</v>
+        <v>46118.55576952547</v>
       </c>
       <c r="C59" s="9">
-        <v>46181.67196634259</v>
+        <v>46181.67190112268</v>
       </c>
       <c r="D59" s="9">
-        <v>46181.67205032408</v>
+        <v>46181.67191517361</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
+        <v>182</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I59" s="9">
+        <v>46153</v>
+      </c>
+      <c r="J59" s="9">
+        <v>46154</v>
+      </c>
       <c r="K59" s="10" t="s">
         <v>26</v>
       </c>
@@ -4935,53 +4923,63 @@
         <v>26</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="10"/>
-      <c r="S59" s="10"/>
-      <c r="T59" s="10"/>
-      <c r="U59" s="10"/>
+        <v>184</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>46154</v>
+      </c>
+      <c r="R59" s="9">
+        <v>46153</v>
+      </c>
+      <c r="S59" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T59" s="10">
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.55576952547</v>
+        <v>46118.55577607639</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.67190112268</v>
+        <v>46181.671950752316</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.67191517361</v>
+        <v>46181.671966932874</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I60" s="5">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="J60" s="5">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
@@ -4993,22 +4991,22 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="Q60" s="5">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="R60" s="5">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5019,35 +5017,27 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B61" s="9">
-        <v>46118.55577607639</v>
-      </c>
-      <c r="C61" s="9">
-        <v>46181.671950752316</v>
-      </c>
+        <v>46118.55578122685</v>
+      </c>
+      <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46181.671966932874</v>
+        <v>46191.710350381945</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="I61" s="9">
-        <v>46155</v>
-      </c>
-      <c r="J61" s="9">
-        <v>46156</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
       <c r="K61" s="10" t="s">
         <v>26</v>
       </c>
@@ -5055,56 +5045,56 @@
         <v>26</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>180</v>
+        <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q61" s="9">
-        <v>46156</v>
-      </c>
-      <c r="R61" s="9">
-        <v>46155</v>
-      </c>
-      <c r="S61" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T61" s="10">
-        <v>1</v>
-      </c>
-      <c r="U61" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.55578122685</v>
-      </c>
-      <c r="C62" s="6"/>
+        <v>46118.55578460648</v>
+      </c>
+      <c r="C62" s="5">
+        <v>46181.672212314814</v>
+      </c>
       <c r="D62" s="5">
-        <v>46181.67222487269</v>
+        <v>46181.67222788194</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
+        <v>194</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I62" s="5">
+        <v>46155</v>
+      </c>
+      <c r="J62" s="5">
+        <v>46157</v>
+      </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
       </c>
@@ -5112,53 +5102,63 @@
         <v>26</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+        <v>196</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>46157</v>
+      </c>
+      <c r="R62" s="5">
+        <v>46155</v>
+      </c>
+      <c r="S62" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T62" s="6">
+        <v>1</v>
+      </c>
+      <c r="U62" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B63" s="9">
+        <v>46118.555790115744</v>
+      </c>
+      <c r="C63" s="9">
+        <v>46191.71033274305</v>
+      </c>
+      <c r="D63" s="9">
+        <v>46191.71034409722</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B63" s="9">
-        <v>46118.55578460648</v>
-      </c>
-      <c r="C63" s="9">
-        <v>46181.672212314814</v>
-      </c>
-      <c r="D63" s="9">
-        <v>46181.67222788194</v>
-      </c>
-      <c r="E63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>197</v>
-      </c>
       <c r="I63" s="9">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="J63" s="9">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="K63" s="10" t="s">
         <v>26</v>
@@ -5170,22 +5170,22 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="Q63" s="9">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="R63" s="9">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="S63" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="T63" s="10">
         <v>1</v>
@@ -5199,23 +5199,25 @@
         <v>199</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.555790115744</v>
-      </c>
-      <c r="C64" s="6"/>
+        <v>46118.59005789352</v>
+      </c>
+      <c r="C64" s="5">
+        <v>46181.6723374537</v>
+      </c>
       <c r="D64" s="5">
-        <v>46181.67269046296</v>
+        <v>46181.672338564815</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I64" s="5">
         <v>46160</v>
@@ -5233,54 +5235,44 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46164</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46160</v>
-      </c>
-      <c r="S64" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T64" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B65" s="9">
-        <v>46118.59005789352</v>
+        <v>46118.590067604164</v>
       </c>
       <c r="C65" s="9">
-        <v>46181.6723374537</v>
+        <v>46181.672350925925</v>
       </c>
       <c r="D65" s="9">
-        <v>46181.672338564815</v>
+        <v>46181.672352442125</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I65" s="9">
         <v>46160</v>
@@ -5298,13 +5290,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5317,25 +5309,25 @@
         <v>204</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.590067604164</v>
+        <v>46118.5900759838</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.672350925925</v>
+        <v>46181.67236503473</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.672352442125</v>
+        <v>46181.672366307874</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I66" s="5">
         <v>46160</v>
@@ -5353,13 +5345,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5369,28 +5361,28 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B67" s="9">
-        <v>46118.5900759838</v>
+        <v>46118.590097962966</v>
       </c>
       <c r="C67" s="9">
-        <v>46181.67236503473</v>
+        <v>46191.71030983796</v>
       </c>
       <c r="D67" s="9">
-        <v>46181.672366307874</v>
+        <v>46191.71031108796</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I67" s="9">
         <v>46160</v>
@@ -5408,13 +5400,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5424,26 +5416,28 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.590097962966</v>
-      </c>
-      <c r="C68" s="6"/>
+        <v>46118.59010253473</v>
+      </c>
+      <c r="C68" s="5">
+        <v>46191.71031711806</v>
+      </c>
       <c r="D68" s="5">
-        <v>46181.67222335648</v>
+        <v>46191.710318530095</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I68" s="5">
         <v>46160</v>
@@ -5461,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5477,32 +5471,34 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B69" s="9">
+        <v>46118.55579684028</v>
+      </c>
+      <c r="C69" s="9">
+        <v>46191.70935185185</v>
+      </c>
+      <c r="D69" s="9">
+        <v>46191.709365358794</v>
+      </c>
+      <c r="E69" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B69" s="9">
-        <v>46118.59010253473</v>
-      </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="9">
-        <v>46181.67222453703</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>143</v>
-      </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I69" s="9">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="J69" s="9">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="K69" s="10" t="s">
         <v>26</v>
@@ -5514,42 +5510,54 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>205</v>
+        <v>139</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="10"/>
-      <c r="T69" s="10"/>
-      <c r="U69" s="10"/>
+        <v>190</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>46167</v>
+      </c>
+      <c r="R69" s="9">
+        <v>46167</v>
+      </c>
+      <c r="S69" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T69" s="10">
+        <v>1</v>
+      </c>
+      <c r="U69" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>209</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.55579684028</v>
-      </c>
-      <c r="C70" s="6"/>
+        <v>46118.59015388889</v>
+      </c>
+      <c r="C70" s="5">
+        <v>46181.67244342592</v>
+      </c>
       <c r="D70" s="5">
-        <v>46181.67273439815</v>
+        <v>46181.67244473379</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I70" s="5">
         <v>46167</v>
@@ -5567,54 +5575,44 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q70" s="5">
-        <v>46167</v>
-      </c>
-      <c r="R70" s="5">
-        <v>46167</v>
-      </c>
-      <c r="S70" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T70" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="U70" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="Q70" s="6"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="6"/>
+      <c r="T70" s="6"/>
+      <c r="U70" s="6"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B71" s="9">
-        <v>46118.59015388889</v>
+        <v>46118.59016236111</v>
       </c>
       <c r="C71" s="9">
-        <v>46181.67244342592</v>
+        <v>46181.672456597225</v>
       </c>
       <c r="D71" s="9">
-        <v>46181.67244473379</v>
+        <v>46181.672458078705</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I71" s="9">
         <v>46167</v>
@@ -5632,13 +5630,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="O71" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="O71" s="10" t="s">
-        <v>212</v>
-      </c>
       <c r="P71" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5648,28 +5646,28 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.59016236111</v>
+        <v>46118.59017135417</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.672456597225</v>
+        <v>46181.67246365741</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.672458078705</v>
+        <v>46181.672464999996</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I72" s="5">
         <v>46167</v>
@@ -5687,13 +5685,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="O72" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="O72" s="6" t="s">
-        <v>212</v>
-      </c>
       <c r="P72" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5703,28 +5701,28 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B73" s="9">
-        <v>46118.59017135417</v>
+        <v>46118.59019241898</v>
       </c>
       <c r="C73" s="9">
-        <v>46181.67246365741</v>
+        <v>46191.70928226852</v>
       </c>
       <c r="D73" s="9">
-        <v>46181.672464999996</v>
+        <v>46191.7103152662</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I73" s="9">
         <v>46167</v>
@@ -5742,13 +5740,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="O73" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="O73" s="10" t="s">
-        <v>212</v>
-      </c>
       <c r="P73" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5758,26 +5756,28 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.59019241898</v>
-      </c>
-      <c r="C74" s="6"/>
+        <v>46118.590197488425</v>
+      </c>
+      <c r="C74" s="5">
+        <v>46191.70933641204</v>
+      </c>
       <c r="D74" s="5">
-        <v>46167.16804956019</v>
+        <v>46191.7103265162</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I74" s="5">
         <v>46167</v>
@@ -5795,13 +5795,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="O74" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="O74" s="6" t="s">
-        <v>212</v>
-      </c>
       <c r="P74" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5811,33 +5811,27 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B75" s="9">
-        <v>46118.590197488425</v>
+        <v>46118.55580327546</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46167.16805100694</v>
+        <v>46118.58538233796</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I75" s="9">
-        <v>46167</v>
-      </c>
-      <c r="J75" s="9">
-        <v>46167</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H75" s="10"/>
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
       <c r="K75" s="10" t="s">
         <v>26</v>
       </c>
@@ -5845,16 +5839,16 @@
         <v>26</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>210</v>
+        <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5867,24 +5861,28 @@
         <v>218</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.55580327546</v>
+        <v>46118.55580685185</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.58538233796</v>
+        <v>46182.67872560185</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
+        <v>182</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>183</v>
+      </c>
       <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
+      <c r="J76" s="5">
+        <v>46113</v>
+      </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
       </c>
@@ -5892,49 +5890,59 @@
         <v>26</v>
       </c>
       <c r="M76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>46113</v>
+      </c>
+      <c r="R76" s="5">
+        <v>46113</v>
+      </c>
+      <c r="S76" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T76" s="6">
         <v>0</v>
       </c>
-      <c r="N76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
+      <c r="U76" s="11" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B77" s="9">
-        <v>46118.55580685185</v>
+        <v>46118.55581320602</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46182.67872560185</v>
+        <v>46130.19341753473</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>26</v>
@@ -5946,28 +5954,28 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q77" s="9">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="R77" s="9">
-        <v>46113</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>33</v>
+        <v>46129</v>
+      </c>
+      <c r="S77" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="11" t="s">
-        <v>65</v>
+      <c r="U77" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -5975,11 +5983,11 @@
         <v>223</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.55581320602</v>
+        <v>46118.55581936342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46130.19341753473</v>
+        <v>46182.67901537037</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>224</v>
@@ -5988,14 +5996,14 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
-        <v>46129</v>
+        <v>46146</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -6007,28 +6015,28 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q78" s="5">
-        <v>46129</v>
+        <v>46146</v>
       </c>
       <c r="R78" s="5">
-        <v>46129</v>
+        <v>46146</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>98</v>
+      <c r="U78" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6036,28 +6044,24 @@
         <v>225</v>
       </c>
       <c r="B79" s="9">
-        <v>46118.55581936342</v>
+        <v>46118.55582516204</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.67901537037</v>
+        <v>46118.63827943287</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>226</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>185</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="10"/>
       <c r="I79" s="10"/>
-      <c r="J79" s="9">
-        <v>46146</v>
-      </c>
+      <c r="J79" s="10"/>
       <c r="K79" s="10" t="s">
         <v>26</v>
       </c>
@@ -6065,56 +6069,52 @@
         <v>26</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>180</v>
+        <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>118</v>
+        <v>227</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q79" s="9">
-        <v>46146</v>
-      </c>
-      <c r="R79" s="9">
-        <v>46146</v>
-      </c>
-      <c r="S79" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T79" s="10">
-        <v>0</v>
-      </c>
-      <c r="U79" s="11" t="s">
-        <v>65</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="10"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B80" s="5">
-        <v>46118.55582516204</v>
+        <v>46118.55582877315</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46118.63827943287</v>
+        <v>46175.185741284724</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I80" s="5">
+        <v>46168</v>
+      </c>
+      <c r="J80" s="5">
+        <v>46174</v>
+      </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
       </c>
@@ -6122,45 +6122,55 @@
         <v>26</v>
       </c>
       <c r="M80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>46174</v>
+      </c>
+      <c r="R80" s="5">
+        <v>46168</v>
+      </c>
+      <c r="S80" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="N80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
+      <c r="U80" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>230</v>
       </c>
       <c r="B81" s="9">
-        <v>46118.55582877315</v>
+        <v>46118.590250625</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46175.185741284724</v>
+        <v>46181.67244934027</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I81" s="9">
         <v>46168</v>
@@ -6178,52 +6188,42 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>141</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q81" s="9">
-        <v>46174</v>
-      </c>
-      <c r="R81" s="9">
-        <v>46168</v>
-      </c>
-      <c r="S81" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T81" s="10">
-        <v>0</v>
-      </c>
-      <c r="U81" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>232</v>
       </c>
       <c r="B82" s="5">
-        <v>46118.590250625</v>
+        <v>46118.590259641205</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46181.67244934027</v>
+        <v>46181.67246390047</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I82" s="5">
         <v>46168</v>
@@ -6241,13 +6241,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6257,26 +6257,26 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B83" s="9">
-        <v>46118.590259641205</v>
+        <v>46118.59026761574</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46181.67246390047</v>
+        <v>46181.67246981482</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I83" s="9">
         <v>46168</v>
@@ -6294,13 +6294,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="O83" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6310,26 +6310,26 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B84" s="5">
-        <v>46118.59026761574</v>
+        <v>46118.590275636576</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46181.67246981482</v>
+        <v>46191.70929190972</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I84" s="5">
         <v>46168</v>
@@ -6347,13 +6347,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6363,26 +6363,26 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B85" s="9">
-        <v>46118.590275636576</v>
+        <v>46118.59028430555</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46174.169199641205</v>
+        <v>46191.70934756944</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I85" s="9">
         <v>46168</v>
@@ -6400,13 +6400,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6416,32 +6416,32 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B86" s="5">
-        <v>46118.59028430555</v>
+        <v>46118.55583459491</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46174.16920103009</v>
+        <v>46176.1814233912</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I86" s="5">
-        <v>46168</v>
+        <v>46175</v>
       </c>
       <c r="J86" s="5">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6453,46 +6453,54 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="6"/>
-      <c r="S86" s="6"/>
-      <c r="T86" s="6"/>
-      <c r="U86" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="Q86" s="5">
+        <v>46175</v>
+      </c>
+      <c r="R86" s="5">
+        <v>46175</v>
+      </c>
+      <c r="S86" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T86" s="6">
+        <v>0</v>
+      </c>
+      <c r="U86" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>238</v>
       </c>
       <c r="B87" s="9">
-        <v>46118.55583459491</v>
+        <v>46118.59033478009</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46176.1814233912</v>
+        <v>46175.16810725695</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>239</v>
+        <v>141</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I87" s="9">
-        <v>46175</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I87" s="10"/>
       <c r="J87" s="9">
         <v>46175</v>
       </c>
@@ -6506,52 +6514,42 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>141</v>
+        <v>239</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q87" s="9">
-        <v>46175</v>
-      </c>
-      <c r="R87" s="9">
-        <v>46175</v>
-      </c>
-      <c r="S87" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T87" s="10">
-        <v>0</v>
-      </c>
-      <c r="U87" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="10"/>
+      <c r="U87" s="10"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B88" s="5">
-        <v>46118.59033478009</v>
+        <v>46118.59034447916</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46175.16810725695</v>
+        <v>46175.1681088426</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6567,13 +6565,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O88" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="O88" s="6" t="s">
-        <v>241</v>
-      </c>
       <c r="P88" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6583,26 +6581,26 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B89" s="9">
-        <v>46118.59034447916</v>
+        <v>46118.590352141204</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46175.1681088426</v>
+        <v>46175.16811023148</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6618,13 +6616,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="O89" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="O89" s="10" t="s">
-        <v>241</v>
-      </c>
       <c r="P89" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6634,26 +6632,26 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B90" s="5">
-        <v>46118.590352141204</v>
+        <v>46118.59035967593</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46175.16811023148</v>
+        <v>46175.168111493054</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6669,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="O90" s="6" t="s">
-        <v>241</v>
-      </c>
       <c r="P90" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6685,26 +6683,26 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B91" s="9">
-        <v>46118.59035967593</v>
+        <v>46118.59036834491</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46175.168111493054</v>
+        <v>46175.168112893516</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6720,13 +6718,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="O91" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="O91" s="10" t="s">
-        <v>241</v>
-      </c>
       <c r="P91" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6736,30 +6734,30 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B92" s="5">
-        <v>46118.59036834491</v>
+        <v>46118.55584244213</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46175.168112893516</v>
+        <v>46177.19457946759</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>143</v>
+        <v>246</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -6771,42 +6769,52 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6"/>
-      <c r="S92" s="6"/>
-      <c r="T92" s="6"/>
-      <c r="U92" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>46176</v>
+      </c>
+      <c r="R92" s="5">
+        <v>46176</v>
+      </c>
+      <c r="S92" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T92" s="6">
+        <v>0</v>
+      </c>
+      <c r="U92" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
         <v>247</v>
       </c>
       <c r="B93" s="9">
-        <v>46118.55584244213</v>
+        <v>46118.59042068287</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46177.19457946759</v>
+        <v>46176.16819081019</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>248</v>
+        <v>141</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6822,52 +6830,42 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q93" s="9">
-        <v>46176</v>
-      </c>
-      <c r="R93" s="9">
-        <v>46176</v>
-      </c>
-      <c r="S93" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T93" s="10">
-        <v>0</v>
-      </c>
-      <c r="U93" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B94" s="5">
-        <v>46118.59042068287</v>
+        <v>46118.5904280324</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46176.16819081019</v>
+        <v>46176.168192418976</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6883,13 +6881,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="O94" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="O94" s="6" t="s">
-        <v>250</v>
-      </c>
       <c r="P94" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6899,26 +6897,26 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B95" s="9">
-        <v>46118.5904280324</v>
+        <v>46118.59044465278</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46176.168192418976</v>
+        <v>46176.16819494213</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -6934,13 +6932,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="O95" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="O95" s="10" t="s">
-        <v>250</v>
-      </c>
       <c r="P95" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6950,26 +6948,26 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B96" s="5">
-        <v>46118.59044465278</v>
+        <v>46118.5904391088</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46176.16819494213</v>
+        <v>46176.16819359954</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -6985,13 +6983,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="O96" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="O96" s="6" t="s">
-        <v>250</v>
-      </c>
       <c r="P96" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7001,26 +6999,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B97" s="9">
-        <v>46118.5904391088</v>
+        <v>46118.59045233796</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46176.16819359954</v>
+        <v>46176.16819640047</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7036,13 +7034,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="O97" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="O97" s="10" t="s">
-        <v>250</v>
-      </c>
       <c r="P97" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7052,30 +7050,30 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B98" s="5">
-        <v>46118.59045233796</v>
+        <v>46118.55584987269</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46176.16819640047</v>
+        <v>46178.17851013889</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>143</v>
+        <v>255</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -7087,42 +7085,52 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>250</v>
+        <v>139</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6"/>
-      <c r="S98" s="6"/>
-      <c r="T98" s="6"/>
-      <c r="U98" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="Q98" s="5">
+        <v>46177</v>
+      </c>
+      <c r="R98" s="5">
+        <v>46177</v>
+      </c>
+      <c r="S98" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T98" s="6">
+        <v>0</v>
+      </c>
+      <c r="U98" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>256</v>
       </c>
       <c r="B99" s="9">
-        <v>46118.55584987269</v>
+        <v>46118.590539282406</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46178.17851013889</v>
+        <v>46177.168168738426</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7138,52 +7146,42 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>141</v>
+        <v>257</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q99" s="9">
-        <v>46177</v>
-      </c>
-      <c r="R99" s="9">
-        <v>46177</v>
-      </c>
-      <c r="S99" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T99" s="10">
-        <v>0</v>
-      </c>
-      <c r="U99" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
+      <c r="U99" s="10"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B100" s="5">
-        <v>46118.590539282406</v>
+        <v>46118.590546666666</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46177.168168738426</v>
+        <v>46177.168170543984</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7199,13 +7197,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7218,23 +7216,23 @@
         <v>261</v>
       </c>
       <c r="B101" s="9">
-        <v>46118.590546666666</v>
+        <v>46118.590554027774</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46177.168170543984</v>
+        <v>46177.16817181713</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7250,13 +7248,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>262</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7269,23 +7267,23 @@
         <v>263</v>
       </c>
       <c r="B102" s="5">
-        <v>46118.590554027774</v>
+        <v>46118.59056115741</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46177.16817181713</v>
+        <v>46177.16817290509</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7301,13 +7299,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7317,26 +7315,26 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B103" s="9">
-        <v>46118.59056115741</v>
+        <v>46118.590569293985</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46177.16817290509</v>
+        <v>46177.16817414352</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7352,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>262</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7368,30 +7366,32 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B104" s="5">
-        <v>46118.590569293985</v>
+        <v>46118.5558574537</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46177.16817414352</v>
+        <v>46179.20438387731</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>143</v>
+        <v>266</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I104" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="I104" s="5">
+        <v>46178</v>
+      </c>
       <c r="J104" s="5">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7403,46 +7403,54 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>264</v>
+        <v>139</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6"/>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6"/>
+        <v>226</v>
+      </c>
+      <c r="Q104" s="5">
+        <v>46178</v>
+      </c>
+      <c r="R104" s="5">
+        <v>46178</v>
+      </c>
+      <c r="S104" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T104" s="6">
+        <v>0</v>
+      </c>
+      <c r="U104" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
         <v>267</v>
       </c>
       <c r="B105" s="9">
-        <v>46118.5558574537</v>
+        <v>46118.5906265625</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46179.20438387731</v>
+        <v>46178.16912293981</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I105" s="9">
-        <v>46178</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I105" s="10"/>
       <c r="J105" s="9">
         <v>46178</v>
       </c>
@@ -7456,52 +7464,42 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>141</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q105" s="9">
-        <v>46178</v>
-      </c>
-      <c r="R105" s="9">
-        <v>46178</v>
-      </c>
-      <c r="S105" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T105" s="10">
-        <v>0</v>
-      </c>
-      <c r="U105" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="10"/>
+      <c r="U105" s="10"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>269</v>
       </c>
       <c r="B106" s="5">
-        <v>46118.5906265625</v>
+        <v>46118.59063387732</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46178.16912293981</v>
+        <v>46178.169124884254</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7517,13 +7515,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="O106" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="P106" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7533,26 +7531,26 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B107" s="9">
-        <v>46118.59063387732</v>
+        <v>46118.590655486114</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46178.169124884254</v>
+        <v>46178.16913978009</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7568,13 +7566,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="O107" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="P107" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="O107" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="P107" s="10" t="s">
-        <v>270</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7584,26 +7582,26 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B108" s="5">
-        <v>46118.590655486114</v>
+        <v>46118.59066162037</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46178.16913978009</v>
+        <v>46178.16914135417</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7619,13 +7617,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7635,26 +7633,26 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B109" s="9">
-        <v>46118.59066162037</v>
+        <v>46118.59066710648</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46178.16914135417</v>
+        <v>46178.16914265046</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I109" s="10"/>
       <c r="J109" s="9">
@@ -7670,13 +7668,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="O109" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="P109" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="O109" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="P109" s="10" t="s">
-        <v>270</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7686,30 +7684,30 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B110" s="5">
-        <v>46118.59066710648</v>
+        <v>46118.55591270833</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46178.16914265046</v>
+        <v>46183.194774386575</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>26</v>
@@ -7721,44 +7719,56 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-      <c r="U110" s="6"/>
+        <v>275</v>
+      </c>
+      <c r="Q110" s="5">
+        <v>46182</v>
+      </c>
+      <c r="R110" s="5">
+        <v>46182</v>
+      </c>
+      <c r="S110" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T110" s="6">
+        <v>0</v>
+      </c>
+      <c r="U110" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B111" s="9">
-        <v>46118.55591270833</v>
+        <v>46118.590705243056</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46183.194774386575</v>
+        <v>46182.168110810184</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>276</v>
+        <v>141</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I111" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="I111" s="9">
+        <v>46182</v>
+      </c>
       <c r="J111" s="9">
         <v>46182</v>
       </c>
@@ -7772,7 +7782,7 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>141</v>
@@ -7780,44 +7790,34 @@
       <c r="P111" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="Q111" s="9">
-        <v>46182</v>
-      </c>
-      <c r="R111" s="9">
-        <v>46182</v>
-      </c>
-      <c r="S111" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T111" s="10">
-        <v>0</v>
-      </c>
-      <c r="U111" s="12" t="s">
-        <v>98</v>
-      </c>
+      <c r="Q111" s="10"/>
+      <c r="R111" s="10"/>
+      <c r="S111" s="10"/>
+      <c r="T111" s="10"/>
+      <c r="U111" s="10"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>278</v>
       </c>
       <c r="B112" s="5">
-        <v>46118.590705243056</v>
+        <v>46118.59071275463</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.168110810184</v>
+        <v>46182.1681121875</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I112" s="5">
         <v>46182</v>
@@ -7835,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7851,26 +7851,26 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B113" s="9">
-        <v>46118.59071275463</v>
+        <v>46118.590720092594</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46182.1681121875</v>
+        <v>46182.16811331018</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I113" s="9">
         <v>46182</v>
@@ -7888,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7904,26 +7904,26 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B114" s="5">
-        <v>46118.590720092594</v>
+        <v>46118.590727835646</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.16811331018</v>
+        <v>46182.16811451389</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I114" s="5">
         <v>46182</v>
@@ -7941,13 +7941,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7957,26 +7957,26 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B115" s="9">
-        <v>46118.590727835646</v>
+        <v>46118.59073534722</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46182.16811451389</v>
+        <v>46182.16811570602</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I115" s="9">
         <v>46182</v>
@@ -7994,13 +7994,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8010,33 +8010,27 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B116" s="5">
-        <v>46118.59073534722</v>
+        <v>46118.55591954861</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46182.16811570602</v>
+        <v>46118.63950689815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>143</v>
+        <v>283</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I116" s="5">
-        <v>46182</v>
-      </c>
-      <c r="J116" s="5">
-        <v>46182</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
       <c r="K116" s="6" t="s">
         <v>26</v>
       </c>
@@ -8044,16 +8038,16 @@
         <v>26</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>276</v>
+        <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>143</v>
+        <v>284</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>279</v>
+        <v>26</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8063,27 +8057,31 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B117" s="9">
-        <v>46118.55591954861</v>
+        <v>46118.555923148146</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46118.63950689815</v>
+        <v>46184.18063726852</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="10"/>
+        <v>287</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>288</v>
+      </c>
       <c r="I117" s="10"/>
-      <c r="J117" s="10"/>
+      <c r="J117" s="9">
+        <v>46183</v>
+      </c>
       <c r="K117" s="10" t="s">
         <v>26</v>
       </c>
@@ -8091,45 +8089,55 @@
         <v>26</v>
       </c>
       <c r="M117" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N117" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="O117" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="P117" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q117" s="9">
+        <v>46183</v>
+      </c>
+      <c r="R117" s="9">
+        <v>46183</v>
+      </c>
+      <c r="S117" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T117" s="10">
         <v>0</v>
       </c>
-      <c r="N117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O117" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="P117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q117" s="10"/>
-      <c r="R117" s="10"/>
-      <c r="S117" s="10"/>
-      <c r="T117" s="10"/>
-      <c r="U117" s="10"/>
+      <c r="U117" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B118" s="5">
-        <v>46118.555923148146</v>
+        <v>46118.590793020834</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46184.18063726852</v>
+        <v>46183.16824416666</v>
       </c>
       <c r="E118" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>288</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8145,52 +8153,42 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>276</v>
+        <v>141</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q118" s="5">
-        <v>46183</v>
-      </c>
-      <c r="R118" s="5">
-        <v>46183</v>
-      </c>
-      <c r="S118" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T118" s="6">
-        <v>0</v>
-      </c>
-      <c r="U118" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Q118" s="6"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="6"/>
+      <c r="T118" s="6"/>
+      <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B119" s="9">
-        <v>46118.590793020834</v>
+        <v>46118.59080049768</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46183.16824416666</v>
+        <v>46183.16824571759</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8206,13 +8204,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8222,26 +8220,26 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B120" s="5">
-        <v>46118.59080049768</v>
+        <v>46118.59080680556</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46183.16824571759</v>
+        <v>46183.168246875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8257,13 +8255,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8273,26 +8271,26 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B121" s="9">
-        <v>46118.59080680556</v>
+        <v>46118.59081555555</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46183.168246875</v>
+        <v>46183.16824814815</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I121" s="10"/>
       <c r="J121" s="9">
@@ -8308,13 +8306,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8324,26 +8322,26 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B122" s="5">
-        <v>46118.59081555555</v>
+        <v>46118.590822777776</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46183.16824814815</v>
+        <v>46183.16824943287</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8359,13 +8357,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8375,30 +8373,30 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B123" s="9">
-        <v>46118.590822777776</v>
+        <v>46118.55592798611</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46183.16824943287</v>
+        <v>46185.17432103009</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>143</v>
+        <v>295</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>289</v>
+        <v>73</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>290</v>
+        <v>73</v>
       </c>
       <c r="I123" s="10"/>
       <c r="J123" s="9">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="K123" s="10" t="s">
         <v>26</v>
@@ -8410,42 +8408,52 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>143</v>
+        <v>296</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q123" s="10"/>
-      <c r="R123" s="10"/>
-      <c r="S123" s="10"/>
-      <c r="T123" s="10"/>
-      <c r="U123" s="10"/>
+        <v>283</v>
+      </c>
+      <c r="Q123" s="9">
+        <v>46184</v>
+      </c>
+      <c r="R123" s="9">
+        <v>46184</v>
+      </c>
+      <c r="S123" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T123" s="10">
+        <v>0</v>
+      </c>
+      <c r="U123" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B124" s="5">
-        <v>46118.55592798611</v>
+        <v>46118.59087519676</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46185.17432103009</v>
+        <v>46184.168032511574</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>297</v>
+        <v>141</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -8461,52 +8469,42 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="O124" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="P124" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="P124" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q124" s="5">
-        <v>46184</v>
-      </c>
-      <c r="R124" s="5">
-        <v>46184</v>
-      </c>
-      <c r="S124" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T124" s="6">
-        <v>0</v>
-      </c>
-      <c r="U124" s="12" t="s">
-        <v>98</v>
-      </c>
+      <c r="Q124" s="6"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="6"/>
+      <c r="T124" s="6"/>
+      <c r="U124" s="6"/>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
         <v>299</v>
       </c>
       <c r="B125" s="9">
-        <v>46118.59087519676</v>
+        <v>46118.590883240744</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46184.168032511574</v>
+        <v>46184.168034201386</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I125" s="10"/>
       <c r="J125" s="9">
@@ -8522,13 +8520,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8538,26 +8536,26 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B126" s="5">
-        <v>46118.590883240744</v>
+        <v>46118.59089157407</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46184.168034201386</v>
+        <v>46184.16803541667</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8573,13 +8571,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8589,26 +8587,26 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B127" s="9">
-        <v>46118.59089157407</v>
+        <v>46118.590897835646</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46184.16803541667</v>
+        <v>46184.168036863426</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8624,13 +8622,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8640,26 +8638,26 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B128" s="5">
-        <v>46118.590897835646</v>
+        <v>46118.5909049537</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46184.168036863426</v>
+        <v>46184.16803811342</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8675,13 +8673,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8691,30 +8689,30 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B129" s="9">
-        <v>46118.5909049537</v>
+        <v>46118.555932511576</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46184.16803811342</v>
+        <v>46186.16794060185</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>158</v>
+        <v>304</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="K129" s="10" t="s">
         <v>26</v>
@@ -8726,42 +8724,52 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q129" s="10"/>
-      <c r="R129" s="10"/>
-      <c r="S129" s="10"/>
-      <c r="T129" s="10"/>
-      <c r="U129" s="10"/>
+        <v>283</v>
+      </c>
+      <c r="Q129" s="9">
+        <v>46185</v>
+      </c>
+      <c r="R129" s="9">
+        <v>46185</v>
+      </c>
+      <c r="S129" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T129" s="10">
+        <v>0</v>
+      </c>
+      <c r="U129" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>305</v>
       </c>
       <c r="B130" s="5">
-        <v>46118.555932511576</v>
+        <v>46118.59095414352</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46186.16794060185</v>
+        <v>46185.168594965275</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>306</v>
+        <v>141</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -8777,52 +8785,42 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>141</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q130" s="5">
-        <v>46185</v>
-      </c>
-      <c r="R130" s="5">
-        <v>46185</v>
-      </c>
-      <c r="S130" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T130" s="6">
-        <v>0</v>
-      </c>
-      <c r="U130" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="Q130" s="6"/>
+      <c r="R130" s="6"/>
+      <c r="S130" s="6"/>
+      <c r="T130" s="6"/>
+      <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
         <v>307</v>
       </c>
       <c r="B131" s="9">
-        <v>46118.59095414352</v>
+        <v>46118.590966759264</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46185.168594965275</v>
+        <v>46185.16859673611</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -8838,13 +8836,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="O131" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="P131" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="O131" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="P131" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -8854,26 +8852,26 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B132" s="5">
-        <v>46118.590966759264</v>
+        <v>46118.590973796294</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46185.16859673611</v>
+        <v>46185.168597951386</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -8889,13 +8887,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="O132" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="O132" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>308</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -8905,26 +8903,26 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B133" s="9">
-        <v>46118.590973796294</v>
+        <v>46118.590979953704</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46185.168597951386</v>
+        <v>46185.16859903935</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -8940,13 +8938,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="O133" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="P133" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="O133" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="P133" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -8956,26 +8954,26 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B134" s="5">
-        <v>46118.590979953704</v>
+        <v>46118.59098489583</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46185.16859903935</v>
+        <v>46185.16860023148</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -8991,13 +8989,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="O134" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="P134" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="O134" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="P134" s="6" t="s">
-        <v>308</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9007,30 +9005,30 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B135" s="9">
-        <v>46118.59098489583</v>
+        <v>46118.55593715278</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46185.16860023148</v>
+        <v>46189.2078791088</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>143</v>
+        <v>312</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I135" s="10"/>
       <c r="J135" s="9">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="K135" s="10" t="s">
         <v>26</v>
@@ -9042,42 +9040,52 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q135" s="10"/>
-      <c r="R135" s="10"/>
-      <c r="S135" s="10"/>
-      <c r="T135" s="10"/>
-      <c r="U135" s="10"/>
+        <v>313</v>
+      </c>
+      <c r="Q135" s="9">
+        <v>46188</v>
+      </c>
+      <c r="R135" s="9">
+        <v>46188</v>
+      </c>
+      <c r="S135" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T135" s="10">
+        <v>0</v>
+      </c>
+      <c r="U135" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B136" s="5">
-        <v>46118.55593715278</v>
+        <v>46118.59103105324</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46189.2078791088</v>
+        <v>46188.168568113426</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>314</v>
+        <v>141</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9093,52 +9101,42 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>141</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q136" s="5">
-        <v>46188</v>
-      </c>
-      <c r="R136" s="5">
-        <v>46188</v>
-      </c>
-      <c r="S136" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T136" s="6">
-        <v>0</v>
-      </c>
-      <c r="U136" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="Q136" s="6"/>
+      <c r="R136" s="6"/>
+      <c r="S136" s="6"/>
+      <c r="T136" s="6"/>
+      <c r="U136" s="6"/>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B137" s="9">
-        <v>46118.59103105324</v>
+        <v>46118.591039039355</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46188.168568113426</v>
+        <v>46188.16856979167</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I137" s="10"/>
       <c r="J137" s="9">
@@ -9154,13 +9152,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9170,26 +9168,26 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B138" s="5">
-        <v>46118.591039039355</v>
+        <v>46118.59104641204</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46188.16856979167</v>
+        <v>46188.168570995374</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9205,13 +9203,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9221,26 +9219,26 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B139" s="9">
-        <v>46118.59104641204</v>
+        <v>46118.59105258102</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46188.168570995374</v>
+        <v>46188.1685722338</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I139" s="10"/>
       <c r="J139" s="9">
@@ -9256,13 +9254,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9272,26 +9270,26 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B140" s="5">
-        <v>46118.59105258102</v>
+        <v>46118.59105829861</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46188.1685722338</v>
+        <v>46188.16857356481</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9307,13 +9305,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9323,31 +9321,27 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B141" s="9">
-        <v>46118.59105829861</v>
+        <v>46118.55594259259</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46188.16857356481</v>
+        <v>46118.64758575232</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>143</v>
+        <v>320</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>197</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H141" s="10"/>
       <c r="I141" s="10"/>
-      <c r="J141" s="9">
-        <v>46188</v>
-      </c>
+      <c r="J141" s="10"/>
       <c r="K141" s="10" t="s">
         <v>26</v>
       </c>
@@ -9355,16 +9349,16 @@
         <v>26</v>
       </c>
       <c r="M141" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>314</v>
+        <v>26</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>143</v>
+        <v>321</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>314</v>
+        <v>26</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9374,27 +9368,33 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B142" s="5">
-        <v>46118.55594259259</v>
+        <v>46118.55594550926</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46118.64758575232</v>
+        <v>46190.178547442134</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
+        <v>324</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="I142" s="5">
+        <v>46189</v>
+      </c>
+      <c r="J142" s="5">
+        <v>46197</v>
+      </c>
       <c r="K142" s="6" t="s">
         <v>26</v>
       </c>
@@ -9402,45 +9402,55 @@
         <v>26</v>
       </c>
       <c r="M142" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N142" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="O142" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="P142" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q142" s="5">
+        <v>46197</v>
+      </c>
+      <c r="R142" s="5">
+        <v>46189</v>
+      </c>
+      <c r="S142" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="T142" s="6">
         <v>0</v>
       </c>
-      <c r="N142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O142" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="P142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q142" s="6"/>
-      <c r="R142" s="6"/>
-      <c r="S142" s="6"/>
-      <c r="T142" s="6"/>
-      <c r="U142" s="6"/>
+      <c r="U142" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B143" s="9">
-        <v>46118.55594550926</v>
+        <v>46118.55595019676</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46190.178547442134</v>
+        <v>46190.178546655094</v>
       </c>
       <c r="E143" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="F143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>327</v>
       </c>
       <c r="I143" s="9">
         <v>46189</v>
@@ -9458,13 +9468,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="Q143" s="9">
         <v>46197</v>
@@ -9473,76 +9483,13 @@
         <v>46189</v>
       </c>
       <c r="S143" s="11" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="T143" s="10">
         <v>0</v>
       </c>
       <c r="U143" s="12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B144" s="5">
-        <v>46118.55595019676</v>
-      </c>
-      <c r="C144" s="6"/>
-      <c r="D144" s="5">
-        <v>46190.178546655094</v>
-      </c>
-      <c r="E144" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="I144" s="5">
-        <v>46189</v>
-      </c>
-      <c r="J144" s="5">
-        <v>46197</v>
-      </c>
-      <c r="K144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N144" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="O144" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="P144" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q144" s="5">
-        <v>46197</v>
-      </c>
-      <c r="R144" s="5">
-        <v>46189</v>
-      </c>
-      <c r="S144" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="T144" s="6">
-        <v>0</v>
-      </c>
-      <c r="U144" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="329">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46182.679019351854</v>
+        <v>46192.88990037037</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2646,7 +2646,9 @@
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
+      <c r="U19" s="11" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -2842,9 +2844,11 @@
       <c r="B23" s="9">
         <v>46118.555640624996</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46192.88987828704</v>
+      </c>
       <c r="D23" s="9">
-        <v>46191.87648125</v>
+        <v>46192.88989348379</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>101</v>
@@ -2892,10 +2896,10 @@
         <v>84</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>96</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -2905,9 +2909,11 @@
       <c r="B24" s="5">
         <v>46118.55564542824</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46192.8897287963</v>
+      </c>
       <c r="D24" s="5">
-        <v>46169.855451180556</v>
+        <v>46192.88973167824</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>104</v>
@@ -2964,9 +2970,11 @@
       <c r="B25" s="9">
         <v>46118.55564990741</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46192.889863564815</v>
+      </c>
       <c r="D25" s="9">
-        <v>46169.85550466435</v>
+        <v>46192.88986527778</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -5926,7 +5934,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46130.19341753473</v>
+        <v>46192.88988357639</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>222</v>
@@ -5974,8 +5982,8 @@
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="12" t="s">
-        <v>96</v>
+      <c r="U77" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="329">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -216,9 +216,6 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1213955244874822</t>
   </si>
   <si>
@@ -652,6 +649,9 @@
   </si>
   <si>
     <t>Control de calidad Armado,Preparación Materiales,Armado</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213964514187677</t>
@@ -1131,12 +1131,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2059,9 +2059,11 @@
       <c r="B10" s="5">
         <v>46118.5554109375</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46192.91325913194</v>
+      </c>
       <c r="D10" s="5">
-        <v>46191.71013903935</v>
+        <v>46192.91327583333</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2096,14 +2098,16 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="11" t="s">
-        <v>51</v>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="9">
         <v>46118.55558501158</v>
@@ -2115,7 +2119,7 @@
         <v>46171.91061798611</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
@@ -2136,7 +2140,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2148,7 +2152,7 @@
         <v>43</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="9">
         <v>46104</v>
@@ -2168,7 +2172,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46118.55558986111</v>
@@ -2180,7 +2184,7 @@
         <v>46134.85090979167</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2201,7 +2205,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2213,7 +2217,7 @@
         <v>43</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46104</v>
@@ -2233,7 +2237,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46118.55559503472</v>
@@ -2245,7 +2249,7 @@
         <v>46134.85046350694</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2266,7 +2270,7 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
@@ -2278,7 +2282,7 @@
         <v>43</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="9">
         <v>46105</v>
@@ -2298,17 +2302,19 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46118.55541763889</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46192.913118993056</v>
+      </c>
       <c r="D14" s="5">
-        <v>46181.67168136574</v>
+        <v>46192.91314039352</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2332,7 +2338,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2340,12 +2346,16 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="9">
         <v>46118.55560518519</v>
@@ -2357,7 +2367,7 @@
         <v>46134.85202921296</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2378,19 +2388,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="Q15" s="9">
         <v>46106</v>
@@ -2410,26 +2420,28 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="5">
         <v>46118.555610462965</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46192.91310200232</v>
+      </c>
       <c r="D16" s="5">
-        <v>46169.85490482639</v>
+        <v>46192.91310392361</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="H16" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I16" s="5">
         <v>46105</v>
@@ -2441,19 +2453,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="5">
         <v>46106</v>
@@ -2473,7 +2485,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="9">
         <v>46118.555615578705</v>
@@ -2485,7 +2497,7 @@
         <v>46134.85241319444</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2506,19 +2518,19 @@
         <v>26</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="9">
         <v>46106</v>
@@ -2538,7 +2550,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46118.55562122686</v>
@@ -2550,16 +2562,16 @@
         <v>46181.671691550924</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I18" s="5">
         <v>46135</v>
@@ -2577,13 +2589,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="Q18" s="5">
         <v>46121</v>
@@ -2591,8 +2603,8 @@
       <c r="R18" s="5">
         <v>46121</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>84</v>
+      <c r="S18" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2603,17 +2615,19 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
         <v>46118.55542568287</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46192.91329202546</v>
+      </c>
       <c r="D19" s="9">
-        <v>46192.88990037037</v>
+        <v>46192.91330840278</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>25</v>
@@ -2637,7 +2651,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>26</v>
@@ -2645,14 +2659,16 @@
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="11" t="s">
-        <v>51</v>
+      <c r="T19" s="10">
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46118.5556269213</v>
@@ -2664,16 +2680,16 @@
         <v>46182.67873262732</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="I20" s="5">
         <v>46107</v>
@@ -2691,13 +2707,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46048</v>
@@ -2717,7 +2733,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" s="9">
         <v>46118.55563141203</v>
@@ -2729,16 +2745,16 @@
         <v>46169.85558454861</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="I21" s="9">
         <v>46107</v>
@@ -2756,13 +2772,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
@@ -2772,13 +2788,13 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="12" t="s">
-        <v>96</v>
+      <c r="U21" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B22" s="5">
         <v>46118.55563607639</v>
@@ -2790,16 +2806,16 @@
         <v>46182.67870440972</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="I22" s="5">
         <v>46111</v>
@@ -2817,13 +2833,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2833,13 +2849,13 @@
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="12" t="s">
-        <v>96</v>
+      <c r="U22" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B23" s="9">
         <v>46118.555640624996</v>
@@ -2851,16 +2867,16 @@
         <v>46192.88989348379</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="I23" s="9">
         <v>46107</v>
@@ -2878,13 +2894,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q23" s="9">
         <v>46128</v>
@@ -2892,8 +2908,8 @@
       <c r="R23" s="9">
         <v>46107</v>
       </c>
-      <c r="S23" s="12" t="s">
-        <v>84</v>
+      <c r="S23" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T23" s="10">
         <v>1</v>
@@ -2904,7 +2920,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46118.55564542824</v>
@@ -2913,19 +2929,19 @@
         <v>46192.8897287963</v>
       </c>
       <c r="D24" s="5">
-        <v>46192.88973167824</v>
+        <v>46192.913113912036</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="I24" s="5">
         <v>46107</v>
@@ -2943,13 +2959,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2959,13 +2975,13 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>96</v>
+      <c r="U24" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46118.55564990741</v>
@@ -2977,16 +2993,16 @@
         <v>46192.88986527778</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="I25" s="9">
         <v>46111</v>
@@ -3004,13 +3020,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3020,13 +3036,13 @@
       <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="12" t="s">
-        <v>96</v>
+      <c r="U25" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46118.555654606476</v>
@@ -3038,16 +3054,16 @@
         <v>46182.67902225694</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="I26" s="5">
         <v>46107</v>
@@ -3065,13 +3081,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q26" s="5">
         <v>46142</v>
@@ -3079,8 +3095,8 @@
       <c r="R26" s="5">
         <v>46107</v>
       </c>
-      <c r="S26" s="12" t="s">
-        <v>84</v>
+      <c r="S26" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3091,7 +3107,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46118.55565927083</v>
@@ -3103,16 +3119,16 @@
         <v>46169.85540111111</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="I27" s="9">
         <v>46107</v>
@@ -3130,13 +3146,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3146,13 +3162,13 @@
       <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
-        <v>96</v>
+      <c r="U27" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46118.55566380787</v>
@@ -3164,16 +3180,16 @@
         <v>46182.67899886574</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="I28" s="5">
         <v>46118</v>
@@ -3191,13 +3207,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3207,13 +3223,13 @@
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>96</v>
+      <c r="U28" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46118.55566881945</v>
@@ -3225,16 +3241,16 @@
         <v>46169.85534873843</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="I29" s="9">
         <v>46118</v>
@@ -3252,13 +3268,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3268,13 +3284,13 @@
       <c r="T29" s="10">
         <v>0</v>
       </c>
-      <c r="U29" s="12" t="s">
-        <v>96</v>
+      <c r="U29" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46118.55567340278</v>
@@ -3286,16 +3302,16 @@
         <v>46181.671818483796</v>
       </c>
       <c r="E30" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I30" s="5">
         <v>46136</v>
@@ -3313,13 +3329,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q30" s="5">
         <v>46150</v>
@@ -3327,8 +3343,8 @@
       <c r="R30" s="5">
         <v>46136</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>84</v>
+      <c r="S30" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3339,7 +3355,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B31" s="9">
         <v>46118.55568293981</v>
@@ -3351,16 +3367,16 @@
         <v>46181.671733344905</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I31" s="9">
         <v>46136</v>
@@ -3378,13 +3394,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3394,13 +3410,13 @@
       <c r="T31" s="10">
         <v>0</v>
       </c>
-      <c r="U31" s="12" t="s">
-        <v>96</v>
+      <c r="U31" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B32" s="5">
         <v>46118.55568802083</v>
@@ -3412,16 +3428,16 @@
         <v>46181.67179341435</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I32" s="5">
         <v>46142</v>
@@ -3439,13 +3455,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3455,13 +3471,13 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="12" t="s">
-        <v>96</v>
+      <c r="U32" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B33" s="9">
         <v>46118.5554312037</v>
@@ -3471,7 +3487,7 @@
         <v>46135.50561945602</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>25</v>
@@ -3495,7 +3511,7 @@
         <v>26</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3508,7 +3524,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46118.55573724537</v>
@@ -3520,16 +3536,16 @@
         <v>46134.856103495375</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I34" s="5">
         <v>46106</v>
@@ -3547,13 +3563,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="5">
         <v>46112</v>
@@ -3573,7 +3589,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B35" s="9">
         <v>46118.58934402778</v>
@@ -3585,16 +3601,16 @@
         <v>46134.85589640046</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I35" s="9">
         <v>46106</v>
@@ -3612,13 +3628,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3628,7 +3644,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46118.58935734954</v>
@@ -3640,16 +3656,16 @@
         <v>46134.855904895834</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46106</v>
@@ -3667,13 +3683,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3683,7 +3699,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46118.58936491898</v>
@@ -3695,16 +3711,16 @@
         <v>46134.85606556713</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46106</v>
@@ -3722,13 +3738,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3738,7 +3754,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46118.58937265046</v>
@@ -3750,16 +3766,16 @@
         <v>46134.85607190972</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I38" s="5">
         <v>46106</v>
@@ -3777,13 +3793,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3793,7 +3809,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46118.5893790625</v>
@@ -3805,16 +3821,16 @@
         <v>46134.85607811343</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I39" s="9">
         <v>46106</v>
@@ -3832,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3848,7 +3864,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46118.55574388889</v>
@@ -3860,16 +3876,16 @@
         <v>46135.52260231481</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I40" s="5">
         <v>46127</v>
@@ -3887,13 +3903,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q40" s="5">
         <v>46133</v>
@@ -3901,8 +3917,8 @@
       <c r="R40" s="5">
         <v>46127</v>
       </c>
-      <c r="S40" s="12" t="s">
-        <v>84</v>
+      <c r="S40" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3913,7 +3929,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="9">
         <v>46118.58948621528</v>
@@ -3925,16 +3941,16 @@
         <v>46135.50526961806</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I41" s="9">
         <v>46127</v>
@@ -3952,13 +3968,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="P41" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3968,7 +3984,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46118.589619189814</v>
@@ -3980,16 +3996,16 @@
         <v>46135.50528020834</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46127</v>
@@ -4007,13 +4023,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4023,7 +4039,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46118.589635729164</v>
@@ -4035,16 +4051,16 @@
         <v>46135.50528708333</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I43" s="9">
         <v>46127</v>
@@ -4062,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O43" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4078,7 +4094,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46118.58964931713</v>
@@ -4090,16 +4106,16 @@
         <v>46135.50529516204</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I44" s="5">
         <v>46127</v>
@@ -4117,13 +4133,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4133,7 +4149,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B45" s="9">
         <v>46118.5896587037</v>
@@ -4145,16 +4161,16 @@
         <v>46135.50530211805</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I45" s="9">
         <v>46127</v>
@@ -4172,13 +4188,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O45" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4188,7 +4204,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B46" s="5">
         <v>46118.55575109954</v>
@@ -4200,16 +4216,16 @@
         <v>46135.50560496528</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I46" s="5">
         <v>46134</v>
@@ -4227,13 +4243,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q46" s="5">
         <v>46134</v>
@@ -4241,8 +4257,8 @@
       <c r="R46" s="5">
         <v>46134</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>84</v>
+      <c r="S46" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4253,7 +4269,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B47" s="9">
         <v>46118.58972679398</v>
@@ -4265,16 +4281,16 @@
         <v>46135.505555069445</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="9">
@@ -4290,13 +4306,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4306,7 +4322,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B48" s="5">
         <v>46118.58974760417</v>
@@ -4318,16 +4334,16 @@
         <v>46135.50556056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4343,13 +4359,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4359,7 +4375,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B49" s="9">
         <v>46118.58975269676</v>
@@ -4371,16 +4387,16 @@
         <v>46135.50556795139</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4396,13 +4412,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4412,7 +4428,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B50" s="5">
         <v>46118.58976391204</v>
@@ -4424,16 +4440,16 @@
         <v>46135.50557504629</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4449,13 +4465,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4465,7 +4481,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B51" s="9">
         <v>46118.589758912036</v>
@@ -4477,16 +4493,16 @@
         <v>46135.50558240741</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4502,13 +4518,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4518,7 +4534,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B52" s="5">
         <v>46118.55575893518</v>
@@ -4528,16 +4544,16 @@
         <v>46182.20622399305</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="I52" s="5">
         <v>46181</v>
@@ -4555,13 +4571,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q52" s="5">
         <v>46181</v>
@@ -4569,19 +4585,19 @@
       <c r="R52" s="5">
         <v>46181</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>84</v>
+      <c r="S52" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
-      <c r="U52" s="12" t="s">
-        <v>96</v>
+      <c r="U52" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B53" s="9">
         <v>46118.589869131945</v>
@@ -4591,16 +4607,16 @@
         <v>46181.168647604165</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="I53" s="9">
         <v>46181</v>
@@ -4618,13 +4634,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4634,7 +4650,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B54" s="5">
         <v>46118.589883333334</v>
@@ -4644,16 +4660,16 @@
         <v>46181.16864912037</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="I54" s="5">
         <v>46181</v>
@@ -4671,13 +4687,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4687,7 +4703,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B55" s="9">
         <v>46118.589890312505</v>
@@ -4697,16 +4713,16 @@
         <v>46181.16865042824</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="I55" s="9">
         <v>46181</v>
@@ -4724,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4740,7 +4756,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B56" s="5">
         <v>46118.58992050926</v>
@@ -4750,16 +4766,16 @@
         <v>46181.168653182875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="I56" s="5">
         <v>46181</v>
@@ -4777,13 +4793,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4793,7 +4809,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B57" s="9">
         <v>46118.589899548606</v>
@@ -4803,16 +4819,16 @@
         <v>46181.168651678236</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="I57" s="9">
         <v>46181</v>
@@ -4830,13 +4846,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4846,7 +4862,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B58" s="5">
         <v>46118.55576480324</v>
@@ -4858,7 +4874,7 @@
         <v>46181.67205032408</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4882,7 +4898,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4895,7 +4911,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B59" s="9">
         <v>46118.55576952547</v>
@@ -4907,16 +4923,16 @@
         <v>46181.67191517361</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="H59" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I59" s="9">
         <v>46153</v>
@@ -4934,13 +4950,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q59" s="9">
         <v>46154</v>
@@ -4948,8 +4964,8 @@
       <c r="R59" s="9">
         <v>46153</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>84</v>
+      <c r="S59" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -4960,7 +4976,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B60" s="5">
         <v>46118.55577607639</v>
@@ -4972,16 +4988,16 @@
         <v>46181.671966932874</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I60" s="5">
         <v>46155</v>
@@ -4999,13 +5015,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q60" s="5">
         <v>46156</v>
@@ -5013,8 +5029,8 @@
       <c r="R60" s="5">
         <v>46155</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>84</v>
+      <c r="S60" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5025,7 +5041,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B61" s="9">
         <v>46118.55578122685</v>
@@ -5035,7 +5051,7 @@
         <v>46191.710350381945</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5059,7 +5075,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5068,8 +5084,8 @@
       <c r="R61" s="10"/>
       <c r="S61" s="10"/>
       <c r="T61" s="10"/>
-      <c r="U61" s="11" t="s">
-        <v>51</v>
+      <c r="U61" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5113,10 +5129,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>196</v>
@@ -5127,8 +5143,8 @@
       <c r="R62" s="5">
         <v>46155</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>84</v>
+      <c r="S62" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5178,13 +5194,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q63" s="9">
         <v>46164</v>
@@ -5192,8 +5208,8 @@
       <c r="R63" s="9">
         <v>46160</v>
       </c>
-      <c r="S63" s="12" t="s">
-        <v>84</v>
+      <c r="S63" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T63" s="10">
         <v>1</v>
@@ -5216,7 +5232,7 @@
         <v>46181.672338564815</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5271,7 +5287,7 @@
         <v>46181.672352442125</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5326,7 +5342,7 @@
         <v>46181.672366307874</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5381,7 +5397,7 @@
         <v>46191.71031108796</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5436,7 +5452,7 @@
         <v>46191.710318530095</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5518,13 +5534,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q69" s="9">
         <v>46167</v>
@@ -5532,8 +5548,8 @@
       <c r="R69" s="9">
         <v>46167</v>
       </c>
-      <c r="S69" s="12" t="s">
-        <v>84</v>
+      <c r="S69" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T69" s="10">
         <v>1</v>
@@ -5556,7 +5572,7 @@
         <v>46181.67244473379</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5611,7 +5627,7 @@
         <v>46181.672458078705</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5666,7 +5682,7 @@
         <v>46181.672464999996</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5721,16 +5737,16 @@
         <v>46191.7103152662</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I73" s="9">
         <v>46167</v>
@@ -5776,16 +5792,16 @@
         <v>46191.7103265162</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I74" s="5">
         <v>46167</v>
@@ -5829,7 +5845,7 @@
         <v>46118.58538233796</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -5882,10 +5898,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5901,10 +5917,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>220</v>
@@ -5921,8 +5937,8 @@
       <c r="T76" s="6">
         <v>0</v>
       </c>
-      <c r="U76" s="11" t="s">
-        <v>51</v>
+      <c r="U76" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -5943,10 +5959,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -5962,10 +5978,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>220</v>
@@ -5976,14 +5992,14 @@
       <c r="R77" s="9">
         <v>46129</v>
       </c>
-      <c r="S77" s="12" t="s">
-        <v>84</v>
+      <c r="S77" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="11" t="s">
-        <v>51</v>
+      <c r="U77" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6004,10 +6020,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6023,10 +6039,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>220</v>
@@ -6037,14 +6053,14 @@
       <c r="R78" s="5">
         <v>46146</v>
       </c>
-      <c r="S78" s="12" t="s">
-        <v>84</v>
+      <c r="S78" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="11" t="s">
-        <v>51</v>
+      <c r="U78" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6112,10 +6128,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I80" s="5">
         <v>46168</v>
@@ -6136,7 +6152,7 @@
         <v>226</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>226</v>
@@ -6147,14 +6163,14 @@
       <c r="R80" s="5">
         <v>46168</v>
       </c>
-      <c r="S80" s="12" t="s">
-        <v>84</v>
+      <c r="S80" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="12" t="s">
-        <v>96</v>
+      <c r="U80" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6169,16 +6185,16 @@
         <v>46181.67244934027</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I81" s="9">
         <v>46168</v>
@@ -6199,7 +6215,7 @@
         <v>229</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>231</v>
@@ -6222,16 +6238,16 @@
         <v>46181.67246390047</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I82" s="5">
         <v>46168</v>
@@ -6252,7 +6268,7 @@
         <v>229</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>231</v>
@@ -6275,16 +6291,16 @@
         <v>46181.67246981482</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I83" s="9">
         <v>46168</v>
@@ -6305,7 +6321,7 @@
         <v>229</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>231</v>
@@ -6328,16 +6344,16 @@
         <v>46191.70929190972</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I84" s="5">
         <v>46168</v>
@@ -6358,7 +6374,7 @@
         <v>229</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>231</v>
@@ -6381,16 +6397,16 @@
         <v>46191.70934756944</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I85" s="9">
         <v>46168</v>
@@ -6411,7 +6427,7 @@
         <v>229</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>231</v>
@@ -6440,10 +6456,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I86" s="5">
         <v>46175</v>
@@ -6464,7 +6480,7 @@
         <v>226</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>226</v>
@@ -6475,14 +6491,14 @@
       <c r="R86" s="5">
         <v>46175</v>
       </c>
-      <c r="S86" s="12" t="s">
-        <v>84</v>
+      <c r="S86" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="12" t="s">
-        <v>96</v>
+      <c r="U86" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6497,16 +6513,16 @@
         <v>46175.16810725695</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6548,16 +6564,16 @@
         <v>46175.1681088426</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6599,16 +6615,16 @@
         <v>46175.16811023148</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6650,16 +6666,16 @@
         <v>46175.168111493054</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6701,16 +6717,16 @@
         <v>46175.168112893516</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6758,10 +6774,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6780,7 +6796,7 @@
         <v>226</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>226</v>
@@ -6791,14 +6807,14 @@
       <c r="R92" s="5">
         <v>46176</v>
       </c>
-      <c r="S92" s="12" t="s">
-        <v>84</v>
+      <c r="S92" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T92" s="6">
         <v>0</v>
       </c>
-      <c r="U92" s="12" t="s">
-        <v>96</v>
+      <c r="U92" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -6813,16 +6829,16 @@
         <v>46176.16819081019</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6864,16 +6880,16 @@
         <v>46176.168192418976</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6915,16 +6931,16 @@
         <v>46176.16819494213</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -6966,16 +6982,16 @@
         <v>46176.16819359954</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7017,16 +7033,16 @@
         <v>46176.16819640047</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7074,10 +7090,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7096,7 +7112,7 @@
         <v>226</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>226</v>
@@ -7107,14 +7123,14 @@
       <c r="R98" s="5">
         <v>46177</v>
       </c>
-      <c r="S98" s="12" t="s">
-        <v>84</v>
+      <c r="S98" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
-      <c r="U98" s="12" t="s">
-        <v>96</v>
+      <c r="U98" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7129,16 +7145,16 @@
         <v>46177.168168738426</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7180,16 +7196,16 @@
         <v>46177.168170543984</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7231,16 +7247,16 @@
         <v>46177.16817181713</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7282,16 +7298,16 @@
         <v>46177.16817290509</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7333,16 +7349,16 @@
         <v>46177.16817414352</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7390,10 +7406,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I104" s="5">
         <v>46178</v>
@@ -7414,7 +7430,7 @@
         <v>226</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>226</v>
@@ -7425,14 +7441,14 @@
       <c r="R104" s="5">
         <v>46178</v>
       </c>
-      <c r="S104" s="12" t="s">
-        <v>84</v>
+      <c r="S104" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
-      <c r="U104" s="12" t="s">
-        <v>96</v>
+      <c r="U104" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7447,16 +7463,16 @@
         <v>46178.16912293981</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7475,7 +7491,7 @@
         <v>266</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>268</v>
@@ -7498,16 +7514,16 @@
         <v>46178.169124884254</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7526,7 +7542,7 @@
         <v>266</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>268</v>
@@ -7549,16 +7565,16 @@
         <v>46178.16913978009</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7577,7 +7593,7 @@
         <v>266</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>268</v>
@@ -7600,16 +7616,16 @@
         <v>46178.16914135417</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7628,7 +7644,7 @@
         <v>266</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>268</v>
@@ -7651,16 +7667,16 @@
         <v>46178.16914265046</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I109" s="10"/>
       <c r="J109" s="9">
@@ -7679,7 +7695,7 @@
         <v>266</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>268</v>
@@ -7708,10 +7724,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -7730,7 +7746,7 @@
         <v>226</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>275</v>
@@ -7741,14 +7757,14 @@
       <c r="R110" s="5">
         <v>46182</v>
       </c>
-      <c r="S110" s="12" t="s">
-        <v>84</v>
+      <c r="S110" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
       </c>
-      <c r="U110" s="12" t="s">
-        <v>96</v>
+      <c r="U110" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -7763,16 +7779,16 @@
         <v>46182.168110810184</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I111" s="9">
         <v>46182</v>
@@ -7793,7 +7809,7 @@
         <v>274</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>277</v>
@@ -7816,16 +7832,16 @@
         <v>46182.1681121875</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I112" s="5">
         <v>46182</v>
@@ -7846,7 +7862,7 @@
         <v>274</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>277</v>
@@ -7869,16 +7885,16 @@
         <v>46182.16811331018</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I113" s="9">
         <v>46182</v>
@@ -7899,7 +7915,7 @@
         <v>274</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>277</v>
@@ -7922,16 +7938,16 @@
         <v>46182.16811451389</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I114" s="5">
         <v>46182</v>
@@ -7952,7 +7968,7 @@
         <v>274</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>277</v>
@@ -7975,16 +7991,16 @@
         <v>46182.16811570602</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I115" s="9">
         <v>46182</v>
@@ -8005,7 +8021,7 @@
         <v>274</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>277</v>
@@ -8114,14 +8130,14 @@
       <c r="R117" s="9">
         <v>46183</v>
       </c>
-      <c r="S117" s="12" t="s">
-        <v>84</v>
+      <c r="S117" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T117" s="10">
         <v>0</v>
       </c>
-      <c r="U117" s="12" t="s">
-        <v>96</v>
+      <c r="U117" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8136,7 +8152,7 @@
         <v>46183.16824416666</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8164,10 +8180,10 @@
         <v>286</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8187,7 +8203,7 @@
         <v>46183.16824571759</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8215,10 +8231,10 @@
         <v>286</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8238,7 +8254,7 @@
         <v>46183.168246875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8266,10 +8282,10 @@
         <v>286</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8289,7 +8305,7 @@
         <v>46183.16824814815</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8317,10 +8333,10 @@
         <v>286</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8340,7 +8356,7 @@
         <v>46183.16824943287</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8368,10 +8384,10 @@
         <v>286</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8397,10 +8413,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I123" s="10"/>
       <c r="J123" s="9">
@@ -8430,14 +8446,14 @@
       <c r="R123" s="9">
         <v>46184</v>
       </c>
-      <c r="S123" s="12" t="s">
-        <v>84</v>
+      <c r="S123" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T123" s="10">
         <v>0</v>
       </c>
-      <c r="U123" s="12" t="s">
-        <v>96</v>
+      <c r="U123" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
@@ -8452,16 +8468,16 @@
         <v>46184.168032511574</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -8480,7 +8496,7 @@
         <v>295</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>298</v>
@@ -8503,16 +8519,16 @@
         <v>46184.168034201386</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I125" s="10"/>
       <c r="J125" s="9">
@@ -8531,7 +8547,7 @@
         <v>295</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>298</v>
@@ -8554,16 +8570,16 @@
         <v>46184.16803541667</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8582,7 +8598,7 @@
         <v>295</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>298</v>
@@ -8605,16 +8621,16 @@
         <v>46184.168036863426</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8633,7 +8649,7 @@
         <v>295</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>298</v>
@@ -8656,16 +8672,16 @@
         <v>46184.16803811342</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8684,7 +8700,7 @@
         <v>295</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>298</v>
@@ -8735,7 +8751,7 @@
         <v>283</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>283</v>
@@ -8746,14 +8762,14 @@
       <c r="R129" s="9">
         <v>46185</v>
       </c>
-      <c r="S129" s="12" t="s">
-        <v>84</v>
+      <c r="S129" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>
       </c>
-      <c r="U129" s="12" t="s">
-        <v>96</v>
+      <c r="U129" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -8768,7 +8784,7 @@
         <v>46185.168594965275</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8796,7 +8812,7 @@
         <v>304</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>306</v>
@@ -8819,7 +8835,7 @@
         <v>46185.16859673611</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -8847,7 +8863,7 @@
         <v>304</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>306</v>
@@ -8870,7 +8886,7 @@
         <v>46185.168597951386</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -8898,7 +8914,7 @@
         <v>304</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>306</v>
@@ -8921,7 +8937,7 @@
         <v>46185.16859903935</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -8949,7 +8965,7 @@
         <v>304</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>306</v>
@@ -8972,7 +8988,7 @@
         <v>46185.16860023148</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9000,7 +9016,7 @@
         <v>304</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>306</v>
@@ -9051,7 +9067,7 @@
         <v>283</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>313</v>
@@ -9062,14 +9078,14 @@
       <c r="R135" s="9">
         <v>46188</v>
       </c>
-      <c r="S135" s="12" t="s">
-        <v>84</v>
+      <c r="S135" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T135" s="10">
         <v>0</v>
       </c>
-      <c r="U135" s="12" t="s">
-        <v>96</v>
+      <c r="U135" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9084,7 +9100,7 @@
         <v>46188.168568113426</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9112,7 +9128,7 @@
         <v>312</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>312</v>
@@ -9135,7 +9151,7 @@
         <v>46188.16856979167</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9163,7 +9179,7 @@
         <v>312</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>312</v>
@@ -9186,7 +9202,7 @@
         <v>46188.168570995374</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9214,7 +9230,7 @@
         <v>312</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>312</v>
@@ -9237,7 +9253,7 @@
         <v>46188.1685722338</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9265,7 +9281,7 @@
         <v>312</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>312</v>
@@ -9288,7 +9304,7 @@
         <v>46188.16857356481</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9316,7 +9332,7 @@
         <v>312</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>312</v>
@@ -9427,14 +9443,14 @@
       <c r="R142" s="5">
         <v>46189</v>
       </c>
-      <c r="S142" s="11" t="s">
+      <c r="S142" s="12" t="s">
         <v>326</v>
       </c>
       <c r="T142" s="6">
         <v>0</v>
       </c>
-      <c r="U142" s="12" t="s">
-        <v>96</v>
+      <c r="U142" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -9490,14 +9506,14 @@
       <c r="R143" s="9">
         <v>46189</v>
       </c>
-      <c r="S143" s="11" t="s">
+      <c r="S143" s="12" t="s">
         <v>326</v>
       </c>
       <c r="T143" s="10">
         <v>0</v>
       </c>
-      <c r="U143" s="12" t="s">
-        <v>96</v>
+      <c r="U143" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -4604,7 +4604,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46181.168647604165</v>
+        <v>46197.50794607639</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>140</v>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.16864912037</v>
+        <v>46197.50794943287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>140</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46181.16865042824</v>
+        <v>46197.50795643518</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>140</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46118.63827943287</v>
+        <v>46197.50782400463</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>226</v>
@@ -6117,9 +6117,11 @@
       <c r="B80" s="5">
         <v>46118.55582877315</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46197.4232071875</v>
+      </c>
       <c r="D80" s="5">
-        <v>46175.185741284724</v>
+        <v>46197.42322075232</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>229</v>
@@ -6167,10 +6169,10 @@
         <v>83</v>
       </c>
       <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="11" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="U80" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6180,9 +6182,11 @@
       <c r="B81" s="9">
         <v>46118.590250625</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="9">
+        <v>46197.42301266204</v>
+      </c>
       <c r="D81" s="9">
-        <v>46181.67244934027</v>
+        <v>46197.423014942135</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>140</v>
@@ -6233,9 +6237,11 @@
       <c r="B82" s="5">
         <v>46118.590259641205</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46197.42305077546</v>
+      </c>
       <c r="D82" s="5">
-        <v>46181.67246390047</v>
+        <v>46197.42305252315</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>140</v>
@@ -6286,9 +6292,11 @@
       <c r="B83" s="9">
         <v>46118.59026761574</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="9">
+        <v>46197.423102430555</v>
+      </c>
       <c r="D83" s="9">
-        <v>46181.67246981482</v>
+        <v>46197.42310400463</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>140</v>
@@ -6339,9 +6347,11 @@
       <c r="B84" s="5">
         <v>46118.590275636576</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46197.42314728009</v>
+      </c>
       <c r="D84" s="5">
-        <v>46191.70929190972</v>
+        <v>46197.423148842594</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>140</v>
@@ -6392,9 +6402,11 @@
       <c r="B85" s="9">
         <v>46118.59028430555</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="9">
+        <v>46197.42319270833</v>
+      </c>
       <c r="D85" s="9">
-        <v>46191.70934756944</v>
+        <v>46197.42319425926</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>140</v>
@@ -6447,7 +6459,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46176.1814233912</v>
+        <v>46197.50731976852</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>237</v>
@@ -6508,9 +6520,11 @@
       <c r="B87" s="9">
         <v>46118.59033478009</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="9">
+        <v>46197.50709427083</v>
+      </c>
       <c r="D87" s="9">
-        <v>46175.16810725695</v>
+        <v>46197.50709627315</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>140</v>
@@ -6559,9 +6573,11 @@
       <c r="B88" s="5">
         <v>46118.59034447916</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46197.50715157407</v>
+      </c>
       <c r="D88" s="5">
-        <v>46175.1681088426</v>
+        <v>46197.507152997685</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>140</v>
@@ -6610,9 +6626,11 @@
       <c r="B89" s="9">
         <v>46118.590352141204</v>
       </c>
-      <c r="C89" s="10"/>
+      <c r="C89" s="9">
+        <v>46197.50723920139</v>
+      </c>
       <c r="D89" s="9">
-        <v>46175.16811023148</v>
+        <v>46197.50724237268</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>140</v>
@@ -6661,9 +6679,11 @@
       <c r="B90" s="5">
         <v>46118.59035967593</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46197.50731302083</v>
+      </c>
       <c r="D90" s="5">
-        <v>46175.168111493054</v>
+        <v>46197.507314386574</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>140</v>
@@ -6714,7 +6734,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46175.168112893516</v>
+        <v>46197.42320116898</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>140</v>
@@ -6763,9 +6783,11 @@
       <c r="B92" s="5">
         <v>46118.55584244213</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46197.50781607639</v>
+      </c>
       <c r="D92" s="5">
-        <v>46177.19457946759</v>
+        <v>46197.50782737268</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>246</v>
@@ -6811,10 +6833,10 @@
         <v>83</v>
       </c>
       <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="11" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="U92" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -6824,9 +6846,11 @@
       <c r="B93" s="9">
         <v>46118.59042068287</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="9">
+        <v>46197.50749427083</v>
+      </c>
       <c r="D93" s="9">
-        <v>46176.16819081019</v>
+        <v>46197.50749574074</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>140</v>
@@ -6875,9 +6899,11 @@
       <c r="B94" s="5">
         <v>46118.5904280324</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46197.507576828706</v>
+      </c>
       <c r="D94" s="5">
-        <v>46176.168192418976</v>
+        <v>46197.50757840278</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>140</v>
@@ -6926,9 +6952,11 @@
       <c r="B95" s="9">
         <v>46118.59044465278</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="9">
+        <v>46197.50767422454</v>
+      </c>
       <c r="D95" s="9">
-        <v>46176.16819494213</v>
+        <v>46197.50767577546</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>140</v>
@@ -6977,9 +7005,11 @@
       <c r="B96" s="5">
         <v>46118.5904391088</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46197.50773788194</v>
+      </c>
       <c r="D96" s="5">
-        <v>46176.16819359954</v>
+        <v>46197.50773945602</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>140</v>
@@ -7028,9 +7058,11 @@
       <c r="B97" s="9">
         <v>46118.59045233796</v>
       </c>
-      <c r="C97" s="10"/>
+      <c r="C97" s="9">
+        <v>46197.507801064814</v>
+      </c>
       <c r="D97" s="9">
-        <v>46176.16819640047</v>
+        <v>46197.50780251157</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>140</v>
@@ -7081,7 +7113,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46178.17851013889</v>
+        <v>46197.42458010417</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>255</v>
@@ -7140,9 +7172,11 @@
       <c r="B99" s="9">
         <v>46118.590539282406</v>
       </c>
-      <c r="C99" s="10"/>
+      <c r="C99" s="9">
+        <v>46197.42437898148</v>
+      </c>
       <c r="D99" s="9">
-        <v>46177.168168738426</v>
+        <v>46197.50749940972</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>140</v>
@@ -7191,9 +7225,11 @@
       <c r="B100" s="5">
         <v>46118.590546666666</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46197.42449445602</v>
+      </c>
       <c r="D100" s="5">
-        <v>46177.168170543984</v>
+        <v>46197.50758304398</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>140</v>
@@ -7242,9 +7278,11 @@
       <c r="B101" s="9">
         <v>46118.590554027774</v>
       </c>
-      <c r="C101" s="10"/>
+      <c r="C101" s="9">
+        <v>46197.42457260417</v>
+      </c>
       <c r="D101" s="9">
-        <v>46177.16817181713</v>
+        <v>46197.50774366898</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>140</v>
@@ -7295,7 +7333,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46177.16817290509</v>
+        <v>46197.507679953706</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>140</v>
@@ -7346,7 +7384,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46177.16817414352</v>
+        <v>46197.50781008102</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>140</v>
@@ -7397,7 +7435,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46179.20438387731</v>
+        <v>46197.507954988425</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>266</v>
@@ -7458,9 +7496,11 @@
       <c r="B105" s="9">
         <v>46118.5906265625</v>
       </c>
-      <c r="C105" s="10"/>
+      <c r="C105" s="9">
+        <v>46197.50793775463</v>
+      </c>
       <c r="D105" s="9">
-        <v>46178.16912293981</v>
+        <v>46197.50793939814</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>140</v>
@@ -7509,9 +7549,11 @@
       <c r="B106" s="5">
         <v>46118.59063387732</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46197.507942592594</v>
+      </c>
       <c r="D106" s="5">
-        <v>46178.169124884254</v>
+        <v>46197.5079440625</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>140</v>
@@ -7560,9 +7602,11 @@
       <c r="B107" s="9">
         <v>46118.590655486114</v>
       </c>
-      <c r="C107" s="10"/>
+      <c r="C107" s="9">
+        <v>46197.507947488426</v>
+      </c>
       <c r="D107" s="9">
-        <v>46178.16913978009</v>
+        <v>46197.50794915509</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>140</v>
@@ -9399,7 +9443,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46190.178547442134</v>
+        <v>46197.1681475</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>323</v>
@@ -9462,7 +9506,7 @@
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46190.178546655094</v>
+        <v>46197.168156134256</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>328</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1689,13 +1689,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.55540376157</v>
+        <v>46118.38873709491</v>
       </c>
       <c r="C4" s="5">
-        <v>46134.84973423611</v>
+        <v>46134.683067569444</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.84974535879</v>
+        <v>46134.683078692135</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1742,13 +1742,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46118.55556929398</v>
+        <v>46118.38890262731</v>
       </c>
       <c r="C5" s="9">
-        <v>46134.847409131944</v>
+        <v>46134.68074246528</v>
       </c>
       <c r="D5" s="9">
-        <v>46134.84745465278</v>
+        <v>46134.680787986115</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1805,13 +1805,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.5555727662</v>
+        <v>46118.388906099535</v>
       </c>
       <c r="C6" s="5">
-        <v>46134.848174328705</v>
+        <v>46134.68150766204</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.84818818287</v>
+        <v>46134.681521516206</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1868,13 +1868,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="9">
-        <v>46118.555575624996</v>
+        <v>46118.38890895833</v>
       </c>
       <c r="C7" s="9">
-        <v>46134.848471840276</v>
+        <v>46134.68180517361</v>
       </c>
       <c r="D7" s="9">
-        <v>46134.84848634259</v>
+        <v>46134.68181967593</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>40</v>
@@ -1931,13 +1931,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.555578287036</v>
+        <v>46118.38891162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46134.849233009256</v>
+        <v>46134.68256634259</v>
       </c>
       <c r="D8" s="5">
-        <v>46191.71012979167</v>
+        <v>46191.543463124995</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1994,13 +1994,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="9">
-        <v>46118.55558168981</v>
+        <v>46118.38891502315</v>
       </c>
       <c r="C9" s="9">
-        <v>46134.84972003472</v>
+        <v>46134.683053368055</v>
       </c>
       <c r="D9" s="9">
-        <v>46134.84973509259</v>
+        <v>46134.683068425926</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>47</v>
@@ -2057,13 +2057,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.5554109375</v>
+        <v>46118.38874427084</v>
       </c>
       <c r="C10" s="5">
-        <v>46192.91325913194</v>
+        <v>46192.74659246528</v>
       </c>
       <c r="D10" s="5">
-        <v>46192.91327583333</v>
+        <v>46192.74660916667</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2110,13 +2110,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="9">
-        <v>46118.55558501158</v>
+        <v>46118.38891834491</v>
       </c>
       <c r="C11" s="9">
-        <v>46134.851535752314</v>
+        <v>46134.68486908565</v>
       </c>
       <c r="D11" s="9">
-        <v>46171.91061798611</v>
+        <v>46171.74395131944</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>52</v>
@@ -2175,13 +2175,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.55558986111</v>
+        <v>46118.38892319445</v>
       </c>
       <c r="C12" s="5">
-        <v>46134.850894386575</v>
+        <v>46134.6842277199</v>
       </c>
       <c r="D12" s="5">
-        <v>46134.85090979167</v>
+        <v>46134.684243125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2240,13 +2240,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46118.55559503472</v>
+        <v>46118.388928368055</v>
       </c>
       <c r="C13" s="9">
-        <v>46134.85044589121</v>
+        <v>46134.683779224535</v>
       </c>
       <c r="D13" s="9">
-        <v>46134.85046350694</v>
+        <v>46134.683796840276</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2305,13 +2305,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.55541763889</v>
+        <v>46118.388750972226</v>
       </c>
       <c r="C14" s="5">
-        <v>46192.913118993056</v>
+        <v>46192.74645232639</v>
       </c>
       <c r="D14" s="5">
-        <v>46192.91314039352</v>
+        <v>46192.74647372685</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2358,13 +2358,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46118.55560518519</v>
+        <v>46118.38893851852</v>
       </c>
       <c r="C15" s="9">
-        <v>46134.85201509259</v>
+        <v>46134.685348425926</v>
       </c>
       <c r="D15" s="9">
-        <v>46134.85202921296</v>
+        <v>46134.6853625463</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2423,13 +2423,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.555610462965</v>
+        <v>46118.38894379629</v>
       </c>
       <c r="C16" s="5">
-        <v>46192.91310200232</v>
+        <v>46192.74643533565</v>
       </c>
       <c r="D16" s="5">
-        <v>46192.91310392361</v>
+        <v>46192.746437256945</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2488,13 +2488,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46118.555615578705</v>
+        <v>46118.388948912034</v>
       </c>
       <c r="C17" s="9">
-        <v>46134.8523972338</v>
+        <v>46134.68573056713</v>
       </c>
       <c r="D17" s="9">
-        <v>46134.85241319444</v>
+        <v>46134.68574652778</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2553,13 +2553,13 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.55562122686</v>
+        <v>46118.388954560185</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.67167443287</v>
+        <v>46181.5050077662</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.671691550924</v>
+        <v>46181.50502488426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2618,13 +2618,13 @@
         <v>84</v>
       </c>
       <c r="B19" s="9">
-        <v>46118.55542568287</v>
+        <v>46118.388759016205</v>
       </c>
       <c r="C19" s="9">
-        <v>46192.91329202546</v>
+        <v>46192.74662535879</v>
       </c>
       <c r="D19" s="9">
-        <v>46192.91330840278</v>
+        <v>46192.746641736114</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>85</v>
@@ -2671,13 +2671,13 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.5556269213</v>
+        <v>46118.388960254626</v>
       </c>
       <c r="C20" s="5">
-        <v>46182.678718379626</v>
+        <v>46182.51205171296</v>
       </c>
       <c r="D20" s="5">
-        <v>46182.67873262732</v>
+        <v>46182.51206596065</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -2736,13 +2736,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="9">
-        <v>46118.55563141203</v>
+        <v>46118.38896474537</v>
       </c>
       <c r="C21" s="9">
-        <v>46155.897256944445</v>
+        <v>46155.73059027777</v>
       </c>
       <c r="D21" s="9">
-        <v>46169.85558454861</v>
+        <v>46169.68891788194</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>93</v>
@@ -2797,13 +2797,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.55563607639</v>
+        <v>46118.38896940972</v>
       </c>
       <c r="C22" s="5">
-        <v>46182.67870244213</v>
+        <v>46182.512035775464</v>
       </c>
       <c r="D22" s="5">
-        <v>46182.67870440972</v>
+        <v>46182.51203774306</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -2858,13 +2858,13 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46118.555640624996</v>
+        <v>46118.38897395833</v>
       </c>
       <c r="C23" s="9">
-        <v>46192.88987828704</v>
+        <v>46192.72321162037</v>
       </c>
       <c r="D23" s="9">
-        <v>46192.88989348379</v>
+        <v>46192.72322681713</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -2923,13 +2923,13 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.55564542824</v>
+        <v>46118.38897876158</v>
       </c>
       <c r="C24" s="5">
-        <v>46192.8897287963</v>
+        <v>46192.72306212963</v>
       </c>
       <c r="D24" s="5">
-        <v>46192.913113912036</v>
+        <v>46192.74644724537</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -2984,13 +2984,13 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46118.55564990741</v>
+        <v>46118.388983240744</v>
       </c>
       <c r="C25" s="9">
-        <v>46192.889863564815</v>
+        <v>46192.72319689815</v>
       </c>
       <c r="D25" s="9">
-        <v>46192.88986527778</v>
+        <v>46192.723198611115</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3045,13 +3045,13 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.555654606476</v>
+        <v>46118.38898793982</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.67901127315</v>
+        <v>46182.51234460648</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.67902225694</v>
+        <v>46182.51235559028</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3110,13 +3110,13 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46118.55565927083</v>
+        <v>46118.38899260417</v>
       </c>
       <c r="C27" s="9">
-        <v>46134.89289440972</v>
+        <v>46134.72622774306</v>
       </c>
       <c r="D27" s="9">
-        <v>46169.85540111111</v>
+        <v>46169.68873444444</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3171,13 +3171,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.55566380787</v>
+        <v>46118.3889971412</v>
       </c>
       <c r="C28" s="5">
-        <v>46182.67899732639</v>
+        <v>46182.51233065972</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.67899886574</v>
+        <v>46182.51233219907</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3232,13 +3232,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46118.55566881945</v>
+        <v>46118.38900215278</v>
       </c>
       <c r="C29" s="9">
-        <v>46134.892935428245</v>
+        <v>46134.72626876157</v>
       </c>
       <c r="D29" s="9">
-        <v>46169.85534873843</v>
+        <v>46169.68868207176</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3293,13 +3293,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.55567340278</v>
+        <v>46118.389006736106</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.67180701389</v>
+        <v>46181.50514034722</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.671818483796</v>
+        <v>46181.50515181713</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3358,13 +3358,13 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46118.55568293981</v>
+        <v>46118.38901627315</v>
       </c>
       <c r="C31" s="9">
-        <v>46181.671732048606</v>
+        <v>46181.50506538195</v>
       </c>
       <c r="D31" s="9">
-        <v>46181.671733344905</v>
+        <v>46181.50506667824</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3419,13 +3419,13 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.55568802083</v>
+        <v>46118.38902135417</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.671791875</v>
+        <v>46181.505125208336</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.67179341435</v>
+        <v>46181.50512674768</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3480,11 +3480,11 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46118.5554312037</v>
+        <v>46118.38876453704</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46135.50561945602</v>
+        <v>46135.33895278935</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3527,13 +3527,13 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.55573724537</v>
+        <v>46118.389070578705</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.856089803245</v>
+        <v>46134.68942313657</v>
       </c>
       <c r="D34" s="5">
-        <v>46134.856103495375</v>
+        <v>46134.6894368287</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3592,13 +3592,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46118.58934402778</v>
+        <v>46118.422677361115</v>
       </c>
       <c r="C35" s="9">
-        <v>46134.85589491898</v>
+        <v>46134.68922825232</v>
       </c>
       <c r="D35" s="9">
-        <v>46134.85589640046</v>
+        <v>46134.68922973379</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -3647,13 +3647,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.58935734954</v>
+        <v>46118.42269068287</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.85590363426</v>
+        <v>46134.68923696759</v>
       </c>
       <c r="D36" s="5">
-        <v>46134.855904895834</v>
+        <v>46134.68923822917</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3702,13 +3702,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46118.58936491898</v>
+        <v>46118.42269825231</v>
       </c>
       <c r="C37" s="9">
-        <v>46134.856064039355</v>
+        <v>46134.689397372684</v>
       </c>
       <c r="D37" s="9">
-        <v>46134.85606556713</v>
+        <v>46134.68939890046</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>140</v>
@@ -3757,13 +3757,13 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.58937265046</v>
+        <v>46118.4227059838</v>
       </c>
       <c r="C38" s="5">
-        <v>46134.8560703588</v>
+        <v>46134.68940369213</v>
       </c>
       <c r="D38" s="5">
-        <v>46134.85607190972</v>
+        <v>46134.68940524306</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3812,13 +3812,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46118.5893790625</v>
+        <v>46118.42271239583</v>
       </c>
       <c r="C39" s="9">
-        <v>46134.85607678241</v>
+        <v>46134.68941011574</v>
       </c>
       <c r="D39" s="9">
-        <v>46134.85607811343</v>
+        <v>46134.68941144676</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>140</v>
@@ -3867,13 +3867,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.55574388889</v>
+        <v>46118.38907722222</v>
       </c>
       <c r="C40" s="5">
-        <v>46135.505314317124</v>
+        <v>46135.33864765047</v>
       </c>
       <c r="D40" s="5">
-        <v>46135.52260231481</v>
+        <v>46135.35593564815</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3932,13 +3932,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="9">
-        <v>46118.58948621528</v>
+        <v>46118.42281954861</v>
       </c>
       <c r="C41" s="9">
-        <v>46135.505267789355</v>
+        <v>46135.33860112268</v>
       </c>
       <c r="D41" s="9">
-        <v>46135.50526961806</v>
+        <v>46135.33860295139</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>140</v>
@@ -3987,13 +3987,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.589619189814</v>
+        <v>46118.42295252315</v>
       </c>
       <c r="C42" s="5">
-        <v>46135.50527871528</v>
+        <v>46135.33861204861</v>
       </c>
       <c r="D42" s="5">
-        <v>46135.50528020834</v>
+        <v>46135.338613541666</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>140</v>
@@ -4042,13 +4042,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="9">
-        <v>46118.589635729164</v>
+        <v>46118.4229690625</v>
       </c>
       <c r="C43" s="9">
-        <v>46135.50528577546</v>
+        <v>46135.33861910879</v>
       </c>
       <c r="D43" s="9">
-        <v>46135.50528708333</v>
+        <v>46135.33862041667</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>155</v>
@@ -4097,13 +4097,13 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.58964931713</v>
+        <v>46118.42298265046</v>
       </c>
       <c r="C44" s="5">
-        <v>46135.50529321759</v>
+        <v>46135.338626550925</v>
       </c>
       <c r="D44" s="5">
-        <v>46135.50529516204</v>
+        <v>46135.338628495374</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>155</v>
@@ -4152,13 +4152,13 @@
         <v>157</v>
       </c>
       <c r="B45" s="9">
-        <v>46118.5896587037</v>
+        <v>46118.42299203704</v>
       </c>
       <c r="C45" s="9">
-        <v>46135.50530085649</v>
+        <v>46135.338634189815</v>
       </c>
       <c r="D45" s="9">
-        <v>46135.50530211805</v>
+        <v>46135.33863545139</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>140</v>
@@ -4207,13 +4207,13 @@
         <v>158</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.55575109954</v>
+        <v>46118.38908443287</v>
       </c>
       <c r="C46" s="5">
-        <v>46135.505592835645</v>
+        <v>46135.33892616898</v>
       </c>
       <c r="D46" s="5">
-        <v>46135.50560496528</v>
+        <v>46135.338938298606</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>81</v>
@@ -4272,13 +4272,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="9">
-        <v>46118.58972679398</v>
+        <v>46118.423060127316</v>
       </c>
       <c r="C47" s="9">
-        <v>46135.505553229166</v>
+        <v>46135.3388865625</v>
       </c>
       <c r="D47" s="9">
-        <v>46135.505555069445</v>
+        <v>46135.33888840278</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>140</v>
@@ -4325,13 +4325,13 @@
         <v>162</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.58974760417</v>
+        <v>46118.4230809375</v>
       </c>
       <c r="C48" s="5">
-        <v>46135.505559247686</v>
+        <v>46135.338892581014</v>
       </c>
       <c r="D48" s="5">
-        <v>46135.50556056713</v>
+        <v>46135.338893900465</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>140</v>
@@ -4378,13 +4378,13 @@
         <v>163</v>
       </c>
       <c r="B49" s="9">
-        <v>46118.58975269676</v>
+        <v>46118.42308603009</v>
       </c>
       <c r="C49" s="9">
-        <v>46135.505566527776</v>
+        <v>46135.33889986111</v>
       </c>
       <c r="D49" s="9">
-        <v>46135.50556795139</v>
+        <v>46135.33890128472</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>140</v>
@@ -4431,13 +4431,13 @@
         <v>164</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.58976391204</v>
+        <v>46118.423097245366</v>
       </c>
       <c r="C50" s="5">
-        <v>46135.505573229166</v>
+        <v>46135.3389065625</v>
       </c>
       <c r="D50" s="5">
-        <v>46135.50557504629</v>
+        <v>46135.33890837963</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>140</v>
@@ -4484,13 +4484,13 @@
         <v>165</v>
       </c>
       <c r="B51" s="9">
-        <v>46118.589758912036</v>
+        <v>46118.42309224537</v>
       </c>
       <c r="C51" s="9">
-        <v>46135.505581006946</v>
+        <v>46135.338914340275</v>
       </c>
       <c r="D51" s="9">
-        <v>46135.50558240741</v>
+        <v>46135.33891574074</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>140</v>
@@ -4537,11 +4537,11 @@
         <v>166</v>
       </c>
       <c r="B52" s="5">
-        <v>46118.55575893518</v>
+        <v>46118.38909226852</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46182.20622399305</v>
+        <v>46182.03955732639</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>167</v>
@@ -4600,11 +4600,11 @@
         <v>170</v>
       </c>
       <c r="B53" s="9">
-        <v>46118.589869131945</v>
+        <v>46118.423202465274</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46197.50794607639</v>
+        <v>46197.341279409724</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>140</v>
@@ -4653,11 +4653,11 @@
         <v>172</v>
       </c>
       <c r="B54" s="5">
-        <v>46118.589883333334</v>
+        <v>46118.42321666666</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46197.50794943287</v>
+        <v>46197.3412827662</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>140</v>
@@ -4706,11 +4706,11 @@
         <v>173</v>
       </c>
       <c r="B55" s="9">
-        <v>46118.589890312505</v>
+        <v>46118.423223645834</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46197.50795643518</v>
+        <v>46197.34128976852</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>140</v>
@@ -4759,11 +4759,11 @@
         <v>174</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.58992050926</v>
+        <v>46118.42325384259</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46181.168653182875</v>
+        <v>46181.0019865162</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>140</v>
@@ -4812,11 +4812,11 @@
         <v>175</v>
       </c>
       <c r="B57" s="9">
-        <v>46118.589899548606</v>
+        <v>46118.42323288195</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46181.168651678236</v>
+        <v>46181.00198501158</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>140</v>
@@ -4865,13 +4865,13 @@
         <v>176</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.55576480324</v>
+        <v>46118.38909813657</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.67196634259</v>
+        <v>46181.505299675926</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.67205032408</v>
+        <v>46181.50538365741</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>177</v>
@@ -4914,13 +4914,13 @@
         <v>179</v>
       </c>
       <c r="B59" s="9">
-        <v>46118.55576952547</v>
+        <v>46118.3891028588</v>
       </c>
       <c r="C59" s="9">
-        <v>46181.67190112268</v>
+        <v>46181.50523445602</v>
       </c>
       <c r="D59" s="9">
-        <v>46181.67191517361</v>
+        <v>46181.50524850695</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>180</v>
@@ -4979,13 +4979,13 @@
         <v>184</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.55577607639</v>
+        <v>46118.38910940972</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.671950752316</v>
+        <v>46181.50528408565</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.671966932874</v>
+        <v>46181.5053002662</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>185</v>
@@ -5044,11 +5044,11 @@
         <v>188</v>
       </c>
       <c r="B61" s="9">
-        <v>46118.55578122685</v>
+        <v>46118.38911456018</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46191.710350381945</v>
+        <v>46191.54368371528</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>189</v>
@@ -5093,13 +5093,13 @@
         <v>192</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.55578460648</v>
+        <v>46118.38911793982</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.672212314814</v>
+        <v>46181.50554564815</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.67222788194</v>
+        <v>46181.50556121528</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>193</v>
@@ -5158,13 +5158,13 @@
         <v>197</v>
       </c>
       <c r="B63" s="9">
-        <v>46118.555790115744</v>
+        <v>46118.38912344907</v>
       </c>
       <c r="C63" s="9">
-        <v>46191.71033274305</v>
+        <v>46191.54366607639</v>
       </c>
       <c r="D63" s="9">
-        <v>46191.71034409722</v>
+        <v>46191.543677430556</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>198</v>
@@ -5223,13 +5223,13 @@
         <v>199</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.59005789352</v>
+        <v>46118.423391226854</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.6723374537</v>
+        <v>46181.50567078704</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.672338564815</v>
+        <v>46181.50567189815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>140</v>
@@ -5278,13 +5278,13 @@
         <v>202</v>
       </c>
       <c r="B65" s="9">
-        <v>46118.590067604164</v>
+        <v>46118.4234009375</v>
       </c>
       <c r="C65" s="9">
-        <v>46181.672350925925</v>
+        <v>46181.50568425926</v>
       </c>
       <c r="D65" s="9">
-        <v>46181.672352442125</v>
+        <v>46181.50568577547</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>140</v>
@@ -5333,13 +5333,13 @@
         <v>204</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.5900759838</v>
+        <v>46118.423409317125</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.67236503473</v>
+        <v>46181.505698368055</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.672366307874</v>
+        <v>46181.5056996412</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>140</v>
@@ -5388,13 +5388,13 @@
         <v>205</v>
       </c>
       <c r="B67" s="9">
-        <v>46118.590097962966</v>
+        <v>46118.423431296294</v>
       </c>
       <c r="C67" s="9">
-        <v>46191.71030983796</v>
+        <v>46191.543643171295</v>
       </c>
       <c r="D67" s="9">
-        <v>46191.71031108796</v>
+        <v>46191.5436444213</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>140</v>
@@ -5443,13 +5443,13 @@
         <v>206</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.59010253473</v>
+        <v>46118.423435868055</v>
       </c>
       <c r="C68" s="5">
-        <v>46191.71031711806</v>
+        <v>46191.54365045139</v>
       </c>
       <c r="D68" s="5">
-        <v>46191.710318530095</v>
+        <v>46191.54365186342</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>140</v>
@@ -5498,13 +5498,13 @@
         <v>207</v>
       </c>
       <c r="B69" s="9">
-        <v>46118.55579684028</v>
+        <v>46118.389130173615</v>
       </c>
       <c r="C69" s="9">
-        <v>46191.70935185185</v>
+        <v>46191.54268518518</v>
       </c>
       <c r="D69" s="9">
-        <v>46191.709365358794</v>
+        <v>46191.54269869213</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>208</v>
@@ -5563,13 +5563,13 @@
         <v>209</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.59015388889</v>
+        <v>46118.42348722222</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.67244342592</v>
+        <v>46181.50577675926</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.67244473379</v>
+        <v>46181.505778067134</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>140</v>
@@ -5618,13 +5618,13 @@
         <v>212</v>
       </c>
       <c r="B71" s="9">
-        <v>46118.59016236111</v>
+        <v>46118.42349569444</v>
       </c>
       <c r="C71" s="9">
-        <v>46181.672456597225</v>
+        <v>46181.505789930554</v>
       </c>
       <c r="D71" s="9">
-        <v>46181.672458078705</v>
+        <v>46181.50579141204</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>140</v>
@@ -5673,13 +5673,13 @@
         <v>213</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.59017135417</v>
+        <v>46118.4235046875</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.67246365741</v>
+        <v>46181.505796990736</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.672464999996</v>
+        <v>46181.50579833333</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>140</v>
@@ -5728,13 +5728,13 @@
         <v>214</v>
       </c>
       <c r="B73" s="9">
-        <v>46118.59019241898</v>
+        <v>46118.42352575231</v>
       </c>
       <c r="C73" s="9">
-        <v>46191.70928226852</v>
+        <v>46191.54261560185</v>
       </c>
       <c r="D73" s="9">
-        <v>46191.7103152662</v>
+        <v>46191.54364859954</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>140</v>
@@ -5783,13 +5783,13 @@
         <v>215</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.590197488425</v>
+        <v>46118.42353082176</v>
       </c>
       <c r="C74" s="5">
-        <v>46191.70933641204</v>
+        <v>46191.542669745366</v>
       </c>
       <c r="D74" s="5">
-        <v>46191.7103265162</v>
+        <v>46191.543659849536</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>140</v>
@@ -5838,11 +5838,11 @@
         <v>216</v>
       </c>
       <c r="B75" s="9">
-        <v>46118.55580327546</v>
+        <v>46118.38913660879</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46118.58538233796</v>
+        <v>46118.4187156713</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>177</v>
@@ -5885,11 +5885,11 @@
         <v>218</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.55580685185</v>
+        <v>46118.38914018519</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46182.67872560185</v>
+        <v>46182.512058935186</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>219</v>
@@ -5946,11 +5946,11 @@
         <v>221</v>
       </c>
       <c r="B77" s="9">
-        <v>46118.55581320602</v>
+        <v>46118.38914653935</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46192.88988357639</v>
+        <v>46192.723216909726</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>222</v>
@@ -6007,11 +6007,11 @@
         <v>223</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.55581936342</v>
+        <v>46118.38915269676</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.67901537037</v>
+        <v>46182.512348703705</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>224</v>
@@ -6068,11 +6068,11 @@
         <v>225</v>
       </c>
       <c r="B79" s="9">
-        <v>46118.55582516204</v>
+        <v>46118.38915849537</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.50782400463</v>
+        <v>46197.34115733796</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>226</v>
@@ -6115,13 +6115,13 @@
         <v>228</v>
       </c>
       <c r="B80" s="5">
-        <v>46118.55582877315</v>
+        <v>46118.38916210648</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.4232071875</v>
+        <v>46197.25654052083</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.42322075232</v>
+        <v>46197.256554085645</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>229</v>
@@ -6180,13 +6180,13 @@
         <v>230</v>
       </c>
       <c r="B81" s="9">
-        <v>46118.590250625</v>
+        <v>46118.423583958334</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.42301266204</v>
+        <v>46197.25634599537</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.423014942135</v>
+        <v>46197.25634827546</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>140</v>
@@ -6235,13 +6235,13 @@
         <v>232</v>
       </c>
       <c r="B82" s="5">
-        <v>46118.590259641205</v>
+        <v>46118.423592974534</v>
       </c>
       <c r="C82" s="5">
-        <v>46197.42305077546</v>
+        <v>46197.2563841088</v>
       </c>
       <c r="D82" s="5">
-        <v>46197.42305252315</v>
+        <v>46197.25638585648</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>140</v>
@@ -6290,13 +6290,13 @@
         <v>233</v>
       </c>
       <c r="B83" s="9">
-        <v>46118.59026761574</v>
+        <v>46118.42360094907</v>
       </c>
       <c r="C83" s="9">
-        <v>46197.423102430555</v>
+        <v>46197.25643576389</v>
       </c>
       <c r="D83" s="9">
-        <v>46197.42310400463</v>
+        <v>46197.256437337965</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>140</v>
@@ -6345,13 +6345,13 @@
         <v>234</v>
       </c>
       <c r="B84" s="5">
-        <v>46118.590275636576</v>
+        <v>46118.42360896991</v>
       </c>
       <c r="C84" s="5">
-        <v>46197.42314728009</v>
+        <v>46197.256480613425</v>
       </c>
       <c r="D84" s="5">
-        <v>46197.423148842594</v>
+        <v>46197.25648217593</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>140</v>
@@ -6400,13 +6400,13 @@
         <v>235</v>
       </c>
       <c r="B85" s="9">
-        <v>46118.59028430555</v>
+        <v>46118.42361763889</v>
       </c>
       <c r="C85" s="9">
-        <v>46197.42319270833</v>
+        <v>46197.25652604167</v>
       </c>
       <c r="D85" s="9">
-        <v>46197.42319425926</v>
+        <v>46197.25652759259</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>140</v>
@@ -6455,11 +6455,11 @@
         <v>236</v>
       </c>
       <c r="B86" s="5">
-        <v>46118.55583459491</v>
+        <v>46118.38916792824</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46197.609448206014</v>
+        <v>46197.44278153935</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>237</v>
@@ -6518,13 +6518,13 @@
         <v>238</v>
       </c>
       <c r="B87" s="9">
-        <v>46118.59033478009</v>
+        <v>46118.42366811342</v>
       </c>
       <c r="C87" s="9">
-        <v>46197.50709427083</v>
+        <v>46197.34042760417</v>
       </c>
       <c r="D87" s="9">
-        <v>46197.50709627315</v>
+        <v>46197.340429606484</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>140</v>
@@ -6571,13 +6571,13 @@
         <v>241</v>
       </c>
       <c r="B88" s="5">
-        <v>46118.59034447916</v>
+        <v>46118.423677812505</v>
       </c>
       <c r="C88" s="5">
-        <v>46197.50715157407</v>
+        <v>46197.34048490741</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.507152997685</v>
+        <v>46197.34048633101</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>140</v>
@@ -6624,13 +6624,13 @@
         <v>242</v>
       </c>
       <c r="B89" s="9">
-        <v>46118.590352141204</v>
+        <v>46118.42368547454</v>
       </c>
       <c r="C89" s="9">
-        <v>46197.50723920139</v>
+        <v>46197.340572534726</v>
       </c>
       <c r="D89" s="9">
-        <v>46197.50724237268</v>
+        <v>46197.34057570602</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>140</v>
@@ -6677,11 +6677,11 @@
         <v>243</v>
       </c>
       <c r="B90" s="5">
-        <v>46118.59035967593</v>
+        <v>46118.42369300926</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46197.609442534726</v>
+        <v>46197.442775868054</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>140</v>
@@ -6728,11 +6728,11 @@
         <v>244</v>
       </c>
       <c r="B91" s="9">
-        <v>46118.59036834491</v>
+        <v>46118.42370167824</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46197.42320116898</v>
+        <v>46197.25653450232</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>140</v>
@@ -6779,13 +6779,13 @@
         <v>245</v>
       </c>
       <c r="B92" s="5">
-        <v>46118.55584244213</v>
+        <v>46118.38917577546</v>
       </c>
       <c r="C92" s="5">
-        <v>46197.50781607639</v>
+        <v>46197.34114940972</v>
       </c>
       <c r="D92" s="5">
-        <v>46197.50782737268</v>
+        <v>46197.34116070602</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>246</v>
@@ -6842,13 +6842,13 @@
         <v>247</v>
       </c>
       <c r="B93" s="9">
-        <v>46118.59042068287</v>
+        <v>46118.4237540162</v>
       </c>
       <c r="C93" s="9">
-        <v>46197.50749427083</v>
+        <v>46197.34082760417</v>
       </c>
       <c r="D93" s="9">
-        <v>46197.50749574074</v>
+        <v>46197.34082907408</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>140</v>
@@ -6895,13 +6895,13 @@
         <v>250</v>
       </c>
       <c r="B94" s="5">
-        <v>46118.5904280324</v>
+        <v>46118.423761365746</v>
       </c>
       <c r="C94" s="5">
-        <v>46197.507576828706</v>
+        <v>46197.340910162035</v>
       </c>
       <c r="D94" s="5">
-        <v>46197.50757840278</v>
+        <v>46197.340911736115</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>140</v>
@@ -6948,13 +6948,13 @@
         <v>251</v>
       </c>
       <c r="B95" s="9">
-        <v>46118.59044465278</v>
+        <v>46118.423777986114</v>
       </c>
       <c r="C95" s="9">
-        <v>46197.50767422454</v>
+        <v>46197.34100755787</v>
       </c>
       <c r="D95" s="9">
-        <v>46197.60944782407</v>
+        <v>46197.442781157406</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>140</v>
@@ -7001,13 +7001,13 @@
         <v>252</v>
       </c>
       <c r="B96" s="5">
-        <v>46118.5904391088</v>
+        <v>46118.423772442125</v>
       </c>
       <c r="C96" s="5">
-        <v>46197.50773788194</v>
+        <v>46197.341071215276</v>
       </c>
       <c r="D96" s="5">
-        <v>46197.50773945602</v>
+        <v>46197.34107278935</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>140</v>
@@ -7054,13 +7054,13 @@
         <v>253</v>
       </c>
       <c r="B97" s="9">
-        <v>46118.59045233796</v>
+        <v>46118.4237856713</v>
       </c>
       <c r="C97" s="9">
-        <v>46197.507801064814</v>
+        <v>46197.34113439815</v>
       </c>
       <c r="D97" s="9">
-        <v>46197.50780251157</v>
+        <v>46197.34113584491</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>140</v>
@@ -7107,11 +7107,11 @@
         <v>254</v>
       </c>
       <c r="B98" s="5">
-        <v>46118.55584987269</v>
+        <v>46118.38918320602</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46197.42458010417</v>
+        <v>46197.2579134375</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>255</v>
@@ -7168,13 +7168,13 @@
         <v>256</v>
       </c>
       <c r="B99" s="9">
-        <v>46118.590539282406</v>
+        <v>46118.42387261574</v>
       </c>
       <c r="C99" s="9">
-        <v>46197.42437898148</v>
+        <v>46197.257712314815</v>
       </c>
       <c r="D99" s="9">
-        <v>46197.50749940972</v>
+        <v>46197.34083274305</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>140</v>
@@ -7221,13 +7221,13 @@
         <v>259</v>
       </c>
       <c r="B100" s="5">
-        <v>46118.590546666666</v>
+        <v>46118.42388</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.42449445602</v>
+        <v>46197.25782778935</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.50758304398</v>
+        <v>46197.34091637732</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>140</v>
@@ -7274,13 +7274,13 @@
         <v>261</v>
       </c>
       <c r="B101" s="9">
-        <v>46118.590554027774</v>
+        <v>46118.42388736111</v>
       </c>
       <c r="C101" s="9">
-        <v>46197.42457260417</v>
+        <v>46197.2579059375</v>
       </c>
       <c r="D101" s="9">
-        <v>46197.50774366898</v>
+        <v>46197.34107700232</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>140</v>
@@ -7327,11 +7327,11 @@
         <v>263</v>
       </c>
       <c r="B102" s="5">
-        <v>46118.59056115741</v>
+        <v>46118.42389449074</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46197.507679953706</v>
+        <v>46197.341013287034</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>140</v>
@@ -7378,11 +7378,11 @@
         <v>264</v>
       </c>
       <c r="B103" s="9">
-        <v>46118.590569293985</v>
+        <v>46118.42390262731</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46197.50781008102</v>
+        <v>46197.34114341435</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>140</v>
@@ -7429,11 +7429,11 @@
         <v>265</v>
       </c>
       <c r="B104" s="5">
-        <v>46118.5558574537</v>
+        <v>46118.38919078704</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46197.507954988425</v>
+        <v>46197.34128832176</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>266</v>
@@ -7492,13 +7492,13 @@
         <v>267</v>
       </c>
       <c r="B105" s="9">
-        <v>46118.5906265625</v>
+        <v>46118.42395989584</v>
       </c>
       <c r="C105" s="9">
-        <v>46197.50793775463</v>
+        <v>46197.341271087964</v>
       </c>
       <c r="D105" s="9">
-        <v>46197.50793939814</v>
+        <v>46197.341272731486</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>140</v>
@@ -7545,13 +7545,13 @@
         <v>269</v>
       </c>
       <c r="B106" s="5">
-        <v>46118.59063387732</v>
+        <v>46118.42396721065</v>
       </c>
       <c r="C106" s="5">
-        <v>46197.507942592594</v>
+        <v>46197.34127592592</v>
       </c>
       <c r="D106" s="5">
-        <v>46197.5079440625</v>
+        <v>46197.34127739583</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>140</v>
@@ -7598,13 +7598,13 @@
         <v>270</v>
       </c>
       <c r="B107" s="9">
-        <v>46118.590655486114</v>
+        <v>46118.42398881944</v>
       </c>
       <c r="C107" s="9">
-        <v>46197.507947488426</v>
+        <v>46197.341280821754</v>
       </c>
       <c r="D107" s="9">
-        <v>46197.50794915509</v>
+        <v>46197.34128248843</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>140</v>
@@ -7651,11 +7651,11 @@
         <v>271</v>
       </c>
       <c r="B108" s="5">
-        <v>46118.59066162037</v>
+        <v>46118.4239949537</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46178.16914135417</v>
+        <v>46178.0024746875</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>140</v>
@@ -7702,11 +7702,11 @@
         <v>272</v>
       </c>
       <c r="B109" s="9">
-        <v>46118.59066710648</v>
+        <v>46118.424000439816</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46178.16914265046</v>
+        <v>46178.0024759838</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>140</v>
@@ -7753,11 +7753,11 @@
         <v>273</v>
       </c>
       <c r="B110" s="5">
-        <v>46118.55591270833</v>
+        <v>46118.38924604167</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46183.194774386575</v>
+        <v>46183.0281077199</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>274</v>
@@ -7814,11 +7814,11 @@
         <v>276</v>
       </c>
       <c r="B111" s="9">
-        <v>46118.590705243056</v>
+        <v>46118.424038576384</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46182.168110810184</v>
+        <v>46182.00144414352</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>140</v>
@@ -7867,11 +7867,11 @@
         <v>278</v>
       </c>
       <c r="B112" s="5">
-        <v>46118.59071275463</v>
+        <v>46118.42404608797</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.1681121875</v>
+        <v>46182.00144552083</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>140</v>
@@ -7920,11 +7920,11 @@
         <v>279</v>
       </c>
       <c r="B113" s="9">
-        <v>46118.590720092594</v>
+        <v>46118.42405342593</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46182.16811331018</v>
+        <v>46182.00144664352</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>140</v>
@@ -7973,11 +7973,11 @@
         <v>280</v>
       </c>
       <c r="B114" s="5">
-        <v>46118.590727835646</v>
+        <v>46118.42406116898</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.16811451389</v>
+        <v>46182.00144784722</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>140</v>
@@ -8026,11 +8026,11 @@
         <v>281</v>
       </c>
       <c r="B115" s="9">
-        <v>46118.59073534722</v>
+        <v>46118.42406868056</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46182.16811570602</v>
+        <v>46182.00144903935</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>140</v>
@@ -8079,11 +8079,11 @@
         <v>282</v>
       </c>
       <c r="B116" s="5">
-        <v>46118.55591954861</v>
+        <v>46118.38925288194</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46118.63950689815</v>
+        <v>46118.47284023148</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>283</v>
@@ -8126,11 +8126,11 @@
         <v>285</v>
       </c>
       <c r="B117" s="9">
-        <v>46118.555923148146</v>
+        <v>46118.38925648148</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46184.18063726852</v>
+        <v>46184.01397060185</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>286</v>
@@ -8187,11 +8187,11 @@
         <v>289</v>
       </c>
       <c r="B118" s="5">
-        <v>46118.590793020834</v>
+        <v>46118.42412635416</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46183.16824416666</v>
+        <v>46183.0015775</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>140</v>
@@ -8238,11 +8238,11 @@
         <v>290</v>
       </c>
       <c r="B119" s="9">
-        <v>46118.59080049768</v>
+        <v>46118.424133831024</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46183.16824571759</v>
+        <v>46183.00157905092</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>140</v>
@@ -8289,11 +8289,11 @@
         <v>291</v>
       </c>
       <c r="B120" s="5">
-        <v>46118.59080680556</v>
+        <v>46118.424140138886</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46183.168246875</v>
+        <v>46183.001580208336</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>140</v>
@@ -8340,11 +8340,11 @@
         <v>292</v>
       </c>
       <c r="B121" s="9">
-        <v>46118.59081555555</v>
+        <v>46118.42414888889</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46183.16824814815</v>
+        <v>46183.00158148148</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>140</v>
@@ -8391,11 +8391,11 @@
         <v>293</v>
       </c>
       <c r="B122" s="5">
-        <v>46118.590822777776</v>
+        <v>46118.42415611111</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46183.16824943287</v>
+        <v>46183.0015827662</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>140</v>
@@ -8442,11 +8442,11 @@
         <v>294</v>
       </c>
       <c r="B123" s="9">
-        <v>46118.55592798611</v>
+        <v>46118.38926131945</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46185.17432103009</v>
+        <v>46185.00765436343</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>295</v>
@@ -8503,11 +8503,11 @@
         <v>297</v>
       </c>
       <c r="B124" s="5">
-        <v>46118.59087519676</v>
+        <v>46118.424208530094</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46184.168032511574</v>
+        <v>46184.0013658449</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>140</v>
@@ -8554,11 +8554,11 @@
         <v>299</v>
       </c>
       <c r="B125" s="9">
-        <v>46118.590883240744</v>
+        <v>46118.42421657407</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46184.168034201386</v>
+        <v>46184.00136753472</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>140</v>
@@ -8605,11 +8605,11 @@
         <v>300</v>
       </c>
       <c r="B126" s="5">
-        <v>46118.59089157407</v>
+        <v>46118.42422490741</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46184.16803541667</v>
+        <v>46184.00136875</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>140</v>
@@ -8656,11 +8656,11 @@
         <v>301</v>
       </c>
       <c r="B127" s="9">
-        <v>46118.590897835646</v>
+        <v>46118.42423116898</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46184.168036863426</v>
+        <v>46184.001370196755</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>155</v>
@@ -8707,11 +8707,11 @@
         <v>302</v>
       </c>
       <c r="B128" s="5">
-        <v>46118.5909049537</v>
+        <v>46118.424238287036</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46184.16803811342</v>
+        <v>46184.001371446764</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>155</v>
@@ -8758,11 +8758,11 @@
         <v>303</v>
       </c>
       <c r="B129" s="9">
-        <v>46118.555932511576</v>
+        <v>46118.389265844904</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46186.16794060185</v>
+        <v>46186.00127393518</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>304</v>
@@ -8819,11 +8819,11 @@
         <v>305</v>
       </c>
       <c r="B130" s="5">
-        <v>46118.59095414352</v>
+        <v>46118.42428747685</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46185.168594965275</v>
+        <v>46185.00192829861</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>140</v>
@@ -8870,11 +8870,11 @@
         <v>307</v>
       </c>
       <c r="B131" s="9">
-        <v>46118.590966759264</v>
+        <v>46118.42430009259</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46185.16859673611</v>
+        <v>46185.00193006944</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>140</v>
@@ -8921,11 +8921,11 @@
         <v>308</v>
       </c>
       <c r="B132" s="5">
-        <v>46118.590973796294</v>
+        <v>46118.42430712963</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46185.168597951386</v>
+        <v>46185.00193128472</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>140</v>
@@ -8972,11 +8972,11 @@
         <v>309</v>
       </c>
       <c r="B133" s="9">
-        <v>46118.590979953704</v>
+        <v>46118.42431328703</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46185.16859903935</v>
+        <v>46185.00193237269</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>140</v>
@@ -9023,11 +9023,11 @@
         <v>310</v>
       </c>
       <c r="B134" s="5">
-        <v>46118.59098489583</v>
+        <v>46118.42431822917</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46185.16860023148</v>
+        <v>46185.00193356481</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>140</v>
@@ -9074,11 +9074,11 @@
         <v>311</v>
       </c>
       <c r="B135" s="9">
-        <v>46118.55593715278</v>
+        <v>46118.38927048611</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46189.2078791088</v>
+        <v>46189.04121244213</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>312</v>
@@ -9135,11 +9135,11 @@
         <v>314</v>
       </c>
       <c r="B136" s="5">
-        <v>46118.59103105324</v>
+        <v>46118.42436438658</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46188.168568113426</v>
+        <v>46188.001901446754</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>140</v>
@@ -9186,11 +9186,11 @@
         <v>315</v>
       </c>
       <c r="B137" s="9">
-        <v>46118.591039039355</v>
+        <v>46118.42437237268</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46188.16856979167</v>
+        <v>46188.001903125</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>140</v>
@@ -9237,11 +9237,11 @@
         <v>316</v>
       </c>
       <c r="B138" s="5">
-        <v>46118.59104641204</v>
+        <v>46118.42437974537</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46188.168570995374</v>
+        <v>46188.0019043287</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>140</v>
@@ -9288,11 +9288,11 @@
         <v>317</v>
       </c>
       <c r="B139" s="9">
-        <v>46118.59105258102</v>
+        <v>46118.42438591435</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46188.1685722338</v>
+        <v>46188.00190556713</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>140</v>
@@ -9339,11 +9339,11 @@
         <v>318</v>
       </c>
       <c r="B140" s="5">
-        <v>46118.59105829861</v>
+        <v>46118.42439163194</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46188.16857356481</v>
+        <v>46188.00190689815</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>140</v>
@@ -9390,11 +9390,11 @@
         <v>319</v>
       </c>
       <c r="B141" s="9">
-        <v>46118.55594259259</v>
+        <v>46118.389275925925</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46118.64758575232</v>
+        <v>46118.48091908565</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>320</v>
@@ -9437,11 +9437,11 @@
         <v>322</v>
       </c>
       <c r="B142" s="5">
-        <v>46118.55594550926</v>
+        <v>46118.38927884259</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46197.1681475</v>
+        <v>46197.001480833336</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>323</v>
@@ -9500,11 +9500,11 @@
         <v>327</v>
       </c>
       <c r="B143" s="9">
-        <v>46118.55595019676</v>
+        <v>46118.389283530094</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46197.168156134256</v>
+        <v>46197.00148946759</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>328</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1689,13 +1689,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.38873709491</v>
+        <v>46118.55540376157</v>
       </c>
       <c r="C4" s="5">
-        <v>46134.683067569444</v>
+        <v>46134.84973423611</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.683078692135</v>
+        <v>46134.84974535879</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1742,13 +1742,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46118.38890262731</v>
+        <v>46118.55556929398</v>
       </c>
       <c r="C5" s="9">
-        <v>46134.68074246528</v>
+        <v>46134.847409131944</v>
       </c>
       <c r="D5" s="9">
-        <v>46134.680787986115</v>
+        <v>46134.84745465278</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1805,13 +1805,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.388906099535</v>
+        <v>46118.5555727662</v>
       </c>
       <c r="C6" s="5">
-        <v>46134.68150766204</v>
+        <v>46134.848174328705</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.681521516206</v>
+        <v>46134.84818818287</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1868,13 +1868,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="9">
-        <v>46118.38890895833</v>
+        <v>46118.555575624996</v>
       </c>
       <c r="C7" s="9">
-        <v>46134.68180517361</v>
+        <v>46134.848471840276</v>
       </c>
       <c r="D7" s="9">
-        <v>46134.68181967593</v>
+        <v>46134.84848634259</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>40</v>
@@ -1931,13 +1931,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.38891162037</v>
+        <v>46118.555578287036</v>
       </c>
       <c r="C8" s="5">
-        <v>46134.68256634259</v>
+        <v>46134.849233009256</v>
       </c>
       <c r="D8" s="5">
-        <v>46191.543463124995</v>
+        <v>46191.71012979167</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1994,13 +1994,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="9">
-        <v>46118.38891502315</v>
+        <v>46118.55558168981</v>
       </c>
       <c r="C9" s="9">
-        <v>46134.683053368055</v>
+        <v>46134.84972003472</v>
       </c>
       <c r="D9" s="9">
-        <v>46134.683068425926</v>
+        <v>46134.84973509259</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>47</v>
@@ -2057,13 +2057,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.38874427084</v>
+        <v>46118.5554109375</v>
       </c>
       <c r="C10" s="5">
-        <v>46192.74659246528</v>
+        <v>46192.91325913194</v>
       </c>
       <c r="D10" s="5">
-        <v>46192.74660916667</v>
+        <v>46192.91327583333</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2110,13 +2110,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="9">
-        <v>46118.38891834491</v>
+        <v>46118.55558501158</v>
       </c>
       <c r="C11" s="9">
-        <v>46134.68486908565</v>
+        <v>46134.851535752314</v>
       </c>
       <c r="D11" s="9">
-        <v>46171.74395131944</v>
+        <v>46171.91061798611</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>52</v>
@@ -2175,13 +2175,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.38892319445</v>
+        <v>46118.55558986111</v>
       </c>
       <c r="C12" s="5">
-        <v>46134.6842277199</v>
+        <v>46134.850894386575</v>
       </c>
       <c r="D12" s="5">
-        <v>46134.684243125</v>
+        <v>46134.85090979167</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2240,13 +2240,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46118.388928368055</v>
+        <v>46118.55559503472</v>
       </c>
       <c r="C13" s="9">
-        <v>46134.683779224535</v>
+        <v>46134.85044589121</v>
       </c>
       <c r="D13" s="9">
-        <v>46134.683796840276</v>
+        <v>46134.85046350694</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2305,13 +2305,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.388750972226</v>
+        <v>46118.55541763889</v>
       </c>
       <c r="C14" s="5">
-        <v>46192.74645232639</v>
+        <v>46192.913118993056</v>
       </c>
       <c r="D14" s="5">
-        <v>46192.74647372685</v>
+        <v>46192.91314039352</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2358,13 +2358,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46118.38893851852</v>
+        <v>46118.55560518519</v>
       </c>
       <c r="C15" s="9">
-        <v>46134.685348425926</v>
+        <v>46134.85201509259</v>
       </c>
       <c r="D15" s="9">
-        <v>46134.6853625463</v>
+        <v>46134.85202921296</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2423,13 +2423,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.38894379629</v>
+        <v>46118.555610462965</v>
       </c>
       <c r="C16" s="5">
-        <v>46192.74643533565</v>
+        <v>46192.91310200232</v>
       </c>
       <c r="D16" s="5">
-        <v>46192.746437256945</v>
+        <v>46192.91310392361</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2488,13 +2488,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46118.388948912034</v>
+        <v>46118.555615578705</v>
       </c>
       <c r="C17" s="9">
-        <v>46134.68573056713</v>
+        <v>46134.8523972338</v>
       </c>
       <c r="D17" s="9">
-        <v>46134.68574652778</v>
+        <v>46134.85241319444</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2553,13 +2553,13 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.388954560185</v>
+        <v>46118.55562122686</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.5050077662</v>
+        <v>46181.67167443287</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.50502488426</v>
+        <v>46181.671691550924</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2618,13 +2618,13 @@
         <v>84</v>
       </c>
       <c r="B19" s="9">
-        <v>46118.388759016205</v>
+        <v>46118.55542568287</v>
       </c>
       <c r="C19" s="9">
-        <v>46192.74662535879</v>
+        <v>46192.91329202546</v>
       </c>
       <c r="D19" s="9">
-        <v>46192.746641736114</v>
+        <v>46192.91330840278</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>85</v>
@@ -2671,13 +2671,13 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.388960254626</v>
+        <v>46118.5556269213</v>
       </c>
       <c r="C20" s="5">
-        <v>46182.51205171296</v>
+        <v>46182.678718379626</v>
       </c>
       <c r="D20" s="5">
-        <v>46182.51206596065</v>
+        <v>46182.67873262732</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -2736,13 +2736,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="9">
-        <v>46118.38896474537</v>
+        <v>46118.55563141203</v>
       </c>
       <c r="C21" s="9">
-        <v>46155.73059027777</v>
+        <v>46155.897256944445</v>
       </c>
       <c r="D21" s="9">
-        <v>46169.68891788194</v>
+        <v>46169.85558454861</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>93</v>
@@ -2797,13 +2797,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.38896940972</v>
+        <v>46118.55563607639</v>
       </c>
       <c r="C22" s="5">
-        <v>46182.512035775464</v>
+        <v>46182.67870244213</v>
       </c>
       <c r="D22" s="5">
-        <v>46182.51203774306</v>
+        <v>46182.67870440972</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -2858,13 +2858,13 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46118.38897395833</v>
+        <v>46118.555640624996</v>
       </c>
       <c r="C23" s="9">
-        <v>46192.72321162037</v>
+        <v>46192.88987828704</v>
       </c>
       <c r="D23" s="9">
-        <v>46192.72322681713</v>
+        <v>46192.88989348379</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -2923,13 +2923,13 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.38897876158</v>
+        <v>46118.55564542824</v>
       </c>
       <c r="C24" s="5">
-        <v>46192.72306212963</v>
+        <v>46192.8897287963</v>
       </c>
       <c r="D24" s="5">
-        <v>46192.74644724537</v>
+        <v>46192.913113912036</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -2984,13 +2984,13 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46118.388983240744</v>
+        <v>46118.55564990741</v>
       </c>
       <c r="C25" s="9">
-        <v>46192.72319689815</v>
+        <v>46192.889863564815</v>
       </c>
       <c r="D25" s="9">
-        <v>46192.723198611115</v>
+        <v>46192.88986527778</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3045,13 +3045,13 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.38898793982</v>
+        <v>46118.555654606476</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.51234460648</v>
+        <v>46182.67901127315</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.51235559028</v>
+        <v>46182.67902225694</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3110,13 +3110,13 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46118.38899260417</v>
+        <v>46118.55565927083</v>
       </c>
       <c r="C27" s="9">
-        <v>46134.72622774306</v>
+        <v>46134.89289440972</v>
       </c>
       <c r="D27" s="9">
-        <v>46169.68873444444</v>
+        <v>46169.85540111111</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3171,13 +3171,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.3889971412</v>
+        <v>46118.55566380787</v>
       </c>
       <c r="C28" s="5">
-        <v>46182.51233065972</v>
+        <v>46182.67899732639</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.51233219907</v>
+        <v>46182.67899886574</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3232,13 +3232,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46118.38900215278</v>
+        <v>46118.55566881945</v>
       </c>
       <c r="C29" s="9">
-        <v>46134.72626876157</v>
+        <v>46134.892935428245</v>
       </c>
       <c r="D29" s="9">
-        <v>46169.68868207176</v>
+        <v>46169.85534873843</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3293,13 +3293,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.389006736106</v>
+        <v>46118.55567340278</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.50514034722</v>
+        <v>46181.67180701389</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.50515181713</v>
+        <v>46181.671818483796</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3358,13 +3358,13 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46118.38901627315</v>
+        <v>46118.55568293981</v>
       </c>
       <c r="C31" s="9">
-        <v>46181.50506538195</v>
+        <v>46181.671732048606</v>
       </c>
       <c r="D31" s="9">
-        <v>46181.50506667824</v>
+        <v>46181.671733344905</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3419,13 +3419,13 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.38902135417</v>
+        <v>46118.55568802083</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.505125208336</v>
+        <v>46181.671791875</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.50512674768</v>
+        <v>46181.67179341435</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3480,11 +3480,11 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46118.38876453704</v>
+        <v>46118.5554312037</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46135.33895278935</v>
+        <v>46135.50561945602</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3527,13 +3527,13 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.389070578705</v>
+        <v>46118.55573724537</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.68942313657</v>
+        <v>46134.856089803245</v>
       </c>
       <c r="D34" s="5">
-        <v>46134.6894368287</v>
+        <v>46134.856103495375</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3592,13 +3592,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46118.422677361115</v>
+        <v>46118.58934402778</v>
       </c>
       <c r="C35" s="9">
-        <v>46134.68922825232</v>
+        <v>46134.85589491898</v>
       </c>
       <c r="D35" s="9">
-        <v>46134.68922973379</v>
+        <v>46134.85589640046</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -3647,13 +3647,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.42269068287</v>
+        <v>46118.58935734954</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.68923696759</v>
+        <v>46134.85590363426</v>
       </c>
       <c r="D36" s="5">
-        <v>46134.68923822917</v>
+        <v>46134.855904895834</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3702,13 +3702,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46118.42269825231</v>
+        <v>46118.58936491898</v>
       </c>
       <c r="C37" s="9">
-        <v>46134.689397372684</v>
+        <v>46134.856064039355</v>
       </c>
       <c r="D37" s="9">
-        <v>46134.68939890046</v>
+        <v>46134.85606556713</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>140</v>
@@ -3757,13 +3757,13 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.4227059838</v>
+        <v>46118.58937265046</v>
       </c>
       <c r="C38" s="5">
-        <v>46134.68940369213</v>
+        <v>46134.8560703588</v>
       </c>
       <c r="D38" s="5">
-        <v>46134.68940524306</v>
+        <v>46134.85607190972</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3812,13 +3812,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46118.42271239583</v>
+        <v>46118.5893790625</v>
       </c>
       <c r="C39" s="9">
-        <v>46134.68941011574</v>
+        <v>46134.85607678241</v>
       </c>
       <c r="D39" s="9">
-        <v>46134.68941144676</v>
+        <v>46134.85607811343</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>140</v>
@@ -3867,13 +3867,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.38907722222</v>
+        <v>46118.55574388889</v>
       </c>
       <c r="C40" s="5">
-        <v>46135.33864765047</v>
+        <v>46135.505314317124</v>
       </c>
       <c r="D40" s="5">
-        <v>46135.35593564815</v>
+        <v>46135.52260231481</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3932,13 +3932,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="9">
-        <v>46118.42281954861</v>
+        <v>46118.58948621528</v>
       </c>
       <c r="C41" s="9">
-        <v>46135.33860112268</v>
+        <v>46135.505267789355</v>
       </c>
       <c r="D41" s="9">
-        <v>46135.33860295139</v>
+        <v>46135.50526961806</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>140</v>
@@ -3987,13 +3987,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.42295252315</v>
+        <v>46118.589619189814</v>
       </c>
       <c r="C42" s="5">
-        <v>46135.33861204861</v>
+        <v>46135.50527871528</v>
       </c>
       <c r="D42" s="5">
-        <v>46135.338613541666</v>
+        <v>46135.50528020834</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>140</v>
@@ -4042,13 +4042,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="9">
-        <v>46118.4229690625</v>
+        <v>46118.589635729164</v>
       </c>
       <c r="C43" s="9">
-        <v>46135.33861910879</v>
+        <v>46135.50528577546</v>
       </c>
       <c r="D43" s="9">
-        <v>46135.33862041667</v>
+        <v>46135.50528708333</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>155</v>
@@ -4097,13 +4097,13 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.42298265046</v>
+        <v>46118.58964931713</v>
       </c>
       <c r="C44" s="5">
-        <v>46135.338626550925</v>
+        <v>46135.50529321759</v>
       </c>
       <c r="D44" s="5">
-        <v>46135.338628495374</v>
+        <v>46135.50529516204</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>155</v>
@@ -4152,13 +4152,13 @@
         <v>157</v>
       </c>
       <c r="B45" s="9">
-        <v>46118.42299203704</v>
+        <v>46118.5896587037</v>
       </c>
       <c r="C45" s="9">
-        <v>46135.338634189815</v>
+        <v>46135.50530085649</v>
       </c>
       <c r="D45" s="9">
-        <v>46135.33863545139</v>
+        <v>46135.50530211805</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>140</v>
@@ -4207,13 +4207,13 @@
         <v>158</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.38908443287</v>
+        <v>46118.55575109954</v>
       </c>
       <c r="C46" s="5">
-        <v>46135.33892616898</v>
+        <v>46135.505592835645</v>
       </c>
       <c r="D46" s="5">
-        <v>46135.338938298606</v>
+        <v>46135.50560496528</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>81</v>
@@ -4272,13 +4272,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="9">
-        <v>46118.423060127316</v>
+        <v>46118.58972679398</v>
       </c>
       <c r="C47" s="9">
-        <v>46135.3388865625</v>
+        <v>46135.505553229166</v>
       </c>
       <c r="D47" s="9">
-        <v>46135.33888840278</v>
+        <v>46135.505555069445</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>140</v>
@@ -4325,13 +4325,13 @@
         <v>162</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.4230809375</v>
+        <v>46118.58974760417</v>
       </c>
       <c r="C48" s="5">
-        <v>46135.338892581014</v>
+        <v>46135.505559247686</v>
       </c>
       <c r="D48" s="5">
-        <v>46135.338893900465</v>
+        <v>46135.50556056713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>140</v>
@@ -4378,13 +4378,13 @@
         <v>163</v>
       </c>
       <c r="B49" s="9">
-        <v>46118.42308603009</v>
+        <v>46118.58975269676</v>
       </c>
       <c r="C49" s="9">
-        <v>46135.33889986111</v>
+        <v>46135.505566527776</v>
       </c>
       <c r="D49" s="9">
-        <v>46135.33890128472</v>
+        <v>46135.50556795139</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>140</v>
@@ -4431,13 +4431,13 @@
         <v>164</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.423097245366</v>
+        <v>46118.58976391204</v>
       </c>
       <c r="C50" s="5">
-        <v>46135.3389065625</v>
+        <v>46135.505573229166</v>
       </c>
       <c r="D50" s="5">
-        <v>46135.33890837963</v>
+        <v>46135.50557504629</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>140</v>
@@ -4484,13 +4484,13 @@
         <v>165</v>
       </c>
       <c r="B51" s="9">
-        <v>46118.42309224537</v>
+        <v>46118.589758912036</v>
       </c>
       <c r="C51" s="9">
-        <v>46135.338914340275</v>
+        <v>46135.505581006946</v>
       </c>
       <c r="D51" s="9">
-        <v>46135.33891574074</v>
+        <v>46135.50558240741</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>140</v>
@@ -4537,11 +4537,11 @@
         <v>166</v>
       </c>
       <c r="B52" s="5">
-        <v>46118.38909226852</v>
+        <v>46118.55575893518</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46182.03955732639</v>
+        <v>46182.20622399305</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>167</v>
@@ -4600,11 +4600,11 @@
         <v>170</v>
       </c>
       <c r="B53" s="9">
-        <v>46118.423202465274</v>
+        <v>46118.589869131945</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46197.341279409724</v>
+        <v>46197.50794607639</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>140</v>
@@ -4653,11 +4653,11 @@
         <v>172</v>
       </c>
       <c r="B54" s="5">
-        <v>46118.42321666666</v>
+        <v>46118.589883333334</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46197.3412827662</v>
+        <v>46197.50794943287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>140</v>
@@ -4706,11 +4706,11 @@
         <v>173</v>
       </c>
       <c r="B55" s="9">
-        <v>46118.423223645834</v>
+        <v>46118.589890312505</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46197.34128976852</v>
+        <v>46197.50795643518</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>140</v>
@@ -4759,11 +4759,11 @@
         <v>174</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.42325384259</v>
+        <v>46118.58992050926</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46181.0019865162</v>
+        <v>46181.168653182875</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>140</v>
@@ -4812,11 +4812,11 @@
         <v>175</v>
       </c>
       <c r="B57" s="9">
-        <v>46118.42323288195</v>
+        <v>46118.589899548606</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46181.00198501158</v>
+        <v>46181.168651678236</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>140</v>
@@ -4865,13 +4865,13 @@
         <v>176</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.38909813657</v>
+        <v>46118.55576480324</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.505299675926</v>
+        <v>46181.67196634259</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.50538365741</v>
+        <v>46181.67205032408</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>177</v>
@@ -4914,13 +4914,13 @@
         <v>179</v>
       </c>
       <c r="B59" s="9">
-        <v>46118.3891028588</v>
+        <v>46118.55576952547</v>
       </c>
       <c r="C59" s="9">
-        <v>46181.50523445602</v>
+        <v>46181.67190112268</v>
       </c>
       <c r="D59" s="9">
-        <v>46181.50524850695</v>
+        <v>46181.67191517361</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>180</v>
@@ -4979,13 +4979,13 @@
         <v>184</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.38910940972</v>
+        <v>46118.55577607639</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.50528408565</v>
+        <v>46181.671950752316</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.5053002662</v>
+        <v>46181.671966932874</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>185</v>
@@ -5044,11 +5044,11 @@
         <v>188</v>
       </c>
       <c r="B61" s="9">
-        <v>46118.38911456018</v>
+        <v>46118.55578122685</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46191.54368371528</v>
+        <v>46191.710350381945</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>189</v>
@@ -5093,13 +5093,13 @@
         <v>192</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.38911793982</v>
+        <v>46118.55578460648</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50554564815</v>
+        <v>46181.672212314814</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.50556121528</v>
+        <v>46181.67222788194</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>193</v>
@@ -5158,13 +5158,13 @@
         <v>197</v>
       </c>
       <c r="B63" s="9">
-        <v>46118.38912344907</v>
+        <v>46118.555790115744</v>
       </c>
       <c r="C63" s="9">
-        <v>46191.54366607639</v>
+        <v>46191.71033274305</v>
       </c>
       <c r="D63" s="9">
-        <v>46191.543677430556</v>
+        <v>46191.71034409722</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>198</v>
@@ -5223,13 +5223,13 @@
         <v>199</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.423391226854</v>
+        <v>46118.59005789352</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.50567078704</v>
+        <v>46181.6723374537</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.50567189815</v>
+        <v>46181.672338564815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>140</v>
@@ -5278,13 +5278,13 @@
         <v>202</v>
       </c>
       <c r="B65" s="9">
-        <v>46118.4234009375</v>
+        <v>46118.590067604164</v>
       </c>
       <c r="C65" s="9">
-        <v>46181.50568425926</v>
+        <v>46181.672350925925</v>
       </c>
       <c r="D65" s="9">
-        <v>46181.50568577547</v>
+        <v>46181.672352442125</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>140</v>
@@ -5333,13 +5333,13 @@
         <v>204</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.423409317125</v>
+        <v>46118.5900759838</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.505698368055</v>
+        <v>46181.67236503473</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.5056996412</v>
+        <v>46181.672366307874</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>140</v>
@@ -5388,13 +5388,13 @@
         <v>205</v>
       </c>
       <c r="B67" s="9">
-        <v>46118.423431296294</v>
+        <v>46118.590097962966</v>
       </c>
       <c r="C67" s="9">
-        <v>46191.543643171295</v>
+        <v>46191.71030983796</v>
       </c>
       <c r="D67" s="9">
-        <v>46191.5436444213</v>
+        <v>46191.71031108796</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>140</v>
@@ -5443,13 +5443,13 @@
         <v>206</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.423435868055</v>
+        <v>46118.59010253473</v>
       </c>
       <c r="C68" s="5">
-        <v>46191.54365045139</v>
+        <v>46191.71031711806</v>
       </c>
       <c r="D68" s="5">
-        <v>46191.54365186342</v>
+        <v>46191.710318530095</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>140</v>
@@ -5498,13 +5498,13 @@
         <v>207</v>
       </c>
       <c r="B69" s="9">
-        <v>46118.389130173615</v>
+        <v>46118.55579684028</v>
       </c>
       <c r="C69" s="9">
-        <v>46191.54268518518</v>
+        <v>46191.70935185185</v>
       </c>
       <c r="D69" s="9">
-        <v>46191.54269869213</v>
+        <v>46191.709365358794</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>208</v>
@@ -5563,13 +5563,13 @@
         <v>209</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.42348722222</v>
+        <v>46118.59015388889</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.50577675926</v>
+        <v>46181.67244342592</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.505778067134</v>
+        <v>46181.67244473379</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>140</v>
@@ -5618,13 +5618,13 @@
         <v>212</v>
       </c>
       <c r="B71" s="9">
-        <v>46118.42349569444</v>
+        <v>46118.59016236111</v>
       </c>
       <c r="C71" s="9">
-        <v>46181.505789930554</v>
+        <v>46181.672456597225</v>
       </c>
       <c r="D71" s="9">
-        <v>46181.50579141204</v>
+        <v>46181.672458078705</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>140</v>
@@ -5673,13 +5673,13 @@
         <v>213</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.4235046875</v>
+        <v>46118.59017135417</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.505796990736</v>
+        <v>46181.67246365741</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.50579833333</v>
+        <v>46181.672464999996</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>140</v>
@@ -5728,13 +5728,13 @@
         <v>214</v>
       </c>
       <c r="B73" s="9">
-        <v>46118.42352575231</v>
+        <v>46118.59019241898</v>
       </c>
       <c r="C73" s="9">
-        <v>46191.54261560185</v>
+        <v>46191.70928226852</v>
       </c>
       <c r="D73" s="9">
-        <v>46191.54364859954</v>
+        <v>46191.7103152662</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>140</v>
@@ -5783,13 +5783,13 @@
         <v>215</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.42353082176</v>
+        <v>46118.590197488425</v>
       </c>
       <c r="C74" s="5">
-        <v>46191.542669745366</v>
+        <v>46191.70933641204</v>
       </c>
       <c r="D74" s="5">
-        <v>46191.543659849536</v>
+        <v>46191.7103265162</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>140</v>
@@ -5838,11 +5838,11 @@
         <v>216</v>
       </c>
       <c r="B75" s="9">
-        <v>46118.38913660879</v>
+        <v>46118.55580327546</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46118.4187156713</v>
+        <v>46118.58538233796</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>177</v>
@@ -5885,11 +5885,11 @@
         <v>218</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.38914018519</v>
+        <v>46118.55580685185</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46182.512058935186</v>
+        <v>46182.67872560185</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>219</v>
@@ -5946,11 +5946,11 @@
         <v>221</v>
       </c>
       <c r="B77" s="9">
-        <v>46118.38914653935</v>
+        <v>46118.55581320602</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46192.723216909726</v>
+        <v>46192.88988357639</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>222</v>
@@ -6007,11 +6007,11 @@
         <v>223</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.38915269676</v>
+        <v>46118.55581936342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.512348703705</v>
+        <v>46182.67901537037</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>224</v>
@@ -6068,11 +6068,11 @@
         <v>225</v>
       </c>
       <c r="B79" s="9">
-        <v>46118.38915849537</v>
+        <v>46118.55582516204</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.34115733796</v>
+        <v>46197.50782400463</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>226</v>
@@ -6115,13 +6115,13 @@
         <v>228</v>
       </c>
       <c r="B80" s="5">
-        <v>46118.38916210648</v>
+        <v>46118.55582877315</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.25654052083</v>
+        <v>46197.4232071875</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.256554085645</v>
+        <v>46197.42322075232</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>229</v>
@@ -6180,13 +6180,13 @@
         <v>230</v>
       </c>
       <c r="B81" s="9">
-        <v>46118.423583958334</v>
+        <v>46118.590250625</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.25634599537</v>
+        <v>46197.42301266204</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.25634827546</v>
+        <v>46197.423014942135</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>140</v>
@@ -6235,13 +6235,13 @@
         <v>232</v>
       </c>
       <c r="B82" s="5">
-        <v>46118.423592974534</v>
+        <v>46118.590259641205</v>
       </c>
       <c r="C82" s="5">
-        <v>46197.2563841088</v>
+        <v>46197.42305077546</v>
       </c>
       <c r="D82" s="5">
-        <v>46197.25638585648</v>
+        <v>46197.42305252315</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>140</v>
@@ -6290,13 +6290,13 @@
         <v>233</v>
       </c>
       <c r="B83" s="9">
-        <v>46118.42360094907</v>
+        <v>46118.59026761574</v>
       </c>
       <c r="C83" s="9">
-        <v>46197.25643576389</v>
+        <v>46197.423102430555</v>
       </c>
       <c r="D83" s="9">
-        <v>46197.256437337965</v>
+        <v>46197.42310400463</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>140</v>
@@ -6345,13 +6345,13 @@
         <v>234</v>
       </c>
       <c r="B84" s="5">
-        <v>46118.42360896991</v>
+        <v>46118.590275636576</v>
       </c>
       <c r="C84" s="5">
-        <v>46197.256480613425</v>
+        <v>46197.42314728009</v>
       </c>
       <c r="D84" s="5">
-        <v>46197.25648217593</v>
+        <v>46197.423148842594</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>140</v>
@@ -6400,13 +6400,13 @@
         <v>235</v>
       </c>
       <c r="B85" s="9">
-        <v>46118.42361763889</v>
+        <v>46118.59028430555</v>
       </c>
       <c r="C85" s="9">
-        <v>46197.25652604167</v>
+        <v>46197.42319270833</v>
       </c>
       <c r="D85" s="9">
-        <v>46197.25652759259</v>
+        <v>46197.42319425926</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>140</v>
@@ -6455,11 +6455,11 @@
         <v>236</v>
       </c>
       <c r="B86" s="5">
-        <v>46118.38916792824</v>
+        <v>46118.55583459491</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46197.44278153935</v>
+        <v>46197.609448206014</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>237</v>
@@ -6518,13 +6518,13 @@
         <v>238</v>
       </c>
       <c r="B87" s="9">
-        <v>46118.42366811342</v>
+        <v>46118.59033478009</v>
       </c>
       <c r="C87" s="9">
-        <v>46197.34042760417</v>
+        <v>46197.50709427083</v>
       </c>
       <c r="D87" s="9">
-        <v>46197.340429606484</v>
+        <v>46197.50709627315</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>140</v>
@@ -6571,13 +6571,13 @@
         <v>241</v>
       </c>
       <c r="B88" s="5">
-        <v>46118.423677812505</v>
+        <v>46118.59034447916</v>
       </c>
       <c r="C88" s="5">
-        <v>46197.34048490741</v>
+        <v>46197.50715157407</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.34048633101</v>
+        <v>46197.507152997685</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>140</v>
@@ -6624,13 +6624,13 @@
         <v>242</v>
       </c>
       <c r="B89" s="9">
-        <v>46118.42368547454</v>
+        <v>46118.590352141204</v>
       </c>
       <c r="C89" s="9">
-        <v>46197.340572534726</v>
+        <v>46197.50723920139</v>
       </c>
       <c r="D89" s="9">
-        <v>46197.34057570602</v>
+        <v>46197.50724237268</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>140</v>
@@ -6677,11 +6677,11 @@
         <v>243</v>
       </c>
       <c r="B90" s="5">
-        <v>46118.42369300926</v>
+        <v>46118.59035967593</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46197.442775868054</v>
+        <v>46197.609442534726</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>140</v>
@@ -6728,11 +6728,11 @@
         <v>244</v>
       </c>
       <c r="B91" s="9">
-        <v>46118.42370167824</v>
+        <v>46118.59036834491</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46197.25653450232</v>
+        <v>46197.42320116898</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>140</v>
@@ -6779,13 +6779,13 @@
         <v>245</v>
       </c>
       <c r="B92" s="5">
-        <v>46118.38917577546</v>
+        <v>46118.55584244213</v>
       </c>
       <c r="C92" s="5">
-        <v>46197.34114940972</v>
+        <v>46197.50781607639</v>
       </c>
       <c r="D92" s="5">
-        <v>46197.34116070602</v>
+        <v>46197.50782737268</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>246</v>
@@ -6842,13 +6842,13 @@
         <v>247</v>
       </c>
       <c r="B93" s="9">
-        <v>46118.4237540162</v>
+        <v>46118.59042068287</v>
       </c>
       <c r="C93" s="9">
-        <v>46197.34082760417</v>
+        <v>46197.50749427083</v>
       </c>
       <c r="D93" s="9">
-        <v>46197.34082907408</v>
+        <v>46197.50749574074</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>140</v>
@@ -6895,13 +6895,13 @@
         <v>250</v>
       </c>
       <c r="B94" s="5">
-        <v>46118.423761365746</v>
+        <v>46118.5904280324</v>
       </c>
       <c r="C94" s="5">
-        <v>46197.340910162035</v>
+        <v>46197.507576828706</v>
       </c>
       <c r="D94" s="5">
-        <v>46197.340911736115</v>
+        <v>46197.50757840278</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>140</v>
@@ -6948,13 +6948,13 @@
         <v>251</v>
       </c>
       <c r="B95" s="9">
-        <v>46118.423777986114</v>
+        <v>46118.59044465278</v>
       </c>
       <c r="C95" s="9">
-        <v>46197.34100755787</v>
+        <v>46197.50767422454</v>
       </c>
       <c r="D95" s="9">
-        <v>46197.442781157406</v>
+        <v>46197.60944782407</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>140</v>
@@ -7001,13 +7001,13 @@
         <v>252</v>
       </c>
       <c r="B96" s="5">
-        <v>46118.423772442125</v>
+        <v>46118.5904391088</v>
       </c>
       <c r="C96" s="5">
-        <v>46197.341071215276</v>
+        <v>46197.50773788194</v>
       </c>
       <c r="D96" s="5">
-        <v>46197.34107278935</v>
+        <v>46197.50773945602</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>140</v>
@@ -7054,13 +7054,13 @@
         <v>253</v>
       </c>
       <c r="B97" s="9">
-        <v>46118.4237856713</v>
+        <v>46118.59045233796</v>
       </c>
       <c r="C97" s="9">
-        <v>46197.34113439815</v>
+        <v>46197.507801064814</v>
       </c>
       <c r="D97" s="9">
-        <v>46197.34113584491</v>
+        <v>46197.50780251157</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>140</v>
@@ -7107,11 +7107,11 @@
         <v>254</v>
       </c>
       <c r="B98" s="5">
-        <v>46118.38918320602</v>
+        <v>46118.55584987269</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46197.2579134375</v>
+        <v>46197.42458010417</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>255</v>
@@ -7168,13 +7168,13 @@
         <v>256</v>
       </c>
       <c r="B99" s="9">
-        <v>46118.42387261574</v>
+        <v>46118.590539282406</v>
       </c>
       <c r="C99" s="9">
-        <v>46197.257712314815</v>
+        <v>46197.42437898148</v>
       </c>
       <c r="D99" s="9">
-        <v>46197.34083274305</v>
+        <v>46197.50749940972</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>140</v>
@@ -7221,13 +7221,13 @@
         <v>259</v>
       </c>
       <c r="B100" s="5">
-        <v>46118.42388</v>
+        <v>46118.590546666666</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.25782778935</v>
+        <v>46197.42449445602</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.34091637732</v>
+        <v>46197.50758304398</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>140</v>
@@ -7274,13 +7274,13 @@
         <v>261</v>
       </c>
       <c r="B101" s="9">
-        <v>46118.42388736111</v>
+        <v>46118.590554027774</v>
       </c>
       <c r="C101" s="9">
-        <v>46197.2579059375</v>
+        <v>46197.42457260417</v>
       </c>
       <c r="D101" s="9">
-        <v>46197.34107700232</v>
+        <v>46197.50774366898</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>140</v>
@@ -7327,11 +7327,11 @@
         <v>263</v>
       </c>
       <c r="B102" s="5">
-        <v>46118.42389449074</v>
+        <v>46118.59056115741</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46197.341013287034</v>
+        <v>46197.507679953706</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>140</v>
@@ -7378,11 +7378,11 @@
         <v>264</v>
       </c>
       <c r="B103" s="9">
-        <v>46118.42390262731</v>
+        <v>46118.590569293985</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46197.34114341435</v>
+        <v>46197.50781008102</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>140</v>
@@ -7429,11 +7429,11 @@
         <v>265</v>
       </c>
       <c r="B104" s="5">
-        <v>46118.38919078704</v>
+        <v>46118.5558574537</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46197.34128832176</v>
+        <v>46197.507954988425</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>266</v>
@@ -7492,13 +7492,13 @@
         <v>267</v>
       </c>
       <c r="B105" s="9">
-        <v>46118.42395989584</v>
+        <v>46118.5906265625</v>
       </c>
       <c r="C105" s="9">
-        <v>46197.341271087964</v>
+        <v>46197.50793775463</v>
       </c>
       <c r="D105" s="9">
-        <v>46197.341272731486</v>
+        <v>46197.50793939814</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>140</v>
@@ -7545,13 +7545,13 @@
         <v>269</v>
       </c>
       <c r="B106" s="5">
-        <v>46118.42396721065</v>
+        <v>46118.59063387732</v>
       </c>
       <c r="C106" s="5">
-        <v>46197.34127592592</v>
+        <v>46197.507942592594</v>
       </c>
       <c r="D106" s="5">
-        <v>46197.34127739583</v>
+        <v>46197.5079440625</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>140</v>
@@ -7598,13 +7598,13 @@
         <v>270</v>
       </c>
       <c r="B107" s="9">
-        <v>46118.42398881944</v>
+        <v>46118.590655486114</v>
       </c>
       <c r="C107" s="9">
-        <v>46197.341280821754</v>
+        <v>46197.507947488426</v>
       </c>
       <c r="D107" s="9">
-        <v>46197.34128248843</v>
+        <v>46197.50794915509</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>140</v>
@@ -7651,11 +7651,11 @@
         <v>271</v>
       </c>
       <c r="B108" s="5">
-        <v>46118.4239949537</v>
+        <v>46118.59066162037</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46178.0024746875</v>
+        <v>46178.16914135417</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>140</v>
@@ -7702,11 +7702,11 @@
         <v>272</v>
       </c>
       <c r="B109" s="9">
-        <v>46118.424000439816</v>
+        <v>46118.59066710648</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46178.0024759838</v>
+        <v>46178.16914265046</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>140</v>
@@ -7753,11 +7753,11 @@
         <v>273</v>
       </c>
       <c r="B110" s="5">
-        <v>46118.38924604167</v>
+        <v>46118.55591270833</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46183.0281077199</v>
+        <v>46183.194774386575</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>274</v>
@@ -7814,11 +7814,11 @@
         <v>276</v>
       </c>
       <c r="B111" s="9">
-        <v>46118.424038576384</v>
+        <v>46118.590705243056</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46182.00144414352</v>
+        <v>46182.168110810184</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>140</v>
@@ -7867,11 +7867,11 @@
         <v>278</v>
       </c>
       <c r="B112" s="5">
-        <v>46118.42404608797</v>
+        <v>46118.59071275463</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.00144552083</v>
+        <v>46182.1681121875</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>140</v>
@@ -7920,11 +7920,11 @@
         <v>279</v>
       </c>
       <c r="B113" s="9">
-        <v>46118.42405342593</v>
+        <v>46118.590720092594</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46182.00144664352</v>
+        <v>46182.16811331018</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>140</v>
@@ -7973,11 +7973,11 @@
         <v>280</v>
       </c>
       <c r="B114" s="5">
-        <v>46118.42406116898</v>
+        <v>46118.590727835646</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.00144784722</v>
+        <v>46182.16811451389</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>140</v>
@@ -8026,11 +8026,11 @@
         <v>281</v>
       </c>
       <c r="B115" s="9">
-        <v>46118.42406868056</v>
+        <v>46118.59073534722</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46182.00144903935</v>
+        <v>46182.16811570602</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>140</v>
@@ -8079,11 +8079,11 @@
         <v>282</v>
       </c>
       <c r="B116" s="5">
-        <v>46118.38925288194</v>
+        <v>46118.55591954861</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46118.47284023148</v>
+        <v>46118.63950689815</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>283</v>
@@ -8126,11 +8126,11 @@
         <v>285</v>
       </c>
       <c r="B117" s="9">
-        <v>46118.38925648148</v>
+        <v>46118.555923148146</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46184.01397060185</v>
+        <v>46184.18063726852</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>286</v>
@@ -8187,11 +8187,11 @@
         <v>289</v>
       </c>
       <c r="B118" s="5">
-        <v>46118.42412635416</v>
+        <v>46118.590793020834</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46183.0015775</v>
+        <v>46183.16824416666</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>140</v>
@@ -8238,11 +8238,11 @@
         <v>290</v>
       </c>
       <c r="B119" s="9">
-        <v>46118.424133831024</v>
+        <v>46118.59080049768</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46183.00157905092</v>
+        <v>46183.16824571759</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>140</v>
@@ -8289,11 +8289,11 @@
         <v>291</v>
       </c>
       <c r="B120" s="5">
-        <v>46118.424140138886</v>
+        <v>46118.59080680556</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46183.001580208336</v>
+        <v>46183.168246875</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>140</v>
@@ -8340,11 +8340,11 @@
         <v>292</v>
       </c>
       <c r="B121" s="9">
-        <v>46118.42414888889</v>
+        <v>46118.59081555555</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46183.00158148148</v>
+        <v>46183.16824814815</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>140</v>
@@ -8391,11 +8391,11 @@
         <v>293</v>
       </c>
       <c r="B122" s="5">
-        <v>46118.42415611111</v>
+        <v>46118.590822777776</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46183.0015827662</v>
+        <v>46183.16824943287</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>140</v>
@@ -8442,11 +8442,11 @@
         <v>294</v>
       </c>
       <c r="B123" s="9">
-        <v>46118.38926131945</v>
+        <v>46118.55592798611</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46185.00765436343</v>
+        <v>46185.17432103009</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>295</v>
@@ -8503,11 +8503,11 @@
         <v>297</v>
       </c>
       <c r="B124" s="5">
-        <v>46118.424208530094</v>
+        <v>46118.59087519676</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46184.0013658449</v>
+        <v>46184.168032511574</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>140</v>
@@ -8554,11 +8554,11 @@
         <v>299</v>
       </c>
       <c r="B125" s="9">
-        <v>46118.42421657407</v>
+        <v>46118.590883240744</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46184.00136753472</v>
+        <v>46184.168034201386</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>140</v>
@@ -8605,11 +8605,11 @@
         <v>300</v>
       </c>
       <c r="B126" s="5">
-        <v>46118.42422490741</v>
+        <v>46118.59089157407</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46184.00136875</v>
+        <v>46184.16803541667</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>140</v>
@@ -8656,11 +8656,11 @@
         <v>301</v>
       </c>
       <c r="B127" s="9">
-        <v>46118.42423116898</v>
+        <v>46118.590897835646</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46184.001370196755</v>
+        <v>46184.168036863426</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>155</v>
@@ -8707,11 +8707,11 @@
         <v>302</v>
       </c>
       <c r="B128" s="5">
-        <v>46118.424238287036</v>
+        <v>46118.5909049537</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46184.001371446764</v>
+        <v>46184.16803811342</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>155</v>
@@ -8758,11 +8758,11 @@
         <v>303</v>
       </c>
       <c r="B129" s="9">
-        <v>46118.389265844904</v>
+        <v>46118.555932511576</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46186.00127393518</v>
+        <v>46186.16794060185</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>304</v>
@@ -8819,11 +8819,11 @@
         <v>305</v>
       </c>
       <c r="B130" s="5">
-        <v>46118.42428747685</v>
+        <v>46118.59095414352</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46185.00192829861</v>
+        <v>46185.168594965275</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>140</v>
@@ -8870,11 +8870,11 @@
         <v>307</v>
       </c>
       <c r="B131" s="9">
-        <v>46118.42430009259</v>
+        <v>46118.590966759264</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46185.00193006944</v>
+        <v>46185.16859673611</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>140</v>
@@ -8921,11 +8921,11 @@
         <v>308</v>
       </c>
       <c r="B132" s="5">
-        <v>46118.42430712963</v>
+        <v>46118.590973796294</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46185.00193128472</v>
+        <v>46185.168597951386</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>140</v>
@@ -8972,11 +8972,11 @@
         <v>309</v>
       </c>
       <c r="B133" s="9">
-        <v>46118.42431328703</v>
+        <v>46118.590979953704</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46185.00193237269</v>
+        <v>46185.16859903935</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>140</v>
@@ -9023,11 +9023,11 @@
         <v>310</v>
       </c>
       <c r="B134" s="5">
-        <v>46118.42431822917</v>
+        <v>46118.59098489583</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46185.00193356481</v>
+        <v>46185.16860023148</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>140</v>
@@ -9074,11 +9074,11 @@
         <v>311</v>
       </c>
       <c r="B135" s="9">
-        <v>46118.38927048611</v>
+        <v>46118.55593715278</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46189.04121244213</v>
+        <v>46189.2078791088</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>312</v>
@@ -9135,11 +9135,11 @@
         <v>314</v>
       </c>
       <c r="B136" s="5">
-        <v>46118.42436438658</v>
+        <v>46118.59103105324</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46188.001901446754</v>
+        <v>46188.168568113426</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>140</v>
@@ -9186,11 +9186,11 @@
         <v>315</v>
       </c>
       <c r="B137" s="9">
-        <v>46118.42437237268</v>
+        <v>46118.591039039355</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46188.001903125</v>
+        <v>46188.16856979167</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>140</v>
@@ -9237,11 +9237,11 @@
         <v>316</v>
       </c>
       <c r="B138" s="5">
-        <v>46118.42437974537</v>
+        <v>46118.59104641204</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46188.0019043287</v>
+        <v>46188.168570995374</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>140</v>
@@ -9288,11 +9288,11 @@
         <v>317</v>
       </c>
       <c r="B139" s="9">
-        <v>46118.42438591435</v>
+        <v>46118.59105258102</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46188.00190556713</v>
+        <v>46188.1685722338</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>140</v>
@@ -9339,11 +9339,11 @@
         <v>318</v>
       </c>
       <c r="B140" s="5">
-        <v>46118.42439163194</v>
+        <v>46118.59105829861</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46188.00190689815</v>
+        <v>46188.16857356481</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>140</v>
@@ -9390,11 +9390,11 @@
         <v>319</v>
       </c>
       <c r="B141" s="9">
-        <v>46118.389275925925</v>
+        <v>46118.55594259259</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46118.48091908565</v>
+        <v>46118.64758575232</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>320</v>
@@ -9437,11 +9437,11 @@
         <v>322</v>
       </c>
       <c r="B142" s="5">
-        <v>46118.38927884259</v>
+        <v>46118.55594550926</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46197.001480833336</v>
+        <v>46197.1681475</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>323</v>
@@ -9500,11 +9500,11 @@
         <v>327</v>
       </c>
       <c r="B143" s="9">
-        <v>46118.389283530094</v>
+        <v>46118.55595019676</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46197.00148946759</v>
+        <v>46197.168156134256</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>328</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -651,94 +651,94 @@
     <t>Control de calidad Armado,Preparación Materiales,Armado</t>
   </si>
   <si>
+    <t>1213964514187677</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,Caldereria:</t>
+  </si>
+  <si>
+    <t>1213963044098529</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1213955238648425</t>
+  </si>
+  <si>
+    <t>OT 4280 ZVN 1-9-63/2,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Armado,OT 4280 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1213955238648426</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4280 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1213955238648427</t>
+  </si>
+  <si>
+    <t>1213955238648428</t>
+  </si>
+  <si>
+    <t>1213955238648429</t>
+  </si>
+  <si>
+    <t>1213955244950397</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213955238648430</t>
+  </si>
+  <si>
+    <t>OT 4280 ZVN 1-9-63/2,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4280 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1213955238648431</t>
+  </si>
+  <si>
+    <t>1213955238648432</t>
+  </si>
+  <si>
+    <t>1213955238648433</t>
+  </si>
+  <si>
+    <t>1213955238648434</t>
+  </si>
+  <si>
+    <t>1213955244950422</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion Rodete,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213955244951637</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,Bodega:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213964514187677</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213963044098529</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1213955238648425</t>
-  </si>
-  <si>
-    <t>OT 4280 ZVN 1-9-63/2,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Armado,OT 4280 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1213955238648426</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4280 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1213955238648427</t>
-  </si>
-  <si>
-    <t>1213955238648428</t>
-  </si>
-  <si>
-    <t>1213955238648429</t>
-  </si>
-  <si>
-    <t>1213955244950397</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213955238648430</t>
-  </si>
-  <si>
-    <t>OT 4280 ZVN 1-9-63/2,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4280 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1213955238648431</t>
-  </si>
-  <si>
-    <t>1213955238648432</t>
-  </si>
-  <si>
-    <t>1213955238648433</t>
-  </si>
-  <si>
-    <t>1213955238648434</t>
-  </si>
-  <si>
-    <t>1213955244950422</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion Rodete,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213955244951637</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,Bodega:</t>
   </si>
   <si>
     <t>1213955244951657</t>
@@ -5046,9 +5046,11 @@
       <c r="B61" s="9">
         <v>46118.55578122685</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46197.775929456024</v>
+      </c>
       <c r="D61" s="9">
-        <v>46191.710350381945</v>
+        <v>46197.77594626158</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>189</v>
@@ -5083,14 +5085,16 @@
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
       <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="12" t="s">
-        <v>191</v>
+      <c r="T61" s="10">
+        <v>1</v>
+      </c>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B62" s="5">
         <v>46118.55578460648</v>
@@ -5102,16 +5106,16 @@
         <v>46181.67222788194</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I62" s="5">
         <v>46155</v>
@@ -5135,7 +5139,7 @@
         <v>180</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q62" s="5">
         <v>46157</v>
@@ -5155,7 +5159,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B63" s="9">
         <v>46118.555790115744</v>
@@ -5167,16 +5171,16 @@
         <v>46191.71034409722</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I63" s="9">
         <v>46160</v>
@@ -5220,7 +5224,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B64" s="5">
         <v>46118.59005789352</v>
@@ -5238,10 +5242,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I64" s="5">
         <v>46160</v>
@@ -5259,13 +5263,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5275,7 +5279,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B65" s="9">
         <v>46118.590067604164</v>
@@ -5293,10 +5297,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I65" s="9">
         <v>46160</v>
@@ -5314,13 +5318,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5330,7 +5334,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B66" s="5">
         <v>46118.5900759838</v>
@@ -5348,10 +5352,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I66" s="5">
         <v>46160</v>
@@ -5369,13 +5373,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5385,7 +5389,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B67" s="9">
         <v>46118.590097962966</v>
@@ -5403,10 +5407,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I67" s="9">
         <v>46160</v>
@@ -5424,13 +5428,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5440,7 +5444,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B68" s="5">
         <v>46118.59010253473</v>
@@ -5458,10 +5462,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I68" s="5">
         <v>46160</v>
@@ -5479,13 +5483,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5495,7 +5499,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B69" s="9">
         <v>46118.55579684028</v>
@@ -5507,16 +5511,16 @@
         <v>46191.709365358794</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I69" s="9">
         <v>46167</v>
@@ -5560,7 +5564,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B70" s="5">
         <v>46118.59015388889</v>
@@ -5578,10 +5582,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I70" s="5">
         <v>46167</v>
@@ -5599,13 +5603,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5615,7 +5619,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B71" s="9">
         <v>46118.59016236111</v>
@@ -5633,10 +5637,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I71" s="9">
         <v>46167</v>
@@ -5654,13 +5658,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O71" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="P71" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="P71" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5670,7 +5674,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B72" s="5">
         <v>46118.59017135417</v>
@@ -5688,10 +5692,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I72" s="5">
         <v>46167</v>
@@ -5709,13 +5713,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5725,7 +5729,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B73" s="9">
         <v>46118.59019241898</v>
@@ -5764,13 +5768,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5780,7 +5784,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B74" s="5">
         <v>46118.590197488425</v>
@@ -5819,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5835,7 +5839,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B75" s="9">
         <v>46118.55580327546</v>
@@ -5869,7 +5873,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -5882,7 +5886,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B76" s="5">
         <v>46118.55580685185</v>
@@ -5892,7 +5896,7 @@
         <v>46182.67872560185</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5923,7 +5927,7 @@
         <v>97</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q76" s="5">
         <v>46113</v>
@@ -5938,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -5984,7 +5988,7 @@
         <v>106</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q77" s="9">
         <v>46129</v>
@@ -5999,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6045,7 +6049,7 @@
         <v>115</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q78" s="5">
         <v>46146</v>
@@ -6060,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -8771,10 +8775,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -8832,10 +8836,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -8883,10 +8887,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -8934,10 +8938,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -8985,10 +8989,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9036,10 +9040,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9087,10 +9091,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I135" s="10"/>
       <c r="J135" s="9">
@@ -9148,10 +9152,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9199,10 +9203,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H137" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I137" s="10"/>
       <c r="J137" s="9">
@@ -9250,10 +9254,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9301,10 +9305,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H139" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I139" s="10"/>
       <c r="J139" s="9">
@@ -9352,10 +9356,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="328">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -1054,9 +1054,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213964514232197</t>
@@ -9445,7 +9442,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46197.1681475</v>
+        <v>46198.16908622685</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>323</v>
@@ -9489,8 +9486,8 @@
       <c r="R142" s="5">
         <v>46189</v>
       </c>
-      <c r="S142" s="12" t="s">
-        <v>326</v>
+      <c r="S142" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T142" s="6">
         <v>0</v>
@@ -9501,17 +9498,17 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B143" s="9">
         <v>46118.55595019676</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46197.168156134256</v>
+        <v>46198.16908620371</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9552,8 +9549,8 @@
       <c r="R143" s="9">
         <v>46189</v>
       </c>
-      <c r="S143" s="12" t="s">
-        <v>326</v>
+      <c r="S143" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="T143" s="10">
         <v>0</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46197.507954988425</v>
+        <v>46198.56425574074</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>266</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46198.56425574074</v>
+        <v>46199.57039738426</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>266</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -738,13 +738,13 @@
     <t>OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,OT 4280 ZVN 1-9-63/2,Bodega:</t>
   </si>
   <si>
+    <t>1213955244951657</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213955244951657</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
   </si>
   <si>
     <t>1213955244957893</t>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46118.58538233796</v>
+        <v>46204.71690917824</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>177</v>
@@ -5888,9 +5888,11 @@
       <c r="B76" s="5">
         <v>46118.55580685185</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46204.71689967593</v>
+      </c>
       <c r="D76" s="5">
-        <v>46182.67872560185</v>
+        <v>46204.716915474535</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>218</v>
@@ -5936,15 +5938,15 @@
         <v>33</v>
       </c>
       <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="12" t="s">
-        <v>220</v>
+        <v>1</v>
+      </c>
+      <c r="U76" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B77" s="9">
         <v>46118.55581320602</v>
@@ -5954,7 +5956,7 @@
         <v>46192.88988357639</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6000,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6061,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6849,7 +6851,7 @@
         <v>46197.50749427083</v>
       </c>
       <c r="D93" s="9">
-        <v>46197.50749574074</v>
+        <v>46204.716905740745</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>140</v>
@@ -6902,7 +6904,7 @@
         <v>46197.507576828706</v>
       </c>
       <c r="D94" s="5">
-        <v>46197.50757840278</v>
+        <v>46204.71690671296</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>140</v>
@@ -6955,7 +6957,7 @@
         <v>46197.50767422454</v>
       </c>
       <c r="D95" s="9">
-        <v>46197.60944782407</v>
+        <v>46204.716907951384</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>140</v>
@@ -7008,7 +7010,7 @@
         <v>46197.50773788194</v>
       </c>
       <c r="D96" s="5">
-        <v>46197.50773945602</v>
+        <v>46204.71690747685</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>140</v>
@@ -7061,7 +7063,7 @@
         <v>46197.507801064814</v>
       </c>
       <c r="D97" s="9">
-        <v>46197.50780251157</v>
+        <v>46204.71690859954</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>140</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1686,13 +1686,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.55540376157</v>
+        <v>46118.38873709491</v>
       </c>
       <c r="C4" s="5">
-        <v>46134.84973423611</v>
+        <v>46134.683067569444</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.84974535879</v>
+        <v>46134.683078692135</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1739,13 +1739,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46118.55556929398</v>
+        <v>46118.38890262731</v>
       </c>
       <c r="C5" s="9">
-        <v>46134.847409131944</v>
+        <v>46134.68074246528</v>
       </c>
       <c r="D5" s="9">
-        <v>46134.84745465278</v>
+        <v>46134.680787986115</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1802,13 +1802,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.5555727662</v>
+        <v>46118.388906099535</v>
       </c>
       <c r="C6" s="5">
-        <v>46134.848174328705</v>
+        <v>46134.68150766204</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.84818818287</v>
+        <v>46134.681521516206</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1865,13 +1865,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="9">
-        <v>46118.555575624996</v>
+        <v>46118.38890895833</v>
       </c>
       <c r="C7" s="9">
-        <v>46134.848471840276</v>
+        <v>46134.68180517361</v>
       </c>
       <c r="D7" s="9">
-        <v>46134.84848634259</v>
+        <v>46134.68181967593</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>40</v>
@@ -1928,13 +1928,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.555578287036</v>
+        <v>46118.38891162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46134.849233009256</v>
+        <v>46134.68256634259</v>
       </c>
       <c r="D8" s="5">
-        <v>46191.71012979167</v>
+        <v>46191.543463124995</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1991,13 +1991,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="9">
-        <v>46118.55558168981</v>
+        <v>46118.38891502315</v>
       </c>
       <c r="C9" s="9">
-        <v>46134.84972003472</v>
+        <v>46134.683053368055</v>
       </c>
       <c r="D9" s="9">
-        <v>46134.84973509259</v>
+        <v>46134.683068425926</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>47</v>
@@ -2054,13 +2054,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.5554109375</v>
+        <v>46118.38874427084</v>
       </c>
       <c r="C10" s="5">
-        <v>46192.91325913194</v>
+        <v>46192.74659246528</v>
       </c>
       <c r="D10" s="5">
-        <v>46192.91327583333</v>
+        <v>46192.74660916667</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2107,13 +2107,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="9">
-        <v>46118.55558501158</v>
+        <v>46118.38891834491</v>
       </c>
       <c r="C11" s="9">
-        <v>46134.851535752314</v>
+        <v>46134.68486908565</v>
       </c>
       <c r="D11" s="9">
-        <v>46171.91061798611</v>
+        <v>46171.74395131944</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>52</v>
@@ -2172,13 +2172,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.55558986111</v>
+        <v>46118.38892319445</v>
       </c>
       <c r="C12" s="5">
-        <v>46134.850894386575</v>
+        <v>46134.6842277199</v>
       </c>
       <c r="D12" s="5">
-        <v>46134.85090979167</v>
+        <v>46134.684243125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2237,13 +2237,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46118.55559503472</v>
+        <v>46118.388928368055</v>
       </c>
       <c r="C13" s="9">
-        <v>46134.85044589121</v>
+        <v>46134.683779224535</v>
       </c>
       <c r="D13" s="9">
-        <v>46134.85046350694</v>
+        <v>46134.683796840276</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2302,13 +2302,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.55541763889</v>
+        <v>46118.388750972226</v>
       </c>
       <c r="C14" s="5">
-        <v>46192.913118993056</v>
+        <v>46192.74645232639</v>
       </c>
       <c r="D14" s="5">
-        <v>46192.91314039352</v>
+        <v>46192.74647372685</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2355,13 +2355,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46118.55560518519</v>
+        <v>46118.38893851852</v>
       </c>
       <c r="C15" s="9">
-        <v>46134.85201509259</v>
+        <v>46134.685348425926</v>
       </c>
       <c r="D15" s="9">
-        <v>46134.85202921296</v>
+        <v>46134.6853625463</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2420,13 +2420,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.555610462965</v>
+        <v>46118.38894379629</v>
       </c>
       <c r="C16" s="5">
-        <v>46192.91310200232</v>
+        <v>46192.74643533565</v>
       </c>
       <c r="D16" s="5">
-        <v>46192.91310392361</v>
+        <v>46192.746437256945</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2485,13 +2485,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46118.555615578705</v>
+        <v>46118.388948912034</v>
       </c>
       <c r="C17" s="9">
-        <v>46134.8523972338</v>
+        <v>46134.68573056713</v>
       </c>
       <c r="D17" s="9">
-        <v>46134.85241319444</v>
+        <v>46134.68574652778</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2550,13 +2550,13 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.55562122686</v>
+        <v>46118.388954560185</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.67167443287</v>
+        <v>46181.5050077662</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.671691550924</v>
+        <v>46181.50502488426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2615,13 +2615,13 @@
         <v>84</v>
       </c>
       <c r="B19" s="9">
-        <v>46118.55542568287</v>
+        <v>46118.388759016205</v>
       </c>
       <c r="C19" s="9">
-        <v>46192.91329202546</v>
+        <v>46192.74662535879</v>
       </c>
       <c r="D19" s="9">
-        <v>46192.91330840278</v>
+        <v>46192.746641736114</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>85</v>
@@ -2668,13 +2668,13 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.5556269213</v>
+        <v>46118.388960254626</v>
       </c>
       <c r="C20" s="5">
-        <v>46182.678718379626</v>
+        <v>46182.51205171296</v>
       </c>
       <c r="D20" s="5">
-        <v>46182.67873262732</v>
+        <v>46182.51206596065</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -2733,13 +2733,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="9">
-        <v>46118.55563141203</v>
+        <v>46118.38896474537</v>
       </c>
       <c r="C21" s="9">
-        <v>46155.897256944445</v>
+        <v>46155.73059027777</v>
       </c>
       <c r="D21" s="9">
-        <v>46169.85558454861</v>
+        <v>46169.68891788194</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>93</v>
@@ -2794,13 +2794,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.55563607639</v>
+        <v>46118.38896940972</v>
       </c>
       <c r="C22" s="5">
-        <v>46182.67870244213</v>
+        <v>46182.512035775464</v>
       </c>
       <c r="D22" s="5">
-        <v>46182.67870440972</v>
+        <v>46182.51203774306</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -2855,13 +2855,13 @@
         <v>99</v>
       </c>
       <c r="B23" s="9">
-        <v>46118.555640624996</v>
+        <v>46118.38897395833</v>
       </c>
       <c r="C23" s="9">
-        <v>46192.88987828704</v>
+        <v>46192.72321162037</v>
       </c>
       <c r="D23" s="9">
-        <v>46192.88989348379</v>
+        <v>46192.72322681713</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>100</v>
@@ -2920,13 +2920,13 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.55564542824</v>
+        <v>46118.38897876158</v>
       </c>
       <c r="C24" s="5">
-        <v>46192.8897287963</v>
+        <v>46192.72306212963</v>
       </c>
       <c r="D24" s="5">
-        <v>46192.913113912036</v>
+        <v>46192.74644724537</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -2981,13 +2981,13 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46118.55564990741</v>
+        <v>46118.388983240744</v>
       </c>
       <c r="C25" s="9">
-        <v>46192.889863564815</v>
+        <v>46192.72319689815</v>
       </c>
       <c r="D25" s="9">
-        <v>46192.88986527778</v>
+        <v>46192.723198611115</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3042,13 +3042,13 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.555654606476</v>
+        <v>46118.38898793982</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.67901127315</v>
+        <v>46182.51234460648</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.67902225694</v>
+        <v>46182.51235559028</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3107,13 +3107,13 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46118.55565927083</v>
+        <v>46118.38899260417</v>
       </c>
       <c r="C27" s="9">
-        <v>46134.89289440972</v>
+        <v>46134.72622774306</v>
       </c>
       <c r="D27" s="9">
-        <v>46169.85540111111</v>
+        <v>46169.68873444444</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3168,13 +3168,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.55566380787</v>
+        <v>46118.3889971412</v>
       </c>
       <c r="C28" s="5">
-        <v>46182.67899732639</v>
+        <v>46182.51233065972</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.67899886574</v>
+        <v>46182.51233219907</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3229,13 +3229,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46118.55566881945</v>
+        <v>46118.38900215278</v>
       </c>
       <c r="C29" s="9">
-        <v>46134.892935428245</v>
+        <v>46134.72626876157</v>
       </c>
       <c r="D29" s="9">
-        <v>46169.85534873843</v>
+        <v>46169.68868207176</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3290,13 +3290,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.55567340278</v>
+        <v>46118.389006736106</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.67180701389</v>
+        <v>46181.50514034722</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.671818483796</v>
+        <v>46181.50515181713</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3355,13 +3355,13 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46118.55568293981</v>
+        <v>46118.38901627315</v>
       </c>
       <c r="C31" s="9">
-        <v>46181.671732048606</v>
+        <v>46181.50506538195</v>
       </c>
       <c r="D31" s="9">
-        <v>46181.671733344905</v>
+        <v>46181.50506667824</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3416,13 +3416,13 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.55568802083</v>
+        <v>46118.38902135417</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.671791875</v>
+        <v>46181.505125208336</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.67179341435</v>
+        <v>46181.50512674768</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3477,11 +3477,11 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46118.5554312037</v>
+        <v>46118.38876453704</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46135.50561945602</v>
+        <v>46135.33895278935</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3524,13 +3524,13 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.55573724537</v>
+        <v>46118.389070578705</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.856089803245</v>
+        <v>46134.68942313657</v>
       </c>
       <c r="D34" s="5">
-        <v>46134.856103495375</v>
+        <v>46134.6894368287</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3589,13 +3589,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46118.58934402778</v>
+        <v>46118.422677361115</v>
       </c>
       <c r="C35" s="9">
-        <v>46134.85589491898</v>
+        <v>46134.68922825232</v>
       </c>
       <c r="D35" s="9">
-        <v>46134.85589640046</v>
+        <v>46134.68922973379</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -3644,13 +3644,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.58935734954</v>
+        <v>46118.42269068287</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.85590363426</v>
+        <v>46134.68923696759</v>
       </c>
       <c r="D36" s="5">
-        <v>46134.855904895834</v>
+        <v>46134.68923822917</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3699,13 +3699,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46118.58936491898</v>
+        <v>46118.42269825231</v>
       </c>
       <c r="C37" s="9">
-        <v>46134.856064039355</v>
+        <v>46134.689397372684</v>
       </c>
       <c r="D37" s="9">
-        <v>46134.85606556713</v>
+        <v>46134.68939890046</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>140</v>
@@ -3754,13 +3754,13 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.58937265046</v>
+        <v>46118.4227059838</v>
       </c>
       <c r="C38" s="5">
-        <v>46134.8560703588</v>
+        <v>46134.68940369213</v>
       </c>
       <c r="D38" s="5">
-        <v>46134.85607190972</v>
+        <v>46134.68940524306</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3809,13 +3809,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46118.5893790625</v>
+        <v>46118.42271239583</v>
       </c>
       <c r="C39" s="9">
-        <v>46134.85607678241</v>
+        <v>46134.68941011574</v>
       </c>
       <c r="D39" s="9">
-        <v>46134.85607811343</v>
+        <v>46134.68941144676</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>140</v>
@@ -3864,13 +3864,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.55574388889</v>
+        <v>46118.38907722222</v>
       </c>
       <c r="C40" s="5">
-        <v>46135.505314317124</v>
+        <v>46135.33864765047</v>
       </c>
       <c r="D40" s="5">
-        <v>46135.52260231481</v>
+        <v>46135.35593564815</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3929,13 +3929,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="9">
-        <v>46118.58948621528</v>
+        <v>46118.42281954861</v>
       </c>
       <c r="C41" s="9">
-        <v>46135.505267789355</v>
+        <v>46135.33860112268</v>
       </c>
       <c r="D41" s="9">
-        <v>46135.50526961806</v>
+        <v>46135.33860295139</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>140</v>
@@ -3984,13 +3984,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.589619189814</v>
+        <v>46118.42295252315</v>
       </c>
       <c r="C42" s="5">
-        <v>46135.50527871528</v>
+        <v>46135.33861204861</v>
       </c>
       <c r="D42" s="5">
-        <v>46135.50528020834</v>
+        <v>46135.338613541666</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>140</v>
@@ -4039,13 +4039,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="9">
-        <v>46118.589635729164</v>
+        <v>46118.4229690625</v>
       </c>
       <c r="C43" s="9">
-        <v>46135.50528577546</v>
+        <v>46135.33861910879</v>
       </c>
       <c r="D43" s="9">
-        <v>46135.50528708333</v>
+        <v>46135.33862041667</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>155</v>
@@ -4094,13 +4094,13 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.58964931713</v>
+        <v>46118.42298265046</v>
       </c>
       <c r="C44" s="5">
-        <v>46135.50529321759</v>
+        <v>46135.338626550925</v>
       </c>
       <c r="D44" s="5">
-        <v>46135.50529516204</v>
+        <v>46135.338628495374</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>155</v>
@@ -4149,13 +4149,13 @@
         <v>157</v>
       </c>
       <c r="B45" s="9">
-        <v>46118.5896587037</v>
+        <v>46118.42299203704</v>
       </c>
       <c r="C45" s="9">
-        <v>46135.50530085649</v>
+        <v>46135.338634189815</v>
       </c>
       <c r="D45" s="9">
-        <v>46135.50530211805</v>
+        <v>46135.33863545139</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>140</v>
@@ -4204,13 +4204,13 @@
         <v>158</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.55575109954</v>
+        <v>46118.38908443287</v>
       </c>
       <c r="C46" s="5">
-        <v>46135.505592835645</v>
+        <v>46135.33892616898</v>
       </c>
       <c r="D46" s="5">
-        <v>46135.50560496528</v>
+        <v>46135.338938298606</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>81</v>
@@ -4269,13 +4269,13 @@
         <v>160</v>
       </c>
       <c r="B47" s="9">
-        <v>46118.58972679398</v>
+        <v>46118.423060127316</v>
       </c>
       <c r="C47" s="9">
-        <v>46135.505553229166</v>
+        <v>46135.3388865625</v>
       </c>
       <c r="D47" s="9">
-        <v>46135.505555069445</v>
+        <v>46135.33888840278</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>140</v>
@@ -4322,13 +4322,13 @@
         <v>162</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.58974760417</v>
+        <v>46118.4230809375</v>
       </c>
       <c r="C48" s="5">
-        <v>46135.505559247686</v>
+        <v>46135.338892581014</v>
       </c>
       <c r="D48" s="5">
-        <v>46135.50556056713</v>
+        <v>46135.338893900465</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>140</v>
@@ -4375,13 +4375,13 @@
         <v>163</v>
       </c>
       <c r="B49" s="9">
-        <v>46118.58975269676</v>
+        <v>46118.42308603009</v>
       </c>
       <c r="C49" s="9">
-        <v>46135.505566527776</v>
+        <v>46135.33889986111</v>
       </c>
       <c r="D49" s="9">
-        <v>46135.50556795139</v>
+        <v>46135.33890128472</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>140</v>
@@ -4428,13 +4428,13 @@
         <v>164</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.58976391204</v>
+        <v>46118.423097245366</v>
       </c>
       <c r="C50" s="5">
-        <v>46135.505573229166</v>
+        <v>46135.3389065625</v>
       </c>
       <c r="D50" s="5">
-        <v>46135.50557504629</v>
+        <v>46135.33890837963</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>140</v>
@@ -4481,13 +4481,13 @@
         <v>165</v>
       </c>
       <c r="B51" s="9">
-        <v>46118.589758912036</v>
+        <v>46118.42309224537</v>
       </c>
       <c r="C51" s="9">
-        <v>46135.505581006946</v>
+        <v>46135.338914340275</v>
       </c>
       <c r="D51" s="9">
-        <v>46135.50558240741</v>
+        <v>46135.33891574074</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>140</v>
@@ -4534,11 +4534,11 @@
         <v>166</v>
       </c>
       <c r="B52" s="5">
-        <v>46118.55575893518</v>
+        <v>46118.38909226852</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46182.20622399305</v>
+        <v>46182.03955732639</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>167</v>
@@ -4597,11 +4597,11 @@
         <v>170</v>
       </c>
       <c r="B53" s="9">
-        <v>46118.589869131945</v>
+        <v>46118.423202465274</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46197.50794607639</v>
+        <v>46205.31827392361</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>140</v>
@@ -4650,11 +4650,11 @@
         <v>172</v>
       </c>
       <c r="B54" s="5">
-        <v>46118.589883333334</v>
+        <v>46118.42321666666</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46197.50794943287</v>
+        <v>46205.318296990736</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>140</v>
@@ -4703,11 +4703,11 @@
         <v>173</v>
       </c>
       <c r="B55" s="9">
-        <v>46118.589890312505</v>
+        <v>46118.423223645834</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46197.50795643518</v>
+        <v>46205.31768317129</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>140</v>
@@ -4756,11 +4756,11 @@
         <v>174</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.58992050926</v>
+        <v>46118.42325384259</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46181.168653182875</v>
+        <v>46181.0019865162</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>140</v>
@@ -4809,11 +4809,11 @@
         <v>175</v>
       </c>
       <c r="B57" s="9">
-        <v>46118.589899548606</v>
+        <v>46118.42323288195</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46181.168651678236</v>
+        <v>46181.00198501158</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>140</v>
@@ -4862,13 +4862,13 @@
         <v>176</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.55576480324</v>
+        <v>46118.38909813657</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.67196634259</v>
+        <v>46181.505299675926</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.67205032408</v>
+        <v>46181.50538365741</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>177</v>
@@ -4911,13 +4911,13 @@
         <v>179</v>
       </c>
       <c r="B59" s="9">
-        <v>46118.55576952547</v>
+        <v>46118.3891028588</v>
       </c>
       <c r="C59" s="9">
-        <v>46181.67190112268</v>
+        <v>46181.50523445602</v>
       </c>
       <c r="D59" s="9">
-        <v>46181.67191517361</v>
+        <v>46181.50524850695</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>180</v>
@@ -4976,13 +4976,13 @@
         <v>184</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.55577607639</v>
+        <v>46118.38910940972</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.671950752316</v>
+        <v>46181.50528408565</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.671966932874</v>
+        <v>46181.5053002662</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>185</v>
@@ -5041,13 +5041,13 @@
         <v>188</v>
       </c>
       <c r="B61" s="9">
-        <v>46118.55578122685</v>
+        <v>46118.38911456018</v>
       </c>
       <c r="C61" s="9">
-        <v>46197.775929456024</v>
+        <v>46197.60926278935</v>
       </c>
       <c r="D61" s="9">
-        <v>46197.77594626158</v>
+        <v>46197.60927959491</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>189</v>
@@ -5094,13 +5094,13 @@
         <v>191</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.55578460648</v>
+        <v>46118.38911793982</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.672212314814</v>
+        <v>46181.50554564815</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.67222788194</v>
+        <v>46181.50556121528</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>192</v>
@@ -5159,13 +5159,13 @@
         <v>196</v>
       </c>
       <c r="B63" s="9">
-        <v>46118.555790115744</v>
+        <v>46118.38912344907</v>
       </c>
       <c r="C63" s="9">
-        <v>46191.71033274305</v>
+        <v>46191.54366607639</v>
       </c>
       <c r="D63" s="9">
-        <v>46191.71034409722</v>
+        <v>46191.543677430556</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>197</v>
@@ -5224,13 +5224,13 @@
         <v>198</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.59005789352</v>
+        <v>46118.423391226854</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.6723374537</v>
+        <v>46181.50567078704</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.672338564815</v>
+        <v>46181.50567189815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>140</v>
@@ -5279,13 +5279,13 @@
         <v>201</v>
       </c>
       <c r="B65" s="9">
-        <v>46118.590067604164</v>
+        <v>46118.4234009375</v>
       </c>
       <c r="C65" s="9">
-        <v>46181.672350925925</v>
+        <v>46181.50568425926</v>
       </c>
       <c r="D65" s="9">
-        <v>46181.672352442125</v>
+        <v>46181.50568577547</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>140</v>
@@ -5334,13 +5334,13 @@
         <v>203</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.5900759838</v>
+        <v>46118.423409317125</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.67236503473</v>
+        <v>46181.505698368055</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.672366307874</v>
+        <v>46181.5056996412</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>140</v>
@@ -5389,13 +5389,13 @@
         <v>204</v>
       </c>
       <c r="B67" s="9">
-        <v>46118.590097962966</v>
+        <v>46118.423431296294</v>
       </c>
       <c r="C67" s="9">
-        <v>46191.71030983796</v>
+        <v>46191.543643171295</v>
       </c>
       <c r="D67" s="9">
-        <v>46191.71031108796</v>
+        <v>46191.5436444213</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>140</v>
@@ -5444,13 +5444,13 @@
         <v>205</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.59010253473</v>
+        <v>46118.423435868055</v>
       </c>
       <c r="C68" s="5">
-        <v>46191.71031711806</v>
+        <v>46191.54365045139</v>
       </c>
       <c r="D68" s="5">
-        <v>46191.710318530095</v>
+        <v>46191.54365186342</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>140</v>
@@ -5499,13 +5499,13 @@
         <v>206</v>
       </c>
       <c r="B69" s="9">
-        <v>46118.55579684028</v>
+        <v>46118.389130173615</v>
       </c>
       <c r="C69" s="9">
-        <v>46191.70935185185</v>
+        <v>46191.54268518518</v>
       </c>
       <c r="D69" s="9">
-        <v>46191.709365358794</v>
+        <v>46191.54269869213</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>207</v>
@@ -5564,13 +5564,13 @@
         <v>208</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.59015388889</v>
+        <v>46118.42348722222</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.67244342592</v>
+        <v>46181.50577675926</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.67244473379</v>
+        <v>46181.505778067134</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>140</v>
@@ -5619,13 +5619,13 @@
         <v>211</v>
       </c>
       <c r="B71" s="9">
-        <v>46118.59016236111</v>
+        <v>46118.42349569444</v>
       </c>
       <c r="C71" s="9">
-        <v>46181.672456597225</v>
+        <v>46181.505789930554</v>
       </c>
       <c r="D71" s="9">
-        <v>46181.672458078705</v>
+        <v>46181.50579141204</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>140</v>
@@ -5674,13 +5674,13 @@
         <v>212</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.59017135417</v>
+        <v>46118.4235046875</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.67246365741</v>
+        <v>46181.505796990736</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.672464999996</v>
+        <v>46181.50579833333</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>140</v>
@@ -5729,13 +5729,13 @@
         <v>213</v>
       </c>
       <c r="B73" s="9">
-        <v>46118.59019241898</v>
+        <v>46118.42352575231</v>
       </c>
       <c r="C73" s="9">
-        <v>46191.70928226852</v>
+        <v>46191.54261560185</v>
       </c>
       <c r="D73" s="9">
-        <v>46191.7103152662</v>
+        <v>46191.54364859954</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>140</v>
@@ -5784,13 +5784,13 @@
         <v>214</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.590197488425</v>
+        <v>46118.42353082176</v>
       </c>
       <c r="C74" s="5">
-        <v>46191.70933641204</v>
+        <v>46191.542669745366</v>
       </c>
       <c r="D74" s="5">
-        <v>46191.7103265162</v>
+        <v>46191.543659849536</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>140</v>
@@ -5839,11 +5839,11 @@
         <v>215</v>
       </c>
       <c r="B75" s="9">
-        <v>46118.55580327546</v>
+        <v>46118.38913660879</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46204.71690917824</v>
+        <v>46204.55024251157</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>177</v>
@@ -5886,13 +5886,13 @@
         <v>217</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.55580685185</v>
+        <v>46118.38914018519</v>
       </c>
       <c r="C76" s="5">
-        <v>46204.71689967593</v>
+        <v>46204.55023300926</v>
       </c>
       <c r="D76" s="5">
-        <v>46204.716915474535</v>
+        <v>46204.55024880787</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>218</v>
@@ -5949,11 +5949,11 @@
         <v>220</v>
       </c>
       <c r="B77" s="9">
-        <v>46118.55581320602</v>
+        <v>46118.38914653935</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46192.88988357639</v>
+        <v>46192.723216909726</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>221</v>
@@ -6010,11 +6010,11 @@
         <v>223</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.55581936342</v>
+        <v>46118.38915269676</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.67901537037</v>
+        <v>46182.512348703705</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>224</v>
@@ -6071,11 +6071,11 @@
         <v>225</v>
       </c>
       <c r="B79" s="9">
-        <v>46118.55582516204</v>
+        <v>46118.38915849537</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.50782400463</v>
+        <v>46197.34115733796</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>226</v>
@@ -6118,13 +6118,13 @@
         <v>228</v>
       </c>
       <c r="B80" s="5">
-        <v>46118.55582877315</v>
+        <v>46118.38916210648</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.4232071875</v>
+        <v>46197.25654052083</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.42322075232</v>
+        <v>46197.256554085645</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>229</v>
@@ -6183,13 +6183,13 @@
         <v>230</v>
       </c>
       <c r="B81" s="9">
-        <v>46118.590250625</v>
+        <v>46118.423583958334</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.42301266204</v>
+        <v>46197.25634599537</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.423014942135</v>
+        <v>46197.25634827546</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>140</v>
@@ -6238,13 +6238,13 @@
         <v>232</v>
       </c>
       <c r="B82" s="5">
-        <v>46118.590259641205</v>
+        <v>46118.423592974534</v>
       </c>
       <c r="C82" s="5">
-        <v>46197.42305077546</v>
+        <v>46197.2563841088</v>
       </c>
       <c r="D82" s="5">
-        <v>46197.42305252315</v>
+        <v>46197.25638585648</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>140</v>
@@ -6293,13 +6293,13 @@
         <v>233</v>
       </c>
       <c r="B83" s="9">
-        <v>46118.59026761574</v>
+        <v>46118.42360094907</v>
       </c>
       <c r="C83" s="9">
-        <v>46197.423102430555</v>
+        <v>46197.25643576389</v>
       </c>
       <c r="D83" s="9">
-        <v>46197.42310400463</v>
+        <v>46197.256437337965</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>140</v>
@@ -6348,13 +6348,13 @@
         <v>234</v>
       </c>
       <c r="B84" s="5">
-        <v>46118.590275636576</v>
+        <v>46118.42360896991</v>
       </c>
       <c r="C84" s="5">
-        <v>46197.42314728009</v>
+        <v>46197.256480613425</v>
       </c>
       <c r="D84" s="5">
-        <v>46197.423148842594</v>
+        <v>46197.25648217593</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>140</v>
@@ -6403,13 +6403,13 @@
         <v>235</v>
       </c>
       <c r="B85" s="9">
-        <v>46118.59028430555</v>
+        <v>46118.42361763889</v>
       </c>
       <c r="C85" s="9">
-        <v>46197.42319270833</v>
+        <v>46197.25652604167</v>
       </c>
       <c r="D85" s="9">
-        <v>46197.42319425926</v>
+        <v>46197.25652759259</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>140</v>
@@ -6458,11 +6458,11 @@
         <v>236</v>
       </c>
       <c r="B86" s="5">
-        <v>46118.55583459491</v>
+        <v>46118.38916792824</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46197.609448206014</v>
+        <v>46197.44278153935</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>237</v>
@@ -6521,13 +6521,13 @@
         <v>238</v>
       </c>
       <c r="B87" s="9">
-        <v>46118.59033478009</v>
+        <v>46118.42366811342</v>
       </c>
       <c r="C87" s="9">
-        <v>46197.50709427083</v>
+        <v>46197.34042760417</v>
       </c>
       <c r="D87" s="9">
-        <v>46197.50709627315</v>
+        <v>46197.340429606484</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>140</v>
@@ -6574,13 +6574,13 @@
         <v>241</v>
       </c>
       <c r="B88" s="5">
-        <v>46118.59034447916</v>
+        <v>46118.423677812505</v>
       </c>
       <c r="C88" s="5">
-        <v>46197.50715157407</v>
+        <v>46197.34048490741</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.507152997685</v>
+        <v>46197.34048633101</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>140</v>
@@ -6627,13 +6627,13 @@
         <v>242</v>
       </c>
       <c r="B89" s="9">
-        <v>46118.590352141204</v>
+        <v>46118.42368547454</v>
       </c>
       <c r="C89" s="9">
-        <v>46197.50723920139</v>
+        <v>46197.340572534726</v>
       </c>
       <c r="D89" s="9">
-        <v>46197.50724237268</v>
+        <v>46197.34057570602</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>140</v>
@@ -6680,11 +6680,11 @@
         <v>243</v>
       </c>
       <c r="B90" s="5">
-        <v>46118.59035967593</v>
+        <v>46118.42369300926</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46197.609442534726</v>
+        <v>46197.442775868054</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>140</v>
@@ -6731,11 +6731,11 @@
         <v>244</v>
       </c>
       <c r="B91" s="9">
-        <v>46118.59036834491</v>
+        <v>46118.42370167824</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46197.42320116898</v>
+        <v>46197.25653450232</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>140</v>
@@ -6782,13 +6782,13 @@
         <v>245</v>
       </c>
       <c r="B92" s="5">
-        <v>46118.55584244213</v>
+        <v>46118.38917577546</v>
       </c>
       <c r="C92" s="5">
-        <v>46197.50781607639</v>
+        <v>46197.34114940972</v>
       </c>
       <c r="D92" s="5">
-        <v>46197.50782737268</v>
+        <v>46197.34116070602</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>246</v>
@@ -6845,13 +6845,13 @@
         <v>247</v>
       </c>
       <c r="B93" s="9">
-        <v>46118.59042068287</v>
+        <v>46118.4237540162</v>
       </c>
       <c r="C93" s="9">
-        <v>46197.50749427083</v>
+        <v>46197.34082760417</v>
       </c>
       <c r="D93" s="9">
-        <v>46204.716905740745</v>
+        <v>46204.55023907407</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>140</v>
@@ -6898,13 +6898,13 @@
         <v>250</v>
       </c>
       <c r="B94" s="5">
-        <v>46118.5904280324</v>
+        <v>46118.423761365746</v>
       </c>
       <c r="C94" s="5">
-        <v>46197.507576828706</v>
+        <v>46197.340910162035</v>
       </c>
       <c r="D94" s="5">
-        <v>46204.71690671296</v>
+        <v>46204.5502400463</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>140</v>
@@ -6951,13 +6951,13 @@
         <v>251</v>
       </c>
       <c r="B95" s="9">
-        <v>46118.59044465278</v>
+        <v>46118.423777986114</v>
       </c>
       <c r="C95" s="9">
-        <v>46197.50767422454</v>
+        <v>46197.34100755787</v>
       </c>
       <c r="D95" s="9">
-        <v>46204.716907951384</v>
+        <v>46204.55024128473</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>140</v>
@@ -7004,13 +7004,13 @@
         <v>252</v>
       </c>
       <c r="B96" s="5">
-        <v>46118.5904391088</v>
+        <v>46118.423772442125</v>
       </c>
       <c r="C96" s="5">
-        <v>46197.50773788194</v>
+        <v>46197.341071215276</v>
       </c>
       <c r="D96" s="5">
-        <v>46204.71690747685</v>
+        <v>46204.55024081019</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>140</v>
@@ -7057,13 +7057,13 @@
         <v>253</v>
       </c>
       <c r="B97" s="9">
-        <v>46118.59045233796</v>
+        <v>46118.4237856713</v>
       </c>
       <c r="C97" s="9">
-        <v>46197.507801064814</v>
+        <v>46197.34113439815</v>
       </c>
       <c r="D97" s="9">
-        <v>46204.71690859954</v>
+        <v>46204.55024193287</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>140</v>
@@ -7110,11 +7110,11 @@
         <v>254</v>
       </c>
       <c r="B98" s="5">
-        <v>46118.55584987269</v>
+        <v>46118.38918320602</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46197.42458010417</v>
+        <v>46197.2579134375</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>255</v>
@@ -7171,13 +7171,13 @@
         <v>256</v>
       </c>
       <c r="B99" s="9">
-        <v>46118.590539282406</v>
+        <v>46118.42387261574</v>
       </c>
       <c r="C99" s="9">
-        <v>46197.42437898148</v>
+        <v>46197.257712314815</v>
       </c>
       <c r="D99" s="9">
-        <v>46197.50749940972</v>
+        <v>46197.34083274305</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>140</v>
@@ -7224,13 +7224,13 @@
         <v>259</v>
       </c>
       <c r="B100" s="5">
-        <v>46118.590546666666</v>
+        <v>46118.42388</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.42449445602</v>
+        <v>46197.25782778935</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.50758304398</v>
+        <v>46197.34091637732</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>140</v>
@@ -7277,13 +7277,13 @@
         <v>261</v>
       </c>
       <c r="B101" s="9">
-        <v>46118.590554027774</v>
+        <v>46118.42388736111</v>
       </c>
       <c r="C101" s="9">
-        <v>46197.42457260417</v>
+        <v>46197.2579059375</v>
       </c>
       <c r="D101" s="9">
-        <v>46197.50774366898</v>
+        <v>46197.34107700232</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>140</v>
@@ -7330,11 +7330,11 @@
         <v>263</v>
       </c>
       <c r="B102" s="5">
-        <v>46118.59056115741</v>
+        <v>46118.42389449074</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46197.507679953706</v>
+        <v>46197.341013287034</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>140</v>
@@ -7381,11 +7381,11 @@
         <v>264</v>
       </c>
       <c r="B103" s="9">
-        <v>46118.590569293985</v>
+        <v>46118.42390262731</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46197.50781008102</v>
+        <v>46197.34114341435</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>140</v>
@@ -7432,11 +7432,11 @@
         <v>265</v>
       </c>
       <c r="B104" s="5">
-        <v>46118.5558574537</v>
+        <v>46118.38919078704</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46199.57039738426</v>
+        <v>46205.31914983796</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>266</v>
@@ -7495,13 +7495,13 @@
         <v>267</v>
       </c>
       <c r="B105" s="9">
-        <v>46118.5906265625</v>
+        <v>46118.42395989584</v>
       </c>
       <c r="C105" s="9">
-        <v>46197.50793775463</v>
+        <v>46205.31826884259</v>
       </c>
       <c r="D105" s="9">
-        <v>46197.50793939814</v>
+        <v>46205.31827017361</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>140</v>
@@ -7548,13 +7548,13 @@
         <v>269</v>
       </c>
       <c r="B106" s="5">
-        <v>46118.59063387732</v>
+        <v>46118.42396721065</v>
       </c>
       <c r="C106" s="5">
-        <v>46197.507942592594</v>
+        <v>46205.31828936342</v>
       </c>
       <c r="D106" s="5">
-        <v>46197.5079440625</v>
+        <v>46205.3182909375</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>140</v>
@@ -7601,13 +7601,11 @@
         <v>270</v>
       </c>
       <c r="B107" s="9">
-        <v>46118.590655486114</v>
-      </c>
-      <c r="C107" s="9">
-        <v>46197.507947488426</v>
-      </c>
+        <v>46118.42398881944</v>
+      </c>
+      <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46197.50794915509</v>
+        <v>46205.31767856481</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>140</v>
@@ -7654,11 +7652,11 @@
         <v>271</v>
       </c>
       <c r="B108" s="5">
-        <v>46118.59066162037</v>
+        <v>46118.4239949537</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46178.16914135417</v>
+        <v>46178.0024746875</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>140</v>
@@ -7705,11 +7703,11 @@
         <v>272</v>
       </c>
       <c r="B109" s="9">
-        <v>46118.59066710648</v>
+        <v>46118.424000439816</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46178.16914265046</v>
+        <v>46178.0024759838</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>140</v>
@@ -7756,11 +7754,11 @@
         <v>273</v>
       </c>
       <c r="B110" s="5">
-        <v>46118.55591270833</v>
+        <v>46118.38924604167</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46183.194774386575</v>
+        <v>46183.0281077199</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>274</v>
@@ -7817,11 +7815,11 @@
         <v>276</v>
       </c>
       <c r="B111" s="9">
-        <v>46118.590705243056</v>
+        <v>46118.424038576384</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46182.168110810184</v>
+        <v>46182.00144414352</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>140</v>
@@ -7870,11 +7868,11 @@
         <v>278</v>
       </c>
       <c r="B112" s="5">
-        <v>46118.59071275463</v>
+        <v>46118.42404608797</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.1681121875</v>
+        <v>46182.00144552083</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>140</v>
@@ -7923,11 +7921,11 @@
         <v>279</v>
       </c>
       <c r="B113" s="9">
-        <v>46118.590720092594</v>
+        <v>46118.42405342593</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46182.16811331018</v>
+        <v>46182.00144664352</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>140</v>
@@ -7976,11 +7974,11 @@
         <v>280</v>
       </c>
       <c r="B114" s="5">
-        <v>46118.590727835646</v>
+        <v>46118.42406116898</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.16811451389</v>
+        <v>46182.00144784722</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>140</v>
@@ -8029,11 +8027,11 @@
         <v>281</v>
       </c>
       <c r="B115" s="9">
-        <v>46118.59073534722</v>
+        <v>46118.42406868056</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46182.16811570602</v>
+        <v>46182.00144903935</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>140</v>
@@ -8082,11 +8080,11 @@
         <v>282</v>
       </c>
       <c r="B116" s="5">
-        <v>46118.55591954861</v>
+        <v>46118.38925288194</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46118.63950689815</v>
+        <v>46118.47284023148</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>283</v>
@@ -8129,11 +8127,11 @@
         <v>285</v>
       </c>
       <c r="B117" s="9">
-        <v>46118.555923148146</v>
+        <v>46118.38925648148</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46184.18063726852</v>
+        <v>46184.01397060185</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>286</v>
@@ -8190,11 +8188,11 @@
         <v>289</v>
       </c>
       <c r="B118" s="5">
-        <v>46118.590793020834</v>
+        <v>46118.42412635416</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46183.16824416666</v>
+        <v>46183.0015775</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>140</v>
@@ -8241,11 +8239,11 @@
         <v>290</v>
       </c>
       <c r="B119" s="9">
-        <v>46118.59080049768</v>
+        <v>46118.424133831024</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46183.16824571759</v>
+        <v>46183.00157905092</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>140</v>
@@ -8292,11 +8290,11 @@
         <v>291</v>
       </c>
       <c r="B120" s="5">
-        <v>46118.59080680556</v>
+        <v>46118.424140138886</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46183.168246875</v>
+        <v>46183.001580208336</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>140</v>
@@ -8343,11 +8341,11 @@
         <v>292</v>
       </c>
       <c r="B121" s="9">
-        <v>46118.59081555555</v>
+        <v>46118.42414888889</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46183.16824814815</v>
+        <v>46183.00158148148</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>140</v>
@@ -8394,11 +8392,11 @@
         <v>293</v>
       </c>
       <c r="B122" s="5">
-        <v>46118.590822777776</v>
+        <v>46118.42415611111</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46183.16824943287</v>
+        <v>46183.0015827662</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>140</v>
@@ -8445,11 +8443,11 @@
         <v>294</v>
       </c>
       <c r="B123" s="9">
-        <v>46118.55592798611</v>
+        <v>46118.38926131945</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46185.17432103009</v>
+        <v>46185.00765436343</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>295</v>
@@ -8506,11 +8504,11 @@
         <v>297</v>
       </c>
       <c r="B124" s="5">
-        <v>46118.59087519676</v>
+        <v>46118.424208530094</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46184.168032511574</v>
+        <v>46184.0013658449</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>140</v>
@@ -8557,11 +8555,11 @@
         <v>299</v>
       </c>
       <c r="B125" s="9">
-        <v>46118.590883240744</v>
+        <v>46118.42421657407</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46184.168034201386</v>
+        <v>46184.00136753472</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>140</v>
@@ -8608,11 +8606,11 @@
         <v>300</v>
       </c>
       <c r="B126" s="5">
-        <v>46118.59089157407</v>
+        <v>46118.42422490741</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46184.16803541667</v>
+        <v>46184.00136875</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>140</v>
@@ -8659,11 +8657,11 @@
         <v>301</v>
       </c>
       <c r="B127" s="9">
-        <v>46118.590897835646</v>
+        <v>46118.42423116898</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46184.168036863426</v>
+        <v>46184.001370196755</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>155</v>
@@ -8710,11 +8708,11 @@
         <v>302</v>
       </c>
       <c r="B128" s="5">
-        <v>46118.5909049537</v>
+        <v>46118.424238287036</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46184.16803811342</v>
+        <v>46184.001371446764</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>155</v>
@@ -8761,11 +8759,11 @@
         <v>303</v>
       </c>
       <c r="B129" s="9">
-        <v>46118.555932511576</v>
+        <v>46118.389265844904</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46186.16794060185</v>
+        <v>46186.00127393518</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>304</v>
@@ -8822,11 +8820,11 @@
         <v>305</v>
       </c>
       <c r="B130" s="5">
-        <v>46118.59095414352</v>
+        <v>46118.42428747685</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46185.168594965275</v>
+        <v>46185.00192829861</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>140</v>
@@ -8873,11 +8871,11 @@
         <v>307</v>
       </c>
       <c r="B131" s="9">
-        <v>46118.590966759264</v>
+        <v>46118.42430009259</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46185.16859673611</v>
+        <v>46185.00193006944</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>140</v>
@@ -8924,11 +8922,11 @@
         <v>308</v>
       </c>
       <c r="B132" s="5">
-        <v>46118.590973796294</v>
+        <v>46118.42430712963</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46185.168597951386</v>
+        <v>46185.00193128472</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>140</v>
@@ -8975,11 +8973,11 @@
         <v>309</v>
       </c>
       <c r="B133" s="9">
-        <v>46118.590979953704</v>
+        <v>46118.42431328703</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46185.16859903935</v>
+        <v>46185.00193237269</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>140</v>
@@ -9026,11 +9024,11 @@
         <v>310</v>
       </c>
       <c r="B134" s="5">
-        <v>46118.59098489583</v>
+        <v>46118.42431822917</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46185.16860023148</v>
+        <v>46185.00193356481</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>140</v>
@@ -9077,11 +9075,11 @@
         <v>311</v>
       </c>
       <c r="B135" s="9">
-        <v>46118.55593715278</v>
+        <v>46118.38927048611</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46189.2078791088</v>
+        <v>46189.04121244213</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>312</v>
@@ -9138,11 +9136,11 @@
         <v>314</v>
       </c>
       <c r="B136" s="5">
-        <v>46118.59103105324</v>
+        <v>46118.42436438658</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46188.168568113426</v>
+        <v>46188.001901446754</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>140</v>
@@ -9189,11 +9187,11 @@
         <v>315</v>
       </c>
       <c r="B137" s="9">
-        <v>46118.591039039355</v>
+        <v>46118.42437237268</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46188.16856979167</v>
+        <v>46188.001903125</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>140</v>
@@ -9240,11 +9238,11 @@
         <v>316</v>
       </c>
       <c r="B138" s="5">
-        <v>46118.59104641204</v>
+        <v>46118.42437974537</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46188.168570995374</v>
+        <v>46188.0019043287</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>140</v>
@@ -9291,11 +9289,11 @@
         <v>317</v>
       </c>
       <c r="B139" s="9">
-        <v>46118.59105258102</v>
+        <v>46118.42438591435</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46188.1685722338</v>
+        <v>46188.00190556713</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>140</v>
@@ -9342,11 +9340,11 @@
         <v>318</v>
       </c>
       <c r="B140" s="5">
-        <v>46118.59105829861</v>
+        <v>46118.42439163194</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46188.16857356481</v>
+        <v>46188.00190689815</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>140</v>
@@ -9393,11 +9391,11 @@
         <v>319</v>
       </c>
       <c r="B141" s="9">
-        <v>46118.55594259259</v>
+        <v>46118.389275925925</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46118.64758575232</v>
+        <v>46118.48091908565</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>320</v>
@@ -9440,11 +9438,11 @@
         <v>322</v>
       </c>
       <c r="B142" s="5">
-        <v>46118.55594550926</v>
+        <v>46118.38927884259</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46198.16908622685</v>
+        <v>46198.00241956019</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>323</v>
@@ -9503,11 +9501,11 @@
         <v>326</v>
       </c>
       <c r="B143" s="9">
-        <v>46118.55595019676</v>
+        <v>46118.389283530094</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.16908620371</v>
+        <v>46198.002419537035</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>327</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="327">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -742,9 +742,6 @@
   </si>
   <si>
     <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213955244957893</t>
@@ -1089,7 +1086,7 @@
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1129,11 +1126,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFe8384f"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1179,7 +1171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1198,7 +1190,6 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5841,9 +5832,11 @@
       <c r="B75" s="9">
         <v>46118.55580327546</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9">
+        <v>46205.906285624995</v>
+      </c>
       <c r="D75" s="9">
-        <v>46204.71690917824</v>
+        <v>46205.90630074074</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>177</v>
@@ -5878,8 +5871,12 @@
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
       <c r="S75" s="10"/>
-      <c r="T75" s="10"/>
-      <c r="U75" s="10"/>
+      <c r="T75" s="10">
+        <v>1</v>
+      </c>
+      <c r="U75" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
@@ -5951,9 +5948,11 @@
       <c r="B77" s="9">
         <v>46118.55581320602</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="9">
+        <v>46205.90465295139</v>
+      </c>
       <c r="D77" s="9">
-        <v>46192.88988357639</v>
+        <v>46205.90467159722</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>221</v>
@@ -5999,25 +5998,27 @@
         <v>83</v>
       </c>
       <c r="T77" s="10">
-        <v>0</v>
-      </c>
-      <c r="U77" s="12" t="s">
-        <v>222</v>
+        <v>1</v>
+      </c>
+      <c r="U77" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B78" s="5">
         <v>46118.55581936342</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46205.90626957176</v>
+      </c>
       <c r="D78" s="5">
-        <v>46182.67901537037</v>
+        <v>46205.90628471065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6060,15 +6061,15 @@
         <v>83</v>
       </c>
       <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="12" t="s">
-        <v>222</v>
+        <v>1</v>
+      </c>
+      <c r="U78" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B79" s="9">
         <v>46118.55582516204</v>
@@ -6078,7 +6079,7 @@
         <v>46197.50782400463</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6102,7 +6103,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6115,7 +6116,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B80" s="5">
         <v>46118.55582877315</v>
@@ -6127,7 +6128,7 @@
         <v>46197.42322075232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6154,13 +6155,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6180,7 +6181,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B81" s="9">
         <v>46118.590250625</v>
@@ -6219,13 +6220,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6235,7 +6236,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B82" s="5">
         <v>46118.590259641205</v>
@@ -6274,13 +6275,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6290,7 +6291,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B83" s="9">
         <v>46118.59026761574</v>
@@ -6329,13 +6330,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6345,7 +6346,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B84" s="5">
         <v>46118.590275636576</v>
@@ -6384,13 +6385,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6400,7 +6401,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B85" s="9">
         <v>46118.59028430555</v>
@@ -6439,13 +6440,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6455,7 +6456,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B86" s="5">
         <v>46118.55583459491</v>
@@ -6465,7 +6466,7 @@
         <v>46197.609448206014</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6492,13 +6493,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q86" s="5">
         <v>46175</v>
@@ -6518,7 +6519,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B87" s="9">
         <v>46118.59033478009</v>
@@ -6527,7 +6528,7 @@
         <v>46197.50709427083</v>
       </c>
       <c r="D87" s="9">
-        <v>46197.50709627315</v>
+        <v>46205.90627537037</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>140</v>
@@ -6555,13 +6556,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O87" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="P87" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="P87" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6571,7 +6572,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B88" s="5">
         <v>46118.59034447916</v>
@@ -6580,7 +6581,7 @@
         <v>46197.50715157407</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.507152997685</v>
+        <v>46205.90627636574</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>140</v>
@@ -6608,13 +6609,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6624,7 +6625,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B89" s="9">
         <v>46118.590352141204</v>
@@ -6633,7 +6634,7 @@
         <v>46197.50723920139</v>
       </c>
       <c r="D89" s="9">
-        <v>46197.50724237268</v>
+        <v>46205.90627747685</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>140</v>
@@ -6661,13 +6662,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6677,14 +6678,14 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B90" s="5">
         <v>46118.59035967593</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46197.609442534726</v>
+        <v>46205.90627893519</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>140</v>
@@ -6712,13 +6713,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6728,14 +6729,14 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B91" s="9">
         <v>46118.59036834491</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46197.42320116898</v>
+        <v>46205.9062803125</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>140</v>
@@ -6763,13 +6764,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6779,7 +6780,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B92" s="5">
         <v>46118.55584244213</v>
@@ -6791,7 +6792,7 @@
         <v>46197.50782737268</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6816,13 +6817,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q92" s="5">
         <v>46176</v>
@@ -6842,7 +6843,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B93" s="9">
         <v>46118.59042068287</v>
@@ -6879,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O93" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>249</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6895,7 +6896,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B94" s="5">
         <v>46118.5904280324</v>
@@ -6932,13 +6933,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6948,7 +6949,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B95" s="9">
         <v>46118.59044465278</v>
@@ -6985,13 +6986,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O95" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="P95" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="P95" s="10" t="s">
-        <v>249</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7001,7 +7002,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B96" s="5">
         <v>46118.5904391088</v>
@@ -7038,13 +7039,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7054,7 +7055,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B97" s="9">
         <v>46118.59045233796</v>
@@ -7091,13 +7092,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O97" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>249</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7107,7 +7108,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B98" s="5">
         <v>46118.55584987269</v>
@@ -7117,7 +7118,7 @@
         <v>46197.42458010417</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7142,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q98" s="5">
         <v>46177</v>
@@ -7168,7 +7169,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B99" s="9">
         <v>46118.590539282406</v>
@@ -7177,7 +7178,7 @@
         <v>46197.42437898148</v>
       </c>
       <c r="D99" s="9">
-        <v>46197.50749940972</v>
+        <v>46205.90466006944</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>140</v>
@@ -7205,13 +7206,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O99" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="P99" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="P99" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7221,7 +7222,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B100" s="5">
         <v>46118.590546666666</v>
@@ -7230,7 +7231,7 @@
         <v>46197.42449445602</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.50758304398</v>
+        <v>46205.90466118055</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>140</v>
@@ -7258,13 +7259,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7274,7 +7275,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B101" s="9">
         <v>46118.590554027774</v>
@@ -7283,7 +7284,7 @@
         <v>46197.42457260417</v>
       </c>
       <c r="D101" s="9">
-        <v>46197.50774366898</v>
+        <v>46205.90466188657</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>140</v>
@@ -7311,13 +7312,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7327,14 +7328,14 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B102" s="5">
         <v>46118.59056115741</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46197.507679953706</v>
+        <v>46205.904663124995</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>140</v>
@@ -7362,13 +7363,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7378,14 +7379,14 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B103" s="9">
         <v>46118.590569293985</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46197.50781008102</v>
+        <v>46205.90466431713</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>140</v>
@@ -7413,13 +7414,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7429,7 +7430,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B104" s="5">
         <v>46118.5558574537</v>
@@ -7439,7 +7440,7 @@
         <v>46205.48581650463</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7466,13 +7467,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q104" s="5">
         <v>46178</v>
@@ -7492,7 +7493,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B105" s="9">
         <v>46118.5906265625</v>
@@ -7529,13 +7530,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7545,7 +7546,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B106" s="5">
         <v>46118.59063387732</v>
@@ -7582,13 +7583,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7598,7 +7599,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B107" s="9">
         <v>46118.590655486114</v>
@@ -7633,13 +7634,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7649,7 +7650,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B108" s="5">
         <v>46118.59066162037</v>
@@ -7684,13 +7685,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7700,7 +7701,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B109" s="9">
         <v>46118.59066710648</v>
@@ -7735,13 +7736,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7751,7 +7752,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B110" s="5">
         <v>46118.55591270833</v>
@@ -7761,7 +7762,7 @@
         <v>46183.194774386575</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7786,13 +7787,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q110" s="5">
         <v>46182</v>
@@ -7812,7 +7813,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B111" s="9">
         <v>46118.590705243056</v>
@@ -7849,13 +7850,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7865,7 +7866,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B112" s="5">
         <v>46118.59071275463</v>
@@ -7902,13 +7903,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7918,7 +7919,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B113" s="9">
         <v>46118.590720092594</v>
@@ -7955,13 +7956,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7971,7 +7972,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B114" s="5">
         <v>46118.590727835646</v>
@@ -8008,13 +8009,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8024,7 +8025,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B115" s="9">
         <v>46118.59073534722</v>
@@ -8061,13 +8062,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8077,7 +8078,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B116" s="5">
         <v>46118.55591954861</v>
@@ -8087,7 +8088,7 @@
         <v>46118.63950689815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8111,7 +8112,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8124,7 +8125,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B117" s="9">
         <v>46118.555923148146</v>
@@ -8134,16 +8135,16 @@
         <v>46184.18063726852</v>
       </c>
       <c r="E117" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G117" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="F117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G117" s="10" t="s">
+      <c r="H117" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8159,13 +8160,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q117" s="9">
         <v>46183</v>
@@ -8185,7 +8186,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B118" s="5">
         <v>46118.590793020834</v>
@@ -8201,10 +8202,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8220,7 +8221,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>140</v>
@@ -8236,7 +8237,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B119" s="9">
         <v>46118.59080049768</v>
@@ -8252,10 +8253,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8271,7 +8272,7 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>140</v>
@@ -8287,7 +8288,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B120" s="5">
         <v>46118.59080680556</v>
@@ -8303,10 +8304,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8322,7 +8323,7 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>140</v>
@@ -8338,7 +8339,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B121" s="9">
         <v>46118.59081555555</v>
@@ -8354,10 +8355,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="I121" s="10"/>
       <c r="J121" s="9">
@@ -8373,7 +8374,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>140</v>
@@ -8389,7 +8390,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B122" s="5">
         <v>46118.590822777776</v>
@@ -8405,10 +8406,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8424,7 +8425,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>140</v>
@@ -8440,7 +8441,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B123" s="9">
         <v>46118.55592798611</v>
@@ -8450,7 +8451,7 @@
         <v>46185.17432103009</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8475,13 +8476,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q123" s="9">
         <v>46184</v>
@@ -8501,7 +8502,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B124" s="5">
         <v>46118.59087519676</v>
@@ -8536,13 +8537,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8552,7 +8553,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B125" s="9">
         <v>46118.590883240744</v>
@@ -8587,13 +8588,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8603,7 +8604,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B126" s="5">
         <v>46118.59089157407</v>
@@ -8638,13 +8639,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8654,7 +8655,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B127" s="9">
         <v>46118.590897835646</v>
@@ -8689,13 +8690,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8705,7 +8706,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B128" s="5">
         <v>46118.5909049537</v>
@@ -8740,13 +8741,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8756,17 +8757,17 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B129" s="9">
         <v>46118.555932511576</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46186.16794060185</v>
+        <v>46205.9034525</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8791,13 +8792,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O129" s="10" t="s">
         <v>138</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q129" s="9">
         <v>46185</v>
@@ -8817,14 +8818,16 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B130" s="5">
         <v>46118.59095414352</v>
       </c>
-      <c r="C130" s="6"/>
+      <c r="C130" s="5">
+        <v>46205.90322601852</v>
+      </c>
       <c r="D130" s="5">
-        <v>46185.168594965275</v>
+        <v>46205.903228587966</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>140</v>
@@ -8852,13 +8855,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8868,14 +8871,16 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B131" s="9">
         <v>46118.590966759264</v>
       </c>
-      <c r="C131" s="10"/>
+      <c r="C131" s="9">
+        <v>46205.903334953706</v>
+      </c>
       <c r="D131" s="9">
-        <v>46185.16859673611</v>
+        <v>46205.90334321759</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>140</v>
@@ -8903,13 +8908,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -8919,14 +8924,16 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B132" s="5">
         <v>46118.590973796294</v>
       </c>
-      <c r="C132" s="6"/>
+      <c r="C132" s="5">
+        <v>46205.90344625</v>
+      </c>
       <c r="D132" s="5">
-        <v>46185.168597951386</v>
+        <v>46205.903448171295</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>140</v>
@@ -8954,13 +8961,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -8970,7 +8977,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B133" s="9">
         <v>46118.590979953704</v>
@@ -9005,13 +9012,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>155</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9021,7 +9028,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B134" s="5">
         <v>46118.59098489583</v>
@@ -9056,13 +9063,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>155</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9072,7 +9079,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B135" s="9">
         <v>46118.55593715278</v>
@@ -9082,7 +9089,7 @@
         <v>46189.2078791088</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9107,13 +9114,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>138</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q135" s="9">
         <v>46188</v>
@@ -9133,14 +9140,14 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B136" s="5">
         <v>46118.59103105324</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46188.168568113426</v>
+        <v>46205.90323694445</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>140</v>
@@ -9168,13 +9175,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9184,14 +9191,14 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B137" s="9">
         <v>46118.591039039355</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46188.16856979167</v>
+        <v>46205.903351307876</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>140</v>
@@ -9219,13 +9226,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9235,14 +9242,14 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B138" s="5">
         <v>46118.59104641204</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46188.168570995374</v>
+        <v>46205.90345366899</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>140</v>
@@ -9270,13 +9277,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9286,7 +9293,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B139" s="9">
         <v>46118.59105258102</v>
@@ -9321,13 +9328,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9337,7 +9344,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B140" s="5">
         <v>46118.59105829861</v>
@@ -9372,13 +9379,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9388,7 +9395,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B141" s="9">
         <v>46118.55594259259</v>
@@ -9398,7 +9405,7 @@
         <v>46118.64758575232</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>25</v>
@@ -9422,7 +9429,7 @@
         <v>26</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>26</v>
@@ -9435,7 +9442,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B142" s="5">
         <v>46118.55594550926</v>
@@ -9445,16 +9452,16 @@
         <v>46198.16908622685</v>
       </c>
       <c r="E142" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G142" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G142" s="6" t="s">
+      <c r="H142" s="6" t="s">
         <v>324</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>325</v>
       </c>
       <c r="I142" s="5">
         <v>46189</v>
@@ -9472,13 +9479,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q142" s="5">
         <v>46197</v>
@@ -9498,7 +9505,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B143" s="9">
         <v>46118.55595019676</v>
@@ -9508,16 +9515,16 @@
         <v>46198.16908620371</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>325</v>
       </c>
       <c r="I143" s="9">
         <v>46189</v>
@@ -9535,13 +9542,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q143" s="9">
         <v>46197</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -7437,7 +7437,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46205.48581650463</v>
+        <v>46206.491583634255</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>265</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -6076,7 +6076,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.50782400463</v>
+        <v>46209.59626342593</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>225</v>
@@ -6461,9 +6461,11 @@
       <c r="B86" s="5">
         <v>46118.55583459491</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46209.59615225694</v>
+      </c>
       <c r="D86" s="5">
-        <v>46197.609448206014</v>
+        <v>46209.5961674537</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>236</v>
@@ -6511,10 +6513,10 @@
         <v>83</v>
       </c>
       <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="11" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="U86" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6683,9 +6685,11 @@
       <c r="B90" s="5">
         <v>46118.59035967593</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46209.595921608794</v>
+      </c>
       <c r="D90" s="5">
-        <v>46205.90627893519</v>
+        <v>46209.59592381945</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>140</v>
@@ -6734,9 +6738,11 @@
       <c r="B91" s="9">
         <v>46118.59036834491</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="9">
+        <v>46209.595953703705</v>
+      </c>
       <c r="D91" s="9">
-        <v>46205.9062803125</v>
+        <v>46209.59595494213</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>140</v>
@@ -6958,7 +6964,7 @@
         <v>46197.50767422454</v>
       </c>
       <c r="D95" s="9">
-        <v>46204.716907951384</v>
+        <v>46209.59592782408</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>140</v>
@@ -7064,7 +7070,7 @@
         <v>46197.507801064814</v>
       </c>
       <c r="D97" s="9">
-        <v>46204.71690859954</v>
+        <v>46209.595960335646</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>140</v>
@@ -7113,9 +7119,11 @@
       <c r="B98" s="5">
         <v>46118.55584987269</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46209.596253842596</v>
+      </c>
       <c r="D98" s="5">
-        <v>46197.42458010417</v>
+        <v>46209.59626658565</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>254</v>
@@ -7161,10 +7169,10 @@
         <v>83</v>
       </c>
       <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="11" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="U98" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7333,9 +7341,11 @@
       <c r="B102" s="5">
         <v>46118.59056115741</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46209.59622841435</v>
+      </c>
       <c r="D102" s="5">
-        <v>46205.904663124995</v>
+        <v>46209.596230208335</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>140</v>
@@ -7384,9 +7394,11 @@
       <c r="B103" s="9">
         <v>46118.590569293985</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C103" s="9">
+        <v>46209.59623454861</v>
+      </c>
       <c r="D103" s="9">
-        <v>46205.90466431713</v>
+        <v>46209.5962359838</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>140</v>
@@ -7657,7 +7669,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46178.16914135417</v>
+        <v>46209.59623668982</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>140</v>
@@ -7708,7 +7720,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46178.16914265046</v>
+        <v>46209.59624372685</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>140</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="328">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -988,6 +988,9 @@
   </si>
   <si>
     <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213955238648475</t>
@@ -1086,7 +1089,7 @@
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1126,6 +1129,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFe8384f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1171,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1190,6 +1198,7 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8097,7 +8106,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46118.63950689815</v>
+        <v>46211.68919077546</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>282</v>
@@ -8774,9 +8783,11 @@
       <c r="B129" s="9">
         <v>46118.555932511576</v>
       </c>
-      <c r="C129" s="10"/>
+      <c r="C129" s="9">
+        <v>46211.68918386574</v>
+      </c>
       <c r="D129" s="9">
-        <v>46205.9034525</v>
+        <v>46211.689641018515</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>303</v>
@@ -8822,15 +8833,15 @@
         <v>83</v>
       </c>
       <c r="T129" s="10">
-        <v>0</v>
-      </c>
-      <c r="U129" s="11" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="U129" s="12" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B130" s="5">
         <v>46118.59095414352</v>
@@ -8873,7 +8884,7 @@
         <v>140</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8883,7 +8894,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B131" s="9">
         <v>46118.590966759264</v>
@@ -8926,7 +8937,7 @@
         <v>140</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -8936,7 +8947,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B132" s="5">
         <v>46118.590973796294</v>
@@ -8979,7 +8990,7 @@
         <v>140</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -8989,14 +9000,16 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B133" s="9">
         <v>46118.590979953704</v>
       </c>
-      <c r="C133" s="10"/>
+      <c r="C133" s="9">
+        <v>46211.68925275463</v>
+      </c>
       <c r="D133" s="9">
-        <v>46185.16859903935</v>
+        <v>46211.68925461806</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>140</v>
@@ -9030,7 +9043,7 @@
         <v>155</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9040,14 +9053,16 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B134" s="5">
         <v>46118.59098489583</v>
       </c>
-      <c r="C134" s="6"/>
+      <c r="C134" s="5">
+        <v>46211.6896266088</v>
+      </c>
       <c r="D134" s="5">
-        <v>46185.16860023148</v>
+        <v>46211.68962842593</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>140</v>
@@ -9081,7 +9096,7 @@
         <v>155</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9091,7 +9106,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B135" s="9">
         <v>46118.55593715278</v>
@@ -9101,7 +9116,7 @@
         <v>46189.2078791088</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9132,7 +9147,7 @@
         <v>138</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q135" s="9">
         <v>46188</v>
@@ -9152,7 +9167,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B136" s="5">
         <v>46118.59103105324</v>
@@ -9187,13 +9202,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9203,7 +9218,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B137" s="9">
         <v>46118.591039039355</v>
@@ -9238,13 +9253,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9254,7 +9269,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B138" s="5">
         <v>46118.59104641204</v>
@@ -9289,13 +9304,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9305,14 +9320,14 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B139" s="9">
         <v>46118.59105258102</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46188.1685722338</v>
+        <v>46211.68926010416</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>140</v>
@@ -9340,13 +9355,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>140</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9356,14 +9371,14 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B140" s="5">
         <v>46118.59105829861</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46188.16857356481</v>
+        <v>46211.689634594906</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>140</v>
@@ -9391,13 +9406,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9407,7 +9422,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B141" s="9">
         <v>46118.55594259259</v>
@@ -9417,7 +9432,7 @@
         <v>46118.64758575232</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>25</v>
@@ -9441,7 +9456,7 @@
         <v>26</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>26</v>
@@ -9454,7 +9469,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B142" s="5">
         <v>46118.55594550926</v>
@@ -9464,16 +9479,16 @@
         <v>46198.16908622685</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I142" s="5">
         <v>46189</v>
@@ -9491,13 +9506,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q142" s="5">
         <v>46197</v>
@@ -9517,7 +9532,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B143" s="9">
         <v>46118.55595019676</v>
@@ -9527,16 +9542,16 @@
         <v>46198.16908620371</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I143" s="9">
         <v>46189</v>
@@ -9554,13 +9569,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q143" s="9">
         <v>46197</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46205.48434983796</v>
+        <v>46212.603153310185</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>140</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46181.168651678236</v>
+        <v>46212.6031597338</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>140</v>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46206.491583634255</v>
+        <v>46212.604835833336</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>265</v>
@@ -7625,9 +7625,11 @@
       <c r="B107" s="9">
         <v>46118.590655486114</v>
       </c>
-      <c r="C107" s="10"/>
+      <c r="C107" s="9">
+        <v>46212.603143518514</v>
+      </c>
       <c r="D107" s="9">
-        <v>46205.48434523148</v>
+        <v>46212.603145636574</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>140</v>
@@ -7676,9 +7678,11 @@
       <c r="B108" s="5">
         <v>46118.59066162037</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46212.60315292824</v>
+      </c>
       <c r="D108" s="5">
-        <v>46209.59623668982</v>
+        <v>46212.60315480324</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>140</v>
@@ -7780,7 +7784,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46183.194774386575</v>
+        <v>46212.60504456019</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>273</v>
@@ -7839,9 +7843,11 @@
       <c r="B111" s="9">
         <v>46118.590705243056</v>
       </c>
-      <c r="C111" s="10"/>
+      <c r="C111" s="9">
+        <v>46212.604972974535</v>
+      </c>
       <c r="D111" s="9">
-        <v>46182.168110810184</v>
+        <v>46212.60497458333</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>140</v>
@@ -7892,9 +7898,11 @@
       <c r="B112" s="5">
         <v>46118.59071275463</v>
       </c>
-      <c r="C112" s="6"/>
+      <c r="C112" s="5">
+        <v>46212.60503894676</v>
+      </c>
       <c r="D112" s="5">
-        <v>46182.1681121875</v>
+        <v>46212.605040243056</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>140</v>
@@ -8214,7 +8222,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46183.16824416666</v>
+        <v>46212.60498076389</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>140</v>
@@ -8265,7 +8273,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46183.16824571759</v>
+        <v>46212.605045856486</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>140</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -7784,7 +7784,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46212.60504456019</v>
+        <v>46213.545008796296</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>273</v>
@@ -7953,9 +7953,11 @@
       <c r="B113" s="9">
         <v>46118.590720092594</v>
       </c>
-      <c r="C113" s="10"/>
+      <c r="C113" s="9">
+        <v>46213.54487947917</v>
+      </c>
       <c r="D113" s="9">
-        <v>46182.16811331018</v>
+        <v>46213.54488215278</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>140</v>
@@ -8006,9 +8008,11 @@
       <c r="B114" s="5">
         <v>46118.590727835646</v>
       </c>
-      <c r="C114" s="6"/>
+      <c r="C114" s="5">
+        <v>46213.54500266204</v>
+      </c>
       <c r="D114" s="5">
-        <v>46182.16811451389</v>
+        <v>46213.54500438657</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>140</v>
@@ -8324,7 +8328,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46183.168246875</v>
+        <v>46213.54488901621</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>140</v>
@@ -8375,7 +8379,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46183.16824814815</v>
+        <v>46213.54501027778</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>140</v>
@@ -8477,7 +8481,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46185.17432103009</v>
+        <v>46213.54550826389</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>294</v>
@@ -8536,9 +8540,11 @@
       <c r="B124" s="5">
         <v>46118.59087519676</v>
       </c>
-      <c r="C124" s="6"/>
+      <c r="C124" s="5">
+        <v>46213.54530194444</v>
+      </c>
       <c r="D124" s="5">
-        <v>46184.168032511574</v>
+        <v>46213.54530355324</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>140</v>
@@ -8587,9 +8593,11 @@
       <c r="B125" s="9">
         <v>46118.590883240744</v>
       </c>
-      <c r="C125" s="10"/>
+      <c r="C125" s="9">
+        <v>46213.54537613426</v>
+      </c>
       <c r="D125" s="9">
-        <v>46184.168034201386</v>
+        <v>46213.54537761574</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>140</v>
@@ -8638,9 +8646,11 @@
       <c r="B126" s="5">
         <v>46118.59089157407</v>
       </c>
-      <c r="C126" s="6"/>
+      <c r="C126" s="5">
+        <v>46213.545447592594</v>
+      </c>
       <c r="D126" s="5">
-        <v>46184.16803541667</v>
+        <v>46213.545449004625</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>140</v>
@@ -8689,9 +8699,11 @@
       <c r="B127" s="9">
         <v>46118.590897835646</v>
       </c>
-      <c r="C127" s="10"/>
+      <c r="C127" s="9">
+        <v>46213.545501875</v>
+      </c>
       <c r="D127" s="9">
-        <v>46184.168036863426</v>
+        <v>46213.545503692134</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>155</v>
@@ -8858,7 +8870,7 @@
         <v>46205.90322601852</v>
       </c>
       <c r="D130" s="5">
-        <v>46205.903228587966</v>
+        <v>46213.545309085646</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>140</v>
@@ -8911,7 +8923,7 @@
         <v>46205.903334953706</v>
       </c>
       <c r="D131" s="9">
-        <v>46205.90334321759</v>
+        <v>46213.54538173611</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>140</v>
@@ -8964,7 +8976,7 @@
         <v>46205.90344625</v>
       </c>
       <c r="D132" s="5">
-        <v>46205.903448171295</v>
+        <v>46213.54545359954</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>140</v>
@@ -9017,7 +9029,7 @@
         <v>46211.68925275463</v>
       </c>
       <c r="D133" s="9">
-        <v>46211.68925461806</v>
+        <v>46213.5455090162</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>140</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -7458,7 +7458,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46217.59453184028</v>
+        <v>46218.60629443287</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>265</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -3517,7 +3517,7 @@
         <v>46134.856089803245</v>
       </c>
       <c r="D34" s="5">
-        <v>46134.856103495375</v>
+        <v>46222.46568204861</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3857,7 +3857,7 @@
         <v>46135.505314317124</v>
       </c>
       <c r="D40" s="5">
-        <v>46135.52260231481</v>
+        <v>46222.465698368054</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -4197,7 +4197,7 @@
         <v>46135.505592835645</v>
       </c>
       <c r="D46" s="5">
-        <v>46135.50560496528</v>
+        <v>46222.46576027777</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>78</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="326">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>propuesta rodete ot 4280</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete ot 4280</t>
@@ -2417,7 +2420,7 @@
         <v>46192.91310200232</v>
       </c>
       <c r="D16" s="5">
-        <v>46192.91310392361</v>
+        <v>46223.60528942129</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2426,9 +2429,11 @@
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I16" s="5">
         <v>46105</v>
       </c>
@@ -2451,7 +2456,7 @@
         <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="5">
         <v>46106</v>
@@ -2471,7 +2476,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="9">
         <v>46118.555615578705</v>
@@ -2483,7 +2488,7 @@
         <v>46134.85241319444</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2516,7 +2521,7 @@
         <v>52</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="9">
         <v>46106</v>
@@ -2536,7 +2541,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46118.55562122686</v>
@@ -2545,18 +2550,20 @@
         <v>46181.67167443287</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.671691550924</v>
+        <v>46223.6052853125</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I18" s="5">
         <v>46135</v>
       </c>
@@ -2576,10 +2583,10 @@
         <v>64</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46121</v>
@@ -2588,7 +2595,7 @@
         <v>46121</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2599,7 +2606,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46118.55542568287</v>
@@ -2611,7 +2618,7 @@
         <v>46192.91330840278</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>25</v>
@@ -2635,7 +2642,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>26</v>
@@ -2652,7 +2659,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46118.5556269213</v>
@@ -2664,16 +2671,16 @@
         <v>46182.67873262732</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I20" s="5">
         <v>46107</v>
@@ -2691,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="5">
         <v>46048</v>
@@ -2717,7 +2724,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46118.55563141203</v>
@@ -2729,16 +2736,16 @@
         <v>46169.85558454861</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I21" s="9">
         <v>46107</v>
@@ -2756,13 +2763,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>67</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
@@ -2773,12 +2780,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46118.55563607639</v>
@@ -2790,16 +2797,16 @@
         <v>46182.67870440972</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I22" s="5">
         <v>46111</v>
@@ -2817,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2834,12 +2841,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46118.555640624996</v>
@@ -2851,16 +2858,16 @@
         <v>46192.88989348379</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I23" s="9">
         <v>46107</v>
@@ -2878,13 +2885,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q23" s="9">
         <v>46128</v>
@@ -2893,7 +2900,7 @@
         <v>46107</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T23" s="10">
         <v>1</v>
@@ -2904,7 +2911,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46118.55564542824</v>
@@ -2916,16 +2923,16 @@
         <v>46192.913113912036</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I24" s="5">
         <v>46107</v>
@@ -2943,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2960,12 +2967,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46118.55564990741</v>
@@ -2977,16 +2984,16 @@
         <v>46192.88986527778</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I25" s="9">
         <v>46111</v>
@@ -3004,13 +3011,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3021,12 +3028,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46118.555654606476</v>
@@ -3038,16 +3045,16 @@
         <v>46182.67902225694</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I26" s="5">
         <v>46107</v>
@@ -3065,13 +3072,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="5">
         <v>46142</v>
@@ -3080,7 +3087,7 @@
         <v>46107</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3091,7 +3098,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46118.55565927083</v>
@@ -3103,16 +3110,16 @@
         <v>46169.85540111111</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I27" s="9">
         <v>46107</v>
@@ -3130,13 +3137,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3147,12 +3154,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46118.55566380787</v>
@@ -3164,16 +3171,16 @@
         <v>46182.67899886574</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I28" s="5">
         <v>46118</v>
@@ -3191,13 +3198,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3208,12 +3215,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46118.55566881945</v>
@@ -3225,16 +3232,16 @@
         <v>46169.85534873843</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I29" s="9">
         <v>46118</v>
@@ -3252,13 +3259,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3269,12 +3276,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46118.55567340278</v>
@@ -3286,16 +3293,16 @@
         <v>46181.671818483796</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I30" s="5">
         <v>46136</v>
@@ -3313,13 +3320,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q30" s="5">
         <v>46150</v>
@@ -3328,7 +3335,7 @@
         <v>46136</v>
       </c>
       <c r="S30" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3339,7 +3346,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46118.55568293981</v>
@@ -3351,16 +3358,16 @@
         <v>46181.671733344905</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I31" s="9">
         <v>46136</v>
@@ -3378,13 +3385,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3395,12 +3402,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46118.55568802083</v>
@@ -3412,16 +3419,16 @@
         <v>46181.67179341435</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I32" s="5">
         <v>46142</v>
@@ -3439,13 +3446,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3456,12 +3463,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46118.5554312037</v>
@@ -3471,7 +3478,7 @@
         <v>46135.50561945602</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>25</v>
@@ -3495,7 +3502,7 @@
         <v>26</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3508,7 +3515,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46118.55573724537</v>
@@ -3520,16 +3527,16 @@
         <v>46222.46568204861</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I34" s="5">
         <v>46106</v>
@@ -3547,13 +3554,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="5">
         <v>46112</v>
@@ -3573,7 +3580,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46118.58934402778</v>
@@ -3585,16 +3592,16 @@
         <v>46134.85589640046</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="9">
         <v>46106</v>
@@ -3612,13 +3619,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3628,7 +3635,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46118.58935734954</v>
@@ -3640,16 +3647,16 @@
         <v>46134.855904895834</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46106</v>
@@ -3667,13 +3674,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3683,7 +3690,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46118.58936491898</v>
@@ -3695,16 +3702,16 @@
         <v>46134.85606556713</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46106</v>
@@ -3722,13 +3729,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3738,7 +3745,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46118.58937265046</v>
@@ -3750,16 +3757,16 @@
         <v>46134.85607190972</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46106</v>
@@ -3777,13 +3784,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3793,7 +3800,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46118.5893790625</v>
@@ -3805,16 +3812,16 @@
         <v>46134.85607811343</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I39" s="9">
         <v>46106</v>
@@ -3832,13 +3839,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3848,7 +3855,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46118.55574388889</v>
@@ -3860,16 +3867,16 @@
         <v>46222.465698368054</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I40" s="5">
         <v>46127</v>
@@ -3887,13 +3894,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q40" s="5">
         <v>46133</v>
@@ -3902,7 +3909,7 @@
         <v>46127</v>
       </c>
       <c r="S40" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3913,7 +3920,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46118.58948621528</v>
@@ -3925,16 +3932,16 @@
         <v>46135.50526961806</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I41" s="9">
         <v>46127</v>
@@ -3952,13 +3959,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3968,7 +3975,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46118.589619189814</v>
@@ -3980,16 +3987,16 @@
         <v>46135.50528020834</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I42" s="5">
         <v>46127</v>
@@ -4007,13 +4014,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4023,7 +4030,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="9">
         <v>46118.589635729164</v>
@@ -4035,16 +4042,16 @@
         <v>46135.50528708333</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I43" s="9">
         <v>46127</v>
@@ -4062,13 +4069,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4078,7 +4085,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" s="5">
         <v>46118.58964931713</v>
@@ -4090,16 +4097,16 @@
         <v>46135.50529516204</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I44" s="5">
         <v>46127</v>
@@ -4117,13 +4124,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4133,7 +4140,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B45" s="9">
         <v>46118.5896587037</v>
@@ -4145,16 +4152,16 @@
         <v>46135.50530211805</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I45" s="9">
         <v>46127</v>
@@ -4172,13 +4179,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4188,7 +4195,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B46" s="5">
         <v>46118.55575109954</v>
@@ -4200,16 +4207,16 @@
         <v>46222.46576027777</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I46" s="5">
         <v>46134</v>
@@ -4227,13 +4234,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q46" s="5">
         <v>46134</v>
@@ -4242,7 +4249,7 @@
         <v>46134</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4253,7 +4260,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B47" s="9">
         <v>46118.58972679398</v>
@@ -4265,16 +4272,16 @@
         <v>46135.505555069445</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="9">
@@ -4290,13 +4297,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4306,7 +4313,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B48" s="5">
         <v>46118.58974760417</v>
@@ -4318,16 +4325,16 @@
         <v>46135.50556056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4343,13 +4350,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4359,7 +4366,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B49" s="9">
         <v>46118.58975269676</v>
@@ -4371,16 +4378,16 @@
         <v>46135.50556795139</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4396,13 +4403,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4412,7 +4419,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B50" s="5">
         <v>46118.58976391204</v>
@@ -4424,16 +4431,16 @@
         <v>46135.50557504629</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4449,13 +4456,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4465,7 +4472,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B51" s="9">
         <v>46118.589758912036</v>
@@ -4477,16 +4484,16 @@
         <v>46135.50558240741</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4502,13 +4509,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4518,7 +4525,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B52" s="5">
         <v>46118.55575893518</v>
@@ -4528,16 +4535,16 @@
         <v>46182.20622399305</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I52" s="5">
         <v>46181</v>
@@ -4555,13 +4562,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q52" s="5">
         <v>46181</v>
@@ -4570,18 +4577,18 @@
         <v>46181</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B53" s="9">
         <v>46118.589869131945</v>
@@ -4591,16 +4598,16 @@
         <v>46205.48494059028</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I53" s="9">
         <v>46181</v>
@@ -4618,13 +4625,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4634,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B54" s="5">
         <v>46118.589883333334</v>
@@ -4644,16 +4651,16 @@
         <v>46205.48496365741</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I54" s="5">
         <v>46181</v>
@@ -4671,13 +4678,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4687,7 +4694,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B55" s="9">
         <v>46118.589890312505</v>
@@ -4697,16 +4704,16 @@
         <v>46212.603153310185</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I55" s="9">
         <v>46181</v>
@@ -4724,13 +4731,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4740,7 +4747,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B56" s="5">
         <v>46118.58992050926</v>
@@ -4750,16 +4757,16 @@
         <v>46181.168653182875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I56" s="5">
         <v>46181</v>
@@ -4777,13 +4784,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4793,7 +4800,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B57" s="9">
         <v>46118.589899548606</v>
@@ -4803,16 +4810,16 @@
         <v>46212.6031597338</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I57" s="9">
         <v>46181</v>
@@ -4830,13 +4837,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4846,7 +4853,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B58" s="5">
         <v>46118.55576480324</v>
@@ -4858,7 +4865,7 @@
         <v>46181.67205032408</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4882,7 +4889,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4895,7 +4902,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B59" s="9">
         <v>46118.55576952547</v>
@@ -4907,16 +4914,16 @@
         <v>46181.67191517361</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I59" s="9">
         <v>46153</v>
@@ -4934,13 +4941,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q59" s="9">
         <v>46154</v>
@@ -4949,7 +4956,7 @@
         <v>46153</v>
       </c>
       <c r="S59" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -4960,7 +4967,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B60" s="5">
         <v>46118.55577607639</v>
@@ -4972,16 +4979,16 @@
         <v>46181.671966932874</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I60" s="5">
         <v>46155</v>
@@ -4999,13 +5006,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q60" s="5">
         <v>46156</v>
@@ -5014,7 +5021,7 @@
         <v>46155</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5025,7 +5032,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B61" s="9">
         <v>46118.55578122685</v>
@@ -5037,7 +5044,7 @@
         <v>46197.77594626158</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5061,7 +5068,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5078,7 +5085,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B62" s="5">
         <v>46118.55578460648</v>
@@ -5090,16 +5097,16 @@
         <v>46181.67222788194</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I62" s="5">
         <v>46155</v>
@@ -5117,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q62" s="5">
         <v>46157</v>
@@ -5132,7 +5139,7 @@
         <v>46155</v>
       </c>
       <c r="S62" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5143,7 +5150,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B63" s="9">
         <v>46118.555790115744</v>
@@ -5155,16 +5162,16 @@
         <v>46191.71034409722</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I63" s="9">
         <v>46160</v>
@@ -5182,13 +5189,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q63" s="9">
         <v>46164</v>
@@ -5197,7 +5204,7 @@
         <v>46160</v>
       </c>
       <c r="S63" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T63" s="10">
         <v>1</v>
@@ -5208,7 +5215,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B64" s="5">
         <v>46118.59005789352</v>
@@ -5220,16 +5227,16 @@
         <v>46181.672338564815</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I64" s="5">
         <v>46160</v>
@@ -5247,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5263,7 +5270,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B65" s="9">
         <v>46118.590067604164</v>
@@ -5275,16 +5282,16 @@
         <v>46181.672352442125</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I65" s="9">
         <v>46160</v>
@@ -5302,13 +5309,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5318,7 +5325,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B66" s="5">
         <v>46118.5900759838</v>
@@ -5330,16 +5337,16 @@
         <v>46181.672366307874</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I66" s="5">
         <v>46160</v>
@@ -5357,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5373,7 +5380,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B67" s="9">
         <v>46118.590097962966</v>
@@ -5385,16 +5392,16 @@
         <v>46191.71031108796</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I67" s="9">
         <v>46160</v>
@@ -5412,13 +5419,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5428,7 +5435,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B68" s="5">
         <v>46118.59010253473</v>
@@ -5440,16 +5447,16 @@
         <v>46191.710318530095</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I68" s="5">
         <v>46160</v>
@@ -5467,13 +5474,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5483,7 +5490,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B69" s="9">
         <v>46118.55579684028</v>
@@ -5495,16 +5502,16 @@
         <v>46191.709365358794</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I69" s="9">
         <v>46167</v>
@@ -5522,13 +5529,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q69" s="9">
         <v>46167</v>
@@ -5537,7 +5544,7 @@
         <v>46167</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T69" s="10">
         <v>1</v>
@@ -5548,7 +5555,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B70" s="5">
         <v>46118.59015388889</v>
@@ -5560,16 +5567,16 @@
         <v>46181.67244473379</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I70" s="5">
         <v>46167</v>
@@ -5587,13 +5594,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5603,7 +5610,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B71" s="9">
         <v>46118.59016236111</v>
@@ -5615,16 +5622,16 @@
         <v>46181.672458078705</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I71" s="9">
         <v>46167</v>
@@ -5642,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5658,7 +5665,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B72" s="5">
         <v>46118.59017135417</v>
@@ -5670,16 +5677,16 @@
         <v>46181.672464999996</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I72" s="5">
         <v>46167</v>
@@ -5697,13 +5704,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5713,7 +5720,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B73" s="9">
         <v>46118.59019241898</v>
@@ -5725,16 +5732,16 @@
         <v>46191.7103152662</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I73" s="9">
         <v>46167</v>
@@ -5752,13 +5759,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5768,7 +5775,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B74" s="5">
         <v>46118.590197488425</v>
@@ -5780,16 +5787,16 @@
         <v>46191.7103265162</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I74" s="5">
         <v>46167</v>
@@ -5807,13 +5814,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5823,7 +5830,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B75" s="9">
         <v>46118.55580327546</v>
@@ -5835,7 +5842,7 @@
         <v>46205.90630074074</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -5859,7 +5866,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -5876,7 +5883,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B76" s="5">
         <v>46118.55580685185</v>
@@ -5888,16 +5895,16 @@
         <v>46204.716915474535</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5913,13 +5920,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q76" s="5">
         <v>46113</v>
@@ -5939,7 +5946,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B77" s="9">
         <v>46118.55581320602</v>
@@ -5951,16 +5958,16 @@
         <v>46205.90467159722</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -5976,13 +5983,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q77" s="9">
         <v>46129</v>
@@ -5991,7 +5998,7 @@
         <v>46129</v>
       </c>
       <c r="S77" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T77" s="10">
         <v>1</v>
@@ -6002,7 +6009,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B78" s="5">
         <v>46118.55581936342</v>
@@ -6014,16 +6021,16 @@
         <v>46205.90628471065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6039,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q78" s="5">
         <v>46146</v>
@@ -6054,7 +6061,7 @@
         <v>46146</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6065,7 +6072,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B79" s="9">
         <v>46118.55582516204</v>
@@ -6075,7 +6082,7 @@
         <v>46209.59626342593</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>25</v>
@@ -6099,7 +6106,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6112,7 +6119,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B80" s="5">
         <v>46118.55582877315</v>
@@ -6121,18 +6128,20 @@
         <v>46197.4232071875</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.42322075232</v>
+        <v>46223.60610878472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I80" s="5">
         <v>46168</v>
       </c>
@@ -6149,13 +6158,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6164,7 +6173,7 @@
         <v>46168</v>
       </c>
       <c r="S80" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6175,7 +6184,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B81" s="9">
         <v>46118.590250625</v>
@@ -6184,18 +6193,20 @@
         <v>46197.42301266204</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.423014942135</v>
+        <v>46223.60542445602</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I81" s="9">
         <v>46168</v>
       </c>
@@ -6212,13 +6223,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6228,7 +6239,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B82" s="5">
         <v>46118.590259641205</v>
@@ -6237,18 +6248,20 @@
         <v>46197.42305077546</v>
       </c>
       <c r="D82" s="5">
-        <v>46197.42305252315</v>
+        <v>46223.60542057871</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I82" s="5">
         <v>46168</v>
       </c>
@@ -6265,13 +6278,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6281,7 +6294,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B83" s="9">
         <v>46118.59026761574</v>
@@ -6290,18 +6303,20 @@
         <v>46197.423102430555</v>
       </c>
       <c r="D83" s="9">
-        <v>46197.42310400463</v>
+        <v>46223.605416562496</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I83" s="9">
         <v>46168</v>
       </c>
@@ -6318,13 +6333,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6334,7 +6349,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B84" s="5">
         <v>46118.590275636576</v>
@@ -6343,18 +6358,20 @@
         <v>46197.42314728009</v>
       </c>
       <c r="D84" s="5">
-        <v>46197.423148842594</v>
+        <v>46223.60541210648</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I84" s="5">
         <v>46168</v>
       </c>
@@ -6371,13 +6388,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6387,7 +6404,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B85" s="9">
         <v>46118.59028430555</v>
@@ -6396,18 +6413,20 @@
         <v>46197.42319270833</v>
       </c>
       <c r="D85" s="9">
-        <v>46197.42319425926</v>
+        <v>46223.60540677083</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I85" s="9">
         <v>46168</v>
       </c>
@@ -6424,13 +6443,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6440,7 +6459,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B86" s="5">
         <v>46118.55583459491</v>
@@ -6449,18 +6468,20 @@
         <v>46209.59615225694</v>
       </c>
       <c r="D86" s="5">
-        <v>46209.5961674537</v>
+        <v>46223.606105405095</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I86" s="5">
         <v>46175</v>
       </c>
@@ -6477,13 +6498,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q86" s="5">
         <v>46175</v>
@@ -6492,7 +6513,7 @@
         <v>46175</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -6503,7 +6524,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B87" s="9">
         <v>46118.59033478009</v>
@@ -6512,18 +6533,20 @@
         <v>46197.50709427083</v>
       </c>
       <c r="D87" s="9">
-        <v>46205.90627537037</v>
+        <v>46223.605516296295</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
         <v>46175</v>
@@ -6538,13 +6561,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6554,7 +6577,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B88" s="5">
         <v>46118.59034447916</v>
@@ -6563,18 +6586,20 @@
         <v>46197.50715157407</v>
       </c>
       <c r="D88" s="5">
-        <v>46205.90627636574</v>
+        <v>46223.605512650465</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
         <v>46175</v>
@@ -6589,13 +6614,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6605,7 +6630,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B89" s="9">
         <v>46118.590352141204</v>
@@ -6614,18 +6639,20 @@
         <v>46197.50723920139</v>
       </c>
       <c r="D89" s="9">
-        <v>46205.90627747685</v>
+        <v>46223.605509189816</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
         <v>46175</v>
@@ -6640,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6656,7 +6683,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B90" s="5">
         <v>46118.59035967593</v>
@@ -6665,18 +6692,20 @@
         <v>46209.595921608794</v>
       </c>
       <c r="D90" s="5">
-        <v>46209.59592381945</v>
+        <v>46223.60550493056</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
         <v>46175</v>
@@ -6691,13 +6720,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6707,7 +6736,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B91" s="9">
         <v>46118.59036834491</v>
@@ -6716,18 +6745,20 @@
         <v>46209.595953703705</v>
       </c>
       <c r="D91" s="9">
-        <v>46209.59595494213</v>
+        <v>46223.60550006945</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
         <v>46175</v>
@@ -6742,13 +6773,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6758,7 +6789,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B92" s="5">
         <v>46118.55584244213</v>
@@ -6767,18 +6798,20 @@
         <v>46197.50781607639</v>
       </c>
       <c r="D92" s="5">
-        <v>46197.50782737268</v>
+        <v>46223.60610163194</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46176</v>
@@ -6793,13 +6826,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q92" s="5">
         <v>46176</v>
@@ -6808,7 +6841,7 @@
         <v>46176</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -6819,7 +6852,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B93" s="9">
         <v>46118.59042068287</v>
@@ -6828,18 +6861,20 @@
         <v>46197.50749427083</v>
       </c>
       <c r="D93" s="9">
-        <v>46204.716905740745</v>
+        <v>46223.605617071764</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
         <v>46176</v>
@@ -6854,13 +6889,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6870,7 +6905,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B94" s="5">
         <v>46118.5904280324</v>
@@ -6879,18 +6914,20 @@
         <v>46197.507576828706</v>
       </c>
       <c r="D94" s="5">
-        <v>46204.71690671296</v>
+        <v>46223.60561297454</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
         <v>46176</v>
@@ -6905,13 +6942,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6921,7 +6958,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B95" s="9">
         <v>46118.59044465278</v>
@@ -6930,18 +6967,20 @@
         <v>46197.50767422454</v>
       </c>
       <c r="D95" s="9">
-        <v>46209.59592782408</v>
+        <v>46223.605608831014</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
         <v>46176</v>
@@ -6956,13 +6995,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6972,7 +7011,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B96" s="5">
         <v>46118.5904391088</v>
@@ -6981,18 +7020,20 @@
         <v>46197.50773788194</v>
       </c>
       <c r="D96" s="5">
-        <v>46204.71690747685</v>
+        <v>46223.605605289355</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
         <v>46176</v>
@@ -7007,13 +7048,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7023,7 +7064,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B97" s="9">
         <v>46118.59045233796</v>
@@ -7032,18 +7073,20 @@
         <v>46197.507801064814</v>
       </c>
       <c r="D97" s="9">
-        <v>46209.595960335646</v>
+        <v>46223.605599953706</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
         <v>46176</v>
@@ -7058,13 +7101,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7074,7 +7117,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B98" s="5">
         <v>46118.55584987269</v>
@@ -7083,18 +7126,20 @@
         <v>46209.596253842596</v>
       </c>
       <c r="D98" s="5">
-        <v>46209.59626658565</v>
+        <v>46223.60609758102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
         <v>46177</v>
@@ -7109,13 +7154,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q98" s="5">
         <v>46177</v>
@@ -7124,7 +7169,7 @@
         <v>46177</v>
       </c>
       <c r="S98" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -7135,7 +7180,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B99" s="9">
         <v>46118.590539282406</v>
@@ -7144,18 +7189,20 @@
         <v>46197.42437898148</v>
       </c>
       <c r="D99" s="9">
-        <v>46205.90466006944</v>
+        <v>46223.605747187496</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
         <v>46177</v>
@@ -7170,13 +7217,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7186,7 +7233,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B100" s="5">
         <v>46118.590546666666</v>
@@ -7195,18 +7242,20 @@
         <v>46197.42449445602</v>
       </c>
       <c r="D100" s="5">
-        <v>46205.90466118055</v>
+        <v>46223.60574302083</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46177</v>
@@ -7221,13 +7270,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7237,7 +7286,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B101" s="9">
         <v>46118.590554027774</v>
@@ -7246,18 +7295,20 @@
         <v>46197.42457260417</v>
       </c>
       <c r="D101" s="9">
-        <v>46205.90466188657</v>
+        <v>46223.605738252314</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
         <v>46177</v>
@@ -7272,13 +7323,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7288,7 +7339,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B102" s="5">
         <v>46118.59056115741</v>
@@ -7297,18 +7348,20 @@
         <v>46209.59622841435</v>
       </c>
       <c r="D102" s="5">
-        <v>46209.596230208335</v>
+        <v>46223.6057341088</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
         <v>46177</v>
@@ -7323,13 +7376,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7339,7 +7392,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B103" s="9">
         <v>46118.590569293985</v>
@@ -7348,18 +7401,20 @@
         <v>46209.59623454861</v>
       </c>
       <c r="D103" s="9">
-        <v>46209.5962359838</v>
+        <v>46223.60572732639</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
         <v>46177</v>
@@ -7374,13 +7429,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7390,25 +7445,27 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B104" s="5">
         <v>46118.5558574537</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46218.60629443287</v>
+        <v>46223.606089340276</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I104" s="5">
         <v>46178</v>
       </c>
@@ -7425,13 +7482,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q104" s="5">
         <v>46178</v>
@@ -7440,18 +7497,18 @@
         <v>46178</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B105" s="9">
         <v>46118.5906265625</v>
@@ -7460,18 +7517,20 @@
         <v>46205.48493550926</v>
       </c>
       <c r="D105" s="9">
-        <v>46205.48493684028</v>
+        <v>46223.6058402662</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
         <v>46178</v>
@@ -7486,13 +7545,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7502,7 +7561,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B106" s="5">
         <v>46118.59063387732</v>
@@ -7511,18 +7570,20 @@
         <v>46205.48495603009</v>
       </c>
       <c r="D106" s="5">
-        <v>46205.48495760417</v>
+        <v>46223.605836145834</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
         <v>46178</v>
@@ -7537,13 +7598,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7553,7 +7614,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B107" s="9">
         <v>46118.590655486114</v>
@@ -7562,18 +7623,20 @@
         <v>46212.603143518514</v>
       </c>
       <c r="D107" s="9">
-        <v>46212.603145636574</v>
+        <v>46223.60583134259</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
         <v>46178</v>
@@ -7588,13 +7651,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7604,7 +7667,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B108" s="5">
         <v>46118.59066162037</v>
@@ -7613,18 +7676,20 @@
         <v>46212.60315292824</v>
       </c>
       <c r="D108" s="5">
-        <v>46212.60315480324</v>
+        <v>46223.60582783565</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
         <v>46178</v>
@@ -7639,13 +7704,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7655,25 +7720,27 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B109" s="9">
         <v>46118.59066710648</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46209.59624372685</v>
+        <v>46223.60582304398</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I109" s="10"/>
       <c r="J109" s="9">
         <v>46178</v>
@@ -7688,13 +7755,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7704,25 +7771,27 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B110" s="5">
         <v>46118.55591270833</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46213.545008796296</v>
+        <v>46223.60608873842</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46182</v>
@@ -7737,13 +7806,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q110" s="5">
         <v>46182</v>
@@ -7752,18 +7821,18 @@
         <v>46182</v>
       </c>
       <c r="S110" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
       </c>
       <c r="U110" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B111" s="9">
         <v>46118.590705243056</v>
@@ -7772,18 +7841,20 @@
         <v>46212.604972974535</v>
       </c>
       <c r="D111" s="9">
-        <v>46212.60497458333</v>
+        <v>46223.60595203703</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I111" s="9">
         <v>46182</v>
       </c>
@@ -7800,13 +7871,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7816,7 +7887,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B112" s="5">
         <v>46118.59071275463</v>
@@ -7825,18 +7896,20 @@
         <v>46212.60503894676</v>
       </c>
       <c r="D112" s="5">
-        <v>46212.605040243056</v>
+        <v>46223.60594784722</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I112" s="5">
         <v>46182</v>
       </c>
@@ -7853,13 +7926,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7869,7 +7942,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B113" s="9">
         <v>46118.590720092594</v>
@@ -7878,18 +7951,20 @@
         <v>46213.54487947917</v>
       </c>
       <c r="D113" s="9">
-        <v>46213.54488215278</v>
+        <v>46223.605943912036</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I113" s="9">
         <v>46182</v>
       </c>
@@ -7906,13 +7981,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7922,7 +7997,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B114" s="5">
         <v>46118.590727835646</v>
@@ -7931,18 +8006,20 @@
         <v>46213.54500266204</v>
       </c>
       <c r="D114" s="5">
-        <v>46213.54500438657</v>
+        <v>46223.60594033565</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I114" s="5">
         <v>46182</v>
       </c>
@@ -7959,13 +8036,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7975,25 +8052,27 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B115" s="9">
         <v>46118.59073534722</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46182.16811570602</v>
+        <v>46223.60593523148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I115" s="9">
         <v>46182</v>
       </c>
@@ -8010,13 +8089,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8026,7 +8105,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B116" s="5">
         <v>46118.55591954861</v>
@@ -8036,7 +8115,7 @@
         <v>46211.68919077546</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8060,7 +8139,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8073,7 +8152,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B117" s="9">
         <v>46118.555923148146</v>
@@ -8083,16 +8162,16 @@
         <v>46184.18063726852</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8108,13 +8187,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q117" s="9">
         <v>46183</v>
@@ -8123,18 +8202,18 @@
         <v>46183</v>
       </c>
       <c r="S117" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T117" s="10">
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B118" s="5">
         <v>46118.590793020834</v>
@@ -8144,16 +8223,16 @@
         <v>46212.60498076389</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8169,13 +8248,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8185,7 +8264,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B119" s="9">
         <v>46118.59080049768</v>
@@ -8195,16 +8274,16 @@
         <v>46212.605045856486</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8220,13 +8299,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8236,7 +8315,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B120" s="5">
         <v>46118.59080680556</v>
@@ -8246,16 +8325,16 @@
         <v>46213.54488901621</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8271,13 +8350,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8287,7 +8366,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B121" s="9">
         <v>46118.59081555555</v>
@@ -8297,16 +8376,16 @@
         <v>46213.54501027778</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I121" s="10"/>
       <c r="J121" s="9">
@@ -8322,13 +8401,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8338,7 +8417,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B122" s="5">
         <v>46118.590822777776</v>
@@ -8348,16 +8427,16 @@
         <v>46183.16824943287</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8373,13 +8452,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8389,7 +8468,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B123" s="9">
         <v>46118.55592798611</v>
@@ -8399,7 +8478,7 @@
         <v>46213.54550826389</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8422,13 +8501,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q123" s="9">
         <v>46184</v>
@@ -8437,18 +8516,18 @@
         <v>46184</v>
       </c>
       <c r="S123" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T123" s="10">
         <v>0</v>
       </c>
       <c r="U123" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B124" s="5">
         <v>46118.59087519676</v>
@@ -8457,18 +8536,20 @@
         <v>46213.54530194444</v>
       </c>
       <c r="D124" s="5">
-        <v>46213.54530355324</v>
+        <v>46223.60620898148</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
         <v>46184</v>
@@ -8483,13 +8564,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8499,7 +8580,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B125" s="9">
         <v>46118.590883240744</v>
@@ -8508,18 +8589,20 @@
         <v>46213.54537613426</v>
       </c>
       <c r="D125" s="9">
-        <v>46213.54537761574</v>
+        <v>46223.60620524306</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I125" s="10"/>
       <c r="J125" s="9">
         <v>46184</v>
@@ -8534,13 +8617,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8550,7 +8633,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B126" s="5">
         <v>46118.59089157407</v>
@@ -8559,18 +8642,20 @@
         <v>46213.545447592594</v>
       </c>
       <c r="D126" s="5">
-        <v>46213.545449004625</v>
+        <v>46223.60620116898</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
         <v>46184</v>
@@ -8585,13 +8670,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8601,7 +8686,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B127" s="9">
         <v>46118.590897835646</v>
@@ -8610,18 +8695,20 @@
         <v>46213.545501875</v>
       </c>
       <c r="D127" s="9">
-        <v>46213.545503692134</v>
+        <v>46223.606197800924</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
         <v>46184</v>
@@ -8636,13 +8723,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8652,25 +8739,27 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B128" s="5">
         <v>46118.5909049537</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46184.16803811342</v>
+        <v>46223.60619332176</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
         <v>46184</v>
@@ -8685,13 +8774,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8701,7 +8790,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B129" s="9">
         <v>46118.555932511576</v>
@@ -8713,16 +8802,16 @@
         <v>46211.689641018515</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -8738,13 +8827,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q129" s="9">
         <v>46185</v>
@@ -8753,18 +8842,18 @@
         <v>46185</v>
       </c>
       <c r="S129" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T129" s="10">
         <v>1</v>
       </c>
       <c r="U129" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B130" s="5">
         <v>46118.59095414352</v>
@@ -8776,16 +8865,16 @@
         <v>46213.545309085646</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -8801,13 +8890,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8817,7 +8906,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B131" s="9">
         <v>46118.590966759264</v>
@@ -8829,16 +8918,16 @@
         <v>46213.54538173611</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -8854,13 +8943,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -8870,7 +8959,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B132" s="5">
         <v>46118.590973796294</v>
@@ -8882,16 +8971,16 @@
         <v>46213.54545359954</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -8907,13 +8996,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -8923,7 +9012,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B133" s="9">
         <v>46118.590979953704</v>
@@ -8935,16 +9024,16 @@
         <v>46213.5455090162</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -8960,13 +9049,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -8976,7 +9065,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B134" s="5">
         <v>46118.59098489583</v>
@@ -8988,16 +9077,16 @@
         <v>46211.68962842593</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9013,13 +9102,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9029,7 +9118,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B135" s="9">
         <v>46118.55593715278</v>
@@ -9039,16 +9128,16 @@
         <v>46189.2078791088</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I135" s="10"/>
       <c r="J135" s="9">
@@ -9064,13 +9153,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q135" s="9">
         <v>46188</v>
@@ -9079,18 +9168,18 @@
         <v>46188</v>
       </c>
       <c r="S135" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T135" s="10">
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B136" s="5">
         <v>46118.59103105324</v>
@@ -9100,16 +9189,16 @@
         <v>46205.90323694445</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9125,13 +9214,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9141,7 +9230,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B137" s="9">
         <v>46118.591039039355</v>
@@ -9151,16 +9240,16 @@
         <v>46205.903351307876</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I137" s="10"/>
       <c r="J137" s="9">
@@ -9176,13 +9265,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9192,7 +9281,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B138" s="5">
         <v>46118.59104641204</v>
@@ -9202,16 +9291,16 @@
         <v>46205.90345366899</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9227,13 +9316,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9243,7 +9332,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B139" s="9">
         <v>46118.59105258102</v>
@@ -9253,16 +9342,16 @@
         <v>46211.68926010416</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I139" s="10"/>
       <c r="J139" s="9">
@@ -9278,13 +9367,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9294,7 +9383,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B140" s="5">
         <v>46118.59105829861</v>
@@ -9304,16 +9393,16 @@
         <v>46211.689634594906</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9329,13 +9418,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9345,7 +9434,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B141" s="9">
         <v>46118.55594259259</v>
@@ -9355,7 +9444,7 @@
         <v>46118.64758575232</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>25</v>
@@ -9379,7 +9468,7 @@
         <v>26</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>26</v>
@@ -9392,7 +9481,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B142" s="5">
         <v>46118.55594550926</v>
@@ -9402,16 +9491,16 @@
         <v>46198.16908622685</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I142" s="5">
         <v>46189</v>
@@ -9429,13 +9518,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q142" s="5">
         <v>46197</v>
@@ -9444,18 +9533,18 @@
         <v>46189</v>
       </c>
       <c r="S142" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T142" s="6">
         <v>0</v>
       </c>
       <c r="U142" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B143" s="9">
         <v>46118.55595019676</v>
@@ -9465,16 +9554,16 @@
         <v>46198.16908620371</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I143" s="9">
         <v>46189</v>
@@ -9492,13 +9581,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q143" s="9">
         <v>46197</v>
@@ -9507,13 +9596,13 @@
         <v>46189</v>
       </c>
       <c r="S143" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T143" s="10">
         <v>0</v>
       </c>
       <c r="U143" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="326">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46213.54550826389</v>
+        <v>46223.83569194445</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>292</v>
@@ -8484,9 +8484,11 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="I123" s="10"/>
       <c r="J123" s="9">
         <v>46184</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="327">
   <si>
     <t xml:space="preserve">50001532 - XEMORTIZ AMERICAS GOLD </t>
   </si>
@@ -900,6 +900,9 @@
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213955238648460</t>
   </si>
   <si>
@@ -985,9 +988,6 @@
   </si>
   <si>
     <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213955238648475</t>
@@ -6098,9 +6098,11 @@
       <c r="B79" s="9">
         <v>46118.55582516204</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="9">
+        <v>46244.567055057865</v>
+      </c>
       <c r="D79" s="9">
-        <v>46230.57886513889</v>
+        <v>46244.56707113426</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>224</v>
@@ -6135,8 +6137,12 @@
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
       <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
+      <c r="T79" s="10">
+        <v>1</v>
+      </c>
+      <c r="U79" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
@@ -7801,9 +7807,11 @@
       <c r="B110" s="5">
         <v>46118.55591270833</v>
       </c>
-      <c r="C110" s="6"/>
+      <c r="C110" s="5">
+        <v>46244.566615902775</v>
+      </c>
       <c r="D110" s="5">
-        <v>46237.5352658912</v>
+        <v>46244.56662542824</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>272</v>
@@ -7849,15 +7857,15 @@
         <v>82</v>
       </c>
       <c r="T110" s="6">
-        <v>0</v>
-      </c>
-      <c r="U110" s="7" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="U110" s="12" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B111" s="9">
         <v>46118.590705243056</v>
@@ -7902,7 +7910,7 @@
         <v>139</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7912,7 +7920,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B112" s="5">
         <v>46118.59071275463</v>
@@ -7957,7 +7965,7 @@
         <v>139</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7967,7 +7975,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B113" s="9">
         <v>46118.590720092594</v>
@@ -8012,7 +8020,7 @@
         <v>139</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8022,7 +8030,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B114" s="5">
         <v>46118.590727835646</v>
@@ -8067,7 +8075,7 @@
         <v>139</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8077,14 +8085,16 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B115" s="9">
         <v>46118.59073534722</v>
       </c>
-      <c r="C115" s="10"/>
+      <c r="C115" s="9">
+        <v>46244.56660078704</v>
+      </c>
       <c r="D115" s="9">
-        <v>46238.51291310185</v>
+        <v>46244.56660280093</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>139</v>
@@ -8120,7 +8130,7 @@
         <v>139</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8130,17 +8140,19 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B116" s="5">
         <v>46118.55591954861</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="5">
+        <v>46244.56703814815</v>
+      </c>
       <c r="D116" s="5">
-        <v>46211.68919077546</v>
+        <v>46244.56705233797</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8164,7 +8176,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8172,31 +8184,37 @@
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
       <c r="S116" s="6"/>
-      <c r="T116" s="6"/>
-      <c r="U116" s="6"/>
+      <c r="T116" s="6">
+        <v>1</v>
+      </c>
+      <c r="U116" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B117" s="9">
         <v>46118.555923148146</v>
       </c>
-      <c r="C117" s="10"/>
+      <c r="C117" s="9">
+        <v>46244.566789606484</v>
+      </c>
       <c r="D117" s="9">
-        <v>46184.18063726852</v>
+        <v>46244.56679628472</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8212,13 +8230,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>272</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q117" s="9">
         <v>46183</v>
@@ -8230,22 +8248,24 @@
         <v>82</v>
       </c>
       <c r="T117" s="10">
-        <v>0</v>
-      </c>
-      <c r="U117" s="11" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="U117" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B118" s="5">
         <v>46118.590793020834</v>
       </c>
-      <c r="C118" s="6"/>
+      <c r="C118" s="5">
+        <v>46244.5667706713</v>
+      </c>
       <c r="D118" s="5">
-        <v>46212.60498076389</v>
+        <v>46244.56677398148</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>139</v>
@@ -8254,10 +8274,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8273,7 +8293,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>139</v>
@@ -8289,14 +8309,16 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B119" s="9">
         <v>46118.59080049768</v>
       </c>
-      <c r="C119" s="10"/>
+      <c r="C119" s="9">
+        <v>46244.56677130787</v>
+      </c>
       <c r="D119" s="9">
-        <v>46212.605045856486</v>
+        <v>46244.566774363426</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>139</v>
@@ -8305,10 +8327,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8324,7 +8346,7 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>139</v>
@@ -8340,14 +8362,16 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B120" s="5">
         <v>46118.59080680556</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46244.5667718287</v>
+      </c>
       <c r="D120" s="5">
-        <v>46213.54488901621</v>
+        <v>46244.56677471065</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>139</v>
@@ -8356,10 +8380,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8375,7 +8399,7 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>139</v>
@@ -8391,14 +8415,16 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B121" s="9">
         <v>46118.59081555555</v>
       </c>
-      <c r="C121" s="10"/>
+      <c r="C121" s="9">
+        <v>46244.56677233796</v>
+      </c>
       <c r="D121" s="9">
-        <v>46213.54501027778</v>
+        <v>46244.56677506944</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>139</v>
@@ -8407,10 +8433,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I121" s="10"/>
       <c r="J121" s="9">
@@ -8426,7 +8452,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>139</v>
@@ -8442,14 +8468,16 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B122" s="5">
         <v>46118.590822777776</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="5">
+        <v>46244.5667728125</v>
+      </c>
       <c r="D122" s="5">
-        <v>46183.16824943287</v>
+        <v>46244.566775416664</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>139</v>
@@ -8458,10 +8486,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8477,7 +8505,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>139</v>
@@ -8493,17 +8521,19 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B123" s="9">
         <v>46118.55592798611</v>
       </c>
-      <c r="C123" s="10"/>
+      <c r="C123" s="9">
+        <v>46244.56683241898</v>
+      </c>
       <c r="D123" s="9">
-        <v>46237.535299027775</v>
+        <v>46244.56684324074</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8528,13 +8558,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q123" s="9">
         <v>46184</v>
@@ -8546,15 +8576,15 @@
         <v>82</v>
       </c>
       <c r="T123" s="10">
-        <v>0</v>
-      </c>
-      <c r="U123" s="7" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="U123" s="12" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B124" s="5">
         <v>46118.59087519676</v>
@@ -8563,7 +8593,7 @@
         <v>46213.54530194444</v>
       </c>
       <c r="D124" s="5">
-        <v>46223.60620898148</v>
+        <v>46244.566780671295</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>139</v>
@@ -8591,13 +8621,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8607,7 +8637,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B125" s="9">
         <v>46118.590883240744</v>
@@ -8616,7 +8646,7 @@
         <v>46213.54537613426</v>
       </c>
       <c r="D125" s="9">
-        <v>46223.60620524306</v>
+        <v>46244.566780486115</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>139</v>
@@ -8644,13 +8674,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>139</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8660,7 +8690,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B126" s="5">
         <v>46118.59089157407</v>
@@ -8669,7 +8699,7 @@
         <v>46213.545447592594</v>
       </c>
       <c r="D126" s="5">
-        <v>46223.60620116898</v>
+        <v>46244.566780520836</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>139</v>
@@ -8697,13 +8727,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8713,7 +8743,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B127" s="9">
         <v>46118.590897835646</v>
@@ -8722,7 +8752,7 @@
         <v>46213.545501875</v>
       </c>
       <c r="D127" s="9">
-        <v>46223.606197800924</v>
+        <v>46244.566780486115</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>154</v>
@@ -8750,13 +8780,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>139</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8766,14 +8796,16 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B128" s="5">
         <v>46118.5909049537</v>
       </c>
-      <c r="C128" s="6"/>
+      <c r="C128" s="5">
+        <v>46244.56681815972</v>
+      </c>
       <c r="D128" s="5">
-        <v>46223.60619332176</v>
+        <v>46244.566819722226</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>154</v>
@@ -8801,13 +8833,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8817,7 +8849,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B129" s="9">
         <v>46118.555932511576</v>
@@ -8829,7 +8861,7 @@
         <v>46211.689641018515</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8854,13 +8886,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O129" s="10" t="s">
         <v>137</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q129" s="9">
         <v>46185</v>
@@ -8875,7 +8907,7 @@
         <v>1</v>
       </c>
       <c r="U129" s="12" t="s">
-        <v>303</v>
+        <v>274</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -8917,7 +8949,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>139</v>
@@ -8970,7 +9002,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>139</v>
@@ -9023,7 +9055,7 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>139</v>
@@ -9076,7 +9108,7 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>154</v>
@@ -9101,7 +9133,7 @@
         <v>46211.6896266088</v>
       </c>
       <c r="D134" s="5">
-        <v>46211.68962842593</v>
+        <v>46244.566826678245</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>139</v>
@@ -9129,7 +9161,7 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>154</v>
@@ -9150,9 +9182,11 @@
       <c r="B135" s="9">
         <v>46118.55593715278</v>
       </c>
-      <c r="C135" s="10"/>
+      <c r="C135" s="9">
+        <v>46244.56694560185</v>
+      </c>
       <c r="D135" s="9">
-        <v>46189.2078791088</v>
+        <v>46244.56695628472</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>311</v>
@@ -9180,7 +9214,7 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>137</v>
@@ -9198,10 +9232,10 @@
         <v>82</v>
       </c>
       <c r="T135" s="10">
-        <v>0</v>
-      </c>
-      <c r="U135" s="11" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="U135" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9211,9 +9245,11 @@
       <c r="B136" s="5">
         <v>46118.59103105324</v>
       </c>
-      <c r="C136" s="6"/>
+      <c r="C136" s="5">
+        <v>46244.56692866898</v>
+      </c>
       <c r="D136" s="5">
-        <v>46205.90323694445</v>
+        <v>46244.56693162037</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>139</v>
@@ -9262,9 +9298,11 @@
       <c r="B137" s="9">
         <v>46118.591039039355</v>
       </c>
-      <c r="C137" s="10"/>
+      <c r="C137" s="9">
+        <v>46244.56692925926</v>
+      </c>
       <c r="D137" s="9">
-        <v>46205.903351307876</v>
+        <v>46244.56693195602</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>139</v>
@@ -9313,9 +9351,11 @@
       <c r="B138" s="5">
         <v>46118.59104641204</v>
       </c>
-      <c r="C138" s="6"/>
+      <c r="C138" s="5">
+        <v>46244.566929699075</v>
+      </c>
       <c r="D138" s="5">
-        <v>46205.90345366899</v>
+        <v>46244.56693226851</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>139</v>
@@ -9364,9 +9404,11 @@
       <c r="B139" s="9">
         <v>46118.59105258102</v>
       </c>
-      <c r="C139" s="10"/>
+      <c r="C139" s="9">
+        <v>46244.56693015047</v>
+      </c>
       <c r="D139" s="9">
-        <v>46211.68926010416</v>
+        <v>46244.56693260417</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>139</v>
@@ -9415,9 +9457,11 @@
       <c r="B140" s="5">
         <v>46118.59105829861</v>
       </c>
-      <c r="C140" s="6"/>
+      <c r="C140" s="5">
+        <v>46244.56693056713</v>
+      </c>
       <c r="D140" s="5">
-        <v>46211.689634594906</v>
+        <v>46244.56693295139</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>139</v>
@@ -9515,7 +9559,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46198.16908622685</v>
+        <v>46244.56696645833</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>322</v>
@@ -9565,8 +9609,8 @@
       <c r="T142" s="6">
         <v>0</v>
       </c>
-      <c r="U142" s="11" t="s">
-        <v>94</v>
+      <c r="U142" s="12" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -9578,7 +9622,7 @@
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.16908620371</v>
+        <v>46244.566967175924</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>326</v>
@@ -9628,8 +9672,8 @@
       <c r="T143" s="10">
         <v>0</v>
       </c>
-      <c r="U143" s="11" t="s">
-        <v>94</v>
+      <c r="U143" s="12" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -9510,9 +9510,11 @@
       <c r="B141" s="9">
         <v>46118.55594259259</v>
       </c>
-      <c r="C141" s="10"/>
+      <c r="C141" s="9">
+        <v>46245.76537715278</v>
+      </c>
       <c r="D141" s="9">
-        <v>46118.64758575232</v>
+        <v>46245.76544885417</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>319</v>
@@ -9557,9 +9559,11 @@
       <c r="B142" s="5">
         <v>46118.55594550926</v>
       </c>
-      <c r="C142" s="6"/>
+      <c r="C142" s="5">
+        <v>46245.76535796296</v>
+      </c>
       <c r="D142" s="5">
-        <v>46244.56696645833</v>
+        <v>46245.765377662035</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>322</v>
@@ -9607,10 +9611,10 @@
         <v>82</v>
       </c>
       <c r="T142" s="6">
-        <v>0</v>
-      </c>
-      <c r="U142" s="12" t="s">
-        <v>274</v>
+        <v>1</v>
+      </c>
+      <c r="U142" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -9620,9 +9624,11 @@
       <c r="B143" s="9">
         <v>46118.55595019676</v>
       </c>
-      <c r="C143" s="10"/>
+      <c r="C143" s="9">
+        <v>46245.76536282407</v>
+      </c>
       <c r="D143" s="9">
-        <v>46244.566967175924</v>
+        <v>46245.76537818287</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>326</v>
@@ -9670,10 +9676,10 @@
         <v>82</v>
       </c>
       <c r="T143" s="10">
-        <v>0</v>
-      </c>
-      <c r="U143" s="12" t="s">
-        <v>274</v>
+        <v>1</v>
+      </c>
+      <c r="U143" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -2618,7 +2618,7 @@
         <v>46192.91329202546</v>
       </c>
       <c r="D19" s="9">
-        <v>46192.91330840278</v>
+        <v>46250.22613664352</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1683,13 +1683,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.55540376157</v>
+        <v>46118.38873709491</v>
       </c>
       <c r="C4" s="5">
-        <v>46134.84973423611</v>
+        <v>46134.683067569444</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.84974535879</v>
+        <v>46134.683078692135</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1736,13 +1736,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46118.55556929398</v>
+        <v>46118.38890262731</v>
       </c>
       <c r="C5" s="9">
-        <v>46134.847409131944</v>
+        <v>46134.68074246528</v>
       </c>
       <c r="D5" s="9">
-        <v>46134.84745465278</v>
+        <v>46134.680787986115</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1799,13 +1799,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.5555727662</v>
+        <v>46118.388906099535</v>
       </c>
       <c r="C6" s="5">
-        <v>46134.848174328705</v>
+        <v>46134.68150766204</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.84818818287</v>
+        <v>46134.681521516206</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1862,13 +1862,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="9">
-        <v>46118.555575624996</v>
+        <v>46118.38890895833</v>
       </c>
       <c r="C7" s="9">
-        <v>46134.848471840276</v>
+        <v>46134.68180517361</v>
       </c>
       <c r="D7" s="9">
-        <v>46134.84848634259</v>
+        <v>46134.68181967593</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>40</v>
@@ -1925,13 +1925,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.555578287036</v>
+        <v>46118.38891162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46134.849233009256</v>
+        <v>46134.68256634259</v>
       </c>
       <c r="D8" s="5">
-        <v>46191.71012979167</v>
+        <v>46191.543463124995</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1988,13 +1988,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="9">
-        <v>46118.55558168981</v>
+        <v>46118.38891502315</v>
       </c>
       <c r="C9" s="9">
-        <v>46134.84972003472</v>
+        <v>46134.683053368055</v>
       </c>
       <c r="D9" s="9">
-        <v>46134.84973509259</v>
+        <v>46134.683068425926</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>47</v>
@@ -2051,13 +2051,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.5554109375</v>
+        <v>46118.38874427084</v>
       </c>
       <c r="C10" s="5">
-        <v>46192.91325913194</v>
+        <v>46192.74659246528</v>
       </c>
       <c r="D10" s="5">
-        <v>46192.91327583333</v>
+        <v>46192.74660916667</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2104,13 +2104,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="9">
-        <v>46118.55558501158</v>
+        <v>46118.38891834491</v>
       </c>
       <c r="C11" s="9">
-        <v>46134.851535752314</v>
+        <v>46134.68486908565</v>
       </c>
       <c r="D11" s="9">
-        <v>46171.91061798611</v>
+        <v>46171.74395131944</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>52</v>
@@ -2169,13 +2169,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.55558986111</v>
+        <v>46118.38892319445</v>
       </c>
       <c r="C12" s="5">
-        <v>46134.850894386575</v>
+        <v>46134.6842277199</v>
       </c>
       <c r="D12" s="5">
-        <v>46134.85090979167</v>
+        <v>46134.684243125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2234,13 +2234,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46118.55559503472</v>
+        <v>46118.388928368055</v>
       </c>
       <c r="C13" s="9">
-        <v>46134.85044589121</v>
+        <v>46134.683779224535</v>
       </c>
       <c r="D13" s="9">
-        <v>46134.85046350694</v>
+        <v>46134.683796840276</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2299,13 +2299,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.55541763889</v>
+        <v>46118.388750972226</v>
       </c>
       <c r="C14" s="5">
-        <v>46192.913118993056</v>
+        <v>46192.74645232639</v>
       </c>
       <c r="D14" s="5">
-        <v>46192.91314039352</v>
+        <v>46192.74647372685</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2352,13 +2352,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46118.55560518519</v>
+        <v>46118.38893851852</v>
       </c>
       <c r="C15" s="9">
-        <v>46134.85201509259</v>
+        <v>46134.685348425926</v>
       </c>
       <c r="D15" s="9">
-        <v>46134.85202921296</v>
+        <v>46134.6853625463</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2417,13 +2417,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.555610462965</v>
+        <v>46118.38894379629</v>
       </c>
       <c r="C16" s="5">
-        <v>46192.91310200232</v>
+        <v>46192.74643533565</v>
       </c>
       <c r="D16" s="5">
-        <v>46223.60528942129</v>
+        <v>46223.438622754635</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2482,13 +2482,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="9">
-        <v>46118.555615578705</v>
+        <v>46118.388948912034</v>
       </c>
       <c r="C17" s="9">
-        <v>46134.8523972338</v>
+        <v>46134.68573056713</v>
       </c>
       <c r="D17" s="9">
-        <v>46134.85241319444</v>
+        <v>46134.68574652778</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -2547,13 +2547,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.55562122686</v>
+        <v>46118.388954560185</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.67167443287</v>
+        <v>46181.5050077662</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.6052853125</v>
+        <v>46223.43861864583</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2612,13 +2612,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46118.55542568287</v>
+        <v>46118.388759016205</v>
       </c>
       <c r="C19" s="9">
-        <v>46192.91329202546</v>
+        <v>46192.74662535879</v>
       </c>
       <c r="D19" s="9">
-        <v>46250.22613664352</v>
+        <v>46250.059469976855</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2665,13 +2665,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.5556269213</v>
+        <v>46118.388960254626</v>
       </c>
       <c r="C20" s="5">
-        <v>46182.678718379626</v>
+        <v>46182.51205171296</v>
       </c>
       <c r="D20" s="5">
-        <v>46182.67873262732</v>
+        <v>46182.51206596065</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2730,13 +2730,13 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46118.55563141203</v>
+        <v>46118.38896474537</v>
       </c>
       <c r="C21" s="9">
-        <v>46155.897256944445</v>
+        <v>46155.73059027777</v>
       </c>
       <c r="D21" s="9">
-        <v>46169.85558454861</v>
+        <v>46169.68891788194</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2791,13 +2791,13 @@
         <v>95</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.55563607639</v>
+        <v>46118.38896940972</v>
       </c>
       <c r="C22" s="5">
-        <v>46182.67870244213</v>
+        <v>46182.512035775464</v>
       </c>
       <c r="D22" s="5">
-        <v>46182.67870440972</v>
+        <v>46182.51203774306</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2852,13 +2852,13 @@
         <v>98</v>
       </c>
       <c r="B23" s="9">
-        <v>46118.555640624996</v>
+        <v>46118.38897395833</v>
       </c>
       <c r="C23" s="9">
-        <v>46192.88987828704</v>
+        <v>46192.72321162037</v>
       </c>
       <c r="D23" s="9">
-        <v>46192.88989348379</v>
+        <v>46192.72322681713</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>99</v>
@@ -2917,13 +2917,13 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.55564542824</v>
+        <v>46118.38897876158</v>
       </c>
       <c r="C24" s="5">
-        <v>46192.8897287963</v>
+        <v>46192.72306212963</v>
       </c>
       <c r="D24" s="5">
-        <v>46192.913113912036</v>
+        <v>46192.74644724537</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -2978,13 +2978,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46118.55564990741</v>
+        <v>46118.388983240744</v>
       </c>
       <c r="C25" s="9">
-        <v>46192.889863564815</v>
+        <v>46192.72319689815</v>
       </c>
       <c r="D25" s="9">
-        <v>46192.88986527778</v>
+        <v>46192.723198611115</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3039,13 +3039,13 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.555654606476</v>
+        <v>46118.38898793982</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.67901127315</v>
+        <v>46182.51234460648</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.67902225694</v>
+        <v>46182.51235559028</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3104,13 +3104,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46118.55565927083</v>
+        <v>46118.38899260417</v>
       </c>
       <c r="C27" s="9">
-        <v>46134.89289440972</v>
+        <v>46134.72622774306</v>
       </c>
       <c r="D27" s="9">
-        <v>46169.85540111111</v>
+        <v>46169.68873444444</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3165,13 +3165,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.55566380787</v>
+        <v>46118.3889971412</v>
       </c>
       <c r="C28" s="5">
-        <v>46182.67899732639</v>
+        <v>46182.51233065972</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.67899886574</v>
+        <v>46182.51233219907</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3226,13 +3226,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46118.55566881945</v>
+        <v>46118.38900215278</v>
       </c>
       <c r="C29" s="9">
-        <v>46134.892935428245</v>
+        <v>46134.72626876157</v>
       </c>
       <c r="D29" s="9">
-        <v>46169.85534873843</v>
+        <v>46169.68868207176</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3287,13 +3287,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.55567340278</v>
+        <v>46118.389006736106</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.67180701389</v>
+        <v>46181.50514034722</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.671818483796</v>
+        <v>46181.50515181713</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3352,13 +3352,13 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46118.55568293981</v>
+        <v>46118.38901627315</v>
       </c>
       <c r="C31" s="9">
-        <v>46181.671732048606</v>
+        <v>46181.50506538195</v>
       </c>
       <c r="D31" s="9">
-        <v>46181.671733344905</v>
+        <v>46181.50506667824</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3413,13 +3413,13 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.55568802083</v>
+        <v>46118.38902135417</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.671791875</v>
+        <v>46181.505125208336</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.67179341435</v>
+        <v>46181.50512674768</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3474,13 +3474,13 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46118.5554312037</v>
+        <v>46118.38876453704</v>
       </c>
       <c r="C33" s="9">
-        <v>46238.542904270835</v>
+        <v>46238.37623760417</v>
       </c>
       <c r="D33" s="9">
-        <v>46238.54292103009</v>
+        <v>46238.37625436342</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3527,13 +3527,13 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.55573724537</v>
+        <v>46118.389070578705</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.856089803245</v>
+        <v>46134.68942313657</v>
       </c>
       <c r="D34" s="5">
-        <v>46222.46568204861</v>
+        <v>46222.29901538194</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3592,13 +3592,13 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46118.58934402778</v>
+        <v>46118.422677361115</v>
       </c>
       <c r="C35" s="9">
-        <v>46134.85589491898</v>
+        <v>46134.68922825232</v>
       </c>
       <c r="D35" s="9">
-        <v>46134.85589640046</v>
+        <v>46134.68922973379</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3647,13 +3647,13 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.58935734954</v>
+        <v>46118.42269068287</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.85590363426</v>
+        <v>46134.68923696759</v>
       </c>
       <c r="D36" s="5">
-        <v>46134.855904895834</v>
+        <v>46134.68923822917</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3702,13 +3702,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46118.58936491898</v>
+        <v>46118.42269825231</v>
       </c>
       <c r="C37" s="9">
-        <v>46134.856064039355</v>
+        <v>46134.689397372684</v>
       </c>
       <c r="D37" s="9">
-        <v>46134.85606556713</v>
+        <v>46134.68939890046</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>139</v>
@@ -3757,13 +3757,13 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.58937265046</v>
+        <v>46118.4227059838</v>
       </c>
       <c r="C38" s="5">
-        <v>46134.8560703588</v>
+        <v>46134.68940369213</v>
       </c>
       <c r="D38" s="5">
-        <v>46134.85607190972</v>
+        <v>46134.68940524306</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -3812,13 +3812,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="9">
-        <v>46118.5893790625</v>
+        <v>46118.42271239583</v>
       </c>
       <c r="C39" s="9">
-        <v>46134.85607678241</v>
+        <v>46134.68941011574</v>
       </c>
       <c r="D39" s="9">
-        <v>46134.85607811343</v>
+        <v>46134.68941144676</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>139</v>
@@ -3867,13 +3867,13 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.55574388889</v>
+        <v>46118.38907722222</v>
       </c>
       <c r="C40" s="5">
-        <v>46135.505314317124</v>
+        <v>46135.33864765047</v>
       </c>
       <c r="D40" s="5">
-        <v>46222.465698368054</v>
+        <v>46222.29903170139</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3932,13 +3932,13 @@
         <v>149</v>
       </c>
       <c r="B41" s="9">
-        <v>46118.58948621528</v>
+        <v>46118.42281954861</v>
       </c>
       <c r="C41" s="9">
-        <v>46135.505267789355</v>
+        <v>46135.33860112268</v>
       </c>
       <c r="D41" s="9">
-        <v>46135.50526961806</v>
+        <v>46135.33860295139</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>139</v>
@@ -3987,13 +3987,13 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.589619189814</v>
+        <v>46118.42295252315</v>
       </c>
       <c r="C42" s="5">
-        <v>46135.50527871528</v>
+        <v>46135.33861204861</v>
       </c>
       <c r="D42" s="5">
-        <v>46135.50528020834</v>
+        <v>46135.338613541666</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>139</v>
@@ -4042,13 +4042,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="9">
-        <v>46118.589635729164</v>
+        <v>46118.4229690625</v>
       </c>
       <c r="C43" s="9">
-        <v>46135.50528577546</v>
+        <v>46135.33861910879</v>
       </c>
       <c r="D43" s="9">
-        <v>46135.50528708333</v>
+        <v>46135.33862041667</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>154</v>
@@ -4097,13 +4097,13 @@
         <v>155</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.58964931713</v>
+        <v>46118.42298265046</v>
       </c>
       <c r="C44" s="5">
-        <v>46135.50529321759</v>
+        <v>46135.338626550925</v>
       </c>
       <c r="D44" s="5">
-        <v>46135.50529516204</v>
+        <v>46135.338628495374</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>154</v>
@@ -4152,13 +4152,13 @@
         <v>156</v>
       </c>
       <c r="B45" s="9">
-        <v>46118.5896587037</v>
+        <v>46118.42299203704</v>
       </c>
       <c r="C45" s="9">
-        <v>46135.50530085649</v>
+        <v>46135.338634189815</v>
       </c>
       <c r="D45" s="9">
-        <v>46135.50530211805</v>
+        <v>46135.33863545139</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>139</v>
@@ -4207,13 +4207,13 @@
         <v>157</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.55575109954</v>
+        <v>46118.38908443287</v>
       </c>
       <c r="C46" s="5">
-        <v>46135.505592835645</v>
+        <v>46135.33892616898</v>
       </c>
       <c r="D46" s="5">
-        <v>46222.46576027777</v>
+        <v>46222.29909361112</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>80</v>
@@ -4272,13 +4272,13 @@
         <v>159</v>
       </c>
       <c r="B47" s="9">
-        <v>46118.58972679398</v>
+        <v>46118.423060127316</v>
       </c>
       <c r="C47" s="9">
-        <v>46135.505553229166</v>
+        <v>46135.3388865625</v>
       </c>
       <c r="D47" s="9">
-        <v>46135.505555069445</v>
+        <v>46135.33888840278</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>139</v>
@@ -4325,13 +4325,13 @@
         <v>161</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.58974760417</v>
+        <v>46118.4230809375</v>
       </c>
       <c r="C48" s="5">
-        <v>46135.505559247686</v>
+        <v>46135.338892581014</v>
       </c>
       <c r="D48" s="5">
-        <v>46135.50556056713</v>
+        <v>46135.338893900465</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>139</v>
@@ -4378,13 +4378,13 @@
         <v>162</v>
       </c>
       <c r="B49" s="9">
-        <v>46118.58975269676</v>
+        <v>46118.42308603009</v>
       </c>
       <c r="C49" s="9">
-        <v>46135.505566527776</v>
+        <v>46135.33889986111</v>
       </c>
       <c r="D49" s="9">
-        <v>46135.50556795139</v>
+        <v>46135.33890128472</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>139</v>
@@ -4431,13 +4431,13 @@
         <v>163</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.58976391204</v>
+        <v>46118.423097245366</v>
       </c>
       <c r="C50" s="5">
-        <v>46135.505573229166</v>
+        <v>46135.3389065625</v>
       </c>
       <c r="D50" s="5">
-        <v>46135.50557504629</v>
+        <v>46135.33890837963</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>139</v>
@@ -4484,13 +4484,13 @@
         <v>164</v>
       </c>
       <c r="B51" s="9">
-        <v>46118.589758912036</v>
+        <v>46118.42309224537</v>
       </c>
       <c r="C51" s="9">
-        <v>46135.505581006946</v>
+        <v>46135.338914340275</v>
       </c>
       <c r="D51" s="9">
-        <v>46135.50558240741</v>
+        <v>46135.33891574074</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>139</v>
@@ -4537,13 +4537,13 @@
         <v>165</v>
       </c>
       <c r="B52" s="5">
-        <v>46118.55575893518</v>
+        <v>46118.38909226852</v>
       </c>
       <c r="C52" s="5">
-        <v>46238.51292800926</v>
+        <v>46238.346261342595</v>
       </c>
       <c r="D52" s="5">
-        <v>46238.51294119213</v>
+        <v>46238.346274525466</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>166</v>
@@ -4602,13 +4602,13 @@
         <v>169</v>
       </c>
       <c r="B53" s="9">
-        <v>46118.589869131945</v>
+        <v>46118.423202465274</v>
       </c>
       <c r="C53" s="9">
-        <v>46238.51286980324</v>
+        <v>46238.34620313658</v>
       </c>
       <c r="D53" s="9">
-        <v>46238.51287181713</v>
+        <v>46238.34620515046</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>139</v>
@@ -4657,13 +4657,13 @@
         <v>171</v>
       </c>
       <c r="B54" s="5">
-        <v>46118.589883333334</v>
+        <v>46118.42321666666</v>
       </c>
       <c r="C54" s="5">
-        <v>46238.512889942125</v>
+        <v>46238.34622327547</v>
       </c>
       <c r="D54" s="5">
-        <v>46238.512892025465</v>
+        <v>46238.34622535879</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>139</v>
@@ -4712,13 +4712,13 @@
         <v>172</v>
       </c>
       <c r="B55" s="9">
-        <v>46118.589890312505</v>
+        <v>46118.423223645834</v>
       </c>
       <c r="C55" s="9">
-        <v>46238.51289958334</v>
+        <v>46238.346232916665</v>
       </c>
       <c r="D55" s="9">
-        <v>46238.512901145834</v>
+        <v>46238.34623447916</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>139</v>
@@ -4767,13 +4767,13 @@
         <v>173</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.58992050926</v>
+        <v>46118.42325384259</v>
       </c>
       <c r="C56" s="5">
-        <v>46238.51290693287</v>
+        <v>46238.346240266204</v>
       </c>
       <c r="D56" s="5">
-        <v>46238.512908379635</v>
+        <v>46238.34624171296</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>139</v>
@@ -4822,13 +4822,13 @@
         <v>174</v>
       </c>
       <c r="B57" s="9">
-        <v>46118.589899548606</v>
+        <v>46118.42323288195</v>
       </c>
       <c r="C57" s="9">
-        <v>46238.51291261574</v>
+        <v>46238.34624594907</v>
       </c>
       <c r="D57" s="9">
-        <v>46238.51291413195</v>
+        <v>46238.34624746528</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>139</v>
@@ -4877,13 +4877,13 @@
         <v>175</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.55576480324</v>
+        <v>46118.38909813657</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.67196634259</v>
+        <v>46181.505299675926</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.67205032408</v>
+        <v>46181.50538365741</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>176</v>
@@ -4926,13 +4926,13 @@
         <v>178</v>
       </c>
       <c r="B59" s="9">
-        <v>46118.55576952547</v>
+        <v>46118.3891028588</v>
       </c>
       <c r="C59" s="9">
-        <v>46181.67190112268</v>
+        <v>46181.50523445602</v>
       </c>
       <c r="D59" s="9">
-        <v>46181.67191517361</v>
+        <v>46181.50524850695</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>179</v>
@@ -4991,13 +4991,13 @@
         <v>183</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.55577607639</v>
+        <v>46118.38910940972</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.671950752316</v>
+        <v>46181.50528408565</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.671966932874</v>
+        <v>46181.5053002662</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>184</v>
@@ -5056,13 +5056,13 @@
         <v>187</v>
       </c>
       <c r="B61" s="9">
-        <v>46118.55578122685</v>
+        <v>46118.38911456018</v>
       </c>
       <c r="C61" s="9">
-        <v>46197.775929456024</v>
+        <v>46197.60926278935</v>
       </c>
       <c r="D61" s="9">
-        <v>46197.77594626158</v>
+        <v>46197.60927959491</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>188</v>
@@ -5109,13 +5109,13 @@
         <v>190</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.55578460648</v>
+        <v>46118.38911793982</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.672212314814</v>
+        <v>46181.50554564815</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.67222788194</v>
+        <v>46181.50556121528</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>191</v>
@@ -5174,13 +5174,13 @@
         <v>195</v>
       </c>
       <c r="B63" s="9">
-        <v>46118.555790115744</v>
+        <v>46118.38912344907</v>
       </c>
       <c r="C63" s="9">
-        <v>46191.71033274305</v>
+        <v>46191.54366607639</v>
       </c>
       <c r="D63" s="9">
-        <v>46191.71034409722</v>
+        <v>46191.543677430556</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>196</v>
@@ -5239,13 +5239,13 @@
         <v>197</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.59005789352</v>
+        <v>46118.423391226854</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.6723374537</v>
+        <v>46181.50567078704</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.672338564815</v>
+        <v>46181.50567189815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>139</v>
@@ -5294,13 +5294,13 @@
         <v>200</v>
       </c>
       <c r="B65" s="9">
-        <v>46118.590067604164</v>
+        <v>46118.4234009375</v>
       </c>
       <c r="C65" s="9">
-        <v>46181.672350925925</v>
+        <v>46181.50568425926</v>
       </c>
       <c r="D65" s="9">
-        <v>46181.672352442125</v>
+        <v>46181.50568577547</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>139</v>
@@ -5349,13 +5349,13 @@
         <v>202</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.5900759838</v>
+        <v>46118.423409317125</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.67236503473</v>
+        <v>46181.505698368055</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.672366307874</v>
+        <v>46181.5056996412</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>139</v>
@@ -5404,13 +5404,13 @@
         <v>203</v>
       </c>
       <c r="B67" s="9">
-        <v>46118.590097962966</v>
+        <v>46118.423431296294</v>
       </c>
       <c r="C67" s="9">
-        <v>46191.71030983796</v>
+        <v>46191.543643171295</v>
       </c>
       <c r="D67" s="9">
-        <v>46191.71031108796</v>
+        <v>46191.5436444213</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>139</v>
@@ -5459,13 +5459,13 @@
         <v>204</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.59010253473</v>
+        <v>46118.423435868055</v>
       </c>
       <c r="C68" s="5">
-        <v>46191.71031711806</v>
+        <v>46191.54365045139</v>
       </c>
       <c r="D68" s="5">
-        <v>46191.710318530095</v>
+        <v>46191.54365186342</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>139</v>
@@ -5514,13 +5514,13 @@
         <v>205</v>
       </c>
       <c r="B69" s="9">
-        <v>46118.55579684028</v>
+        <v>46118.389130173615</v>
       </c>
       <c r="C69" s="9">
-        <v>46191.70935185185</v>
+        <v>46191.54268518518</v>
       </c>
       <c r="D69" s="9">
-        <v>46191.709365358794</v>
+        <v>46191.54269869213</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>206</v>
@@ -5579,13 +5579,13 @@
         <v>207</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.59015388889</v>
+        <v>46118.42348722222</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.67244342592</v>
+        <v>46181.50577675926</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.67244473379</v>
+        <v>46181.505778067134</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>139</v>
@@ -5634,13 +5634,13 @@
         <v>210</v>
       </c>
       <c r="B71" s="9">
-        <v>46118.59016236111</v>
+        <v>46118.42349569444</v>
       </c>
       <c r="C71" s="9">
-        <v>46181.672456597225</v>
+        <v>46181.505789930554</v>
       </c>
       <c r="D71" s="9">
-        <v>46181.672458078705</v>
+        <v>46181.50579141204</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>139</v>
@@ -5689,13 +5689,13 @@
         <v>211</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.59017135417</v>
+        <v>46118.4235046875</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.67246365741</v>
+        <v>46181.505796990736</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.672464999996</v>
+        <v>46181.50579833333</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>139</v>
@@ -5744,13 +5744,13 @@
         <v>212</v>
       </c>
       <c r="B73" s="9">
-        <v>46118.59019241898</v>
+        <v>46118.42352575231</v>
       </c>
       <c r="C73" s="9">
-        <v>46191.70928226852</v>
+        <v>46191.54261560185</v>
       </c>
       <c r="D73" s="9">
-        <v>46191.7103152662</v>
+        <v>46191.54364859954</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>139</v>
@@ -5799,13 +5799,13 @@
         <v>213</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.590197488425</v>
+        <v>46118.42353082176</v>
       </c>
       <c r="C74" s="5">
-        <v>46191.70933641204</v>
+        <v>46191.542669745366</v>
       </c>
       <c r="D74" s="5">
-        <v>46191.7103265162</v>
+        <v>46191.543659849536</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>139</v>
@@ -5854,13 +5854,13 @@
         <v>214</v>
       </c>
       <c r="B75" s="9">
-        <v>46118.55580327546</v>
+        <v>46118.38913660879</v>
       </c>
       <c r="C75" s="9">
-        <v>46205.906285624995</v>
+        <v>46205.73961895834</v>
       </c>
       <c r="D75" s="9">
-        <v>46205.90630074074</v>
+        <v>46205.739634074074</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>176</v>
@@ -5907,13 +5907,13 @@
         <v>216</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.55580685185</v>
+        <v>46118.38914018519</v>
       </c>
       <c r="C76" s="5">
-        <v>46204.71689967593</v>
+        <v>46204.55023300926</v>
       </c>
       <c r="D76" s="5">
-        <v>46204.716915474535</v>
+        <v>46204.55024880787</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>217</v>
@@ -5970,13 +5970,13 @@
         <v>219</v>
       </c>
       <c r="B77" s="9">
-        <v>46118.55581320602</v>
+        <v>46118.38914653935</v>
       </c>
       <c r="C77" s="9">
-        <v>46205.90465295139</v>
+        <v>46205.73798628472</v>
       </c>
       <c r="D77" s="9">
-        <v>46205.90467159722</v>
+        <v>46205.73800493055</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>220</v>
@@ -6033,13 +6033,13 @@
         <v>221</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.55581936342</v>
+        <v>46118.38915269676</v>
       </c>
       <c r="C78" s="5">
-        <v>46205.90626957176</v>
+        <v>46205.739602905094</v>
       </c>
       <c r="D78" s="5">
-        <v>46205.90628471065</v>
+        <v>46205.73961804398</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>222</v>
@@ -6096,13 +6096,13 @@
         <v>223</v>
       </c>
       <c r="B79" s="9">
-        <v>46118.55582516204</v>
+        <v>46118.38915849537</v>
       </c>
       <c r="C79" s="9">
-        <v>46244.567055057865</v>
+        <v>46244.40038839121</v>
       </c>
       <c r="D79" s="9">
-        <v>46244.56707113426</v>
+        <v>46244.4004044676</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>224</v>
@@ -6149,13 +6149,13 @@
         <v>226</v>
       </c>
       <c r="B80" s="5">
-        <v>46118.55582877315</v>
+        <v>46118.38916210648</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.4232071875</v>
+        <v>46197.25654052083</v>
       </c>
       <c r="D80" s="5">
-        <v>46223.60610878472</v>
+        <v>46223.439442118055</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>227</v>
@@ -6214,13 +6214,13 @@
         <v>228</v>
       </c>
       <c r="B81" s="9">
-        <v>46118.590250625</v>
+        <v>46118.423583958334</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.42301266204</v>
+        <v>46197.25634599537</v>
       </c>
       <c r="D81" s="9">
-        <v>46223.60542445602</v>
+        <v>46223.43875778935</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>139</v>
@@ -6269,13 +6269,13 @@
         <v>230</v>
       </c>
       <c r="B82" s="5">
-        <v>46118.590259641205</v>
+        <v>46118.423592974534</v>
       </c>
       <c r="C82" s="5">
-        <v>46197.42305077546</v>
+        <v>46197.2563841088</v>
       </c>
       <c r="D82" s="5">
-        <v>46223.60542057871</v>
+        <v>46223.438753912036</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>139</v>
@@ -6324,13 +6324,13 @@
         <v>231</v>
       </c>
       <c r="B83" s="9">
-        <v>46118.59026761574</v>
+        <v>46118.42360094907</v>
       </c>
       <c r="C83" s="9">
-        <v>46197.423102430555</v>
+        <v>46197.25643576389</v>
       </c>
       <c r="D83" s="9">
-        <v>46223.605416562496</v>
+        <v>46223.43874989584</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>139</v>
@@ -6379,13 +6379,13 @@
         <v>232</v>
       </c>
       <c r="B84" s="5">
-        <v>46118.590275636576</v>
+        <v>46118.42360896991</v>
       </c>
       <c r="C84" s="5">
-        <v>46197.42314728009</v>
+        <v>46197.256480613425</v>
       </c>
       <c r="D84" s="5">
-        <v>46223.60541210648</v>
+        <v>46223.43874543982</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>139</v>
@@ -6434,13 +6434,13 @@
         <v>233</v>
       </c>
       <c r="B85" s="9">
-        <v>46118.59028430555</v>
+        <v>46118.42361763889</v>
       </c>
       <c r="C85" s="9">
-        <v>46197.42319270833</v>
+        <v>46197.25652604167</v>
       </c>
       <c r="D85" s="9">
-        <v>46223.60540677083</v>
+        <v>46223.43874010417</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>139</v>
@@ -6489,13 +6489,13 @@
         <v>234</v>
       </c>
       <c r="B86" s="5">
-        <v>46118.55583459491</v>
+        <v>46118.38916792824</v>
       </c>
       <c r="C86" s="5">
-        <v>46209.59615225694</v>
+        <v>46209.42948559028</v>
       </c>
       <c r="D86" s="5">
-        <v>46223.606105405095</v>
+        <v>46223.43943873842</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>235</v>
@@ -6554,13 +6554,13 @@
         <v>236</v>
       </c>
       <c r="B87" s="9">
-        <v>46118.59033478009</v>
+        <v>46118.42366811342</v>
       </c>
       <c r="C87" s="9">
-        <v>46197.50709427083</v>
+        <v>46197.34042760417</v>
       </c>
       <c r="D87" s="9">
-        <v>46223.605516296295</v>
+        <v>46223.43884962963</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>139</v>
@@ -6607,13 +6607,13 @@
         <v>239</v>
       </c>
       <c r="B88" s="5">
-        <v>46118.59034447916</v>
+        <v>46118.423677812505</v>
       </c>
       <c r="C88" s="5">
-        <v>46197.50715157407</v>
+        <v>46197.34048490741</v>
       </c>
       <c r="D88" s="5">
-        <v>46223.605512650465</v>
+        <v>46223.438845983794</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>139</v>
@@ -6660,13 +6660,13 @@
         <v>240</v>
       </c>
       <c r="B89" s="9">
-        <v>46118.590352141204</v>
+        <v>46118.42368547454</v>
       </c>
       <c r="C89" s="9">
-        <v>46197.50723920139</v>
+        <v>46197.340572534726</v>
       </c>
       <c r="D89" s="9">
-        <v>46223.605509189816</v>
+        <v>46223.438842523145</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>139</v>
@@ -6713,13 +6713,13 @@
         <v>241</v>
       </c>
       <c r="B90" s="5">
-        <v>46118.59035967593</v>
+        <v>46118.42369300926</v>
       </c>
       <c r="C90" s="5">
-        <v>46209.595921608794</v>
+        <v>46209.42925494213</v>
       </c>
       <c r="D90" s="5">
-        <v>46223.60550493056</v>
+        <v>46223.438838263886</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>139</v>
@@ -6766,13 +6766,13 @@
         <v>242</v>
       </c>
       <c r="B91" s="9">
-        <v>46118.59036834491</v>
+        <v>46118.42370167824</v>
       </c>
       <c r="C91" s="9">
-        <v>46209.595953703705</v>
+        <v>46209.42928703704</v>
       </c>
       <c r="D91" s="9">
-        <v>46223.60550006945</v>
+        <v>46223.438833402775</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>139</v>
@@ -6819,13 +6819,13 @@
         <v>243</v>
       </c>
       <c r="B92" s="5">
-        <v>46118.55584244213</v>
+        <v>46118.38917577546</v>
       </c>
       <c r="C92" s="5">
-        <v>46197.50781607639</v>
+        <v>46197.34114940972</v>
       </c>
       <c r="D92" s="5">
-        <v>46223.60610163194</v>
+        <v>46223.43943496528</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>244</v>
@@ -6882,13 +6882,13 @@
         <v>245</v>
       </c>
       <c r="B93" s="9">
-        <v>46118.59042068287</v>
+        <v>46118.4237540162</v>
       </c>
       <c r="C93" s="9">
-        <v>46197.50749427083</v>
+        <v>46197.34082760417</v>
       </c>
       <c r="D93" s="9">
-        <v>46223.605617071764</v>
+        <v>46223.43895040509</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>139</v>
@@ -6935,13 +6935,13 @@
         <v>248</v>
       </c>
       <c r="B94" s="5">
-        <v>46118.5904280324</v>
+        <v>46118.423761365746</v>
       </c>
       <c r="C94" s="5">
-        <v>46197.507576828706</v>
+        <v>46197.340910162035</v>
       </c>
       <c r="D94" s="5">
-        <v>46223.60561297454</v>
+        <v>46223.43894630787</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>139</v>
@@ -6988,13 +6988,13 @@
         <v>249</v>
       </c>
       <c r="B95" s="9">
-        <v>46118.59044465278</v>
+        <v>46118.423777986114</v>
       </c>
       <c r="C95" s="9">
-        <v>46197.50767422454</v>
+        <v>46197.34100755787</v>
       </c>
       <c r="D95" s="9">
-        <v>46223.605608831014</v>
+        <v>46223.43894216436</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>139</v>
@@ -7041,13 +7041,13 @@
         <v>250</v>
       </c>
       <c r="B96" s="5">
-        <v>46118.5904391088</v>
+        <v>46118.423772442125</v>
       </c>
       <c r="C96" s="5">
-        <v>46197.50773788194</v>
+        <v>46197.341071215276</v>
       </c>
       <c r="D96" s="5">
-        <v>46223.605605289355</v>
+        <v>46223.43893862268</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>139</v>
@@ -7094,13 +7094,13 @@
         <v>251</v>
       </c>
       <c r="B97" s="9">
-        <v>46118.59045233796</v>
+        <v>46118.4237856713</v>
       </c>
       <c r="C97" s="9">
-        <v>46197.507801064814</v>
+        <v>46197.34113439815</v>
       </c>
       <c r="D97" s="9">
-        <v>46223.605599953706</v>
+        <v>46223.438933287034</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>139</v>
@@ -7147,13 +7147,13 @@
         <v>252</v>
       </c>
       <c r="B98" s="5">
-        <v>46118.55584987269</v>
+        <v>46118.38918320602</v>
       </c>
       <c r="C98" s="5">
-        <v>46209.596253842596</v>
+        <v>46209.429587175924</v>
       </c>
       <c r="D98" s="5">
-        <v>46223.60609758102</v>
+        <v>46223.43943091435</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>253</v>
@@ -7210,13 +7210,13 @@
         <v>254</v>
       </c>
       <c r="B99" s="9">
-        <v>46118.590539282406</v>
+        <v>46118.42387261574</v>
       </c>
       <c r="C99" s="9">
-        <v>46197.42437898148</v>
+        <v>46197.257712314815</v>
       </c>
       <c r="D99" s="9">
-        <v>46223.605747187496</v>
+        <v>46223.43908052084</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>139</v>
@@ -7263,13 +7263,13 @@
         <v>257</v>
       </c>
       <c r="B100" s="5">
-        <v>46118.590546666666</v>
+        <v>46118.42388</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.42449445602</v>
+        <v>46197.25782778935</v>
       </c>
       <c r="D100" s="5">
-        <v>46223.60574302083</v>
+        <v>46223.43907635417</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>139</v>
@@ -7316,13 +7316,13 @@
         <v>259</v>
       </c>
       <c r="B101" s="9">
-        <v>46118.590554027774</v>
+        <v>46118.42388736111</v>
       </c>
       <c r="C101" s="9">
-        <v>46197.42457260417</v>
+        <v>46197.2579059375</v>
       </c>
       <c r="D101" s="9">
-        <v>46223.605738252314</v>
+        <v>46223.43907158565</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>139</v>
@@ -7369,13 +7369,13 @@
         <v>261</v>
       </c>
       <c r="B102" s="5">
-        <v>46118.59056115741</v>
+        <v>46118.42389449074</v>
       </c>
       <c r="C102" s="5">
-        <v>46209.59622841435</v>
+        <v>46209.42956174769</v>
       </c>
       <c r="D102" s="5">
-        <v>46223.6057341088</v>
+        <v>46223.43906744213</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>139</v>
@@ -7422,13 +7422,13 @@
         <v>262</v>
       </c>
       <c r="B103" s="9">
-        <v>46118.590569293985</v>
+        <v>46118.42390262731</v>
       </c>
       <c r="C103" s="9">
-        <v>46209.59623454861</v>
+        <v>46209.42956788195</v>
       </c>
       <c r="D103" s="9">
-        <v>46223.60572732639</v>
+        <v>46223.43906065972</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>139</v>
@@ -7475,13 +7475,13 @@
         <v>263</v>
       </c>
       <c r="B104" s="5">
-        <v>46118.5558574537</v>
+        <v>46118.38919078704</v>
       </c>
       <c r="C104" s="5">
-        <v>46230.57885586805</v>
+        <v>46230.41218920139</v>
       </c>
       <c r="D104" s="5">
-        <v>46230.57917039352</v>
+        <v>46230.41250372685</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>264</v>
@@ -7540,13 +7540,13 @@
         <v>265</v>
       </c>
       <c r="B105" s="9">
-        <v>46118.5906265625</v>
+        <v>46118.42395989584</v>
       </c>
       <c r="C105" s="9">
-        <v>46205.48493550926</v>
+        <v>46205.31826884259</v>
       </c>
       <c r="D105" s="9">
-        <v>46223.6058402662</v>
+        <v>46223.43917359954</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>139</v>
@@ -7593,13 +7593,13 @@
         <v>267</v>
       </c>
       <c r="B106" s="5">
-        <v>46118.59063387732</v>
+        <v>46118.42396721065</v>
       </c>
       <c r="C106" s="5">
-        <v>46205.48495603009</v>
+        <v>46205.31828936342</v>
       </c>
       <c r="D106" s="5">
-        <v>46223.605836145834</v>
+        <v>46223.43916947917</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>139</v>
@@ -7646,13 +7646,13 @@
         <v>268</v>
       </c>
       <c r="B107" s="9">
-        <v>46118.590655486114</v>
+        <v>46118.42398881944</v>
       </c>
       <c r="C107" s="9">
-        <v>46212.603143518514</v>
+        <v>46212.43647685186</v>
       </c>
       <c r="D107" s="9">
-        <v>46223.60583134259</v>
+        <v>46223.439164675925</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>139</v>
@@ -7699,13 +7699,13 @@
         <v>269</v>
       </c>
       <c r="B108" s="5">
-        <v>46118.59066162037</v>
+        <v>46118.4239949537</v>
       </c>
       <c r="C108" s="5">
-        <v>46212.60315292824</v>
+        <v>46212.43648626158</v>
       </c>
       <c r="D108" s="5">
-        <v>46223.60582783565</v>
+        <v>46223.43916116898</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>139</v>
@@ -7752,13 +7752,13 @@
         <v>270</v>
       </c>
       <c r="B109" s="9">
-        <v>46118.59066710648</v>
+        <v>46118.424000439816</v>
       </c>
       <c r="C109" s="9">
-        <v>46230.578839814814</v>
+        <v>46230.41217314814</v>
       </c>
       <c r="D109" s="9">
-        <v>46230.57884116899</v>
+        <v>46230.412174502315</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>139</v>
@@ -7805,13 +7805,13 @@
         <v>271</v>
       </c>
       <c r="B110" s="5">
-        <v>46118.55591270833</v>
+        <v>46118.38924604167</v>
       </c>
       <c r="C110" s="5">
-        <v>46244.566615902775</v>
+        <v>46244.39994923611</v>
       </c>
       <c r="D110" s="5">
-        <v>46244.56662542824</v>
+        <v>46244.39995876157</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>272</v>
@@ -7868,13 +7868,13 @@
         <v>275</v>
       </c>
       <c r="B111" s="9">
-        <v>46118.590705243056</v>
+        <v>46118.424038576384</v>
       </c>
       <c r="C111" s="9">
-        <v>46212.604972974535</v>
+        <v>46212.43830630787</v>
       </c>
       <c r="D111" s="9">
-        <v>46238.51287651621</v>
+        <v>46238.34620984954</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>139</v>
@@ -7923,13 +7923,13 @@
         <v>277</v>
       </c>
       <c r="B112" s="5">
-        <v>46118.59071275463</v>
+        <v>46118.42404608797</v>
       </c>
       <c r="C112" s="5">
-        <v>46212.60503894676</v>
+        <v>46212.43837228009</v>
       </c>
       <c r="D112" s="5">
-        <v>46238.51289673611</v>
+        <v>46238.346230069445</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>139</v>
@@ -7978,13 +7978,13 @@
         <v>278</v>
       </c>
       <c r="B113" s="9">
-        <v>46118.590720092594</v>
+        <v>46118.42405342593</v>
       </c>
       <c r="C113" s="9">
-        <v>46213.54487947917</v>
+        <v>46213.3782128125</v>
       </c>
       <c r="D113" s="9">
-        <v>46238.5129065625</v>
+        <v>46238.346239895836</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>139</v>
@@ -8033,13 +8033,13 @@
         <v>279</v>
       </c>
       <c r="B114" s="5">
-        <v>46118.590727835646</v>
+        <v>46118.42406116898</v>
       </c>
       <c r="C114" s="5">
-        <v>46213.54500266204</v>
+        <v>46213.37833599537</v>
       </c>
       <c r="D114" s="5">
-        <v>46238.512922442125</v>
+        <v>46238.34625577547</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>139</v>
@@ -8088,13 +8088,13 @@
         <v>280</v>
       </c>
       <c r="B115" s="9">
-        <v>46118.59073534722</v>
+        <v>46118.42406868056</v>
       </c>
       <c r="C115" s="9">
-        <v>46244.56660078704</v>
+        <v>46244.399934120374</v>
       </c>
       <c r="D115" s="9">
-        <v>46244.56660280093</v>
+        <v>46244.39993613426</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>139</v>
@@ -8143,13 +8143,13 @@
         <v>281</v>
       </c>
       <c r="B116" s="5">
-        <v>46118.55591954861</v>
+        <v>46118.38925288194</v>
       </c>
       <c r="C116" s="5">
-        <v>46244.56703814815</v>
+        <v>46244.40037148148</v>
       </c>
       <c r="D116" s="5">
-        <v>46244.56705233797</v>
+        <v>46244.400385671295</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>282</v>
@@ -8196,13 +8196,13 @@
         <v>284</v>
       </c>
       <c r="B117" s="9">
-        <v>46118.555923148146</v>
+        <v>46118.38925648148</v>
       </c>
       <c r="C117" s="9">
-        <v>46244.566789606484</v>
+        <v>46244.40012293981</v>
       </c>
       <c r="D117" s="9">
-        <v>46244.56679628472</v>
+        <v>46244.40012961805</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>285</v>
@@ -8259,13 +8259,13 @@
         <v>288</v>
       </c>
       <c r="B118" s="5">
-        <v>46118.590793020834</v>
+        <v>46118.42412635416</v>
       </c>
       <c r="C118" s="5">
-        <v>46244.5667706713</v>
+        <v>46244.40010400463</v>
       </c>
       <c r="D118" s="5">
-        <v>46244.56677398148</v>
+        <v>46244.40010731481</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>139</v>
@@ -8312,13 +8312,13 @@
         <v>289</v>
       </c>
       <c r="B119" s="9">
-        <v>46118.59080049768</v>
+        <v>46118.424133831024</v>
       </c>
       <c r="C119" s="9">
-        <v>46244.56677130787</v>
+        <v>46244.4001046412</v>
       </c>
       <c r="D119" s="9">
-        <v>46244.566774363426</v>
+        <v>46244.400107696754</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>139</v>
@@ -8365,13 +8365,13 @@
         <v>290</v>
       </c>
       <c r="B120" s="5">
-        <v>46118.59080680556</v>
+        <v>46118.424140138886</v>
       </c>
       <c r="C120" s="5">
-        <v>46244.5667718287</v>
+        <v>46244.400105162036</v>
       </c>
       <c r="D120" s="5">
-        <v>46244.56677471065</v>
+        <v>46244.40010804398</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>139</v>
@@ -8418,13 +8418,13 @@
         <v>291</v>
       </c>
       <c r="B121" s="9">
-        <v>46118.59081555555</v>
+        <v>46118.42414888889</v>
       </c>
       <c r="C121" s="9">
-        <v>46244.56677233796</v>
+        <v>46244.400105671295</v>
       </c>
       <c r="D121" s="9">
-        <v>46244.56677506944</v>
+        <v>46244.40010840278</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>139</v>
@@ -8471,13 +8471,13 @@
         <v>292</v>
       </c>
       <c r="B122" s="5">
-        <v>46118.590822777776</v>
+        <v>46118.42415611111</v>
       </c>
       <c r="C122" s="5">
-        <v>46244.5667728125</v>
+        <v>46244.40010614583</v>
       </c>
       <c r="D122" s="5">
-        <v>46244.566775416664</v>
+        <v>46244.40010875</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>139</v>
@@ -8524,13 +8524,13 @@
         <v>293</v>
       </c>
       <c r="B123" s="9">
-        <v>46118.55592798611</v>
+        <v>46118.38926131945</v>
       </c>
       <c r="C123" s="9">
-        <v>46244.56683241898</v>
+        <v>46244.40016575232</v>
       </c>
       <c r="D123" s="9">
-        <v>46244.56684324074</v>
+        <v>46244.400176574076</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>294</v>
@@ -8587,13 +8587,13 @@
         <v>296</v>
       </c>
       <c r="B124" s="5">
-        <v>46118.59087519676</v>
+        <v>46118.424208530094</v>
       </c>
       <c r="C124" s="5">
-        <v>46213.54530194444</v>
+        <v>46213.37863527778</v>
       </c>
       <c r="D124" s="5">
-        <v>46244.566780671295</v>
+        <v>46244.40011400463</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>139</v>
@@ -8640,13 +8640,13 @@
         <v>298</v>
       </c>
       <c r="B125" s="9">
-        <v>46118.590883240744</v>
+        <v>46118.42421657407</v>
       </c>
       <c r="C125" s="9">
-        <v>46213.54537613426</v>
+        <v>46213.37870946759</v>
       </c>
       <c r="D125" s="9">
-        <v>46244.566780486115</v>
+        <v>46244.40011381944</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>139</v>
@@ -8693,13 +8693,13 @@
         <v>299</v>
       </c>
       <c r="B126" s="5">
-        <v>46118.59089157407</v>
+        <v>46118.42422490741</v>
       </c>
       <c r="C126" s="5">
-        <v>46213.545447592594</v>
+        <v>46213.37878092592</v>
       </c>
       <c r="D126" s="5">
-        <v>46244.566780520836</v>
+        <v>46244.400113854164</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>139</v>
@@ -8746,13 +8746,13 @@
         <v>300</v>
       </c>
       <c r="B127" s="9">
-        <v>46118.590897835646</v>
+        <v>46118.42423116898</v>
       </c>
       <c r="C127" s="9">
-        <v>46213.545501875</v>
+        <v>46213.378835208336</v>
       </c>
       <c r="D127" s="9">
-        <v>46244.566780486115</v>
+        <v>46244.40011381944</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>154</v>
@@ -8799,13 +8799,13 @@
         <v>301</v>
       </c>
       <c r="B128" s="5">
-        <v>46118.5909049537</v>
+        <v>46118.424238287036</v>
       </c>
       <c r="C128" s="5">
-        <v>46244.56681815972</v>
+        <v>46244.40015149306</v>
       </c>
       <c r="D128" s="5">
-        <v>46244.566819722226</v>
+        <v>46244.400153055554</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>154</v>
@@ -8852,13 +8852,13 @@
         <v>302</v>
       </c>
       <c r="B129" s="9">
-        <v>46118.555932511576</v>
+        <v>46118.389265844904</v>
       </c>
       <c r="C129" s="9">
-        <v>46211.68918386574</v>
+        <v>46211.522517199075</v>
       </c>
       <c r="D129" s="9">
-        <v>46211.689641018515</v>
+        <v>46211.52297435185</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>303</v>
@@ -8915,13 +8915,13 @@
         <v>304</v>
       </c>
       <c r="B130" s="5">
-        <v>46118.59095414352</v>
+        <v>46118.42428747685</v>
       </c>
       <c r="C130" s="5">
-        <v>46205.90322601852</v>
+        <v>46205.73655935185</v>
       </c>
       <c r="D130" s="5">
-        <v>46213.545309085646</v>
+        <v>46213.37864241898</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>139</v>
@@ -8968,13 +8968,13 @@
         <v>306</v>
       </c>
       <c r="B131" s="9">
-        <v>46118.590966759264</v>
+        <v>46118.42430009259</v>
       </c>
       <c r="C131" s="9">
-        <v>46205.903334953706</v>
+        <v>46205.736668287034</v>
       </c>
       <c r="D131" s="9">
-        <v>46213.54538173611</v>
+        <v>46213.37871506944</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>139</v>
@@ -9021,13 +9021,13 @@
         <v>307</v>
       </c>
       <c r="B132" s="5">
-        <v>46118.590973796294</v>
+        <v>46118.42430712963</v>
       </c>
       <c r="C132" s="5">
-        <v>46205.90344625</v>
+        <v>46205.736779583334</v>
       </c>
       <c r="D132" s="5">
-        <v>46213.54545359954</v>
+        <v>46213.378786932866</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>139</v>
@@ -9074,13 +9074,13 @@
         <v>308</v>
       </c>
       <c r="B133" s="9">
-        <v>46118.590979953704</v>
+        <v>46118.42431328703</v>
       </c>
       <c r="C133" s="9">
-        <v>46211.68925275463</v>
+        <v>46211.52258608796</v>
       </c>
       <c r="D133" s="9">
-        <v>46213.5455090162</v>
+        <v>46213.378842349535</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>139</v>
@@ -9127,13 +9127,13 @@
         <v>309</v>
       </c>
       <c r="B134" s="5">
-        <v>46118.59098489583</v>
+        <v>46118.42431822917</v>
       </c>
       <c r="C134" s="5">
-        <v>46211.6896266088</v>
+        <v>46211.52295994213</v>
       </c>
       <c r="D134" s="5">
-        <v>46244.566826678245</v>
+        <v>46244.40016001157</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>139</v>
@@ -9180,13 +9180,13 @@
         <v>310</v>
       </c>
       <c r="B135" s="9">
-        <v>46118.55593715278</v>
+        <v>46118.38927048611</v>
       </c>
       <c r="C135" s="9">
-        <v>46244.56694560185</v>
+        <v>46244.40027893518</v>
       </c>
       <c r="D135" s="9">
-        <v>46244.56695628472</v>
+        <v>46244.40028961806</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>311</v>
@@ -9243,13 +9243,13 @@
         <v>313</v>
       </c>
       <c r="B136" s="5">
-        <v>46118.59103105324</v>
+        <v>46118.42436438658</v>
       </c>
       <c r="C136" s="5">
-        <v>46244.56692866898</v>
+        <v>46244.40026200232</v>
       </c>
       <c r="D136" s="5">
-        <v>46244.56693162037</v>
+        <v>46244.4002649537</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>139</v>
@@ -9296,13 +9296,13 @@
         <v>314</v>
       </c>
       <c r="B137" s="9">
-        <v>46118.591039039355</v>
+        <v>46118.42437237268</v>
       </c>
       <c r="C137" s="9">
-        <v>46244.56692925926</v>
+        <v>46244.40026259259</v>
       </c>
       <c r="D137" s="9">
-        <v>46244.56693195602</v>
+        <v>46244.400265289354</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>139</v>
@@ -9349,13 +9349,13 @@
         <v>315</v>
       </c>
       <c r="B138" s="5">
-        <v>46118.59104641204</v>
+        <v>46118.42437974537</v>
       </c>
       <c r="C138" s="5">
-        <v>46244.566929699075</v>
+        <v>46244.40026303241</v>
       </c>
       <c r="D138" s="5">
-        <v>46244.56693226851</v>
+        <v>46244.40026560186</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>139</v>
@@ -9402,13 +9402,13 @@
         <v>316</v>
       </c>
       <c r="B139" s="9">
-        <v>46118.59105258102</v>
+        <v>46118.42438591435</v>
       </c>
       <c r="C139" s="9">
-        <v>46244.56693015047</v>
+        <v>46244.400263483796</v>
       </c>
       <c r="D139" s="9">
-        <v>46244.56693260417</v>
+        <v>46244.4002659375</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>139</v>
@@ -9455,13 +9455,13 @@
         <v>317</v>
       </c>
       <c r="B140" s="5">
-        <v>46118.59105829861</v>
+        <v>46118.42439163194</v>
       </c>
       <c r="C140" s="5">
-        <v>46244.56693056713</v>
+        <v>46244.40026390046</v>
       </c>
       <c r="D140" s="5">
-        <v>46244.56693295139</v>
+        <v>46244.40026628472</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>139</v>
@@ -9508,13 +9508,13 @@
         <v>318</v>
       </c>
       <c r="B141" s="9">
-        <v>46118.55594259259</v>
+        <v>46118.389275925925</v>
       </c>
       <c r="C141" s="9">
-        <v>46245.76537715278</v>
+        <v>46245.59871048611</v>
       </c>
       <c r="D141" s="9">
-        <v>46245.76544885417</v>
+        <v>46245.5987821875</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>319</v>
@@ -9557,13 +9557,13 @@
         <v>321</v>
       </c>
       <c r="B142" s="5">
-        <v>46118.55594550926</v>
+        <v>46118.38927884259</v>
       </c>
       <c r="C142" s="5">
-        <v>46245.76535796296</v>
+        <v>46245.5986912963</v>
       </c>
       <c r="D142" s="5">
-        <v>46245.765377662035</v>
+        <v>46245.59871099537</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>322</v>
@@ -9622,13 +9622,13 @@
         <v>325</v>
       </c>
       <c r="B143" s="9">
-        <v>46118.55595019676</v>
+        <v>46118.389283530094</v>
       </c>
       <c r="C143" s="9">
-        <v>46245.76536282407</v>
+        <v>46245.59869615741</v>
       </c>
       <c r="D143" s="9">
-        <v>46245.76537818287</v>
+        <v>46245.5987115162</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>326</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1683,13 +1683,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46118.38873709491</v>
+        <v>46118.55540376157</v>
       </c>
       <c r="C4" s="5">
-        <v>46134.683067569444</v>
+        <v>46134.84973423611</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.683078692135</v>
+        <v>46134.84974535879</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1736,13 +1736,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46118.38890262731</v>
+        <v>46118.55556929398</v>
       </c>
       <c r="C5" s="9">
-        <v>46134.68074246528</v>
+        <v>46134.847409131944</v>
       </c>
       <c r="D5" s="9">
-        <v>46134.680787986115</v>
+        <v>46134.84745465278</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1799,13 +1799,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46118.388906099535</v>
+        <v>46118.5555727662</v>
       </c>
       <c r="C6" s="5">
-        <v>46134.68150766204</v>
+        <v>46134.848174328705</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.681521516206</v>
+        <v>46134.84818818287</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1862,13 +1862,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="9">
-        <v>46118.38890895833</v>
+        <v>46118.555575624996</v>
       </c>
       <c r="C7" s="9">
-        <v>46134.68180517361</v>
+        <v>46134.848471840276</v>
       </c>
       <c r="D7" s="9">
-        <v>46134.68181967593</v>
+        <v>46134.84848634259</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>40</v>
@@ -1925,13 +1925,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46118.38891162037</v>
+        <v>46118.555578287036</v>
       </c>
       <c r="C8" s="5">
-        <v>46134.68256634259</v>
+        <v>46134.849233009256</v>
       </c>
       <c r="D8" s="5">
-        <v>46191.543463124995</v>
+        <v>46191.71012979167</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1988,13 +1988,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="9">
-        <v>46118.38891502315</v>
+        <v>46118.55558168981</v>
       </c>
       <c r="C9" s="9">
-        <v>46134.683053368055</v>
+        <v>46134.84972003472</v>
       </c>
       <c r="D9" s="9">
-        <v>46134.683068425926</v>
+        <v>46134.84973509259</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>47</v>
@@ -2051,13 +2051,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46118.38874427084</v>
+        <v>46118.5554109375</v>
       </c>
       <c r="C10" s="5">
-        <v>46192.74659246528</v>
+        <v>46192.91325913194</v>
       </c>
       <c r="D10" s="5">
-        <v>46192.74660916667</v>
+        <v>46192.91327583333</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2104,13 +2104,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="9">
-        <v>46118.38891834491</v>
+        <v>46118.55558501158</v>
       </c>
       <c r="C11" s="9">
-        <v>46134.68486908565</v>
+        <v>46134.851535752314</v>
       </c>
       <c r="D11" s="9">
-        <v>46171.74395131944</v>
+        <v>46171.91061798611</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>52</v>
@@ -2169,13 +2169,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46118.38892319445</v>
+        <v>46118.55558986111</v>
       </c>
       <c r="C12" s="5">
-        <v>46134.6842277199</v>
+        <v>46134.850894386575</v>
       </c>
       <c r="D12" s="5">
-        <v>46134.684243125</v>
+        <v>46134.85090979167</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2234,13 +2234,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46118.388928368055</v>
+        <v>46118.55559503472</v>
       </c>
       <c r="C13" s="9">
-        <v>46134.683779224535</v>
+        <v>46134.85044589121</v>
       </c>
       <c r="D13" s="9">
-        <v>46134.683796840276</v>
+        <v>46134.85046350694</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2299,13 +2299,13 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46118.388750972226</v>
+        <v>46118.55541763889</v>
       </c>
       <c r="C14" s="5">
-        <v>46192.74645232639</v>
+        <v>46192.913118993056</v>
       </c>
       <c r="D14" s="5">
-        <v>46192.74647372685</v>
+        <v>46192.91314039352</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2352,13 +2352,13 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46118.38893851852</v>
+        <v>46118.55560518519</v>
       </c>
       <c r="C15" s="9">
-        <v>46134.685348425926</v>
+        <v>46134.85201509259</v>
       </c>
       <c r="D15" s="9">
-        <v>46134.6853625463</v>
+        <v>46134.85202921296</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2417,13 +2417,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46118.38894379629</v>
+        <v>46118.555610462965</v>
       </c>
       <c r="C16" s="5">
-        <v>46192.74643533565</v>
+        <v>46192.91310200232</v>
       </c>
       <c r="D16" s="5">
-        <v>46223.438622754635</v>
+        <v>46223.60528942129</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2482,13 +2482,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="9">
-        <v>46118.388948912034</v>
+        <v>46118.555615578705</v>
       </c>
       <c r="C17" s="9">
-        <v>46134.68573056713</v>
+        <v>46134.8523972338</v>
       </c>
       <c r="D17" s="9">
-        <v>46134.68574652778</v>
+        <v>46134.85241319444</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -2547,13 +2547,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46118.388954560185</v>
+        <v>46118.55562122686</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.5050077662</v>
+        <v>46181.67167443287</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.43861864583</v>
+        <v>46223.6052853125</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2612,13 +2612,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46118.388759016205</v>
+        <v>46118.55542568287</v>
       </c>
       <c r="C19" s="9">
-        <v>46192.74662535879</v>
+        <v>46192.91329202546</v>
       </c>
       <c r="D19" s="9">
-        <v>46250.059469976855</v>
+        <v>46250.22613664352</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2665,13 +2665,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46118.388960254626</v>
+        <v>46118.5556269213</v>
       </c>
       <c r="C20" s="5">
-        <v>46182.51205171296</v>
+        <v>46182.678718379626</v>
       </c>
       <c r="D20" s="5">
-        <v>46182.51206596065</v>
+        <v>46182.67873262732</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2730,13 +2730,13 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46118.38896474537</v>
+        <v>46118.55563141203</v>
       </c>
       <c r="C21" s="9">
-        <v>46155.73059027777</v>
+        <v>46155.897256944445</v>
       </c>
       <c r="D21" s="9">
-        <v>46169.68891788194</v>
+        <v>46169.85558454861</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2791,13 +2791,13 @@
         <v>95</v>
       </c>
       <c r="B22" s="5">
-        <v>46118.38896940972</v>
+        <v>46118.55563607639</v>
       </c>
       <c r="C22" s="5">
-        <v>46182.512035775464</v>
+        <v>46182.67870244213</v>
       </c>
       <c r="D22" s="5">
-        <v>46182.51203774306</v>
+        <v>46182.67870440972</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2852,13 +2852,13 @@
         <v>98</v>
       </c>
       <c r="B23" s="9">
-        <v>46118.38897395833</v>
+        <v>46118.555640624996</v>
       </c>
       <c r="C23" s="9">
-        <v>46192.72321162037</v>
+        <v>46192.88987828704</v>
       </c>
       <c r="D23" s="9">
-        <v>46192.72322681713</v>
+        <v>46192.88989348379</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>99</v>
@@ -2917,13 +2917,13 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46118.38897876158</v>
+        <v>46118.55564542824</v>
       </c>
       <c r="C24" s="5">
-        <v>46192.72306212963</v>
+        <v>46192.8897287963</v>
       </c>
       <c r="D24" s="5">
-        <v>46192.74644724537</v>
+        <v>46192.913113912036</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -2978,13 +2978,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46118.388983240744</v>
+        <v>46118.55564990741</v>
       </c>
       <c r="C25" s="9">
-        <v>46192.72319689815</v>
+        <v>46192.889863564815</v>
       </c>
       <c r="D25" s="9">
-        <v>46192.723198611115</v>
+        <v>46192.88986527778</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3039,13 +3039,13 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46118.38898793982</v>
+        <v>46118.555654606476</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.51234460648</v>
+        <v>46182.67901127315</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.51235559028</v>
+        <v>46182.67902225694</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3104,13 +3104,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46118.38899260417</v>
+        <v>46118.55565927083</v>
       </c>
       <c r="C27" s="9">
-        <v>46134.72622774306</v>
+        <v>46134.89289440972</v>
       </c>
       <c r="D27" s="9">
-        <v>46169.68873444444</v>
+        <v>46169.85540111111</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3165,13 +3165,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46118.3889971412</v>
+        <v>46118.55566380787</v>
       </c>
       <c r="C28" s="5">
-        <v>46182.51233065972</v>
+        <v>46182.67899732639</v>
       </c>
       <c r="D28" s="5">
-        <v>46182.51233219907</v>
+        <v>46182.67899886574</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3226,13 +3226,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46118.38900215278</v>
+        <v>46118.55566881945</v>
       </c>
       <c r="C29" s="9">
-        <v>46134.72626876157</v>
+        <v>46134.892935428245</v>
       </c>
       <c r="D29" s="9">
-        <v>46169.68868207176</v>
+        <v>46169.85534873843</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3287,13 +3287,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46118.389006736106</v>
+        <v>46118.55567340278</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.50514034722</v>
+        <v>46181.67180701389</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.50515181713</v>
+        <v>46181.671818483796</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3352,13 +3352,13 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46118.38901627315</v>
+        <v>46118.55568293981</v>
       </c>
       <c r="C31" s="9">
-        <v>46181.50506538195</v>
+        <v>46181.671732048606</v>
       </c>
       <c r="D31" s="9">
-        <v>46181.50506667824</v>
+        <v>46181.671733344905</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3413,13 +3413,13 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46118.38902135417</v>
+        <v>46118.55568802083</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.505125208336</v>
+        <v>46181.671791875</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.50512674768</v>
+        <v>46181.67179341435</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3474,13 +3474,13 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46118.38876453704</v>
+        <v>46118.5554312037</v>
       </c>
       <c r="C33" s="9">
-        <v>46238.37623760417</v>
+        <v>46238.542904270835</v>
       </c>
       <c r="D33" s="9">
-        <v>46238.37625436342</v>
+        <v>46238.54292103009</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3527,13 +3527,13 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46118.389070578705</v>
+        <v>46118.55573724537</v>
       </c>
       <c r="C34" s="5">
-        <v>46134.68942313657</v>
+        <v>46134.856089803245</v>
       </c>
       <c r="D34" s="5">
-        <v>46222.29901538194</v>
+        <v>46222.46568204861</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3592,13 +3592,13 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46118.422677361115</v>
+        <v>46118.58934402778</v>
       </c>
       <c r="C35" s="9">
-        <v>46134.68922825232</v>
+        <v>46134.85589491898</v>
       </c>
       <c r="D35" s="9">
-        <v>46134.68922973379</v>
+        <v>46134.85589640046</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3647,13 +3647,13 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46118.42269068287</v>
+        <v>46118.58935734954</v>
       </c>
       <c r="C36" s="5">
-        <v>46134.68923696759</v>
+        <v>46134.85590363426</v>
       </c>
       <c r="D36" s="5">
-        <v>46134.68923822917</v>
+        <v>46134.855904895834</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3702,13 +3702,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46118.42269825231</v>
+        <v>46118.58936491898</v>
       </c>
       <c r="C37" s="9">
-        <v>46134.689397372684</v>
+        <v>46134.856064039355</v>
       </c>
       <c r="D37" s="9">
-        <v>46134.68939890046</v>
+        <v>46134.85606556713</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>139</v>
@@ -3757,13 +3757,13 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46118.4227059838</v>
+        <v>46118.58937265046</v>
       </c>
       <c r="C38" s="5">
-        <v>46134.68940369213</v>
+        <v>46134.8560703588</v>
       </c>
       <c r="D38" s="5">
-        <v>46134.68940524306</v>
+        <v>46134.85607190972</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -3812,13 +3812,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="9">
-        <v>46118.42271239583</v>
+        <v>46118.5893790625</v>
       </c>
       <c r="C39" s="9">
-        <v>46134.68941011574</v>
+        <v>46134.85607678241</v>
       </c>
       <c r="D39" s="9">
-        <v>46134.68941144676</v>
+        <v>46134.85607811343</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>139</v>
@@ -3867,13 +3867,13 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46118.38907722222</v>
+        <v>46118.55574388889</v>
       </c>
       <c r="C40" s="5">
-        <v>46135.33864765047</v>
+        <v>46135.505314317124</v>
       </c>
       <c r="D40" s="5">
-        <v>46222.29903170139</v>
+        <v>46222.465698368054</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3932,13 +3932,13 @@
         <v>149</v>
       </c>
       <c r="B41" s="9">
-        <v>46118.42281954861</v>
+        <v>46118.58948621528</v>
       </c>
       <c r="C41" s="9">
-        <v>46135.33860112268</v>
+        <v>46135.505267789355</v>
       </c>
       <c r="D41" s="9">
-        <v>46135.33860295139</v>
+        <v>46135.50526961806</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>139</v>
@@ -3987,13 +3987,13 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46118.42295252315</v>
+        <v>46118.589619189814</v>
       </c>
       <c r="C42" s="5">
-        <v>46135.33861204861</v>
+        <v>46135.50527871528</v>
       </c>
       <c r="D42" s="5">
-        <v>46135.338613541666</v>
+        <v>46135.50528020834</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>139</v>
@@ -4042,13 +4042,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="9">
-        <v>46118.4229690625</v>
+        <v>46118.589635729164</v>
       </c>
       <c r="C43" s="9">
-        <v>46135.33861910879</v>
+        <v>46135.50528577546</v>
       </c>
       <c r="D43" s="9">
-        <v>46135.33862041667</v>
+        <v>46135.50528708333</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>154</v>
@@ -4097,13 +4097,13 @@
         <v>155</v>
       </c>
       <c r="B44" s="5">
-        <v>46118.42298265046</v>
+        <v>46118.58964931713</v>
       </c>
       <c r="C44" s="5">
-        <v>46135.338626550925</v>
+        <v>46135.50529321759</v>
       </c>
       <c r="D44" s="5">
-        <v>46135.338628495374</v>
+        <v>46135.50529516204</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>154</v>
@@ -4152,13 +4152,13 @@
         <v>156</v>
       </c>
       <c r="B45" s="9">
-        <v>46118.42299203704</v>
+        <v>46118.5896587037</v>
       </c>
       <c r="C45" s="9">
-        <v>46135.338634189815</v>
+        <v>46135.50530085649</v>
       </c>
       <c r="D45" s="9">
-        <v>46135.33863545139</v>
+        <v>46135.50530211805</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>139</v>
@@ -4207,13 +4207,13 @@
         <v>157</v>
       </c>
       <c r="B46" s="5">
-        <v>46118.38908443287</v>
+        <v>46118.55575109954</v>
       </c>
       <c r="C46" s="5">
-        <v>46135.33892616898</v>
+        <v>46135.505592835645</v>
       </c>
       <c r="D46" s="5">
-        <v>46222.29909361112</v>
+        <v>46222.46576027777</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>80</v>
@@ -4272,13 +4272,13 @@
         <v>159</v>
       </c>
       <c r="B47" s="9">
-        <v>46118.423060127316</v>
+        <v>46118.58972679398</v>
       </c>
       <c r="C47" s="9">
-        <v>46135.3388865625</v>
+        <v>46135.505553229166</v>
       </c>
       <c r="D47" s="9">
-        <v>46135.33888840278</v>
+        <v>46135.505555069445</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>139</v>
@@ -4325,13 +4325,13 @@
         <v>161</v>
       </c>
       <c r="B48" s="5">
-        <v>46118.4230809375</v>
+        <v>46118.58974760417</v>
       </c>
       <c r="C48" s="5">
-        <v>46135.338892581014</v>
+        <v>46135.505559247686</v>
       </c>
       <c r="D48" s="5">
-        <v>46135.338893900465</v>
+        <v>46135.50556056713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>139</v>
@@ -4378,13 +4378,13 @@
         <v>162</v>
       </c>
       <c r="B49" s="9">
-        <v>46118.42308603009</v>
+        <v>46118.58975269676</v>
       </c>
       <c r="C49" s="9">
-        <v>46135.33889986111</v>
+        <v>46135.505566527776</v>
       </c>
       <c r="D49" s="9">
-        <v>46135.33890128472</v>
+        <v>46135.50556795139</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>139</v>
@@ -4431,13 +4431,13 @@
         <v>163</v>
       </c>
       <c r="B50" s="5">
-        <v>46118.423097245366</v>
+        <v>46118.58976391204</v>
       </c>
       <c r="C50" s="5">
-        <v>46135.3389065625</v>
+        <v>46135.505573229166</v>
       </c>
       <c r="D50" s="5">
-        <v>46135.33890837963</v>
+        <v>46135.50557504629</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>139</v>
@@ -4484,13 +4484,13 @@
         <v>164</v>
       </c>
       <c r="B51" s="9">
-        <v>46118.42309224537</v>
+        <v>46118.589758912036</v>
       </c>
       <c r="C51" s="9">
-        <v>46135.338914340275</v>
+        <v>46135.505581006946</v>
       </c>
       <c r="D51" s="9">
-        <v>46135.33891574074</v>
+        <v>46135.50558240741</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>139</v>
@@ -4537,13 +4537,13 @@
         <v>165</v>
       </c>
       <c r="B52" s="5">
-        <v>46118.38909226852</v>
+        <v>46118.55575893518</v>
       </c>
       <c r="C52" s="5">
-        <v>46238.346261342595</v>
+        <v>46238.51292800926</v>
       </c>
       <c r="D52" s="5">
-        <v>46238.346274525466</v>
+        <v>46238.51294119213</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>166</v>
@@ -4602,13 +4602,13 @@
         <v>169</v>
       </c>
       <c r="B53" s="9">
-        <v>46118.423202465274</v>
+        <v>46118.589869131945</v>
       </c>
       <c r="C53" s="9">
-        <v>46238.34620313658</v>
+        <v>46238.51286980324</v>
       </c>
       <c r="D53" s="9">
-        <v>46238.34620515046</v>
+        <v>46238.51287181713</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>139</v>
@@ -4657,13 +4657,13 @@
         <v>171</v>
       </c>
       <c r="B54" s="5">
-        <v>46118.42321666666</v>
+        <v>46118.589883333334</v>
       </c>
       <c r="C54" s="5">
-        <v>46238.34622327547</v>
+        <v>46238.512889942125</v>
       </c>
       <c r="D54" s="5">
-        <v>46238.34622535879</v>
+        <v>46238.512892025465</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>139</v>
@@ -4712,13 +4712,13 @@
         <v>172</v>
       </c>
       <c r="B55" s="9">
-        <v>46118.423223645834</v>
+        <v>46118.589890312505</v>
       </c>
       <c r="C55" s="9">
-        <v>46238.346232916665</v>
+        <v>46238.51289958334</v>
       </c>
       <c r="D55" s="9">
-        <v>46238.34623447916</v>
+        <v>46238.512901145834</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>139</v>
@@ -4767,13 +4767,13 @@
         <v>173</v>
       </c>
       <c r="B56" s="5">
-        <v>46118.42325384259</v>
+        <v>46118.58992050926</v>
       </c>
       <c r="C56" s="5">
-        <v>46238.346240266204</v>
+        <v>46238.51290693287</v>
       </c>
       <c r="D56" s="5">
-        <v>46238.34624171296</v>
+        <v>46238.512908379635</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>139</v>
@@ -4822,13 +4822,13 @@
         <v>174</v>
       </c>
       <c r="B57" s="9">
-        <v>46118.42323288195</v>
+        <v>46118.589899548606</v>
       </c>
       <c r="C57" s="9">
-        <v>46238.34624594907</v>
+        <v>46238.51291261574</v>
       </c>
       <c r="D57" s="9">
-        <v>46238.34624746528</v>
+        <v>46238.51291413195</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>139</v>
@@ -4877,13 +4877,13 @@
         <v>175</v>
       </c>
       <c r="B58" s="5">
-        <v>46118.38909813657</v>
+        <v>46118.55576480324</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.505299675926</v>
+        <v>46181.67196634259</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.50538365741</v>
+        <v>46181.67205032408</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>176</v>
@@ -4926,13 +4926,13 @@
         <v>178</v>
       </c>
       <c r="B59" s="9">
-        <v>46118.3891028588</v>
+        <v>46118.55576952547</v>
       </c>
       <c r="C59" s="9">
-        <v>46181.50523445602</v>
+        <v>46181.67190112268</v>
       </c>
       <c r="D59" s="9">
-        <v>46181.50524850695</v>
+        <v>46181.67191517361</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>179</v>
@@ -4991,13 +4991,13 @@
         <v>183</v>
       </c>
       <c r="B60" s="5">
-        <v>46118.38910940972</v>
+        <v>46118.55577607639</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.50528408565</v>
+        <v>46181.671950752316</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.5053002662</v>
+        <v>46181.671966932874</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>184</v>
@@ -5056,13 +5056,13 @@
         <v>187</v>
       </c>
       <c r="B61" s="9">
-        <v>46118.38911456018</v>
+        <v>46118.55578122685</v>
       </c>
       <c r="C61" s="9">
-        <v>46197.60926278935</v>
+        <v>46197.775929456024</v>
       </c>
       <c r="D61" s="9">
-        <v>46197.60927959491</v>
+        <v>46197.77594626158</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>188</v>
@@ -5109,13 +5109,13 @@
         <v>190</v>
       </c>
       <c r="B62" s="5">
-        <v>46118.38911793982</v>
+        <v>46118.55578460648</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50554564815</v>
+        <v>46181.672212314814</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.50556121528</v>
+        <v>46181.67222788194</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>191</v>
@@ -5174,13 +5174,13 @@
         <v>195</v>
       </c>
       <c r="B63" s="9">
-        <v>46118.38912344907</v>
+        <v>46118.555790115744</v>
       </c>
       <c r="C63" s="9">
-        <v>46191.54366607639</v>
+        <v>46191.71033274305</v>
       </c>
       <c r="D63" s="9">
-        <v>46191.543677430556</v>
+        <v>46191.71034409722</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>196</v>
@@ -5239,13 +5239,13 @@
         <v>197</v>
       </c>
       <c r="B64" s="5">
-        <v>46118.423391226854</v>
+        <v>46118.59005789352</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.50567078704</v>
+        <v>46181.6723374537</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.50567189815</v>
+        <v>46181.672338564815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>139</v>
@@ -5294,13 +5294,13 @@
         <v>200</v>
       </c>
       <c r="B65" s="9">
-        <v>46118.4234009375</v>
+        <v>46118.590067604164</v>
       </c>
       <c r="C65" s="9">
-        <v>46181.50568425926</v>
+        <v>46181.672350925925</v>
       </c>
       <c r="D65" s="9">
-        <v>46181.50568577547</v>
+        <v>46181.672352442125</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>139</v>
@@ -5349,13 +5349,13 @@
         <v>202</v>
       </c>
       <c r="B66" s="5">
-        <v>46118.423409317125</v>
+        <v>46118.5900759838</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.505698368055</v>
+        <v>46181.67236503473</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.5056996412</v>
+        <v>46181.672366307874</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>139</v>
@@ -5404,13 +5404,13 @@
         <v>203</v>
       </c>
       <c r="B67" s="9">
-        <v>46118.423431296294</v>
+        <v>46118.590097962966</v>
       </c>
       <c r="C67" s="9">
-        <v>46191.543643171295</v>
+        <v>46191.71030983796</v>
       </c>
       <c r="D67" s="9">
-        <v>46191.5436444213</v>
+        <v>46191.71031108796</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>139</v>
@@ -5459,13 +5459,13 @@
         <v>204</v>
       </c>
       <c r="B68" s="5">
-        <v>46118.423435868055</v>
+        <v>46118.59010253473</v>
       </c>
       <c r="C68" s="5">
-        <v>46191.54365045139</v>
+        <v>46191.71031711806</v>
       </c>
       <c r="D68" s="5">
-        <v>46191.54365186342</v>
+        <v>46191.710318530095</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>139</v>
@@ -5514,13 +5514,13 @@
         <v>205</v>
       </c>
       <c r="B69" s="9">
-        <v>46118.389130173615</v>
+        <v>46118.55579684028</v>
       </c>
       <c r="C69" s="9">
-        <v>46191.54268518518</v>
+        <v>46191.70935185185</v>
       </c>
       <c r="D69" s="9">
-        <v>46191.54269869213</v>
+        <v>46191.709365358794</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>206</v>
@@ -5579,13 +5579,13 @@
         <v>207</v>
       </c>
       <c r="B70" s="5">
-        <v>46118.42348722222</v>
+        <v>46118.59015388889</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.50577675926</v>
+        <v>46181.67244342592</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.505778067134</v>
+        <v>46181.67244473379</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>139</v>
@@ -5634,13 +5634,13 @@
         <v>210</v>
       </c>
       <c r="B71" s="9">
-        <v>46118.42349569444</v>
+        <v>46118.59016236111</v>
       </c>
       <c r="C71" s="9">
-        <v>46181.505789930554</v>
+        <v>46181.672456597225</v>
       </c>
       <c r="D71" s="9">
-        <v>46181.50579141204</v>
+        <v>46181.672458078705</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>139</v>
@@ -5689,13 +5689,13 @@
         <v>211</v>
       </c>
       <c r="B72" s="5">
-        <v>46118.4235046875</v>
+        <v>46118.59017135417</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.505796990736</v>
+        <v>46181.67246365741</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.50579833333</v>
+        <v>46181.672464999996</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>139</v>
@@ -5744,13 +5744,13 @@
         <v>212</v>
       </c>
       <c r="B73" s="9">
-        <v>46118.42352575231</v>
+        <v>46118.59019241898</v>
       </c>
       <c r="C73" s="9">
-        <v>46191.54261560185</v>
+        <v>46191.70928226852</v>
       </c>
       <c r="D73" s="9">
-        <v>46191.54364859954</v>
+        <v>46191.7103152662</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>139</v>
@@ -5799,13 +5799,13 @@
         <v>213</v>
       </c>
       <c r="B74" s="5">
-        <v>46118.42353082176</v>
+        <v>46118.590197488425</v>
       </c>
       <c r="C74" s="5">
-        <v>46191.542669745366</v>
+        <v>46191.70933641204</v>
       </c>
       <c r="D74" s="5">
-        <v>46191.543659849536</v>
+        <v>46191.7103265162</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>139</v>
@@ -5854,13 +5854,13 @@
         <v>214</v>
       </c>
       <c r="B75" s="9">
-        <v>46118.38913660879</v>
+        <v>46118.55580327546</v>
       </c>
       <c r="C75" s="9">
-        <v>46205.73961895834</v>
+        <v>46205.906285624995</v>
       </c>
       <c r="D75" s="9">
-        <v>46205.739634074074</v>
+        <v>46205.90630074074</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>176</v>
@@ -5907,13 +5907,13 @@
         <v>216</v>
       </c>
       <c r="B76" s="5">
-        <v>46118.38914018519</v>
+        <v>46118.55580685185</v>
       </c>
       <c r="C76" s="5">
-        <v>46204.55023300926</v>
+        <v>46204.71689967593</v>
       </c>
       <c r="D76" s="5">
-        <v>46204.55024880787</v>
+        <v>46204.716915474535</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>217</v>
@@ -5970,13 +5970,13 @@
         <v>219</v>
       </c>
       <c r="B77" s="9">
-        <v>46118.38914653935</v>
+        <v>46118.55581320602</v>
       </c>
       <c r="C77" s="9">
-        <v>46205.73798628472</v>
+        <v>46205.90465295139</v>
       </c>
       <c r="D77" s="9">
-        <v>46205.73800493055</v>
+        <v>46205.90467159722</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>220</v>
@@ -6033,13 +6033,13 @@
         <v>221</v>
       </c>
       <c r="B78" s="5">
-        <v>46118.38915269676</v>
+        <v>46118.55581936342</v>
       </c>
       <c r="C78" s="5">
-        <v>46205.739602905094</v>
+        <v>46205.90626957176</v>
       </c>
       <c r="D78" s="5">
-        <v>46205.73961804398</v>
+        <v>46205.90628471065</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>222</v>
@@ -6096,13 +6096,13 @@
         <v>223</v>
       </c>
       <c r="B79" s="9">
-        <v>46118.38915849537</v>
+        <v>46118.55582516204</v>
       </c>
       <c r="C79" s="9">
-        <v>46244.40038839121</v>
+        <v>46244.567055057865</v>
       </c>
       <c r="D79" s="9">
-        <v>46244.4004044676</v>
+        <v>46244.56707113426</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>224</v>
@@ -6149,13 +6149,13 @@
         <v>226</v>
       </c>
       <c r="B80" s="5">
-        <v>46118.38916210648</v>
+        <v>46118.55582877315</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.25654052083</v>
+        <v>46197.4232071875</v>
       </c>
       <c r="D80" s="5">
-        <v>46223.439442118055</v>
+        <v>46223.60610878472</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>227</v>
@@ -6214,13 +6214,13 @@
         <v>228</v>
       </c>
       <c r="B81" s="9">
-        <v>46118.423583958334</v>
+        <v>46118.590250625</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.25634599537</v>
+        <v>46197.42301266204</v>
       </c>
       <c r="D81" s="9">
-        <v>46223.43875778935</v>
+        <v>46223.60542445602</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>139</v>
@@ -6269,13 +6269,13 @@
         <v>230</v>
       </c>
       <c r="B82" s="5">
-        <v>46118.423592974534</v>
+        <v>46118.590259641205</v>
       </c>
       <c r="C82" s="5">
-        <v>46197.2563841088</v>
+        <v>46197.42305077546</v>
       </c>
       <c r="D82" s="5">
-        <v>46223.438753912036</v>
+        <v>46223.60542057871</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>139</v>
@@ -6324,13 +6324,13 @@
         <v>231</v>
       </c>
       <c r="B83" s="9">
-        <v>46118.42360094907</v>
+        <v>46118.59026761574</v>
       </c>
       <c r="C83" s="9">
-        <v>46197.25643576389</v>
+        <v>46197.423102430555</v>
       </c>
       <c r="D83" s="9">
-        <v>46223.43874989584</v>
+        <v>46223.605416562496</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>139</v>
@@ -6379,13 +6379,13 @@
         <v>232</v>
       </c>
       <c r="B84" s="5">
-        <v>46118.42360896991</v>
+        <v>46118.590275636576</v>
       </c>
       <c r="C84" s="5">
-        <v>46197.256480613425</v>
+        <v>46197.42314728009</v>
       </c>
       <c r="D84" s="5">
-        <v>46223.43874543982</v>
+        <v>46223.60541210648</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>139</v>
@@ -6434,13 +6434,13 @@
         <v>233</v>
       </c>
       <c r="B85" s="9">
-        <v>46118.42361763889</v>
+        <v>46118.59028430555</v>
       </c>
       <c r="C85" s="9">
-        <v>46197.25652604167</v>
+        <v>46197.42319270833</v>
       </c>
       <c r="D85" s="9">
-        <v>46223.43874010417</v>
+        <v>46223.60540677083</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>139</v>
@@ -6489,13 +6489,13 @@
         <v>234</v>
       </c>
       <c r="B86" s="5">
-        <v>46118.38916792824</v>
+        <v>46118.55583459491</v>
       </c>
       <c r="C86" s="5">
-        <v>46209.42948559028</v>
+        <v>46209.59615225694</v>
       </c>
       <c r="D86" s="5">
-        <v>46223.43943873842</v>
+        <v>46223.606105405095</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>235</v>
@@ -6554,13 +6554,13 @@
         <v>236</v>
       </c>
       <c r="B87" s="9">
-        <v>46118.42366811342</v>
+        <v>46118.59033478009</v>
       </c>
       <c r="C87" s="9">
-        <v>46197.34042760417</v>
+        <v>46197.50709427083</v>
       </c>
       <c r="D87" s="9">
-        <v>46223.43884962963</v>
+        <v>46223.605516296295</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>139</v>
@@ -6607,13 +6607,13 @@
         <v>239</v>
       </c>
       <c r="B88" s="5">
-        <v>46118.423677812505</v>
+        <v>46118.59034447916</v>
       </c>
       <c r="C88" s="5">
-        <v>46197.34048490741</v>
+        <v>46197.50715157407</v>
       </c>
       <c r="D88" s="5">
-        <v>46223.438845983794</v>
+        <v>46223.605512650465</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>139</v>
@@ -6660,13 +6660,13 @@
         <v>240</v>
       </c>
       <c r="B89" s="9">
-        <v>46118.42368547454</v>
+        <v>46118.590352141204</v>
       </c>
       <c r="C89" s="9">
-        <v>46197.340572534726</v>
+        <v>46197.50723920139</v>
       </c>
       <c r="D89" s="9">
-        <v>46223.438842523145</v>
+        <v>46223.605509189816</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>139</v>
@@ -6713,13 +6713,13 @@
         <v>241</v>
       </c>
       <c r="B90" s="5">
-        <v>46118.42369300926</v>
+        <v>46118.59035967593</v>
       </c>
       <c r="C90" s="5">
-        <v>46209.42925494213</v>
+        <v>46209.595921608794</v>
       </c>
       <c r="D90" s="5">
-        <v>46223.438838263886</v>
+        <v>46223.60550493056</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>139</v>
@@ -6766,13 +6766,13 @@
         <v>242</v>
       </c>
       <c r="B91" s="9">
-        <v>46118.42370167824</v>
+        <v>46118.59036834491</v>
       </c>
       <c r="C91" s="9">
-        <v>46209.42928703704</v>
+        <v>46209.595953703705</v>
       </c>
       <c r="D91" s="9">
-        <v>46223.438833402775</v>
+        <v>46223.60550006945</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>139</v>
@@ -6819,13 +6819,13 @@
         <v>243</v>
       </c>
       <c r="B92" s="5">
-        <v>46118.38917577546</v>
+        <v>46118.55584244213</v>
       </c>
       <c r="C92" s="5">
-        <v>46197.34114940972</v>
+        <v>46197.50781607639</v>
       </c>
       <c r="D92" s="5">
-        <v>46223.43943496528</v>
+        <v>46223.60610163194</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>244</v>
@@ -6882,13 +6882,13 @@
         <v>245</v>
       </c>
       <c r="B93" s="9">
-        <v>46118.4237540162</v>
+        <v>46118.59042068287</v>
       </c>
       <c r="C93" s="9">
-        <v>46197.34082760417</v>
+        <v>46197.50749427083</v>
       </c>
       <c r="D93" s="9">
-        <v>46223.43895040509</v>
+        <v>46223.605617071764</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>139</v>
@@ -6935,13 +6935,13 @@
         <v>248</v>
       </c>
       <c r="B94" s="5">
-        <v>46118.423761365746</v>
+        <v>46118.5904280324</v>
       </c>
       <c r="C94" s="5">
-        <v>46197.340910162035</v>
+        <v>46197.507576828706</v>
       </c>
       <c r="D94" s="5">
-        <v>46223.43894630787</v>
+        <v>46223.60561297454</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>139</v>
@@ -6988,13 +6988,13 @@
         <v>249</v>
       </c>
       <c r="B95" s="9">
-        <v>46118.423777986114</v>
+        <v>46118.59044465278</v>
       </c>
       <c r="C95" s="9">
-        <v>46197.34100755787</v>
+        <v>46197.50767422454</v>
       </c>
       <c r="D95" s="9">
-        <v>46223.43894216436</v>
+        <v>46223.605608831014</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>139</v>
@@ -7041,13 +7041,13 @@
         <v>250</v>
       </c>
       <c r="B96" s="5">
-        <v>46118.423772442125</v>
+        <v>46118.5904391088</v>
       </c>
       <c r="C96" s="5">
-        <v>46197.341071215276</v>
+        <v>46197.50773788194</v>
       </c>
       <c r="D96" s="5">
-        <v>46223.43893862268</v>
+        <v>46223.605605289355</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>139</v>
@@ -7094,13 +7094,13 @@
         <v>251</v>
       </c>
       <c r="B97" s="9">
-        <v>46118.4237856713</v>
+        <v>46118.59045233796</v>
       </c>
       <c r="C97" s="9">
-        <v>46197.34113439815</v>
+        <v>46197.507801064814</v>
       </c>
       <c r="D97" s="9">
-        <v>46223.438933287034</v>
+        <v>46223.605599953706</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>139</v>
@@ -7147,13 +7147,13 @@
         <v>252</v>
       </c>
       <c r="B98" s="5">
-        <v>46118.38918320602</v>
+        <v>46118.55584987269</v>
       </c>
       <c r="C98" s="5">
-        <v>46209.429587175924</v>
+        <v>46209.596253842596</v>
       </c>
       <c r="D98" s="5">
-        <v>46223.43943091435</v>
+        <v>46223.60609758102</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>253</v>
@@ -7210,13 +7210,13 @@
         <v>254</v>
       </c>
       <c r="B99" s="9">
-        <v>46118.42387261574</v>
+        <v>46118.590539282406</v>
       </c>
       <c r="C99" s="9">
-        <v>46197.257712314815</v>
+        <v>46197.42437898148</v>
       </c>
       <c r="D99" s="9">
-        <v>46223.43908052084</v>
+        <v>46223.605747187496</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>139</v>
@@ -7263,13 +7263,13 @@
         <v>257</v>
       </c>
       <c r="B100" s="5">
-        <v>46118.42388</v>
+        <v>46118.590546666666</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.25782778935</v>
+        <v>46197.42449445602</v>
       </c>
       <c r="D100" s="5">
-        <v>46223.43907635417</v>
+        <v>46223.60574302083</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>139</v>
@@ -7316,13 +7316,13 @@
         <v>259</v>
       </c>
       <c r="B101" s="9">
-        <v>46118.42388736111</v>
+        <v>46118.590554027774</v>
       </c>
       <c r="C101" s="9">
-        <v>46197.2579059375</v>
+        <v>46197.42457260417</v>
       </c>
       <c r="D101" s="9">
-        <v>46223.43907158565</v>
+        <v>46223.605738252314</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>139</v>
@@ -7369,13 +7369,13 @@
         <v>261</v>
       </c>
       <c r="B102" s="5">
-        <v>46118.42389449074</v>
+        <v>46118.59056115741</v>
       </c>
       <c r="C102" s="5">
-        <v>46209.42956174769</v>
+        <v>46209.59622841435</v>
       </c>
       <c r="D102" s="5">
-        <v>46223.43906744213</v>
+        <v>46223.6057341088</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>139</v>
@@ -7422,13 +7422,13 @@
         <v>262</v>
       </c>
       <c r="B103" s="9">
-        <v>46118.42390262731</v>
+        <v>46118.590569293985</v>
       </c>
       <c r="C103" s="9">
-        <v>46209.42956788195</v>
+        <v>46209.59623454861</v>
       </c>
       <c r="D103" s="9">
-        <v>46223.43906065972</v>
+        <v>46223.60572732639</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>139</v>
@@ -7475,13 +7475,13 @@
         <v>263</v>
       </c>
       <c r="B104" s="5">
-        <v>46118.38919078704</v>
+        <v>46118.5558574537</v>
       </c>
       <c r="C104" s="5">
-        <v>46230.41218920139</v>
+        <v>46230.57885586805</v>
       </c>
       <c r="D104" s="5">
-        <v>46230.41250372685</v>
+        <v>46230.57917039352</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>264</v>
@@ -7540,13 +7540,13 @@
         <v>265</v>
       </c>
       <c r="B105" s="9">
-        <v>46118.42395989584</v>
+        <v>46118.5906265625</v>
       </c>
       <c r="C105" s="9">
-        <v>46205.31826884259</v>
+        <v>46205.48493550926</v>
       </c>
       <c r="D105" s="9">
-        <v>46223.43917359954</v>
+        <v>46223.6058402662</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>139</v>
@@ -7593,13 +7593,13 @@
         <v>267</v>
       </c>
       <c r="B106" s="5">
-        <v>46118.42396721065</v>
+        <v>46118.59063387732</v>
       </c>
       <c r="C106" s="5">
-        <v>46205.31828936342</v>
+        <v>46205.48495603009</v>
       </c>
       <c r="D106" s="5">
-        <v>46223.43916947917</v>
+        <v>46223.605836145834</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>139</v>
@@ -7646,13 +7646,13 @@
         <v>268</v>
       </c>
       <c r="B107" s="9">
-        <v>46118.42398881944</v>
+        <v>46118.590655486114</v>
       </c>
       <c r="C107" s="9">
-        <v>46212.43647685186</v>
+        <v>46212.603143518514</v>
       </c>
       <c r="D107" s="9">
-        <v>46223.439164675925</v>
+        <v>46223.60583134259</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>139</v>
@@ -7699,13 +7699,13 @@
         <v>269</v>
       </c>
       <c r="B108" s="5">
-        <v>46118.4239949537</v>
+        <v>46118.59066162037</v>
       </c>
       <c r="C108" s="5">
-        <v>46212.43648626158</v>
+        <v>46212.60315292824</v>
       </c>
       <c r="D108" s="5">
-        <v>46223.43916116898</v>
+        <v>46223.60582783565</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>139</v>
@@ -7752,13 +7752,13 @@
         <v>270</v>
       </c>
       <c r="B109" s="9">
-        <v>46118.424000439816</v>
+        <v>46118.59066710648</v>
       </c>
       <c r="C109" s="9">
-        <v>46230.41217314814</v>
+        <v>46230.578839814814</v>
       </c>
       <c r="D109" s="9">
-        <v>46230.412174502315</v>
+        <v>46230.57884116899</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>139</v>
@@ -7805,13 +7805,13 @@
         <v>271</v>
       </c>
       <c r="B110" s="5">
-        <v>46118.38924604167</v>
+        <v>46118.55591270833</v>
       </c>
       <c r="C110" s="5">
-        <v>46244.39994923611</v>
+        <v>46244.566615902775</v>
       </c>
       <c r="D110" s="5">
-        <v>46244.39995876157</v>
+        <v>46244.56662542824</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>272</v>
@@ -7868,13 +7868,13 @@
         <v>275</v>
       </c>
       <c r="B111" s="9">
-        <v>46118.424038576384</v>
+        <v>46118.590705243056</v>
       </c>
       <c r="C111" s="9">
-        <v>46212.43830630787</v>
+        <v>46212.604972974535</v>
       </c>
       <c r="D111" s="9">
-        <v>46238.34620984954</v>
+        <v>46238.51287651621</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>139</v>
@@ -7923,13 +7923,13 @@
         <v>277</v>
       </c>
       <c r="B112" s="5">
-        <v>46118.42404608797</v>
+        <v>46118.59071275463</v>
       </c>
       <c r="C112" s="5">
-        <v>46212.43837228009</v>
+        <v>46212.60503894676</v>
       </c>
       <c r="D112" s="5">
-        <v>46238.346230069445</v>
+        <v>46238.51289673611</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>139</v>
@@ -7978,13 +7978,13 @@
         <v>278</v>
       </c>
       <c r="B113" s="9">
-        <v>46118.42405342593</v>
+        <v>46118.590720092594</v>
       </c>
       <c r="C113" s="9">
-        <v>46213.3782128125</v>
+        <v>46213.54487947917</v>
       </c>
       <c r="D113" s="9">
-        <v>46238.346239895836</v>
+        <v>46238.5129065625</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>139</v>
@@ -8033,13 +8033,13 @@
         <v>279</v>
       </c>
       <c r="B114" s="5">
-        <v>46118.42406116898</v>
+        <v>46118.590727835646</v>
       </c>
       <c r="C114" s="5">
-        <v>46213.37833599537</v>
+        <v>46213.54500266204</v>
       </c>
       <c r="D114" s="5">
-        <v>46238.34625577547</v>
+        <v>46238.512922442125</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>139</v>
@@ -8088,13 +8088,13 @@
         <v>280</v>
       </c>
       <c r="B115" s="9">
-        <v>46118.42406868056</v>
+        <v>46118.59073534722</v>
       </c>
       <c r="C115" s="9">
-        <v>46244.399934120374</v>
+        <v>46244.56660078704</v>
       </c>
       <c r="D115" s="9">
-        <v>46244.39993613426</v>
+        <v>46244.56660280093</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>139</v>
@@ -8143,13 +8143,13 @@
         <v>281</v>
       </c>
       <c r="B116" s="5">
-        <v>46118.38925288194</v>
+        <v>46118.55591954861</v>
       </c>
       <c r="C116" s="5">
-        <v>46244.40037148148</v>
+        <v>46244.56703814815</v>
       </c>
       <c r="D116" s="5">
-        <v>46244.400385671295</v>
+        <v>46244.56705233797</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>282</v>
@@ -8196,13 +8196,13 @@
         <v>284</v>
       </c>
       <c r="B117" s="9">
-        <v>46118.38925648148</v>
+        <v>46118.555923148146</v>
       </c>
       <c r="C117" s="9">
-        <v>46244.40012293981</v>
+        <v>46244.566789606484</v>
       </c>
       <c r="D117" s="9">
-        <v>46244.40012961805</v>
+        <v>46244.56679628472</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>285</v>
@@ -8259,13 +8259,13 @@
         <v>288</v>
       </c>
       <c r="B118" s="5">
-        <v>46118.42412635416</v>
+        <v>46118.590793020834</v>
       </c>
       <c r="C118" s="5">
-        <v>46244.40010400463</v>
+        <v>46244.5667706713</v>
       </c>
       <c r="D118" s="5">
-        <v>46244.40010731481</v>
+        <v>46244.56677398148</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>139</v>
@@ -8312,13 +8312,13 @@
         <v>289</v>
       </c>
       <c r="B119" s="9">
-        <v>46118.424133831024</v>
+        <v>46118.59080049768</v>
       </c>
       <c r="C119" s="9">
-        <v>46244.4001046412</v>
+        <v>46244.56677130787</v>
       </c>
       <c r="D119" s="9">
-        <v>46244.400107696754</v>
+        <v>46244.566774363426</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>139</v>
@@ -8365,13 +8365,13 @@
         <v>290</v>
       </c>
       <c r="B120" s="5">
-        <v>46118.424140138886</v>
+        <v>46118.59080680556</v>
       </c>
       <c r="C120" s="5">
-        <v>46244.400105162036</v>
+        <v>46244.5667718287</v>
       </c>
       <c r="D120" s="5">
-        <v>46244.40010804398</v>
+        <v>46244.56677471065</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>139</v>
@@ -8418,13 +8418,13 @@
         <v>291</v>
       </c>
       <c r="B121" s="9">
-        <v>46118.42414888889</v>
+        <v>46118.59081555555</v>
       </c>
       <c r="C121" s="9">
-        <v>46244.400105671295</v>
+        <v>46244.56677233796</v>
       </c>
       <c r="D121" s="9">
-        <v>46244.40010840278</v>
+        <v>46244.56677506944</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>139</v>
@@ -8471,13 +8471,13 @@
         <v>292</v>
       </c>
       <c r="B122" s="5">
-        <v>46118.42415611111</v>
+        <v>46118.590822777776</v>
       </c>
       <c r="C122" s="5">
-        <v>46244.40010614583</v>
+        <v>46244.5667728125</v>
       </c>
       <c r="D122" s="5">
-        <v>46244.40010875</v>
+        <v>46244.566775416664</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>139</v>
@@ -8524,13 +8524,13 @@
         <v>293</v>
       </c>
       <c r="B123" s="9">
-        <v>46118.38926131945</v>
+        <v>46118.55592798611</v>
       </c>
       <c r="C123" s="9">
-        <v>46244.40016575232</v>
+        <v>46244.56683241898</v>
       </c>
       <c r="D123" s="9">
-        <v>46244.400176574076</v>
+        <v>46244.56684324074</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>294</v>
@@ -8587,13 +8587,13 @@
         <v>296</v>
       </c>
       <c r="B124" s="5">
-        <v>46118.424208530094</v>
+        <v>46118.59087519676</v>
       </c>
       <c r="C124" s="5">
-        <v>46213.37863527778</v>
+        <v>46213.54530194444</v>
       </c>
       <c r="D124" s="5">
-        <v>46244.40011400463</v>
+        <v>46244.566780671295</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>139</v>
@@ -8640,13 +8640,13 @@
         <v>298</v>
       </c>
       <c r="B125" s="9">
-        <v>46118.42421657407</v>
+        <v>46118.590883240744</v>
       </c>
       <c r="C125" s="9">
-        <v>46213.37870946759</v>
+        <v>46213.54537613426</v>
       </c>
       <c r="D125" s="9">
-        <v>46244.40011381944</v>
+        <v>46244.566780486115</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>139</v>
@@ -8693,13 +8693,13 @@
         <v>299</v>
       </c>
       <c r="B126" s="5">
-        <v>46118.42422490741</v>
+        <v>46118.59089157407</v>
       </c>
       <c r="C126" s="5">
-        <v>46213.37878092592</v>
+        <v>46213.545447592594</v>
       </c>
       <c r="D126" s="5">
-        <v>46244.400113854164</v>
+        <v>46244.566780520836</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>139</v>
@@ -8746,13 +8746,13 @@
         <v>300</v>
       </c>
       <c r="B127" s="9">
-        <v>46118.42423116898</v>
+        <v>46118.590897835646</v>
       </c>
       <c r="C127" s="9">
-        <v>46213.378835208336</v>
+        <v>46213.545501875</v>
       </c>
       <c r="D127" s="9">
-        <v>46244.40011381944</v>
+        <v>46244.566780486115</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>154</v>
@@ -8799,13 +8799,13 @@
         <v>301</v>
       </c>
       <c r="B128" s="5">
-        <v>46118.424238287036</v>
+        <v>46118.5909049537</v>
       </c>
       <c r="C128" s="5">
-        <v>46244.40015149306</v>
+        <v>46244.56681815972</v>
       </c>
       <c r="D128" s="5">
-        <v>46244.400153055554</v>
+        <v>46244.566819722226</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>154</v>
@@ -8852,13 +8852,13 @@
         <v>302</v>
       </c>
       <c r="B129" s="9">
-        <v>46118.389265844904</v>
+        <v>46118.555932511576</v>
       </c>
       <c r="C129" s="9">
-        <v>46211.522517199075</v>
+        <v>46211.68918386574</v>
       </c>
       <c r="D129" s="9">
-        <v>46211.52297435185</v>
+        <v>46211.689641018515</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>303</v>
@@ -8915,13 +8915,13 @@
         <v>304</v>
       </c>
       <c r="B130" s="5">
-        <v>46118.42428747685</v>
+        <v>46118.59095414352</v>
       </c>
       <c r="C130" s="5">
-        <v>46205.73655935185</v>
+        <v>46205.90322601852</v>
       </c>
       <c r="D130" s="5">
-        <v>46213.37864241898</v>
+        <v>46213.545309085646</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>139</v>
@@ -8968,13 +8968,13 @@
         <v>306</v>
       </c>
       <c r="B131" s="9">
-        <v>46118.42430009259</v>
+        <v>46118.590966759264</v>
       </c>
       <c r="C131" s="9">
-        <v>46205.736668287034</v>
+        <v>46205.903334953706</v>
       </c>
       <c r="D131" s="9">
-        <v>46213.37871506944</v>
+        <v>46213.54538173611</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>139</v>
@@ -9021,13 +9021,13 @@
         <v>307</v>
       </c>
       <c r="B132" s="5">
-        <v>46118.42430712963</v>
+        <v>46118.590973796294</v>
       </c>
       <c r="C132" s="5">
-        <v>46205.736779583334</v>
+        <v>46205.90344625</v>
       </c>
       <c r="D132" s="5">
-        <v>46213.378786932866</v>
+        <v>46213.54545359954</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>139</v>
@@ -9074,13 +9074,13 @@
         <v>308</v>
       </c>
       <c r="B133" s="9">
-        <v>46118.42431328703</v>
+        <v>46118.590979953704</v>
       </c>
       <c r="C133" s="9">
-        <v>46211.52258608796</v>
+        <v>46211.68925275463</v>
       </c>
       <c r="D133" s="9">
-        <v>46213.378842349535</v>
+        <v>46213.5455090162</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>139</v>
@@ -9127,13 +9127,13 @@
         <v>309</v>
       </c>
       <c r="B134" s="5">
-        <v>46118.42431822917</v>
+        <v>46118.59098489583</v>
       </c>
       <c r="C134" s="5">
-        <v>46211.52295994213</v>
+        <v>46211.6896266088</v>
       </c>
       <c r="D134" s="5">
-        <v>46244.40016001157</v>
+        <v>46244.566826678245</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>139</v>
@@ -9180,13 +9180,13 @@
         <v>310</v>
       </c>
       <c r="B135" s="9">
-        <v>46118.38927048611</v>
+        <v>46118.55593715278</v>
       </c>
       <c r="C135" s="9">
-        <v>46244.40027893518</v>
+        <v>46244.56694560185</v>
       </c>
       <c r="D135" s="9">
-        <v>46244.40028961806</v>
+        <v>46244.56695628472</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>311</v>
@@ -9243,13 +9243,13 @@
         <v>313</v>
       </c>
       <c r="B136" s="5">
-        <v>46118.42436438658</v>
+        <v>46118.59103105324</v>
       </c>
       <c r="C136" s="5">
-        <v>46244.40026200232</v>
+        <v>46244.56692866898</v>
       </c>
       <c r="D136" s="5">
-        <v>46244.4002649537</v>
+        <v>46244.56693162037</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>139</v>
@@ -9296,13 +9296,13 @@
         <v>314</v>
       </c>
       <c r="B137" s="9">
-        <v>46118.42437237268</v>
+        <v>46118.591039039355</v>
       </c>
       <c r="C137" s="9">
-        <v>46244.40026259259</v>
+        <v>46244.56692925926</v>
       </c>
       <c r="D137" s="9">
-        <v>46244.400265289354</v>
+        <v>46244.56693195602</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>139</v>
@@ -9349,13 +9349,13 @@
         <v>315</v>
       </c>
       <c r="B138" s="5">
-        <v>46118.42437974537</v>
+        <v>46118.59104641204</v>
       </c>
       <c r="C138" s="5">
-        <v>46244.40026303241</v>
+        <v>46244.566929699075</v>
       </c>
       <c r="D138" s="5">
-        <v>46244.40026560186</v>
+        <v>46244.56693226851</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>139</v>
@@ -9402,13 +9402,13 @@
         <v>316</v>
       </c>
       <c r="B139" s="9">
-        <v>46118.42438591435</v>
+        <v>46118.59105258102</v>
       </c>
       <c r="C139" s="9">
-        <v>46244.400263483796</v>
+        <v>46244.56693015047</v>
       </c>
       <c r="D139" s="9">
-        <v>46244.4002659375</v>
+        <v>46244.56693260417</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>139</v>
@@ -9455,13 +9455,13 @@
         <v>317</v>
       </c>
       <c r="B140" s="5">
-        <v>46118.42439163194</v>
+        <v>46118.59105829861</v>
       </c>
       <c r="C140" s="5">
-        <v>46244.40026390046</v>
+        <v>46244.56693056713</v>
       </c>
       <c r="D140" s="5">
-        <v>46244.40026628472</v>
+        <v>46244.56693295139</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>139</v>
@@ -9508,13 +9508,13 @@
         <v>318</v>
       </c>
       <c r="B141" s="9">
-        <v>46118.389275925925</v>
+        <v>46118.55594259259</v>
       </c>
       <c r="C141" s="9">
-        <v>46245.59871048611</v>
+        <v>46245.76537715278</v>
       </c>
       <c r="D141" s="9">
-        <v>46245.5987821875</v>
+        <v>46245.76544885417</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>319</v>
@@ -9557,13 +9557,13 @@
         <v>321</v>
       </c>
       <c r="B142" s="5">
-        <v>46118.38927884259</v>
+        <v>46118.55594550926</v>
       </c>
       <c r="C142" s="5">
-        <v>46245.5986912963</v>
+        <v>46245.76535796296</v>
       </c>
       <c r="D142" s="5">
-        <v>46245.59871099537</v>
+        <v>46245.765377662035</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>322</v>
@@ -9622,13 +9622,13 @@
         <v>325</v>
       </c>
       <c r="B143" s="9">
-        <v>46118.389283530094</v>
+        <v>46118.55595019676</v>
       </c>
       <c r="C143" s="9">
-        <v>46245.59869615741</v>
+        <v>46245.76536282407</v>
       </c>
       <c r="D143" s="9">
-        <v>46245.5987115162</v>
+        <v>46245.76537818287</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>326</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -2057,7 +2057,7 @@
         <v>46192.91325913194</v>
       </c>
       <c r="D10" s="5">
-        <v>46192.91327583333</v>
+        <v>46263.332481018515</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>

--- a/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001532 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -6495,7 +6495,7 @@
         <v>46209.59615225694</v>
       </c>
       <c r="D86" s="5">
-        <v>46223.606105405095</v>
+        <v>46271.58919859954</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>235</v>
